--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -291,101 +291,101 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>-16.8206</v>
+        <v>-10.1987</v>
       </c>
       <c t="n" r="E3">
-        <v>-6.5926</v>
+        <v>-7.1233</v>
       </c>
       <c t="n" r="F3">
-        <v>54.1565</v>
+        <v>60.4734</v>
       </c>
       <c t="n" r="G3">
-        <v>-1.9059</v>
+        <v>5.4842</v>
       </c>
       <c t="n" r="H3">
-        <v>160.8606</v>
+        <v>166.1955</v>
       </c>
       <c t="n" r="I3">
-        <v>522.4087</v>
+        <v>550.0479</v>
       </c>
       <c t="n" r="J3">
-        <v>1381.7861</v>
+        <v>1499.8112</v>
       </c>
     </row>
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">ZGD</t>
+          <t xml:space="preserve">ZKP</t>
         </is>
       </c>
       <c t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY ALTIN KATILIM  BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D4">
-        <v>-9.3652</v>
+        <v>14.6275</v>
       </c>
       <c t="n" r="E4">
-        <v>8.0150</v>
+        <v>30.2051</v>
       </c>
       <c t="n" r="F4">
-        <v>25.5004</v>
+        <v>43.6899</v>
       </c>
       <c t="n" r="G4">
-        <v>3.2212</v>
+        <v>37.2432</v>
       </c>
       <c t="n" r="H4">
-        <v>78.9082</v>
+        <v>76.9338</v>
       </c>
       <c t="n" r="I4">
-        <v>440.4798</v>
+        <v>229.9974</v>
       </c>
       <c t="n" r="J4">
-        <v>1484.2672</v>
+        <v>1186.8728</v>
       </c>
     </row>
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">FGA</t>
+          <t xml:space="preserve">ZKE</t>
         </is>
       </c>
       <c t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D5">
-        <v>-9.8024</v>
+        <v>20.8753</v>
       </c>
       <c t="n" r="E5">
-        <v>5.5016</v>
+        <v>35.7254</v>
       </c>
       <c t="n" r="F5">
-        <v>23.8064</v>
+        <v>48.0851</v>
       </c>
       <c t="n" r="G5">
-        <v>6.8352</v>
+        <v>42.4478</v>
       </c>
       <c t="n" r="H5">
-        <v>76.8992</v>
+        <v>76.0065</v>
       </c>
       <c t="n" r="I5">
-        <v>413.0396</v>
+        <v>197.3342</v>
       </c>
       <c t="n" r="J5">
-        <v>1317.7435</v>
+        <v>757.5653</v>
       </c>
     </row>
     <row r="6">
@@ -405,95 +405,95 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>-10.6965</v>
+        <v>-7.0886</v>
       </c>
       <c t="n" r="E6">
-        <v>5.4719</v>
+        <v>6.1844</v>
       </c>
       <c t="n" r="F6">
-        <v>21.6949</v>
+        <v>25.8465</v>
       </c>
       <c t="n" r="G6">
-        <v>1.9886</v>
+        <v>4.2614</v>
       </c>
       <c t="n" r="H6">
-        <v>76.6732</v>
+        <v>72.5435</v>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">ZKP</t>
+          <t xml:space="preserve">ZGD</t>
         </is>
       </c>
       <c t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY ALTIN KATILIM  BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D7">
-        <v>5.3979</v>
+        <v>-6.4885</v>
       </c>
       <c t="n" r="E7">
-        <v>20.8000</v>
+        <v>7.6135</v>
       </c>
       <c t="n" r="F7">
-        <v>28.6932</v>
+        <v>26.1261</v>
       </c>
       <c t="n" r="G7">
-        <v>22.4324</v>
+        <v>5.2255</v>
       </c>
       <c t="n" r="H7">
-        <v>58.1704</v>
+        <v>71.8494</v>
       </c>
       <c t="n" r="I7">
-        <v>206.4123</v>
+        <v>446.4684</v>
       </c>
       <c t="n" r="J7">
-        <v>1007.5795</v>
+        <v>1524.6684</v>
       </c>
     </row>
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">ZKE</t>
+          <t xml:space="preserve">FGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D8">
-        <v>10.9982</v>
+        <v>-5.9936</v>
       </c>
       <c t="n" r="E8">
-        <v>25.7919</v>
+        <v>5.5079</v>
       </c>
       <c t="n" r="F8">
-        <v>33.0722</v>
+        <v>23.6508</v>
       </c>
       <c t="n" r="G8">
-        <v>25.1740</v>
+        <v>9.4101</v>
       </c>
       <c t="n" r="H8">
-        <v>56.1798</v>
+        <v>69.8401</v>
       </c>
       <c t="n" r="I8">
-        <v>170.5237</v>
+        <v>417.4934</v>
       </c>
       <c t="n" r="J8">
-        <v>626.3658</v>
+        <v>1362.4531</v>
       </c>
     </row>
     <row r="9">
@@ -513,25 +513,25 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>4.3656</v>
+        <v>9.4999</v>
       </c>
       <c t="n" r="E9">
-        <v>16.0263</v>
+        <v>22.8620</v>
       </c>
       <c t="n" r="F9">
-        <v>21.6861</v>
+        <v>34.3156</v>
       </c>
       <c t="n" r="G9">
-        <v>26.1682</v>
+        <v>37.8230</v>
       </c>
       <c t="n" r="H9">
-        <v>53.5631</v>
+        <v>66.4122</v>
       </c>
       <c t="n" r="I9">
-        <v>176.5060</v>
+        <v>190.1620</v>
       </c>
       <c t="n" r="J9">
-        <v>1056.7540</v>
+        <v>1218.0862</v>
       </c>
     </row>
     <row r="10">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>3.8156</v>
+        <v>9.3064</v>
       </c>
       <c t="n" r="E10">
-        <v>14.7823</v>
+        <v>23.2673</v>
       </c>
       <c t="n" r="F10">
-        <v>20.3894</v>
+        <v>33.6315</v>
       </c>
       <c t="n" r="G10">
-        <v>25.3132</v>
+        <v>37.6197</v>
       </c>
       <c t="n" r="H10">
-        <v>51.8304</v>
+        <v>65.8526</v>
       </c>
     </row>
     <row r="11">
@@ -583,30 +583,30 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>5.1282</v>
+        <v>6.6561</v>
       </c>
       <c t="n" r="E11">
-        <v>6.8136</v>
+        <v>8.8398</v>
       </c>
       <c t="n" r="F11">
-        <v>11.1961</v>
+        <v>16.4465</v>
       </c>
       <c t="n" r="G11">
-        <v>12.0925</v>
+        <v>17.3852</v>
       </c>
       <c t="n" r="H11">
-        <v>50.9202</v>
+        <v>58.4950</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">ZRE</t>
+          <t xml:space="preserve">BOE</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY RİSK EŞİT BANKA DIŞI 20 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C12">
@@ -615,36 +615,30 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>3.9657</v>
+        <v>7.7469</v>
       </c>
       <c t="n" r="E12">
-        <v>18.7319</v>
+        <v>18.1220</v>
       </c>
       <c t="n" r="F12">
-        <v>30.5578</v>
+        <v>35.7388</v>
       </c>
       <c t="n" r="G12">
-        <v>27.1634</v>
+        <v>29.2539</v>
       </c>
       <c t="n" r="H12">
-        <v>44.6161</v>
-      </c>
-      <c t="n" r="I12">
-        <v>130.1911</v>
-      </c>
-      <c t="n" r="J12">
-        <v>809.2675</v>
+        <v>58.0632</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">OHY</t>
+          <t xml:space="preserve">ZBB</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C13">
@@ -653,30 +647,36 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>2.2258</v>
+        <v>7.9980</v>
       </c>
       <c t="n" r="E13">
-        <v>10.1342</v>
+        <v>18.4291</v>
       </c>
       <c t="n" r="F13">
-        <v>20.6002</v>
+        <v>35.1172</v>
       </c>
       <c t="n" r="G13">
-        <v>17.0155</v>
+        <v>29.5386</v>
       </c>
       <c t="n" r="H13">
-        <v>44.2243</v>
+        <v>57.8033</v>
+      </c>
+      <c t="n" r="I13">
+        <v>197.3934</v>
+      </c>
+      <c t="n" r="J13">
+        <v>1184.4672</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">ZEA</t>
+          <t xml:space="preserve">OHY</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C14">
@@ -685,36 +685,30 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>2.3593</v>
+        <v>7.7197</v>
       </c>
       <c t="n" r="E14">
-        <v>14.6450</v>
+        <v>17.5751</v>
       </c>
       <c t="n" r="F14">
-        <v>28.3779</v>
+        <v>33.3754</v>
       </c>
       <c t="n" r="G14">
-        <v>21.7377</v>
+        <v>28.2378</v>
       </c>
       <c t="n" r="H14">
-        <v>43.8674</v>
-      </c>
-      <c t="n" r="I14">
-        <v>149.7919</v>
-      </c>
-      <c t="n" r="J14">
-        <v>901.9477</v>
+        <v>57.5848</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">BOE</t>
+          <t xml:space="preserve">ZRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY RİSK EŞİT BANKA DIŞI 20 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C15">
@@ -723,30 +717,36 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>2.0975</v>
+        <v>8.7195</v>
       </c>
       <c t="n" r="E15">
-        <v>10.4569</v>
+        <v>26.6335</v>
       </c>
       <c t="n" r="F15">
-        <v>22.3090</v>
+        <v>43.7903</v>
       </c>
       <c t="n" r="G15">
-        <v>17.8665</v>
+        <v>38.3780</v>
       </c>
       <c t="n" r="H15">
-        <v>43.6777</v>
+        <v>56.6784</v>
+      </c>
+      <c t="n" r="I15">
+        <v>138.4327</v>
+      </c>
+      <c t="n" r="J15">
+        <v>927.6657</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">ZBB</t>
+          <t xml:space="preserve">ZEA</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C16">
@@ -755,36 +755,36 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>1.6222</v>
+        <v>7.6543</v>
       </c>
       <c t="n" r="E16">
-        <v>9.7175</v>
+        <v>22.8169</v>
       </c>
       <c t="n" r="F16">
-        <v>21.3371</v>
+        <v>41.9682</v>
       </c>
       <c t="n" r="G16">
-        <v>17.9114</v>
+        <v>32.6572</v>
       </c>
       <c t="n" r="H16">
-        <v>43.4799</v>
+        <v>55.1601</v>
       </c>
       <c t="n" r="I16">
-        <v>184.5838</v>
+        <v>158.3619</v>
       </c>
       <c t="n" r="J16">
-        <v>1037.6684</v>
+        <v>1039.3728</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">ZPT</t>
+          <t xml:space="preserve">ZBP</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C17">
@@ -793,33 +793,36 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>7.7755</v>
+        <v>5.8735</v>
       </c>
       <c t="n" r="E17">
-        <v>24.3760</v>
+        <v>4.7120</v>
       </c>
       <c t="n" r="F17">
-        <v>21.3193</v>
+        <v>28.4404</v>
       </c>
       <c t="n" r="G17">
-        <v>28.1533</v>
+        <v>8.6957</v>
       </c>
       <c t="n" r="H17">
-        <v>40.0187</v>
+        <v>52.2843</v>
       </c>
       <c t="n" r="I17">
-        <v>219.9327</v>
+        <v>302.4530</v>
+      </c>
+      <c t="n" r="J17">
+        <v>1875.5409</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">ZTM</t>
+          <t xml:space="preserve">BLH</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST TEMETTÜ 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C18">
@@ -828,25 +831,19 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>1.7461</v>
+        <v>5.1227</v>
       </c>
       <c t="n" r="E18">
-        <v>8.9009</v>
+        <v>4.4982</v>
       </c>
       <c t="n" r="F18">
-        <v>21.0137</v>
+        <v>27.2939</v>
       </c>
       <c t="n" r="G18">
-        <v>14.5237</v>
+        <v>8.4802</v>
       </c>
       <c t="n" r="H18">
-        <v>37.0813</v>
-      </c>
-      <c t="n" r="I18">
-        <v>194.2485</v>
-      </c>
-      <c t="n" r="J18">
-        <v>897.0998</v>
+        <v>50.8423</v>
       </c>
     </row>
     <row r="19">
@@ -866,33 +863,33 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>2.2167</v>
+        <v>8.2541</v>
       </c>
       <c t="n" r="E19">
-        <v>8.3808</v>
+        <v>16.4033</v>
       </c>
       <c t="n" r="F19">
-        <v>19.0352</v>
+        <v>32.5748</v>
       </c>
       <c t="n" r="G19">
-        <v>15.8629</v>
+        <v>27.1574</v>
       </c>
       <c t="n" r="H19">
-        <v>35.8631</v>
+        <v>50.7674</v>
       </c>
       <c t="n" r="I19">
-        <v>197.7821</v>
+        <v>213.3208</v>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">OPE</t>
+          <t xml:space="preserve">ZTM</t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY BIST TEMETTÜ 25 ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST TEMETTÜ 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C20">
@@ -901,30 +898,36 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>1.6149</v>
+        <v>5.0708</v>
       </c>
       <c t="n" r="E20">
-        <v>8.9456</v>
+        <v>15.2938</v>
       </c>
       <c t="n" r="F20">
-        <v>19.5615</v>
+        <v>33.1299</v>
       </c>
       <c t="n" r="G20">
-        <v>13.3487</v>
+        <v>23.5510</v>
       </c>
       <c t="n" r="H20">
-        <v>32.3268</v>
+        <v>48.4194</v>
+      </c>
+      <c t="n" r="I20">
+        <v>205.5189</v>
+      </c>
+      <c t="n" r="J20">
+        <v>996.6884</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">DJA</t>
+          <t xml:space="preserve">ZPT</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">QNB PORTFÖY QNB TEMİZ ENERJİ ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C21">
@@ -933,36 +936,33 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>13.1142</v>
+        <v>11.7180</v>
       </c>
       <c t="n" r="E21">
-        <v>12.4663</v>
+        <v>30.0578</v>
       </c>
       <c t="n" r="F21">
-        <v>7.9560</v>
+        <v>30.6013</v>
       </c>
       <c t="n" r="G21">
-        <v>15.5017</v>
+        <v>37.7663</v>
       </c>
       <c t="n" r="H21">
-        <v>31.1076</v>
+        <v>46.9436</v>
       </c>
       <c t="n" r="I21">
-        <v>93.9007</v>
-      </c>
-      <c t="n" r="J21">
-        <v>690.9953</v>
+        <v>231.3697</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">ZBP</t>
+          <t xml:space="preserve">OPE</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY BIST TEMETTÜ 25 ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C22">
@@ -971,36 +971,30 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>-4.4490</v>
+        <v>3.4127</v>
       </c>
       <c t="n" r="E22">
-        <v>-7.5000</v>
+        <v>13.3783</v>
       </c>
       <c t="n" r="F22">
-        <v>10.9890</v>
+        <v>29.1058</v>
       </c>
       <c t="n" r="G22">
-        <v>-3.2867</v>
+        <v>20.3695</v>
       </c>
       <c t="n" r="H22">
-        <v>30.6643</v>
-      </c>
-      <c t="n" r="I22">
-        <v>285.8943</v>
-      </c>
-      <c t="n" r="J22">
-        <v>1598.6364</v>
+        <v>41.8617</v>
       </c>
     </row>
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">BLH</t>
+          <t xml:space="preserve">DJA</t>
         </is>
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">QNB PORTFÖY QNB TEMİZ ENERJİ ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C23">
@@ -1009,92 +1003,98 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>-4.2798</v>
+        <v>12.0799</v>
       </c>
       <c t="n" r="E23">
-        <v>-6.5139</v>
+        <v>16.5897</v>
       </c>
       <c t="n" r="F23">
-        <v>11.2907</v>
+        <v>16.2829</v>
       </c>
       <c t="n" r="G23">
-        <v>-2.9515</v>
+        <v>22.3183</v>
       </c>
       <c t="n" r="H23">
-        <v>30.6256</v>
+        <v>35.3369</v>
+      </c>
+      <c t="n" r="I23">
+        <v>95.5199</v>
+      </c>
+      <c t="n" r="J23">
+        <v>756.5544</v>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">FUS</t>
+          <t xml:space="preserve">ZEO</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">QNB PORTFÖY AMERİKAN DOLARI YABANCI BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 50-30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">Yabancı Fon</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D24">
-        <v>1.1628</v>
+        <v>2.0996</v>
       </c>
       <c t="n" r="E24">
-        <v>4.0877</v>
+        <v>6.8045</v>
       </c>
       <c t="n" r="F24">
-        <v>7.4350</v>
+        <v>24.4730</v>
       </c>
       <c t="n" r="G24">
-        <v>3.9323</v>
+        <v>13.2937</v>
       </c>
       <c t="n" r="H24">
-        <v>17.6338</v>
+        <v>24.6482</v>
       </c>
       <c t="n" r="I24">
-        <v>124.5403</v>
-      </c>
-      <c t="n" r="J24">
-        <v>434.4254</v>
+        <v>118.9266</v>
       </c>
     </row>
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">ZEO</t>
+          <t xml:space="preserve">FUS</t>
         </is>
       </c>
       <c t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 50-30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">QNB PORTFÖY AMERİKAN DOLARI YABANCI BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Yabancı Fon</t>
         </is>
       </c>
       <c t="n" r="D25">
-        <v>-2.3275</v>
+        <v>1.1862</v>
       </c>
       <c t="n" r="E25">
-        <v>1.5398</v>
+        <v>3.7736</v>
       </c>
       <c t="n" r="F25">
-        <v>15.6544</v>
+        <v>7.1795</v>
       </c>
       <c t="n" r="G25">
-        <v>5.4363</v>
+        <v>4.0319</v>
       </c>
       <c t="n" r="H25">
-        <v>16.4480</v>
+        <v>17.3169</v>
       </c>
       <c t="n" r="I25">
-        <v>111.7431</v>
+        <v>123.5175</v>
+      </c>
+      <c t="n" r="J25">
+        <v>435.8974</v>
       </c>
     </row>
     <row r="26">
@@ -1113,6 +1113,9 @@
           <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
+      <c t="n" r="D26">
+        <v>-7.3886</v>
+      </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
@@ -1131,16 +1134,16 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>0.4595</v>
+        <v>4.2715</v>
       </c>
       <c t="n" r="E27">
-        <v>4.1126</v>
+        <v>11.2436</v>
       </c>
       <c t="n" r="F27">
-        <v>13.8192</v>
+        <v>25.4563</v>
       </c>
       <c t="n" r="G27">
-        <v>10.3717</v>
+        <v>19.8715</v>
       </c>
     </row>
     <row r="28">
@@ -1177,13 +1180,13 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>3.2258</v>
+        <v>3.0429</v>
       </c>
       <c t="n" r="E29">
-        <v>9.6673</v>
+        <v>9.6559</v>
       </c>
       <c t="n" r="G29">
-        <v>10.3256</v>
+        <v>10.8713</v>
       </c>
     </row>
     <row r="30">
@@ -1203,16 +1206,16 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>3.2331</v>
+        <v>3.1378</v>
       </c>
       <c t="n" r="E30">
-        <v>9.5333</v>
+        <v>9.6070</v>
       </c>
       <c t="n" r="F30">
-        <v>20.4650</v>
+        <v>20.4625</v>
       </c>
       <c t="n" r="G30">
-        <v>9.9720</v>
+        <v>10.5727</v>
       </c>
     </row>
     <row r="31">
@@ -1232,16 +1235,16 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>6.4784</v>
+        <v>10.0032</v>
       </c>
       <c t="n" r="E31">
-        <v>23.5544</v>
+        <v>25.2488</v>
       </c>
       <c t="n" r="F31">
-        <v>30.5233</v>
+        <v>38.7788</v>
       </c>
       <c t="n" r="G31">
-        <v>29.0258</v>
+        <v>36.7955</v>
       </c>
     </row>
     <row r="32">
@@ -1261,13 +1264,13 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>3.2737</v>
+        <v>3.2104</v>
       </c>
       <c t="n" r="E32">
-        <v>9.7403</v>
+        <v>9.7831</v>
       </c>
       <c t="n" r="G32">
-        <v>10.2003</v>
+        <v>10.8058</v>
       </c>
     </row>
     <row r="33">
@@ -1287,13 +1290,13 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>3.2329</v>
+        <v>3.1684</v>
       </c>
       <c t="n" r="E33">
-        <v>9.6520</v>
+        <v>9.7921</v>
       </c>
       <c t="n" r="G33">
-        <v>10.0605</v>
+        <v>10.7126</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -291,25 +291,25 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>-10.1987</v>
+        <v>-9.4178</v>
       </c>
       <c t="n" r="E3">
-        <v>-7.1233</v>
+        <v>-13.8156</v>
       </c>
       <c t="n" r="F3">
-        <v>60.4734</v>
+        <v>51.7673</v>
       </c>
       <c t="n" r="G3">
-        <v>5.4842</v>
+        <v>2.8783</v>
       </c>
       <c t="n" r="H3">
-        <v>166.1955</v>
+        <v>159.6192</v>
       </c>
       <c t="n" r="I3">
-        <v>550.0479</v>
+        <v>516.8377</v>
       </c>
       <c t="n" r="J3">
-        <v>1499.8112</v>
+        <v>1440.6570</v>
       </c>
     </row>
     <row r="4">
@@ -329,63 +329,63 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>14.6275</v>
+        <v>13.2420</v>
       </c>
       <c t="n" r="E4">
-        <v>30.2051</v>
+        <v>25.1261</v>
       </c>
       <c t="n" r="F4">
-        <v>43.6899</v>
+        <v>41.4718</v>
       </c>
       <c t="n" r="G4">
-        <v>37.2432</v>
+        <v>34.0541</v>
       </c>
       <c t="n" r="H4">
-        <v>76.9338</v>
+        <v>72.8223</v>
       </c>
       <c t="n" r="I4">
-        <v>229.9974</v>
+        <v>222.7486</v>
       </c>
       <c t="n" r="J4">
-        <v>1186.8728</v>
+        <v>1155.0607</v>
       </c>
     </row>
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">ZKE</t>
+          <t xml:space="preserve">ZGD</t>
         </is>
       </c>
       <c t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY ALTIN KATILIM  BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D5">
-        <v>20.8753</v>
+        <v>-5.7319</v>
       </c>
       <c t="n" r="E5">
-        <v>35.7254</v>
+        <v>6.3962</v>
       </c>
       <c t="n" r="F5">
-        <v>48.0851</v>
+        <v>21.5449</v>
       </c>
       <c t="n" r="G5">
-        <v>42.4478</v>
+        <v>4.1875</v>
       </c>
       <c t="n" r="H5">
-        <v>76.0065</v>
+        <v>70.1543</v>
       </c>
       <c t="n" r="I5">
-        <v>197.3342</v>
+        <v>431.5924</v>
       </c>
       <c t="n" r="J5">
-        <v>757.5653</v>
+        <v>1506.1576</v>
       </c>
     </row>
     <row r="6">
@@ -405,144 +405,138 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>-7.0886</v>
+        <v>-7.1566</v>
       </c>
       <c t="n" r="E6">
-        <v>6.1844</v>
+        <v>3.7661</v>
       </c>
       <c t="n" r="F6">
-        <v>25.8465</v>
+        <v>21.4016</v>
       </c>
       <c t="n" r="G6">
-        <v>4.2614</v>
+        <v>2.7344</v>
       </c>
       <c t="n" r="H6">
-        <v>72.5435</v>
+        <v>70.0165</v>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">ZGD</t>
+          <t xml:space="preserve">ZPP</t>
         </is>
       </c>
       <c t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY ALTIN KATILIM  BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D7">
-        <v>-6.4885</v>
+        <v>11.7323</v>
       </c>
       <c t="n" r="E7">
-        <v>7.6135</v>
+        <v>22.6976</v>
       </c>
       <c t="n" r="F7">
-        <v>26.1261</v>
+        <v>38.0473</v>
       </c>
       <c t="n" r="G7">
-        <v>5.2255</v>
+        <v>39.5272</v>
       </c>
       <c t="n" r="H7">
-        <v>71.8494</v>
+        <v>68.4700</v>
       </c>
       <c t="n" r="I7">
-        <v>446.4684</v>
+        <v>191.0550</v>
       </c>
       <c t="n" r="J7">
-        <v>1524.6684</v>
+        <v>1240.0211</v>
       </c>
     </row>
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">FGA</t>
+          <t xml:space="preserve">BND</t>
         </is>
       </c>
       <c t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D8">
-        <v>-5.9936</v>
+        <v>11.4706</v>
       </c>
       <c t="n" r="E8">
-        <v>5.5079</v>
+        <v>22.4556</v>
       </c>
       <c t="n" r="F8">
-        <v>23.6508</v>
+        <v>38.1195</v>
       </c>
       <c t="n" r="G8">
-        <v>9.4101</v>
+        <v>39.6463</v>
       </c>
       <c t="n" r="H8">
-        <v>69.8401</v>
-      </c>
-      <c t="n" r="I8">
-        <v>417.4934</v>
-      </c>
-      <c t="n" r="J8">
-        <v>1362.4531</v>
+        <v>68.2948</v>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">ZPP</t>
+          <t xml:space="preserve">FGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D9">
-        <v>9.4999</v>
+        <v>-6.6099</v>
       </c>
       <c t="n" r="E9">
-        <v>22.8620</v>
+        <v>4.2081</v>
       </c>
       <c t="n" r="F9">
-        <v>34.3156</v>
+        <v>18.5403</v>
       </c>
       <c t="n" r="G9">
-        <v>37.8230</v>
+        <v>7.8184</v>
       </c>
       <c t="n" r="H9">
-        <v>66.4122</v>
+        <v>67.3692</v>
       </c>
       <c t="n" r="I9">
-        <v>190.1620</v>
+        <v>403.0581</v>
       </c>
       <c t="n" r="J9">
-        <v>1218.0862</v>
+        <v>1334.3548</v>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">BND</t>
+          <t xml:space="preserve">ZKE</t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C10">
@@ -551,30 +545,36 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>9.3064</v>
+        <v>12.5436</v>
       </c>
       <c t="n" r="E10">
-        <v>23.2673</v>
+        <v>25.1938</v>
       </c>
       <c t="n" r="F10">
-        <v>33.6315</v>
+        <v>40.4959</v>
       </c>
       <c t="n" r="G10">
-        <v>37.6197</v>
+        <v>32.2145</v>
       </c>
       <c t="n" r="H10">
-        <v>65.8526</v>
+        <v>63.3623</v>
+      </c>
+      <c t="n" r="I10">
+        <v>175.1278</v>
+      </c>
+      <c t="n" r="J10">
+        <v>703.4826</v>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">OPK</t>
+          <t xml:space="preserve">ZBB</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C11">
@@ -583,30 +583,36 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>6.6561</v>
+        <v>10.3183</v>
       </c>
       <c t="n" r="E11">
-        <v>8.8398</v>
+        <v>19.1572</v>
       </c>
       <c t="n" r="F11">
-        <v>16.4465</v>
+        <v>38.9140</v>
       </c>
       <c t="n" r="G11">
-        <v>17.3852</v>
+        <v>30.4797</v>
       </c>
       <c t="n" r="H11">
-        <v>58.4950</v>
+        <v>58.9497</v>
+      </c>
+      <c t="n" r="I11">
+        <v>199.8884</v>
+      </c>
+      <c t="n" r="J11">
+        <v>1186.8263</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">BOE</t>
+          <t xml:space="preserve">OHY</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C12">
@@ -615,30 +621,30 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>7.7469</v>
+        <v>9.5545</v>
       </c>
       <c t="n" r="E12">
-        <v>18.1220</v>
+        <v>16.6118</v>
       </c>
       <c t="n" r="F12">
-        <v>35.7388</v>
+        <v>37.3587</v>
       </c>
       <c t="n" r="G12">
-        <v>29.2539</v>
+        <v>29.0264</v>
       </c>
       <c t="n" r="H12">
-        <v>58.0632</v>
+        <v>58.5539</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">ZBB</t>
+          <t xml:space="preserve">BOE</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C13">
@@ -647,36 +653,30 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>7.9980</v>
+        <v>9.3197</v>
       </c>
       <c t="n" r="E13">
-        <v>18.4291</v>
+        <v>16.7110</v>
       </c>
       <c t="n" r="F13">
-        <v>35.1172</v>
+        <v>38.5074</v>
       </c>
       <c t="n" r="G13">
-        <v>29.5386</v>
+        <v>29.3521</v>
       </c>
       <c t="n" r="H13">
-        <v>57.8033</v>
-      </c>
-      <c t="n" r="I13">
-        <v>197.3934</v>
-      </c>
-      <c t="n" r="J13">
-        <v>1184.4672</v>
+        <v>58.1833</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">OHY</t>
+          <t xml:space="preserve">OPK</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C14">
@@ -685,19 +685,19 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>7.7197</v>
+        <v>5.1438</v>
       </c>
       <c t="n" r="E14">
-        <v>17.5751</v>
+        <v>6.5738</v>
       </c>
       <c t="n" r="F14">
-        <v>33.3754</v>
+        <v>15.8395</v>
       </c>
       <c t="n" r="G14">
-        <v>28.2378</v>
+        <v>15.3523</v>
       </c>
       <c t="n" r="H14">
-        <v>57.5848</v>
+        <v>55.7501</v>
       </c>
     </row>
     <row r="15">
@@ -717,25 +717,25 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>8.7195</v>
+        <v>9.3943</v>
       </c>
       <c t="n" r="E15">
-        <v>26.6335</v>
+        <v>24.4288</v>
       </c>
       <c t="n" r="F15">
-        <v>43.7903</v>
+        <v>45.7990</v>
       </c>
       <c t="n" r="G15">
-        <v>38.3780</v>
+        <v>37.3690</v>
       </c>
       <c t="n" r="H15">
-        <v>56.6784</v>
+        <v>55.5360</v>
       </c>
       <c t="n" r="I15">
-        <v>138.4327</v>
+        <v>136.6943</v>
       </c>
       <c t="n" r="J15">
-        <v>927.6657</v>
+        <v>918.9983</v>
       </c>
     </row>
     <row r="16">
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>7.6543</v>
+        <v>8.4031</v>
       </c>
       <c t="n" r="E16">
-        <v>22.8169</v>
+        <v>20.5526</v>
       </c>
       <c t="n" r="F16">
-        <v>41.9682</v>
+        <v>43.2313</v>
       </c>
       <c t="n" r="G16">
-        <v>32.6572</v>
+        <v>31.2711</v>
       </c>
       <c t="n" r="H16">
-        <v>55.1601</v>
+        <v>53.5389</v>
       </c>
       <c t="n" r="I16">
-        <v>158.3619</v>
+        <v>154.9908</v>
       </c>
       <c t="n" r="J16">
-        <v>1039.3728</v>
+        <v>1026.8137</v>
       </c>
     </row>
     <row r="17">
@@ -793,36 +793,36 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>5.8735</v>
+        <v>7.9303</v>
       </c>
       <c t="n" r="E17">
-        <v>4.7120</v>
+        <v>3.1817</v>
       </c>
       <c t="n" r="F17">
-        <v>28.4404</v>
+        <v>29.5568</v>
       </c>
       <c t="n" r="G17">
-        <v>8.6957</v>
+        <v>7.4275</v>
       </c>
       <c t="n" r="H17">
-        <v>52.2843</v>
+        <v>50.5076</v>
       </c>
       <c t="n" r="I17">
-        <v>302.4530</v>
+        <v>305.2128</v>
       </c>
       <c t="n" r="J17">
-        <v>1875.5409</v>
+        <v>1845.1734</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">BLH</t>
+          <t xml:space="preserve">ZSR</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST SÜRDÜRÜLEBİLİRLİK 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C18">
@@ -831,30 +831,33 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>5.1227</v>
+        <v>9.0651</v>
       </c>
       <c t="n" r="E18">
-        <v>4.4982</v>
+        <v>14.5709</v>
       </c>
       <c t="n" r="F18">
-        <v>27.2939</v>
+        <v>34.3288</v>
       </c>
       <c t="n" r="G18">
-        <v>8.4802</v>
+        <v>26.7259</v>
       </c>
       <c t="n" r="H18">
-        <v>50.8423</v>
+        <v>50.2558</v>
+      </c>
+      <c t="n" r="I18">
+        <v>209.9317</v>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">ZSR</t>
+          <t xml:space="preserve">ZTM</t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST SÜRDÜRÜLEBİLİRLİK 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST TEMETTÜ 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C19">
@@ -863,33 +866,36 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>8.2541</v>
+        <v>6.0580</v>
       </c>
       <c t="n" r="E19">
-        <v>16.4033</v>
+        <v>12.5533</v>
       </c>
       <c t="n" r="F19">
-        <v>32.5748</v>
+        <v>35.5099</v>
       </c>
       <c t="n" r="G19">
-        <v>27.1574</v>
+        <v>23.0513</v>
       </c>
       <c t="n" r="H19">
-        <v>50.7674</v>
+        <v>47.8191</v>
       </c>
       <c t="n" r="I19">
-        <v>213.3208</v>
+        <v>203.2841</v>
+      </c>
+      <c t="n" r="J19">
+        <v>983.9202</v>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">ZTM</t>
+          <t xml:space="preserve">ZPT</t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST TEMETTÜ 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C20">
@@ -898,36 +904,33 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>5.0708</v>
+        <v>14.6235</v>
       </c>
       <c t="n" r="E20">
-        <v>15.2938</v>
+        <v>29.1152</v>
       </c>
       <c t="n" r="F20">
-        <v>33.1299</v>
+        <v>32.3219</v>
       </c>
       <c t="n" r="G20">
-        <v>23.5510</v>
+        <v>38.3174</v>
       </c>
       <c t="n" r="H20">
-        <v>48.4194</v>
+        <v>47.5313</v>
       </c>
       <c t="n" r="I20">
-        <v>205.5189</v>
-      </c>
-      <c t="n" r="J20">
-        <v>996.6884</v>
+        <v>233.4810</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">ZPT</t>
+          <t xml:space="preserve">BLH</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C21">
@@ -936,22 +939,19 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>11.7180</v>
+        <v>4.5870</v>
       </c>
       <c t="n" r="E21">
-        <v>30.0578</v>
+        <v>1.2629</v>
       </c>
       <c t="n" r="F21">
-        <v>30.6013</v>
+        <v>27.3425</v>
       </c>
       <c t="n" r="G21">
-        <v>37.7663</v>
+        <v>5.9692</v>
       </c>
       <c t="n" r="H21">
-        <v>46.9436</v>
-      </c>
-      <c t="n" r="I21">
-        <v>231.3697</v>
+        <v>47.3507</v>
       </c>
     </row>
     <row r="22">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>3.4127</v>
+        <v>4.3531</v>
       </c>
       <c t="n" r="E22">
-        <v>13.3783</v>
+        <v>11.3442</v>
       </c>
       <c t="n" r="F22">
-        <v>29.1058</v>
+        <v>32.0975</v>
       </c>
       <c t="n" r="G22">
-        <v>20.3695</v>
+        <v>20.1386</v>
       </c>
       <c t="n" r="H22">
-        <v>41.8617</v>
+        <v>41.5895</v>
       </c>
     </row>
     <row r="23">
@@ -1003,25 +1003,25 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>12.0799</v>
+        <v>11.8300</v>
       </c>
       <c t="n" r="E23">
-        <v>16.5897</v>
+        <v>15.9868</v>
       </c>
       <c t="n" r="F23">
-        <v>16.2829</v>
+        <v>18.5210</v>
       </c>
       <c t="n" r="G23">
-        <v>22.3183</v>
+        <v>22.0069</v>
       </c>
       <c t="n" r="H23">
-        <v>35.3369</v>
+        <v>34.9923</v>
       </c>
       <c t="n" r="I23">
-        <v>95.5199</v>
+        <v>95.4545</v>
       </c>
       <c t="n" r="J23">
-        <v>756.5544</v>
+        <v>751.4851</v>
       </c>
     </row>
     <row r="24">
@@ -1041,22 +1041,22 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>2.0996</v>
+        <v>3.4743</v>
       </c>
       <c t="n" r="E24">
-        <v>6.8045</v>
+        <v>4.6571</v>
       </c>
       <c t="n" r="F24">
-        <v>24.4730</v>
+        <v>25.1772</v>
       </c>
       <c t="n" r="G24">
-        <v>13.2937</v>
+        <v>12.9283</v>
       </c>
       <c t="n" r="H24">
-        <v>24.6482</v>
+        <v>24.2461</v>
       </c>
       <c t="n" r="I24">
-        <v>118.9266</v>
+        <v>118.3746</v>
       </c>
     </row>
     <row r="25">
@@ -1076,25 +1076,25 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>1.1862</v>
+        <v>0.8195</v>
       </c>
       <c t="n" r="E25">
-        <v>3.7736</v>
+        <v>3.8739</v>
       </c>
       <c t="n" r="F25">
-        <v>7.1795</v>
+        <v>7.3665</v>
       </c>
       <c t="n" r="G25">
-        <v>4.0319</v>
+        <v>4.1065</v>
       </c>
       <c t="n" r="H25">
-        <v>17.3169</v>
+        <v>17.4011</v>
       </c>
       <c t="n" r="I25">
-        <v>123.5175</v>
+        <v>122.3108</v>
       </c>
       <c t="n" r="J25">
-        <v>435.8974</v>
+        <v>436.7638</v>
       </c>
     </row>
     <row r="26">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>-7.3886</v>
+        <v>-6.3638</v>
       </c>
     </row>
     <row r="27">
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>4.2715</v>
+        <v>3.3932</v>
       </c>
       <c t="n" r="E27">
-        <v>11.2436</v>
+        <v>8.8693</v>
       </c>
       <c t="n" r="F27">
-        <v>25.4563</v>
+        <v>28.8557</v>
       </c>
       <c t="n" r="G27">
-        <v>19.8715</v>
+        <v>18.8619</v>
       </c>
     </row>
     <row r="28">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>3.0429</v>
+        <v>2.9933</v>
       </c>
       <c t="n" r="E29">
-        <v>9.6559</v>
+        <v>9.6196</v>
       </c>
       <c t="n" r="G29">
-        <v>10.8713</v>
+        <v>10.9457</v>
       </c>
     </row>
     <row r="30">
@@ -1206,16 +1206,16 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>3.1378</v>
+        <v>3.0970</v>
       </c>
       <c t="n" r="E30">
-        <v>9.6070</v>
+        <v>9.5559</v>
       </c>
       <c t="n" r="F30">
-        <v>20.4625</v>
+        <v>20.4446</v>
       </c>
       <c t="n" r="G30">
-        <v>10.5727</v>
+        <v>10.6528</v>
       </c>
     </row>
     <row r="31">
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>10.0032</v>
+        <v>11.0139</v>
       </c>
       <c t="n" r="E31">
-        <v>25.2488</v>
+        <v>23.8525</v>
       </c>
       <c t="n" r="F31">
-        <v>38.7788</v>
+        <v>41.6701</v>
       </c>
       <c t="n" r="G31">
-        <v>36.7955</v>
+        <v>37.9630</v>
       </c>
     </row>
     <row r="32">
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>3.2104</v>
+        <v>3.1629</v>
       </c>
       <c t="n" r="E32">
-        <v>9.7831</v>
+        <v>9.8247</v>
       </c>
       <c t="n" r="G32">
-        <v>10.8058</v>
+        <v>10.8989</v>
       </c>
     </row>
     <row r="33">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>3.1684</v>
+        <v>3.1657</v>
       </c>
       <c t="n" r="E33">
-        <v>9.7921</v>
+        <v>9.7325</v>
       </c>
       <c t="n" r="G33">
-        <v>10.7126</v>
+        <v>10.8058</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -291,63 +291,57 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>-9.4178</v>
+        <v>-4.1096</v>
       </c>
       <c t="n" r="E3">
-        <v>-13.8156</v>
+        <v>-10.1412</v>
       </c>
       <c t="n" r="F3">
-        <v>51.7673</v>
+        <v>61.6628</v>
       </c>
       <c t="n" r="G3">
-        <v>2.8783</v>
+        <v>8.9070</v>
       </c>
       <c t="n" r="H3">
-        <v>159.6192</v>
+        <v>177.9984</v>
       </c>
       <c t="n" r="I3">
-        <v>516.8377</v>
+        <v>553.9000</v>
       </c>
       <c t="n" r="J3">
-        <v>1440.6570</v>
+        <v>1541.2661</v>
       </c>
     </row>
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">ZKP</t>
+          <t xml:space="preserve">ILK</t>
         </is>
       </c>
       <c t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D4">
-        <v>13.2420</v>
+        <v>-6.0334</v>
       </c>
       <c t="n" r="E4">
-        <v>25.1261</v>
+        <v>4.5714</v>
       </c>
       <c t="n" r="F4">
-        <v>41.4718</v>
+        <v>20.7921</v>
       </c>
       <c t="n" r="G4">
-        <v>34.0541</v>
+        <v>3.9773</v>
       </c>
       <c t="n" r="H4">
-        <v>72.8223</v>
-      </c>
-      <c t="n" r="I4">
-        <v>222.7486</v>
-      </c>
-      <c t="n" r="J4">
-        <v>1155.0607</v>
+        <v>74.7017</v>
       </c>
     </row>
     <row r="5">
@@ -367,36 +361,36 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>-5.7319</v>
+        <v>-4.5661</v>
       </c>
       <c t="n" r="E5">
-        <v>6.3962</v>
+        <v>8.1071</v>
       </c>
       <c t="n" r="F5">
-        <v>21.5449</v>
+        <v>21.7769</v>
       </c>
       <c t="n" r="G5">
-        <v>4.1875</v>
+        <v>5.4760</v>
       </c>
       <c t="n" r="H5">
-        <v>70.1543</v>
+        <v>74.5853</v>
       </c>
       <c t="n" r="I5">
-        <v>431.5924</v>
+        <v>447.3626</v>
       </c>
       <c t="n" r="J5">
-        <v>1506.1576</v>
+        <v>1541.2341</v>
       </c>
     </row>
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">ILK</t>
+          <t xml:space="preserve">FGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C6">
@@ -405,19 +399,25 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>-7.1566</v>
+        <v>-5.2717</v>
       </c>
       <c t="n" r="E6">
-        <v>3.7661</v>
+        <v>6.6667</v>
       </c>
       <c t="n" r="F6">
-        <v>21.4016</v>
+        <v>19.5741</v>
       </c>
       <c t="n" r="G6">
-        <v>2.7344</v>
+        <v>9.3633</v>
       </c>
       <c t="n" r="H6">
-        <v>70.0165</v>
+        <v>70.2624</v>
+      </c>
+      <c t="n" r="I6">
+        <v>412.2807</v>
+      </c>
+      <c t="n" r="J6">
+        <v>1365.8635</v>
       </c>
     </row>
     <row r="7">
@@ -437,25 +437,25 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>11.7323</v>
+        <v>12.6568</v>
       </c>
       <c t="n" r="E7">
-        <v>22.6976</v>
+        <v>24.0126</v>
       </c>
       <c t="n" r="F7">
-        <v>38.0473</v>
+        <v>42.1667</v>
       </c>
       <c t="n" r="G7">
-        <v>39.5272</v>
+        <v>40.6817</v>
       </c>
       <c t="n" r="H7">
-        <v>68.4700</v>
+        <v>69.4702</v>
       </c>
       <c t="n" r="I7">
-        <v>191.0550</v>
+        <v>199.3683</v>
       </c>
       <c t="n" r="J7">
-        <v>1240.0211</v>
+        <v>1222.4806</v>
       </c>
     </row>
     <row r="8">
@@ -475,68 +475,68 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>11.4706</v>
+        <v>12.2647</v>
       </c>
       <c t="n" r="E8">
-        <v>22.4556</v>
+        <v>24.0494</v>
       </c>
       <c t="n" r="F8">
-        <v>38.1195</v>
+        <v>41.6327</v>
       </c>
       <c t="n" r="G8">
-        <v>39.6463</v>
+        <v>40.6411</v>
       </c>
       <c t="n" r="H8">
-        <v>68.2948</v>
+        <v>68.4466</v>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">FGA</t>
+          <t xml:space="preserve">ZKP</t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D9">
-        <v>-6.6099</v>
+        <v>11.3699</v>
       </c>
       <c t="n" r="E9">
-        <v>4.2081</v>
+        <v>22.8715</v>
       </c>
       <c t="n" r="F9">
-        <v>18.5403</v>
+        <v>40.6574</v>
       </c>
       <c t="n" r="G9">
-        <v>7.8184</v>
+        <v>31.8378</v>
       </c>
       <c t="n" r="H9">
-        <v>67.3692</v>
+        <v>67.6289</v>
       </c>
       <c t="n" r="I9">
-        <v>403.0581</v>
+        <v>220.8366</v>
       </c>
       <c t="n" r="J9">
-        <v>1334.3548</v>
+        <v>1111.6244</v>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">ZKE</t>
+          <t xml:space="preserve">ZBB</t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C10">
@@ -545,36 +545,36 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>12.5436</v>
+        <v>11.8583</v>
       </c>
       <c t="n" r="E10">
-        <v>25.1938</v>
+        <v>19.3319</v>
       </c>
       <c t="n" r="F10">
-        <v>40.4959</v>
+        <v>43.1199</v>
       </c>
       <c t="n" r="G10">
-        <v>32.2145</v>
+        <v>32.3012</v>
       </c>
       <c t="n" r="H10">
-        <v>63.3623</v>
+        <v>60.3385</v>
       </c>
       <c t="n" r="I10">
-        <v>175.1278</v>
+        <v>206.9014</v>
       </c>
       <c t="n" r="J10">
-        <v>703.4826</v>
+        <v>1172.7804</v>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">ZBB</t>
+          <t xml:space="preserve">OHY</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C11">
@@ -583,36 +583,30 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>10.3183</v>
+        <v>10.7906</v>
       </c>
       <c t="n" r="E11">
-        <v>19.1572</v>
+        <v>18.1868</v>
       </c>
       <c t="n" r="F11">
-        <v>38.9140</v>
+        <v>38.9086</v>
       </c>
       <c t="n" r="G11">
-        <v>30.4797</v>
+        <v>30.4823</v>
       </c>
       <c t="n" r="H11">
-        <v>58.9497</v>
-      </c>
-      <c t="n" r="I11">
-        <v>199.8884</v>
-      </c>
-      <c t="n" r="J11">
-        <v>1186.8263</v>
+        <v>59.2154</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">OHY</t>
+          <t xml:space="preserve">ZKE</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C12">
@@ -621,19 +615,25 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>9.5545</v>
+        <v>14.2160</v>
       </c>
       <c t="n" r="E12">
-        <v>16.6118</v>
+        <v>26.0769</v>
       </c>
       <c t="n" r="F12">
-        <v>37.3587</v>
+        <v>45.5595</v>
       </c>
       <c t="n" r="G12">
-        <v>29.0264</v>
+        <v>34.1793</v>
       </c>
       <c t="n" r="H12">
-        <v>58.5539</v>
+        <v>59.1262</v>
+      </c>
+      <c t="n" r="I12">
+        <v>183.6622</v>
+      </c>
+      <c t="n" r="J12">
+        <v>696.4043</v>
       </c>
     </row>
     <row r="13">
@@ -653,30 +653,30 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>9.3197</v>
+        <v>10.1493</v>
       </c>
       <c t="n" r="E13">
-        <v>16.7110</v>
+        <v>17.7009</v>
       </c>
       <c t="n" r="F13">
-        <v>38.5074</v>
+        <v>42.9648</v>
       </c>
       <c t="n" r="G13">
-        <v>29.3521</v>
+        <v>30.3338</v>
       </c>
       <c t="n" r="H13">
-        <v>58.1833</v>
+        <v>58.4958</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">OPK</t>
+          <t xml:space="preserve">ZRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY RİSK EŞİT BANKA DIŞI 20 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C14">
@@ -685,30 +685,36 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>5.1438</v>
+        <v>11.7120</v>
       </c>
       <c t="n" r="E14">
-        <v>6.5738</v>
+        <v>27.4233</v>
       </c>
       <c t="n" r="F14">
-        <v>15.8395</v>
+        <v>52.0185</v>
       </c>
       <c t="n" r="G14">
-        <v>15.3523</v>
+        <v>40.2794</v>
       </c>
       <c t="n" r="H14">
-        <v>55.7501</v>
+        <v>58.1365</v>
+      </c>
+      <c t="n" r="I14">
+        <v>144.0589</v>
+      </c>
+      <c t="n" r="J14">
+        <v>915.4494</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">ZRE</t>
+          <t xml:space="preserve">OPK</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY RİSK EŞİT BANKA DIŞI 20 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C15">
@@ -717,25 +723,19 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>9.3943</v>
+        <v>7.4760</v>
       </c>
       <c t="n" r="E15">
-        <v>24.4288</v>
+        <v>10.1506</v>
       </c>
       <c t="n" r="F15">
-        <v>45.7990</v>
+        <v>20.7466</v>
       </c>
       <c t="n" r="G15">
-        <v>37.3690</v>
+        <v>17.9110</v>
       </c>
       <c t="n" r="H15">
-        <v>55.5360</v>
-      </c>
-      <c t="n" r="I15">
-        <v>136.6943</v>
-      </c>
-      <c t="n" r="J15">
-        <v>918.9983</v>
+        <v>57.1963</v>
       </c>
     </row>
     <row r="16">
@@ -755,36 +755,36 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>8.4031</v>
+        <v>9.7152</v>
       </c>
       <c t="n" r="E16">
-        <v>20.5526</v>
+        <v>22.0118</v>
       </c>
       <c t="n" r="F16">
-        <v>43.2313</v>
+        <v>48.8073</v>
       </c>
       <c t="n" r="G16">
-        <v>31.2711</v>
+        <v>32.8600</v>
       </c>
       <c t="n" r="H16">
-        <v>53.5389</v>
+        <v>54.4204</v>
       </c>
       <c t="n" r="I16">
-        <v>154.9908</v>
+        <v>161.4423</v>
       </c>
       <c t="n" r="J16">
-        <v>1026.8137</v>
+        <v>1010.7971</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">ZBP</t>
+          <t xml:space="preserve">ZSR</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST SÜRDÜRÜLEBİLİRLİK 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C17">
@@ -793,36 +793,33 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>7.9303</v>
+        <v>10.0481</v>
       </c>
       <c t="n" r="E17">
-        <v>3.1817</v>
+        <v>15.7097</v>
       </c>
       <c t="n" r="F17">
-        <v>29.5568</v>
+        <v>38.5208</v>
       </c>
       <c t="n" r="G17">
-        <v>7.4275</v>
+        <v>27.8680</v>
       </c>
       <c t="n" r="H17">
-        <v>50.5076</v>
+        <v>51.6100</v>
       </c>
       <c t="n" r="I17">
-        <v>305.2128</v>
-      </c>
-      <c t="n" r="J17">
-        <v>1845.1734</v>
+        <v>217.2544</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">ZSR</t>
+          <t xml:space="preserve">ZBP</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST SÜRDÜRÜLEBİLİRLİK 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C18">
@@ -831,22 +828,25 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>9.0651</v>
+        <v>8.8404</v>
       </c>
       <c t="n" r="E18">
-        <v>14.5709</v>
+        <v>4.3370</v>
       </c>
       <c t="n" r="F18">
-        <v>34.3288</v>
+        <v>37.0213</v>
       </c>
       <c t="n" r="G18">
-        <v>26.7259</v>
+        <v>8.3333</v>
       </c>
       <c t="n" r="H18">
-        <v>50.2558</v>
+        <v>51.5020</v>
       </c>
       <c t="n" r="I18">
-        <v>209.9317</v>
+        <v>313.3096</v>
+      </c>
+      <c t="n" r="J18">
+        <v>1795.8333</v>
       </c>
     </row>
     <row r="19">
@@ -866,36 +866,36 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>6.0580</v>
+        <v>7.5797</v>
       </c>
       <c t="n" r="E19">
-        <v>12.5533</v>
+        <v>13.8906</v>
       </c>
       <c t="n" r="F19">
-        <v>35.5099</v>
+        <v>40.7588</v>
       </c>
       <c t="n" r="G19">
-        <v>23.0513</v>
+        <v>24.8168</v>
       </c>
       <c t="n" r="H19">
-        <v>47.8191</v>
+        <v>49.8800</v>
       </c>
       <c t="n" r="I19">
-        <v>203.2841</v>
+        <v>206.9299</v>
       </c>
       <c t="n" r="J19">
-        <v>983.9202</v>
+        <v>982.9480</v>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">ZPT</t>
+          <t xml:space="preserve">BLH</t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C20">
@@ -904,33 +904,30 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>14.6235</v>
+        <v>6.3913</v>
       </c>
       <c t="n" r="E20">
-        <v>29.1152</v>
+        <v>3.5986</v>
       </c>
       <c t="n" r="F20">
-        <v>32.3219</v>
+        <v>35.8690</v>
       </c>
       <c t="n" r="G20">
-        <v>38.3174</v>
+        <v>7.7974</v>
       </c>
       <c t="n" r="H20">
-        <v>47.5313</v>
-      </c>
-      <c t="n" r="I20">
-        <v>233.4810</v>
+        <v>49.6636</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">BLH</t>
+          <t xml:space="preserve">ZPT</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C21">
@@ -939,19 +936,22 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>4.5870</v>
+        <v>14.7757</v>
       </c>
       <c t="n" r="E21">
-        <v>1.2629</v>
+        <v>30.0598</v>
       </c>
       <c t="n" r="F21">
-        <v>27.3425</v>
+        <v>38.2303</v>
       </c>
       <c t="n" r="G21">
-        <v>5.9692</v>
+        <v>38.5011</v>
       </c>
       <c t="n" r="H21">
-        <v>47.3507</v>
+        <v>48.7375</v>
+      </c>
+      <c t="n" r="I21">
+        <v>234.4175</v>
       </c>
     </row>
     <row r="22">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>4.3531</v>
+        <v>5.7172</v>
       </c>
       <c t="n" r="E22">
-        <v>11.3442</v>
+        <v>11.9847</v>
       </c>
       <c t="n" r="F22">
-        <v>32.0975</v>
+        <v>36.7765</v>
       </c>
       <c t="n" r="G22">
-        <v>20.1386</v>
+        <v>21.7090</v>
       </c>
       <c t="n" r="H22">
-        <v>41.5895</v>
+        <v>42.4709</v>
       </c>
     </row>
     <row r="23">
@@ -1003,25 +1003,25 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>11.8300</v>
+        <v>12.4960</v>
       </c>
       <c t="n" r="E23">
-        <v>15.9868</v>
+        <v>16.2570</v>
       </c>
       <c t="n" r="F23">
-        <v>18.5210</v>
+        <v>21.6810</v>
       </c>
       <c t="n" r="G23">
-        <v>22.0069</v>
+        <v>22.7336</v>
       </c>
       <c t="n" r="H23">
-        <v>34.9923</v>
+        <v>34.9182</v>
       </c>
       <c t="n" r="I23">
-        <v>95.4545</v>
+        <v>98.2118</v>
       </c>
       <c t="n" r="J23">
-        <v>751.4851</v>
+        <v>738.1380</v>
       </c>
     </row>
     <row r="24">
@@ -1041,22 +1041,22 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>3.4743</v>
+        <v>4.6463</v>
       </c>
       <c t="n" r="E24">
-        <v>4.6571</v>
+        <v>5.1746</v>
       </c>
       <c t="n" r="F24">
-        <v>25.1772</v>
+        <v>29.2123</v>
       </c>
       <c t="n" r="G24">
-        <v>12.9283</v>
+        <v>14.2074</v>
       </c>
       <c t="n" r="H24">
-        <v>24.2461</v>
+        <v>23.7624</v>
       </c>
       <c t="n" r="I24">
-        <v>118.3746</v>
+        <v>120.6142</v>
       </c>
     </row>
     <row r="25">
@@ -1076,25 +1076,25 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>0.8195</v>
+        <v>0.5785</v>
       </c>
       <c t="n" r="E25">
-        <v>3.8739</v>
+        <v>3.6770</v>
       </c>
       <c t="n" r="F25">
-        <v>7.3665</v>
+        <v>6.8904</v>
       </c>
       <c t="n" r="G25">
-        <v>4.1065</v>
+        <v>3.8576</v>
       </c>
       <c t="n" r="H25">
-        <v>17.4011</v>
+        <v>17.3510</v>
       </c>
       <c t="n" r="I25">
-        <v>122.3108</v>
+        <v>116.8693</v>
       </c>
       <c t="n" r="J25">
-        <v>436.7638</v>
+        <v>440.2641</v>
       </c>
     </row>
     <row r="26">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>-6.3638</v>
+        <v>-5.4547</v>
       </c>
     </row>
     <row r="27">
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>3.3932</v>
+        <v>4.9102</v>
       </c>
       <c t="n" r="E27">
-        <v>8.8693</v>
+        <v>9.2723</v>
       </c>
       <c t="n" r="F27">
-        <v>28.8557</v>
+        <v>32.9960</v>
       </c>
       <c t="n" r="G27">
-        <v>18.8619</v>
+        <v>20.6058</v>
       </c>
     </row>
     <row r="28">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>2.9933</v>
+        <v>3.1085</v>
       </c>
       <c t="n" r="E29">
-        <v>9.6196</v>
+        <v>9.6326</v>
       </c>
       <c t="n" r="G29">
-        <v>10.9457</v>
+        <v>11.0697</v>
       </c>
     </row>
     <row r="30">
@@ -1206,16 +1206,16 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>3.0970</v>
+        <v>3.2090</v>
       </c>
       <c t="n" r="E30">
-        <v>9.5559</v>
+        <v>9.5880</v>
       </c>
       <c t="n" r="F30">
-        <v>20.4446</v>
+        <v>20.4704</v>
       </c>
       <c t="n" r="G30">
-        <v>10.6528</v>
+        <v>10.7729</v>
       </c>
     </row>
     <row r="31">
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>11.0139</v>
+        <v>12.0505</v>
       </c>
       <c t="n" r="E31">
-        <v>23.8525</v>
+        <v>25.3261</v>
       </c>
       <c t="n" r="F31">
-        <v>41.6701</v>
+        <v>45.2446</v>
       </c>
       <c t="n" r="G31">
-        <v>37.9630</v>
+        <v>39.2512</v>
       </c>
     </row>
     <row r="32">
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>3.1629</v>
+        <v>3.2929</v>
       </c>
       <c t="n" r="E32">
-        <v>9.8247</v>
+        <v>9.8111</v>
       </c>
       <c t="n" r="G32">
-        <v>10.8989</v>
+        <v>11.0387</v>
       </c>
     </row>
     <row r="33">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>3.1657</v>
+        <v>3.2958</v>
       </c>
       <c t="n" r="E33">
-        <v>9.7325</v>
+        <v>9.7190</v>
       </c>
       <c t="n" r="G33">
-        <v>10.8058</v>
+        <v>10.9455</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -291,25 +291,25 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>-2.4067</v>
+        <v>9.5416</v>
       </c>
       <c t="n" r="E3">
-        <v>-9.3618</v>
+        <v>-9.7359</v>
       </c>
       <c t="n" r="F3">
-        <v>49.4658</v>
+        <v>62.4834</v>
       </c>
       <c t="n" r="G3">
-        <v>8.8292</v>
+        <v>14.3135</v>
       </c>
       <c t="n" r="H3">
-        <v>170.7043</v>
+        <v>188.3634</v>
       </c>
       <c t="n" r="I3">
-        <v>553.4330</v>
+        <v>562.8327</v>
       </c>
       <c t="n" r="J3">
-        <v>1491.5813</v>
+        <v>1582.8905</v>
       </c>
     </row>
     <row r="4">
@@ -329,68 +329,68 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>11.6279</v>
+        <v>12.8156</v>
       </c>
       <c t="n" r="E4">
-        <v>22.5097</v>
+        <v>24.1210</v>
       </c>
       <c t="n" r="F4">
-        <v>44.0000</v>
+        <v>52.0569</v>
       </c>
       <c t="n" r="G4">
-        <v>39.1304</v>
+        <v>42.1095</v>
       </c>
       <c t="n" r="H4">
-        <v>75.0422</v>
+        <v>77.3442</v>
       </c>
     </row>
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">ZKP</t>
+          <t xml:space="preserve">ZGD</t>
         </is>
       </c>
       <c t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY ALTIN KATILIM  BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D5">
-        <v>8.8889</v>
+        <v>-0.2971</v>
       </c>
       <c t="n" r="E5">
-        <v>21.3172</v>
+        <v>9.8981</v>
       </c>
       <c t="n" r="F5">
-        <v>42.8571</v>
+        <v>18.2459</v>
       </c>
       <c t="n" r="G5">
-        <v>32.4324</v>
+        <v>8.0888</v>
       </c>
       <c t="n" r="H5">
-        <v>71.3287</v>
+        <v>75.0522</v>
       </c>
       <c t="n" r="I5">
-        <v>222.2836</v>
+        <v>447.8955</v>
       </c>
       <c t="n" r="J5">
-        <v>1117.0889</v>
+        <v>1548.4716</v>
       </c>
     </row>
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">ZGD</t>
+          <t xml:space="preserve">ILK</t>
         </is>
       </c>
       <c t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY ALTIN KATILIM  BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C6">
@@ -399,36 +399,30 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>-4.3182</v>
+        <v>-3.3117</v>
       </c>
       <c t="n" r="E6">
-        <v>8.3456</v>
+        <v>5.6778</v>
       </c>
       <c t="n" r="F6">
-        <v>15.1172</v>
+        <v>13.4909</v>
       </c>
       <c t="n" r="G6">
-        <v>5.4760</v>
+        <v>5.7528</v>
       </c>
       <c t="n" r="H6">
-        <v>69.9539</v>
-      </c>
-      <c t="n" r="I6">
-        <v>447.3626</v>
-      </c>
-      <c t="n" r="J6">
-        <v>1512.1444</v>
+        <v>74.8884</v>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">ZPP</t>
+          <t xml:space="preserve">ZKP</t>
         </is>
       </c>
       <c t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C7">
@@ -437,36 +431,36 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>13.2755</v>
+        <v>11.4082</v>
       </c>
       <c t="n" r="E7">
-        <v>18.4376</v>
+        <v>22.1598</v>
       </c>
       <c t="n" r="F7">
-        <v>41.6574</v>
+        <v>46.1988</v>
       </c>
       <c t="n" r="G7">
-        <v>40.0220</v>
+        <v>35.1351</v>
       </c>
       <c t="n" r="H7">
-        <v>69.6304</v>
+        <v>74.1553</v>
       </c>
       <c t="n" r="I7">
-        <v>197.9644</v>
+        <v>234.1353</v>
       </c>
       <c t="n" r="J7">
-        <v>1220.3733</v>
+        <v>1168.3917</v>
       </c>
     </row>
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">BND</t>
+          <t xml:space="preserve">ZPP</t>
         </is>
       </c>
       <c t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C8">
@@ -475,138 +469,138 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>14.1780</v>
+        <v>14.3172</v>
       </c>
       <c t="n" r="E8">
-        <v>17.9495</v>
+        <v>20.4735</v>
       </c>
       <c t="n" r="F8">
-        <v>41.1787</v>
+        <v>47.6949</v>
       </c>
       <c t="n" r="G8">
-        <v>39.4620</v>
+        <v>42.6608</v>
       </c>
       <c t="n" r="H8">
-        <v>68.3719</v>
+        <v>71.4569</v>
+      </c>
+      <c t="n" r="I8">
+        <v>207.1733</v>
+      </c>
+      <c t="n" r="J8">
+        <v>1259.3504</v>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">ILK</t>
+          <t xml:space="preserve">OPK</t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D9">
-        <v>-6.7351</v>
+        <v>9.2093</v>
       </c>
       <c t="n" r="E9">
-        <v>3.8942</v>
+        <v>9.8908</v>
       </c>
       <c t="n" r="F9">
-        <v>13.5938</v>
+        <v>28.4933</v>
       </c>
       <c t="n" r="G9">
-        <v>3.2670</v>
+        <v>23.4490</v>
       </c>
       <c t="n" r="H9">
-        <v>68.3260</v>
+        <v>71.1370</v>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">ZKE</t>
+          <t xml:space="preserve">FGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D10">
-        <v>10.0000</v>
+        <v>2.3820</v>
       </c>
       <c t="n" r="E10">
-        <v>25.4497</v>
+        <v>7.0730</v>
       </c>
       <c t="n" r="F10">
-        <v>45.8185</v>
+        <v>19.8705</v>
       </c>
       <c t="n" r="G10">
-        <v>34.1793</v>
+        <v>12.6873</v>
       </c>
       <c t="n" r="H10">
-        <v>67.4157</v>
+        <v>70.6608</v>
       </c>
       <c t="n" r="I10">
-        <v>183.6622</v>
+        <v>417.6344</v>
       </c>
       <c t="n" r="J10">
-        <v>697.5669</v>
+        <v>1376.6871</v>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">FGA</t>
+          <t xml:space="preserve">BND</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D11">
-        <v>-4.6455</v>
+        <v>12.8672</v>
       </c>
       <c t="n" r="E11">
-        <v>5.9303</v>
+        <v>19.4280</v>
       </c>
       <c t="n" r="F11">
-        <v>16.3022</v>
+        <v>46.4177</v>
       </c>
       <c t="n" r="G11">
-        <v>9.5506</v>
+        <v>41.5623</v>
       </c>
       <c t="n" r="H11">
-        <v>65.7224</v>
-      </c>
-      <c t="n" r="I11">
-        <v>413.1579</v>
-      </c>
-      <c t="n" r="J11">
-        <v>1340.8867</v>
+        <v>69.7746</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">OHY</t>
+          <t xml:space="preserve">BOE</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C12">
@@ -615,30 +609,30 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>11.3613</v>
+        <v>15.9778</v>
       </c>
       <c t="n" r="E12">
-        <v>15.8277</v>
+        <v>19.1847</v>
       </c>
       <c t="n" r="F12">
-        <v>42.1539</v>
+        <v>52.6470</v>
       </c>
       <c t="n" r="G12">
-        <v>30.5126</v>
+        <v>36.8128</v>
       </c>
       <c t="n" r="H12">
-        <v>61.5847</v>
+        <v>68.9293</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">ZRE</t>
+          <t xml:space="preserve">ZKE</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY RİSK EŞİT BANKA DIŞI 20 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C13">
@@ -647,36 +641,36 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>10.6568</v>
+        <v>10.9934</v>
       </c>
       <c t="n" r="E13">
-        <v>21.6621</v>
+        <v>26.1099</v>
       </c>
       <c t="n" r="F13">
-        <v>49.0196</v>
+        <v>50.3139</v>
       </c>
       <c t="n" r="G13">
-        <v>38.6108</v>
+        <v>37.2084</v>
       </c>
       <c t="n" r="H13">
-        <v>60.1794</v>
+        <v>67.0154</v>
       </c>
       <c t="n" r="I13">
-        <v>141.1558</v>
+        <v>194.7591</v>
       </c>
       <c t="n" r="J13">
-        <v>907.9007</v>
+        <v>739.6794</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">ZBB</t>
+          <t xml:space="preserve">ZBP</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C14">
@@ -685,36 +679,36 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>10.6405</v>
+        <v>13.4321</v>
       </c>
       <c t="n" r="E14">
-        <v>14.6681</v>
+        <v>6.7743</v>
       </c>
       <c t="n" r="F14">
-        <v>41.4328</v>
+        <v>43.9974</v>
       </c>
       <c t="n" r="G14">
-        <v>30.0546</v>
+        <v>12.9917</v>
       </c>
       <c t="n" r="H14">
-        <v>60.0897</v>
+        <v>65.0038</v>
       </c>
       <c t="n" r="I14">
-        <v>201.6901</v>
+        <v>313.4470</v>
       </c>
       <c t="n" r="J14">
-        <v>1148.2517</v>
+        <v>1917.5601</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">BOE</t>
+          <t xml:space="preserve">ZBB</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C15">
@@ -723,30 +717,36 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>10.2228</v>
+        <v>13.1228</v>
       </c>
       <c t="n" r="E15">
-        <v>14.1991</v>
+        <v>16.9366</v>
       </c>
       <c t="n" r="F15">
-        <v>41.6249</v>
+        <v>47.8684</v>
       </c>
       <c t="n" r="G15">
-        <v>29.4830</v>
+        <v>33.7280</v>
       </c>
       <c t="n" r="H15">
-        <v>59.9434</v>
+        <v>64.2431</v>
+      </c>
+      <c t="n" r="I15">
+        <v>212.3227</v>
+      </c>
+      <c t="n" r="J15">
+        <v>1204.7986</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">OPK</t>
+          <t xml:space="preserve">OHY</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C16">
@@ -755,30 +755,30 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>6.7628</v>
+        <v>12.4743</v>
       </c>
       <c t="n" r="E16">
-        <v>5.3780</v>
+        <v>15.6572</v>
       </c>
       <c t="n" r="F16">
-        <v>19.9928</v>
+        <v>46.8928</v>
       </c>
       <c t="n" r="G16">
-        <v>16.7543</v>
+        <v>32.6357</v>
       </c>
       <c t="n" r="H16">
-        <v>59.7602</v>
+        <v>63.9670</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">ZEA</t>
+          <t xml:space="preserve">BLH</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C17">
@@ -787,36 +787,30 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>9.9553</v>
+        <v>13.0531</v>
       </c>
       <c t="n" r="E17">
-        <v>18.9353</v>
+        <v>5.8848</v>
       </c>
       <c t="n" r="F17">
-        <v>47.4869</v>
+        <v>43.1373</v>
       </c>
       <c t="n" r="G17">
-        <v>32.9277</v>
+        <v>12.5551</v>
       </c>
       <c t="n" r="H17">
-        <v>58.4206</v>
-      </c>
-      <c t="n" r="I17">
-        <v>161.5753</v>
-      </c>
-      <c t="n" r="J17">
-        <v>1015.1446</v>
+        <v>63.3632</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">ZSR</t>
+          <t xml:space="preserve">ZRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST SÜRDÜRÜLEBİLİRLİK 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY RİSK EŞİT BANKA DIŞI 20 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C18">
@@ -825,33 +819,36 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>9.6179</v>
+        <v>12.9822</v>
       </c>
       <c t="n" r="E18">
-        <v>11.8781</v>
+        <v>25.3823</v>
       </c>
       <c t="n" r="F18">
-        <v>37.4071</v>
+        <v>55.0420</v>
       </c>
       <c t="n" r="G18">
-        <v>26.7005</v>
+        <v>43.1898</v>
       </c>
       <c t="n" r="H18">
-        <v>53.2699</v>
+        <v>63.2021</v>
       </c>
       <c t="n" r="I18">
-        <v>214.3577</v>
+        <v>151.9115</v>
+      </c>
+      <c t="n" r="J18">
+        <v>956.7010</v>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">ZPT</t>
+          <t xml:space="preserve">ZEA</t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C19">
@@ -860,33 +857,36 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>16.2087</v>
+        <v>13.0459</v>
       </c>
       <c t="n" r="E19">
-        <v>25.2486</v>
+        <v>21.7860</v>
       </c>
       <c t="n" r="F19">
-        <v>38.8072</v>
+        <v>54.8190</v>
       </c>
       <c t="n" r="G19">
-        <v>38.8072</v>
+        <v>37.3901</v>
       </c>
       <c t="n" r="H19">
-        <v>52.6805</v>
+        <v>62.4301</v>
       </c>
       <c t="n" r="I19">
-        <v>235.1567</v>
+        <v>171.6578</v>
+      </c>
+      <c t="n" r="J19">
+        <v>1073.8879</v>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">ZBP</t>
+          <t xml:space="preserve">ZSR</t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST SÜRDÜRÜLEBİLİRLİK 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C20">
@@ -895,25 +895,22 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>7.8125</v>
+        <v>11.5602</v>
       </c>
       <c t="n" r="E20">
-        <v>4.0201</v>
+        <v>13.9117</v>
       </c>
       <c t="n" r="F20">
-        <v>34.4592</v>
+        <v>43.8498</v>
       </c>
       <c t="n" r="G20">
-        <v>7.1429</v>
+        <v>30.3046</v>
       </c>
       <c t="n" r="H20">
-        <v>51.1501</v>
+        <v>57.1953</v>
       </c>
       <c t="n" r="I20">
-        <v>308.7678</v>
-      </c>
-      <c t="n" r="J20">
-        <v>1758.1688</v>
+        <v>226.1753</v>
       </c>
     </row>
     <row r="21">
@@ -933,36 +930,36 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>6.6225</v>
+        <v>9.2158</v>
       </c>
       <c t="n" r="E21">
-        <v>10.2740</v>
+        <v>13.2344</v>
       </c>
       <c t="n" r="F21">
-        <v>37.5046</v>
+        <v>43.1895</v>
       </c>
       <c t="n" r="G21">
-        <v>23.3511</v>
+        <v>27.1153</v>
       </c>
       <c t="n" r="H21">
-        <v>50.0405</v>
+        <v>56.2014</v>
       </c>
       <c t="n" r="I21">
-        <v>203.3257</v>
+        <v>215.8940</v>
       </c>
       <c t="n" r="J21">
-        <v>965.3049</v>
+        <v>1019.0616</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">BLH</t>
+          <t xml:space="preserve">ZPT</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C22">
@@ -971,19 +968,22 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>7.2345</v>
+        <v>16.0438</v>
       </c>
       <c t="n" r="E22">
-        <v>4.1246</v>
+        <v>28.1924</v>
       </c>
       <c t="n" r="F22">
-        <v>34.0802</v>
+        <v>47.1443</v>
       </c>
       <c t="n" r="G22">
-        <v>6.7621</v>
+        <v>42.6035</v>
       </c>
       <c t="n" r="H22">
-        <v>49.7374</v>
+        <v>52.9419</v>
+      </c>
+      <c t="n" r="I22">
+        <v>249.1754</v>
       </c>
     </row>
     <row r="23">
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>5.2037</v>
+        <v>8.1234</v>
       </c>
       <c t="n" r="E23">
-        <v>8.5310</v>
+        <v>12.0535</v>
       </c>
       <c t="n" r="F23">
-        <v>33.9841</v>
+        <v>39.3247</v>
       </c>
       <c t="n" r="G23">
-        <v>20.4619</v>
+        <v>23.8799</v>
       </c>
       <c t="n" r="H23">
-        <v>44.8889</v>
+        <v>47.0395</v>
       </c>
     </row>
     <row r="24">
@@ -1035,25 +1035,25 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>15.5006</v>
+        <v>14.4121</v>
       </c>
       <c t="n" r="E24">
-        <v>17.4608</v>
+        <v>16.0256</v>
       </c>
       <c t="n" r="F24">
-        <v>18.3882</v>
+        <v>19.5509</v>
       </c>
       <c t="n" r="G24">
-        <v>24.5329</v>
+        <v>25.2595</v>
       </c>
       <c t="n" r="H24">
-        <v>41.4145</v>
+        <v>41.7384</v>
       </c>
       <c t="n" r="I24">
-        <v>101.1176</v>
+        <v>104.0586</v>
       </c>
       <c t="n" r="J24">
-        <v>748.0207</v>
+        <v>766.4433</v>
       </c>
     </row>
     <row r="25">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>5.9966</v>
+        <v>6.9094</v>
       </c>
       <c t="n" r="E25">
-        <v>5.1089</v>
+        <v>7.1754</v>
       </c>
       <c t="n" r="F25">
-        <v>29.0356</v>
+        <v>34.1084</v>
       </c>
       <c t="n" r="G25">
-        <v>14.6642</v>
+        <v>18.0448</v>
       </c>
       <c t="n" r="H25">
-        <v>27.6704</v>
+        <v>29.8492</v>
       </c>
       <c t="n" r="I25">
-        <v>121.4966</v>
+        <v>126.5077</v>
       </c>
     </row>
     <row r="26">
@@ -1108,25 +1108,25 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>1.0138</v>
+        <v>0.6971</v>
       </c>
       <c t="n" r="E26">
-        <v>3.4866</v>
+        <v>3.6112</v>
       </c>
       <c t="n" r="F26">
-        <v>7.1977</v>
+        <v>6.7261</v>
       </c>
       <c t="n" r="G26">
-        <v>4.1563</v>
+        <v>4.2558</v>
       </c>
       <c t="n" r="H26">
-        <v>13.5685</v>
+        <v>17.0439</v>
       </c>
       <c t="n" r="I26">
-        <v>117.4930</v>
+        <v>108.4080</v>
       </c>
       <c t="n" r="J26">
-        <v>444.0010</v>
+        <v>441.7044</v>
       </c>
     </row>
     <row r="27">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>-3.7673</v>
+        <v>-2.2608</v>
       </c>
     </row>
     <row r="28">
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>5.4348</v>
+        <v>9.0213</v>
       </c>
       <c t="n" r="E28">
-        <v>5.4348</v>
+        <v>9.8174</v>
       </c>
       <c t="n" r="F28">
-        <v>32.6748</v>
+        <v>37.5508</v>
       </c>
       <c t="n" r="G28">
-        <v>20.1927</v>
+        <v>24.2313</v>
       </c>
     </row>
     <row r="29">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>3.4737</v>
+        <v>2.9257</v>
       </c>
       <c t="n" r="E30">
-        <v>9.6839</v>
+        <v>9.5620</v>
       </c>
       <c t="n" r="G30">
-        <v>11.5658</v>
+        <v>11.6898</v>
       </c>
     </row>
     <row r="31">
@@ -1238,16 +1238,16 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>3.5794</v>
+        <v>3.0000</v>
       </c>
       <c t="n" r="E31">
-        <v>9.5858</v>
+        <v>9.6177</v>
       </c>
       <c t="n" r="F31">
-        <v>20.4422</v>
+        <v>20.4417</v>
       </c>
       <c t="n" r="G31">
-        <v>11.2535</v>
+        <v>11.3736</v>
       </c>
     </row>
     <row r="32">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>3.6364</v>
+        <v>3.0968</v>
       </c>
       <c t="n" r="E32">
-        <v>9.8165</v>
+        <v>9.8030</v>
       </c>
       <c t="n" r="G32">
-        <v>11.5044</v>
+        <v>11.6442</v>
       </c>
     </row>
     <row r="33">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>3.5946</v>
+        <v>3.0551</v>
       </c>
       <c t="n" r="E33">
-        <v>9.7751</v>
+        <v>9.8624</v>
       </c>
       <c t="n" r="G33">
-        <v>11.4113</v>
+        <v>11.5510</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -291,25 +291,25 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>9.5416</v>
+        <v>5.7398</v>
       </c>
       <c t="n" r="E3">
-        <v>-9.7359</v>
+        <v>-15.5655</v>
       </c>
       <c t="n" r="F3">
-        <v>62.4834</v>
+        <v>57.7864</v>
       </c>
       <c t="n" r="G3">
-        <v>14.3135</v>
+        <v>10.3462</v>
       </c>
       <c t="n" r="H3">
-        <v>188.3634</v>
+        <v>178.3556</v>
       </c>
       <c t="n" r="I3">
-        <v>562.8327</v>
+        <v>534.1082</v>
       </c>
       <c t="n" r="J3">
-        <v>1582.8905</v>
+        <v>1518.1839</v>
       </c>
     </row>
     <row r="4">
@@ -329,68 +329,68 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>12.8156</v>
+        <v>13.7424</v>
       </c>
       <c t="n" r="E4">
-        <v>24.1210</v>
+        <v>24.4406</v>
       </c>
       <c t="n" r="F4">
-        <v>52.0569</v>
+        <v>48.5082</v>
       </c>
       <c t="n" r="G4">
-        <v>42.1095</v>
+        <v>43.2770</v>
       </c>
       <c t="n" r="H4">
-        <v>77.3442</v>
+        <v>78.8011</v>
       </c>
     </row>
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">ZGD</t>
+          <t xml:space="preserve">ZKP</t>
         </is>
       </c>
       <c t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY ALTIN KATILIM  BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D5">
-        <v>-0.2971</v>
+        <v>11.3636</v>
       </c>
       <c t="n" r="E5">
-        <v>9.8981</v>
+        <v>21.7540</v>
       </c>
       <c t="n" r="F5">
-        <v>18.2459</v>
+        <v>45.2907</v>
       </c>
       <c t="n" r="G5">
-        <v>8.0888</v>
+        <v>35.0811</v>
       </c>
       <c t="n" r="H5">
-        <v>75.0522</v>
+        <v>74.0857</v>
       </c>
       <c t="n" r="I5">
-        <v>447.8955</v>
+        <v>236.8833</v>
       </c>
       <c t="n" r="J5">
-        <v>1548.4716</v>
+        <v>1194.8187</v>
       </c>
     </row>
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">ILK</t>
+          <t xml:space="preserve">ZGD</t>
         </is>
       </c>
       <c t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY ALTIN KATILIM  BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C6">
@@ -399,57 +399,57 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>-3.3117</v>
+        <v>-1.5187</v>
       </c>
       <c t="n" r="E6">
-        <v>5.6778</v>
+        <v>6.9943</v>
       </c>
       <c t="n" r="F6">
-        <v>13.4909</v>
+        <v>12.9924</v>
       </c>
       <c t="n" r="G6">
-        <v>5.7528</v>
+        <v>6.7645</v>
       </c>
       <c t="n" r="H6">
-        <v>74.8884</v>
+        <v>72.9075</v>
+      </c>
+      <c t="n" r="I6">
+        <v>438.0592</v>
+      </c>
+      <c t="n" r="J6">
+        <v>1522.9597</v>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">ZKP</t>
+          <t xml:space="preserve">ILK</t>
         </is>
       </c>
       <c t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D7">
-        <v>11.4082</v>
+        <v>-4.9026</v>
       </c>
       <c t="n" r="E7">
-        <v>22.1598</v>
+        <v>3.1701</v>
       </c>
       <c t="n" r="F7">
-        <v>46.1988</v>
+        <v>10.4449</v>
       </c>
       <c t="n" r="G7">
-        <v>35.1351</v>
+        <v>4.0128</v>
       </c>
       <c t="n" r="H7">
-        <v>74.1553</v>
-      </c>
-      <c t="n" r="I7">
-        <v>234.1353</v>
-      </c>
-      <c t="n" r="J7">
-        <v>1168.3917</v>
+        <v>72.0108</v>
       </c>
     </row>
     <row r="8">
@@ -469,36 +469,36 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>14.3172</v>
+        <v>13.2159</v>
       </c>
       <c t="n" r="E8">
-        <v>20.4735</v>
+        <v>17.9170</v>
       </c>
       <c t="n" r="F8">
-        <v>47.6949</v>
+        <v>42.3428</v>
       </c>
       <c t="n" r="G8">
-        <v>42.6608</v>
+        <v>41.2864</v>
       </c>
       <c t="n" r="H8">
-        <v>71.4569</v>
+        <v>69.8051</v>
       </c>
       <c t="n" r="I8">
-        <v>207.1733</v>
+        <v>208.0058</v>
       </c>
       <c t="n" r="J8">
-        <v>1259.3504</v>
+        <v>1271.3981</v>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">OPK</t>
+          <t xml:space="preserve">BND</t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C9">
@@ -507,100 +507,106 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>9.2093</v>
+        <v>12.4559</v>
       </c>
       <c t="n" r="E9">
-        <v>9.8908</v>
+        <v>18.1117</v>
       </c>
       <c t="n" r="F9">
-        <v>28.4933</v>
+        <v>41.9355</v>
       </c>
       <c t="n" r="G9">
-        <v>23.4490</v>
+        <v>41.0464</v>
       </c>
       <c t="n" r="H9">
-        <v>71.1370</v>
+        <v>69.1560</v>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">FGA</t>
+          <t xml:space="preserve">ZKE</t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D10">
-        <v>2.3820</v>
+        <v>11.8874</v>
       </c>
       <c t="n" r="E10">
-        <v>7.0730</v>
+        <v>26.7917</v>
       </c>
       <c t="n" r="F10">
-        <v>19.8705</v>
+        <v>51.9335</v>
       </c>
       <c t="n" r="G10">
-        <v>12.6873</v>
+        <v>38.3135</v>
       </c>
       <c t="n" r="H10">
-        <v>70.6608</v>
+        <v>68.3607</v>
       </c>
       <c t="n" r="I10">
-        <v>417.6344</v>
+        <v>198.1821</v>
       </c>
       <c t="n" r="J10">
-        <v>1376.6871</v>
+        <v>767.7452</v>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">BND</t>
+          <t xml:space="preserve">FGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D11">
-        <v>12.8672</v>
+        <v>0.4679</v>
       </c>
       <c t="n" r="E11">
-        <v>19.4280</v>
+        <v>2.2511</v>
       </c>
       <c t="n" r="F11">
-        <v>46.4177</v>
+        <v>13.1226</v>
       </c>
       <c t="n" r="G11">
-        <v>41.5623</v>
+        <v>10.5805</v>
       </c>
       <c t="n" r="H11">
-        <v>69.7746</v>
+        <v>67.4702</v>
+      </c>
+      <c t="n" r="I11">
+        <v>397.0539</v>
+      </c>
+      <c t="n" r="J11">
+        <v>1345.8864</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">BOE</t>
+          <t xml:space="preserve">OPK</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C12">
@@ -609,30 +615,30 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>15.9778</v>
+        <v>5.2713</v>
       </c>
       <c t="n" r="E12">
-        <v>19.1847</v>
+        <v>6.5265</v>
       </c>
       <c t="n" r="F12">
-        <v>52.6470</v>
+        <v>20.3474</v>
       </c>
       <c t="n" r="G12">
-        <v>36.8128</v>
+        <v>18.9975</v>
       </c>
       <c t="n" r="H12">
-        <v>68.9293</v>
+        <v>64.9660</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">ZKE</t>
+          <t xml:space="preserve">BOE</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C13">
@@ -641,36 +647,30 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>10.9934</v>
+        <v>11.9556</v>
       </c>
       <c t="n" r="E13">
-        <v>26.1099</v>
+        <v>15.5785</v>
       </c>
       <c t="n" r="F13">
-        <v>50.3139</v>
+        <v>42.5141</v>
       </c>
       <c t="n" r="G13">
-        <v>37.2084</v>
+        <v>32.0681</v>
       </c>
       <c t="n" r="H13">
-        <v>67.0154</v>
-      </c>
-      <c t="n" r="I13">
-        <v>194.7591</v>
-      </c>
-      <c t="n" r="J13">
-        <v>739.6794</v>
+        <v>63.0707</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">ZBP</t>
+          <t xml:space="preserve">OHY</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C14">
@@ -679,36 +679,30 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>13.4321</v>
+        <v>11.6255</v>
       </c>
       <c t="n" r="E14">
-        <v>6.7743</v>
+        <v>15.3029</v>
       </c>
       <c t="n" r="F14">
-        <v>43.9974</v>
+        <v>41.4141</v>
       </c>
       <c t="n" r="G14">
-        <v>12.9917</v>
+        <v>31.6348</v>
       </c>
       <c t="n" r="H14">
-        <v>65.0038</v>
-      </c>
-      <c t="n" r="I14">
-        <v>313.4470</v>
-      </c>
-      <c t="n" r="J14">
-        <v>1917.5601</v>
+        <v>62.7297</v>
       </c>
     </row>
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">ZBB</t>
+          <t xml:space="preserve">ZRE</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY RİSK EŞİT BANKA DIŞI 20 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C15">
@@ -717,36 +711,36 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>13.1228</v>
+        <v>12.6148</v>
       </c>
       <c t="n" r="E15">
-        <v>16.9366</v>
+        <v>26.0021</v>
       </c>
       <c t="n" r="F15">
-        <v>47.8684</v>
+        <v>50.6143</v>
       </c>
       <c t="n" r="G15">
-        <v>33.7280</v>
+        <v>42.7241</v>
       </c>
       <c t="n" r="H15">
-        <v>64.2431</v>
+        <v>62.6714</v>
       </c>
       <c t="n" r="I15">
-        <v>212.3227</v>
+        <v>152.5405</v>
       </c>
       <c t="n" r="J15">
-        <v>1204.7986</v>
+        <v>967.9443</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">OHY</t>
+          <t xml:space="preserve">ZBB</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C16">
@@ -755,30 +749,36 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>12.4743</v>
+        <v>11.8901</v>
       </c>
       <c t="n" r="E16">
-        <v>15.6572</v>
+        <v>14.8695</v>
       </c>
       <c t="n" r="F16">
-        <v>46.8928</v>
+        <v>42.1070</v>
       </c>
       <c t="n" r="G16">
-        <v>32.6357</v>
+        <v>32.2708</v>
       </c>
       <c t="n" r="H16">
-        <v>63.9670</v>
+        <v>62.4534</v>
+      </c>
+      <c t="n" r="I16">
+        <v>211.7487</v>
+      </c>
+      <c t="n" r="J16">
+        <v>1199.8210</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">BLH</t>
+          <t xml:space="preserve">ZBP</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C17">
@@ -787,30 +787,36 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>13.0531</v>
+        <v>11.1977</v>
       </c>
       <c t="n" r="E17">
-        <v>5.8848</v>
+        <v>4.9277</v>
       </c>
       <c t="n" r="F17">
-        <v>43.1373</v>
+        <v>34.6759</v>
       </c>
       <c t="n" r="G17">
-        <v>12.5551</v>
+        <v>10.7660</v>
       </c>
       <c t="n" r="H17">
-        <v>63.3632</v>
+        <v>61.7536</v>
+      </c>
+      <c t="n" r="I17">
+        <v>320.4322</v>
+      </c>
+      <c t="n" r="J17">
+        <v>1863.3028</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">ZRE</t>
+          <t xml:space="preserve">BLH</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY RİSK EŞİT BANKA DIŞI 20 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C18">
@@ -819,25 +825,19 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>12.9822</v>
+        <v>11.7257</v>
       </c>
       <c t="n" r="E18">
-        <v>25.3823</v>
+        <v>5.0114</v>
       </c>
       <c t="n" r="F18">
-        <v>55.0420</v>
+        <v>34.7745</v>
       </c>
       <c t="n" r="G18">
-        <v>43.1898</v>
+        <v>11.2335</v>
       </c>
       <c t="n" r="H18">
-        <v>63.2021</v>
-      </c>
-      <c t="n" r="I18">
-        <v>151.9115</v>
-      </c>
-      <c t="n" r="J18">
-        <v>956.7010</v>
+        <v>61.4450</v>
       </c>
     </row>
     <row r="19">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>13.0459</v>
+        <v>12.1001</v>
       </c>
       <c t="n" r="E19">
-        <v>21.7860</v>
+        <v>21.7891</v>
       </c>
       <c t="n" r="F19">
-        <v>54.8190</v>
+        <v>49.0936</v>
       </c>
       <c t="n" r="G19">
-        <v>37.3901</v>
+        <v>36.2407</v>
       </c>
       <c t="n" r="H19">
-        <v>62.4301</v>
+        <v>61.0711</v>
       </c>
       <c t="n" r="I19">
-        <v>171.6578</v>
+        <v>172.8134</v>
       </c>
       <c t="n" r="J19">
-        <v>1073.8879</v>
+        <v>1077.6739</v>
       </c>
     </row>
     <row r="20">
@@ -895,22 +895,22 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>11.5602</v>
+        <v>10.2999</v>
       </c>
       <c t="n" r="E20">
-        <v>13.9117</v>
+        <v>12.6248</v>
       </c>
       <c t="n" r="F20">
-        <v>43.8498</v>
+        <v>38.1600</v>
       </c>
       <c t="n" r="G20">
-        <v>30.3046</v>
+        <v>28.8325</v>
       </c>
       <c t="n" r="H20">
-        <v>57.1953</v>
+        <v>55.4195</v>
       </c>
       <c t="n" r="I20">
-        <v>226.1753</v>
+        <v>225.3846</v>
       </c>
     </row>
     <row r="21">
@@ -930,25 +930,25 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>9.2158</v>
+        <v>8.2427</v>
       </c>
       <c t="n" r="E21">
-        <v>13.2344</v>
+        <v>13.1658</v>
       </c>
       <c t="n" r="F21">
-        <v>43.1895</v>
+        <v>38.8909</v>
       </c>
       <c t="n" r="G21">
-        <v>27.1153</v>
+        <v>25.9827</v>
       </c>
       <c t="n" r="H21">
-        <v>56.2014</v>
+        <v>54.8097</v>
       </c>
       <c t="n" r="I21">
-        <v>215.8940</v>
+        <v>213.5987</v>
       </c>
       <c t="n" r="J21">
-        <v>1019.0616</v>
+        <v>1021.5896</v>
       </c>
     </row>
     <row r="22">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>16.0438</v>
+        <v>16.7912</v>
       </c>
       <c t="n" r="E22">
-        <v>28.1924</v>
+        <v>28.5934</v>
       </c>
       <c t="n" r="F22">
-        <v>47.1443</v>
+        <v>45.1573</v>
       </c>
       <c t="n" r="G22">
-        <v>42.6035</v>
+        <v>43.5219</v>
       </c>
       <c t="n" r="H22">
-        <v>52.9419</v>
+        <v>53.9270</v>
       </c>
       <c t="n" r="I22">
-        <v>249.1754</v>
+        <v>251.9520</v>
       </c>
     </row>
     <row r="23">
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>8.1234</v>
+        <v>7.3977</v>
       </c>
       <c t="n" r="E23">
-        <v>12.0535</v>
+        <v>11.6747</v>
       </c>
       <c t="n" r="F23">
-        <v>39.3247</v>
+        <v>34.3419</v>
       </c>
       <c t="n" r="G23">
-        <v>23.8799</v>
+        <v>23.0485</v>
       </c>
       <c t="n" r="H23">
-        <v>47.0395</v>
+        <v>46.0526</v>
       </c>
     </row>
     <row r="24">
@@ -1035,25 +1035,25 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>14.4121</v>
+        <v>14.3173</v>
       </c>
       <c t="n" r="E24">
-        <v>16.0256</v>
+        <v>15.0811</v>
       </c>
       <c t="n" r="F24">
-        <v>19.5509</v>
+        <v>16.2649</v>
       </c>
       <c t="n" r="G24">
-        <v>25.2595</v>
+        <v>25.1557</v>
       </c>
       <c t="n" r="H24">
-        <v>41.7384</v>
+        <v>41.6210</v>
       </c>
       <c t="n" r="I24">
-        <v>104.0586</v>
+        <v>106.4498</v>
       </c>
       <c t="n" r="J24">
-        <v>766.4433</v>
+        <v>770.3080</v>
       </c>
     </row>
     <row r="25">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>6.9094</v>
+        <v>6.7853</v>
       </c>
       <c t="n" r="E25">
-        <v>7.1754</v>
+        <v>7.3181</v>
       </c>
       <c t="n" r="F25">
-        <v>34.1084</v>
+        <v>31.0152</v>
       </c>
       <c t="n" r="G25">
-        <v>18.0448</v>
+        <v>17.9077</v>
       </c>
       <c t="n" r="H25">
-        <v>29.8492</v>
+        <v>29.6985</v>
       </c>
       <c t="n" r="I25">
-        <v>126.5077</v>
+        <v>130.3642</v>
       </c>
     </row>
     <row r="26">
@@ -1108,25 +1108,25 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.6971</v>
+        <v>0.8413</v>
       </c>
       <c t="n" r="E26">
-        <v>3.6112</v>
+        <v>3.9395</v>
       </c>
       <c t="n" r="F26">
-        <v>6.7261</v>
+        <v>7.0973</v>
       </c>
       <c t="n" r="G26">
-        <v>4.2558</v>
+        <v>4.4052</v>
       </c>
       <c t="n" r="H26">
-        <v>17.0439</v>
+        <v>17.2115</v>
       </c>
       <c t="n" r="I26">
-        <v>108.4080</v>
+        <v>104.8240</v>
       </c>
       <c t="n" r="J26">
-        <v>441.7044</v>
+        <v>441.9897</v>
       </c>
     </row>
     <row r="27">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>-2.2608</v>
+        <v>-3.5556</v>
       </c>
     </row>
     <row r="28">
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>9.0213</v>
+        <v>7.1687</v>
       </c>
       <c t="n" r="E28">
-        <v>9.8174</v>
+        <v>8.3910</v>
       </c>
       <c t="n" r="F28">
-        <v>37.5508</v>
+        <v>34.1230</v>
       </c>
       <c t="n" r="G28">
-        <v>24.2313</v>
+        <v>22.1202</v>
       </c>
     </row>
     <row r="29">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>2.9257</v>
+        <v>3.0171</v>
       </c>
       <c t="n" r="E30">
-        <v>9.5620</v>
+        <v>9.5527</v>
       </c>
       <c t="n" r="G30">
-        <v>11.6898</v>
+        <v>11.7890</v>
       </c>
     </row>
     <row r="31">
@@ -1238,16 +1238,16 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>3.0000</v>
+        <v>3.1111</v>
       </c>
       <c t="n" r="E31">
-        <v>9.6177</v>
+        <v>9.6495</v>
       </c>
       <c t="n" r="F31">
-        <v>20.4417</v>
+        <v>20.4413</v>
       </c>
       <c t="n" r="G31">
-        <v>11.3736</v>
+        <v>11.4938</v>
       </c>
     </row>
     <row r="32">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>3.0968</v>
+        <v>3.1828</v>
       </c>
       <c t="n" r="E32">
-        <v>9.8030</v>
+        <v>9.7941</v>
       </c>
       <c t="n" r="G32">
-        <v>11.6442</v>
+        <v>11.7373</v>
       </c>
     </row>
     <row r="33">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>3.0551</v>
+        <v>3.1411</v>
       </c>
       <c t="n" r="E33">
-        <v>9.8624</v>
+        <v>9.8030</v>
       </c>
       <c t="n" r="G33">
-        <v>11.5510</v>
+        <v>11.6442</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -291,36 +291,36 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>5.7398</v>
+        <v>2.5345</v>
       </c>
       <c t="n" r="E3">
-        <v>-15.5655</v>
+        <v>-17.6347</v>
       </c>
       <c t="n" r="F3">
-        <v>57.7864</v>
+        <v>68.4011</v>
       </c>
       <c t="n" r="G3">
-        <v>10.3462</v>
+        <v>7.0012</v>
       </c>
       <c t="n" r="H3">
-        <v>178.3556</v>
+        <v>165.9513</v>
       </c>
       <c t="n" r="I3">
-        <v>534.1082</v>
+        <v>514.8860</v>
       </c>
       <c t="n" r="J3">
-        <v>1518.1839</v>
+        <v>1425.6211</v>
       </c>
     </row>
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">OHS</t>
+          <t xml:space="preserve">ZKP</t>
         </is>
       </c>
       <c t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C4">
@@ -329,30 +329,36 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>13.7424</v>
+        <v>11.4082</v>
       </c>
       <c t="n" r="E4">
-        <v>24.4406</v>
+        <v>24.3781</v>
       </c>
       <c t="n" r="F4">
-        <v>48.5082</v>
+        <v>44.0922</v>
       </c>
       <c t="n" r="G4">
-        <v>43.2770</v>
+        <v>35.1351</v>
       </c>
       <c t="n" r="H4">
-        <v>78.8011</v>
+        <v>75.5002</v>
+      </c>
+      <c t="n" r="I4">
+        <v>237.0181</v>
+      </c>
+      <c t="n" r="J4">
+        <v>1236.1839</v>
       </c>
     </row>
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">ZKP</t>
+          <t xml:space="preserve">OHS</t>
         </is>
       </c>
       <c t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C5">
@@ -361,106 +367,106 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>11.3636</v>
+        <v>12.5599</v>
       </c>
       <c t="n" r="E5">
-        <v>21.7540</v>
+        <v>25.0710</v>
       </c>
       <c t="n" r="F5">
-        <v>45.2907</v>
+        <v>47.6730</v>
       </c>
       <c t="n" r="G5">
-        <v>35.0811</v>
+        <v>41.7874</v>
       </c>
       <c t="n" r="H5">
-        <v>74.0857</v>
-      </c>
-      <c t="n" r="I5">
-        <v>236.8833</v>
-      </c>
-      <c t="n" r="J5">
-        <v>1194.8187</v>
+        <v>73.9259</v>
       </c>
     </row>
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">ZGD</t>
+          <t xml:space="preserve">ZKE</t>
         </is>
       </c>
       <c t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY ALTIN KATILIM  BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D6">
-        <v>-1.5187</v>
+        <v>12.1523</v>
       </c>
       <c t="n" r="E6">
-        <v>6.9943</v>
+        <v>29.3736</v>
       </c>
       <c t="n" r="F6">
-        <v>12.9924</v>
+        <v>49.8673</v>
       </c>
       <c t="n" r="G6">
-        <v>6.7645</v>
+        <v>38.6410</v>
       </c>
       <c t="n" r="H6">
-        <v>72.9075</v>
+        <v>71.9289</v>
       </c>
       <c t="n" r="I6">
-        <v>438.0592</v>
+        <v>198.8881</v>
       </c>
       <c t="n" r="J6">
-        <v>1522.9597</v>
+        <v>803.2000</v>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">ILK</t>
+          <t xml:space="preserve">ZPP</t>
         </is>
       </c>
       <c t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D7">
-        <v>-4.9026</v>
+        <v>11.8943</v>
       </c>
       <c t="n" r="E7">
-        <v>3.1701</v>
+        <v>20.2367</v>
       </c>
       <c t="n" r="F7">
-        <v>10.4449</v>
+        <v>41.3860</v>
       </c>
       <c t="n" r="G7">
-        <v>4.0128</v>
+        <v>39.6372</v>
       </c>
       <c t="n" r="H7">
-        <v>72.0108</v>
+        <v>68.3234</v>
+      </c>
+      <c t="n" r="I7">
+        <v>204.4104</v>
+      </c>
+      <c t="n" r="J7">
+        <v>1291.0186</v>
       </c>
     </row>
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">ZPP</t>
+          <t xml:space="preserve">BND</t>
         </is>
       </c>
       <c t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C8">
@@ -469,36 +475,30 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>13.2159</v>
+        <v>11.6921</v>
       </c>
       <c t="n" r="E8">
-        <v>17.9170</v>
+        <v>20.3165</v>
       </c>
       <c t="n" r="F8">
-        <v>42.3428</v>
+        <v>41.7070</v>
       </c>
       <c t="n" r="G8">
-        <v>41.2864</v>
+        <v>40.0884</v>
       </c>
       <c t="n" r="H8">
-        <v>69.8051</v>
-      </c>
-      <c t="n" r="I8">
-        <v>208.0058</v>
-      </c>
-      <c t="n" r="J8">
-        <v>1271.3981</v>
+        <v>68.1557</v>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">BND</t>
+          <t xml:space="preserve">OPK</t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST BANKA DIŞI LİKİT 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C9">
@@ -507,68 +507,68 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>12.4559</v>
+        <v>4.8372</v>
       </c>
       <c t="n" r="E9">
-        <v>18.1117</v>
+        <v>6.9260</v>
       </c>
       <c t="n" r="F9">
-        <v>41.9355</v>
+        <v>19.4278</v>
       </c>
       <c t="n" r="G9">
-        <v>41.0464</v>
+        <v>18.5068</v>
       </c>
       <c t="n" r="H9">
-        <v>69.1560</v>
+        <v>63.5704</v>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">ZKE</t>
+          <t xml:space="preserve">ZGD</t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY ALTIN KATILIM  BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D10">
-        <v>11.8874</v>
+        <v>-3.1363</v>
       </c>
       <c t="n" r="E10">
-        <v>26.7917</v>
+        <v>2.3013</v>
       </c>
       <c t="n" r="F10">
-        <v>51.9335</v>
+        <v>14.6094</v>
       </c>
       <c t="n" r="G10">
-        <v>38.3135</v>
+        <v>5.0107</v>
       </c>
       <c t="n" r="H10">
-        <v>68.3607</v>
+        <v>63.3630</v>
       </c>
       <c t="n" r="I10">
-        <v>198.1821</v>
+        <v>429.2208</v>
       </c>
       <c t="n" r="J10">
-        <v>767.7452</v>
+        <v>1467.3077</v>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">FGA</t>
+          <t xml:space="preserve">ILK</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C11">
@@ -577,36 +577,30 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>0.4679</v>
+        <v>-6.2662</v>
       </c>
       <c t="n" r="E11">
-        <v>2.2511</v>
+        <v>-0.4483</v>
       </c>
       <c t="n" r="F11">
-        <v>13.1226</v>
+        <v>12.7734</v>
       </c>
       <c t="n" r="G11">
-        <v>10.5805</v>
+        <v>2.5213</v>
       </c>
       <c t="n" r="H11">
-        <v>67.4702</v>
-      </c>
-      <c t="n" r="I11">
-        <v>397.0539</v>
-      </c>
-      <c t="n" r="J11">
-        <v>1345.8864</v>
+        <v>63.1442</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">OPK</t>
+          <t xml:space="preserve">OHY</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C12">
@@ -615,30 +609,30 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>5.2713</v>
+        <v>11.1626</v>
       </c>
       <c t="n" r="E12">
-        <v>6.5265</v>
+        <v>15.7782</v>
       </c>
       <c t="n" r="F12">
-        <v>20.3474</v>
+        <v>41.0114</v>
       </c>
       <c t="n" r="G12">
-        <v>18.9975</v>
+        <v>31.0889</v>
       </c>
       <c t="n" r="H12">
-        <v>64.9660</v>
+        <v>61.4494</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">BOE</t>
+          <t xml:space="preserve">ZBB</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C13">
@@ -647,30 +641,36 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>11.9556</v>
+        <v>10.9399</v>
       </c>
       <c t="n" r="E13">
-        <v>15.5785</v>
+        <v>15.5698</v>
       </c>
       <c t="n" r="F13">
-        <v>42.5141</v>
+        <v>41.2226</v>
       </c>
       <c t="n" r="G13">
-        <v>32.0681</v>
+        <v>31.1475</v>
       </c>
       <c t="n" r="H13">
-        <v>63.0707</v>
+        <v>60.9538</v>
+      </c>
+      <c t="n" r="I13">
+        <v>209.1013</v>
+      </c>
+      <c t="n" r="J13">
+        <v>1215.4689</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">OHY</t>
+          <t xml:space="preserve">BOE</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C14">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>11.6255</v>
+        <v>10.7628</v>
       </c>
       <c t="n" r="E14">
-        <v>15.3029</v>
+        <v>15.0058</v>
       </c>
       <c t="n" r="F14">
-        <v>41.4141</v>
+        <v>41.1952</v>
       </c>
       <c t="n" r="G14">
-        <v>31.6348</v>
+        <v>30.6610</v>
       </c>
       <c t="n" r="H14">
-        <v>62.7297</v>
+        <v>60.8783</v>
       </c>
     </row>
     <row r="15">
@@ -711,74 +711,74 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>12.6148</v>
+        <v>11.4207</v>
       </c>
       <c t="n" r="E15">
-        <v>26.0021</v>
+        <v>26.0915</v>
       </c>
       <c t="n" r="F15">
-        <v>50.6143</v>
+        <v>49.4456</v>
       </c>
       <c t="n" r="G15">
-        <v>42.7241</v>
+        <v>41.2107</v>
       </c>
       <c t="n" r="H15">
-        <v>62.6714</v>
+        <v>60.3084</v>
       </c>
       <c t="n" r="I15">
-        <v>152.5405</v>
+        <v>149.8627</v>
       </c>
       <c t="n" r="J15">
-        <v>967.9443</v>
+        <v>979.8220</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">ZBB</t>
+          <t xml:space="preserve">FGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D16">
-        <v>11.8901</v>
+        <v>-0.6380</v>
       </c>
       <c t="n" r="E16">
-        <v>14.8695</v>
+        <v>-0.1283</v>
       </c>
       <c t="n" r="F16">
-        <v>42.1070</v>
+        <v>17.7657</v>
       </c>
       <c t="n" r="G16">
-        <v>32.2708</v>
+        <v>9.3633</v>
       </c>
       <c t="n" r="H16">
-        <v>62.4534</v>
+        <v>60.0000</v>
       </c>
       <c t="n" r="I16">
-        <v>211.7487</v>
+        <v>391.5825</v>
       </c>
       <c t="n" r="J16">
-        <v>1199.8210</v>
+        <v>1306.2124</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">ZBP</t>
+          <t xml:space="preserve">ZEA</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C17">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>11.1977</v>
+        <v>11.2656</v>
       </c>
       <c t="n" r="E17">
-        <v>4.9277</v>
+        <v>21.2489</v>
       </c>
       <c t="n" r="F17">
-        <v>34.6759</v>
+        <v>48.2580</v>
       </c>
       <c t="n" r="G17">
-        <v>10.7660</v>
+        <v>35.2265</v>
       </c>
       <c t="n" r="H17">
-        <v>61.7536</v>
+        <v>59.8721</v>
       </c>
       <c t="n" r="I17">
-        <v>320.4322</v>
+        <v>170.7826</v>
       </c>
       <c t="n" r="J17">
-        <v>1863.3028</v>
+        <v>1095.4573</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">BLH</t>
+          <t xml:space="preserve">ZBP</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C18">
@@ -825,30 +825,36 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>11.7257</v>
+        <v>10.2624</v>
       </c>
       <c t="n" r="E18">
-        <v>5.0114</v>
+        <v>1.3856</v>
       </c>
       <c t="n" r="F18">
-        <v>34.7745</v>
+        <v>32.2943</v>
       </c>
       <c t="n" r="G18">
-        <v>11.2335</v>
+        <v>9.8344</v>
       </c>
       <c t="n" r="H18">
-        <v>61.4450</v>
+        <v>59.1301</v>
+      </c>
+      <c t="n" r="I18">
+        <v>316.8959</v>
+      </c>
+      <c t="n" r="J18">
+        <v>1875.7914</v>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">ZEA</t>
+          <t xml:space="preserve">BLH</t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C19">
@@ -857,25 +863,19 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>12.1001</v>
+        <v>10.6637</v>
       </c>
       <c t="n" r="E19">
-        <v>21.7891</v>
+        <v>1.3576</v>
       </c>
       <c t="n" r="F19">
-        <v>49.0936</v>
+        <v>32.0834</v>
       </c>
       <c t="n" r="G19">
-        <v>36.2407</v>
+        <v>10.1762</v>
       </c>
       <c t="n" r="H19">
-        <v>61.0711</v>
-      </c>
-      <c t="n" r="I19">
-        <v>172.8134</v>
-      </c>
-      <c t="n" r="J19">
-        <v>1077.6739</v>
+        <v>57.7918</v>
       </c>
     </row>
     <row r="20">
@@ -895,33 +895,33 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>10.2999</v>
+        <v>9.1265</v>
       </c>
       <c t="n" r="E20">
-        <v>12.6248</v>
+        <v>12.6767</v>
       </c>
       <c t="n" r="F20">
-        <v>38.1600</v>
+        <v>36.8765</v>
       </c>
       <c t="n" r="G20">
-        <v>28.8325</v>
+        <v>27.4619</v>
       </c>
       <c t="n" r="H20">
-        <v>55.4195</v>
+        <v>53.6720</v>
       </c>
       <c t="n" r="I20">
-        <v>225.3846</v>
+        <v>221.9231</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">ZTM</t>
+          <t xml:space="preserve">ZPT</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST TEMETTÜ 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C21">
@@ -930,36 +930,33 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>8.2427</v>
+        <v>14.9975</v>
       </c>
       <c t="n" r="E21">
-        <v>13.1658</v>
+        <v>30.3366</v>
       </c>
       <c t="n" r="F21">
-        <v>38.8909</v>
+        <v>43.0697</v>
       </c>
       <c t="n" r="G21">
-        <v>25.9827</v>
+        <v>41.3177</v>
       </c>
       <c t="n" r="H21">
-        <v>54.8097</v>
+        <v>52.8072</v>
       </c>
       <c t="n" r="I21">
-        <v>213.5987</v>
-      </c>
-      <c t="n" r="J21">
-        <v>1021.5896</v>
+        <v>246.5465</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">ZPT</t>
+          <t xml:space="preserve">ZTM</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST TEMETTÜ 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C22">
@@ -968,22 +965,25 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>16.7912</v>
+        <v>7.3555</v>
       </c>
       <c t="n" r="E22">
-        <v>28.5934</v>
+        <v>12.3054</v>
       </c>
       <c t="n" r="F22">
-        <v>45.1573</v>
+        <v>36.6485</v>
       </c>
       <c t="n" r="G22">
-        <v>43.5219</v>
+        <v>24.9500</v>
       </c>
       <c t="n" r="H22">
-        <v>53.9270</v>
+        <v>52.1704</v>
       </c>
       <c t="n" r="I22">
-        <v>251.9520</v>
+        <v>211.0282</v>
+      </c>
+      <c t="n" r="J22">
+        <v>1035.9782</v>
       </c>
     </row>
     <row r="23">
@@ -1006,16 +1006,16 @@
         <v>7.3977</v>
       </c>
       <c t="n" r="E23">
-        <v>11.6747</v>
+        <v>11.9328</v>
       </c>
       <c t="n" r="F23">
-        <v>34.3419</v>
+        <v>34.1052</v>
       </c>
       <c t="n" r="G23">
         <v>23.0485</v>
       </c>
       <c t="n" r="H23">
-        <v>46.0526</v>
+        <v>46.2932</v>
       </c>
     </row>
     <row r="24">
@@ -1035,25 +1035,25 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>14.3173</v>
+        <v>13.4956</v>
       </c>
       <c t="n" r="E24">
-        <v>15.0811</v>
+        <v>15.8387</v>
       </c>
       <c t="n" r="F24">
-        <v>16.2649</v>
+        <v>17.7377</v>
       </c>
       <c t="n" r="G24">
-        <v>25.1557</v>
+        <v>24.2561</v>
       </c>
       <c t="n" r="H24">
-        <v>41.6210</v>
+        <v>42.4435</v>
       </c>
       <c t="n" r="I24">
-        <v>106.4498</v>
+        <v>104.9658</v>
       </c>
       <c t="n" r="J24">
-        <v>770.3080</v>
+        <v>782.5264</v>
       </c>
     </row>
     <row r="25">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>6.7853</v>
+        <v>5.8337</v>
       </c>
       <c t="n" r="E25">
-        <v>7.3181</v>
+        <v>6.1851</v>
       </c>
       <c t="n" r="F25">
-        <v>31.0152</v>
+        <v>30.0854</v>
       </c>
       <c t="n" r="G25">
-        <v>17.9077</v>
+        <v>16.8570</v>
       </c>
       <c t="n" r="H25">
-        <v>29.6985</v>
+        <v>30.1384</v>
       </c>
       <c t="n" r="I25">
-        <v>130.3642</v>
+        <v>128.3113</v>
       </c>
     </row>
     <row r="26">
@@ -1108,25 +1108,25 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.8413</v>
+        <v>0.9375</v>
       </c>
       <c t="n" r="E26">
-        <v>3.9395</v>
+        <v>3.9614</v>
       </c>
       <c t="n" r="F26">
-        <v>7.0973</v>
+        <v>7.0082</v>
       </c>
       <c t="n" r="G26">
-        <v>4.4052</v>
+        <v>4.5047</v>
       </c>
       <c t="n" r="H26">
-        <v>17.2115</v>
+        <v>17.4217</v>
       </c>
       <c t="n" r="I26">
-        <v>104.8240</v>
+        <v>105.0193</v>
       </c>
       <c t="n" r="J26">
-        <v>441.9897</v>
+        <v>436.6134</v>
       </c>
     </row>
     <row r="27">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>-3.5556</v>
+        <v>-5.2681</v>
       </c>
     </row>
     <row r="28">
@@ -1169,10 +1169,10 @@
         <v>7.1687</v>
       </c>
       <c t="n" r="E28">
-        <v>8.3910</v>
+        <v>8.7454</v>
       </c>
       <c t="n" r="F28">
-        <v>34.1230</v>
+        <v>32.9171</v>
       </c>
       <c t="n" r="G28">
         <v>22.1202</v>
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>3.0171</v>
+        <v>3.1771</v>
       </c>
       <c t="n" r="E30">
-        <v>9.5527</v>
+        <v>9.6163</v>
       </c>
       <c t="n" r="G30">
-        <v>11.7890</v>
+        <v>11.9626</v>
       </c>
     </row>
     <row r="31">
@@ -1238,16 +1238,16 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>3.1111</v>
+        <v>3.3333</v>
       </c>
       <c t="n" r="E31">
-        <v>9.6495</v>
+        <v>9.7993</v>
       </c>
       <c t="n" r="F31">
-        <v>20.4413</v>
+        <v>20.5704</v>
       </c>
       <c t="n" r="G31">
-        <v>11.4938</v>
+        <v>11.7341</v>
       </c>
     </row>
     <row r="32">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>3.1828</v>
+        <v>3.3548</v>
       </c>
       <c t="n" r="E32">
-        <v>9.7941</v>
+        <v>9.8765</v>
       </c>
       <c t="n" r="G32">
-        <v>11.7373</v>
+        <v>11.9236</v>
       </c>
     </row>
     <row r="33">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>3.1411</v>
+        <v>3.3563</v>
       </c>
       <c t="n" r="E33">
-        <v>9.8030</v>
+        <v>9.8811</v>
       </c>
       <c t="n" r="G33">
-        <v>11.6442</v>
+        <v>11.8770</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -291,36 +291,36 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>2.5345</v>
+        <v>7.0276</v>
       </c>
       <c t="n" r="E3">
-        <v>-17.6347</v>
+        <v>-19.8677</v>
       </c>
       <c t="n" r="F3">
-        <v>68.4011</v>
+        <v>69.0730</v>
       </c>
       <c t="n" r="G3">
-        <v>7.0012</v>
+        <v>8.4014</v>
       </c>
       <c t="n" r="H3">
-        <v>165.9513</v>
+        <v>169.7445</v>
       </c>
       <c t="n" r="I3">
-        <v>514.8860</v>
+        <v>522.9325</v>
       </c>
       <c t="n" r="J3">
-        <v>1425.6211</v>
+        <v>1419.6292</v>
       </c>
     </row>
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">ZKP</t>
+          <t xml:space="preserve">OHS</t>
         </is>
       </c>
       <c t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C4">
@@ -329,36 +329,30 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>11.4082</v>
+        <v>11.9645</v>
       </c>
       <c t="n" r="E4">
-        <v>24.3781</v>
+        <v>22.7557</v>
       </c>
       <c t="n" r="F4">
-        <v>44.0922</v>
+        <v>45.8755</v>
       </c>
       <c t="n" r="G4">
-        <v>35.1351</v>
+        <v>42.0290</v>
       </c>
       <c t="n" r="H4">
-        <v>75.5002</v>
-      </c>
-      <c t="n" r="I4">
-        <v>237.0181</v>
-      </c>
-      <c t="n" r="J4">
-        <v>1236.1839</v>
+        <v>78.0469</v>
       </c>
     </row>
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">OHS</t>
+          <t xml:space="preserve">ZKP</t>
         </is>
       </c>
       <c t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST KATILIM 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C5">
@@ -367,19 +361,25 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>12.5599</v>
+        <v>10.7795</v>
       </c>
       <c t="n" r="E5">
-        <v>25.0710</v>
+        <v>18.4286</v>
       </c>
       <c t="n" r="F5">
-        <v>47.6730</v>
+        <v>41.3068</v>
       </c>
       <c t="n" r="G5">
-        <v>41.7874</v>
+        <v>34.4324</v>
       </c>
       <c t="n" r="H5">
-        <v>73.9259</v>
+        <v>74.8330</v>
+      </c>
+      <c t="n" r="I5">
+        <v>235.2656</v>
+      </c>
+      <c t="n" r="J5">
+        <v>1212.4011</v>
       </c>
     </row>
     <row r="6">
@@ -399,25 +399,25 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>12.1523</v>
+        <v>14.9153</v>
       </c>
       <c t="n" r="E6">
-        <v>29.3736</v>
+        <v>22.8261</v>
       </c>
       <c t="n" r="F6">
-        <v>49.8673</v>
+        <v>52.2227</v>
       </c>
       <c t="n" r="G6">
-        <v>38.6410</v>
+        <v>38.7638</v>
       </c>
       <c t="n" r="H6">
-        <v>71.9289</v>
+        <v>72.8534</v>
       </c>
       <c t="n" r="I6">
-        <v>198.8881</v>
+        <v>199.1528</v>
       </c>
       <c t="n" r="J6">
-        <v>803.2000</v>
+        <v>790.2311</v>
       </c>
     </row>
     <row r="7">
@@ -437,25 +437,25 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>11.8943</v>
+        <v>9.0047</v>
       </c>
       <c t="n" r="E7">
-        <v>20.2367</v>
+        <v>17.2654</v>
       </c>
       <c t="n" r="F7">
-        <v>41.3860</v>
+        <v>38.9347</v>
       </c>
       <c t="n" r="G7">
-        <v>39.6372</v>
+        <v>39.0874</v>
       </c>
       <c t="n" r="H7">
-        <v>68.3234</v>
+        <v>66.7765</v>
       </c>
       <c t="n" r="I7">
-        <v>204.4104</v>
+        <v>203.2119</v>
       </c>
       <c t="n" r="J7">
-        <v>1291.0186</v>
+        <v>1266.0907</v>
       </c>
     </row>
     <row r="8">
@@ -475,51 +475,51 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>11.6921</v>
+        <v>10.0671</v>
       </c>
       <c t="n" r="E8">
-        <v>20.3165</v>
+        <v>17.5444</v>
       </c>
       <c t="n" r="F8">
-        <v>41.7070</v>
+        <v>38.9831</v>
       </c>
       <c t="n" r="G8">
-        <v>40.0884</v>
+        <v>38.9831</v>
       </c>
       <c t="n" r="H8">
-        <v>68.1557</v>
+        <v>66.1674</v>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">OPK</t>
+          <t xml:space="preserve">ILK</t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D9">
-        <v>4.8372</v>
+        <v>-2.1448</v>
       </c>
       <c t="n" r="E9">
-        <v>6.9260</v>
+        <v>-1.6835</v>
       </c>
       <c t="n" r="F9">
-        <v>19.4278</v>
+        <v>12.3509</v>
       </c>
       <c t="n" r="G9">
-        <v>18.5068</v>
+        <v>3.6932</v>
       </c>
       <c t="n" r="H9">
-        <v>63.5704</v>
+        <v>65.9091</v>
       </c>
     </row>
     <row r="10">
@@ -539,68 +539,68 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>-3.1363</v>
+        <v>-0.4079</v>
       </c>
       <c t="n" r="E10">
-        <v>2.3013</v>
+        <v>-0.2723</v>
       </c>
       <c t="n" r="F10">
-        <v>14.6094</v>
+        <v>12.8659</v>
       </c>
       <c t="n" r="G10">
-        <v>5.0107</v>
+        <v>4.8676</v>
       </c>
       <c t="n" r="H10">
-        <v>63.3630</v>
+        <v>63.5045</v>
       </c>
       <c t="n" r="I10">
-        <v>429.2208</v>
+        <v>428.4993</v>
       </c>
       <c t="n" r="J10">
-        <v>1467.3077</v>
+        <v>1435.9614</v>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">ILK</t>
+          <t xml:space="preserve">OPK</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY KAR PAYI ÖDEYEN BIST GYO ENDEKSİ HİSSE SENEDİ YOĞUN (TL) BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D11">
-        <v>-6.2662</v>
+        <v>4.1386</v>
       </c>
       <c t="n" r="E11">
-        <v>-0.4483</v>
+        <v>5.9245</v>
       </c>
       <c t="n" r="F11">
-        <v>12.7734</v>
+        <v>18.3211</v>
       </c>
       <c t="n" r="G11">
-        <v>2.5213</v>
+        <v>19.0676</v>
       </c>
       <c t="n" r="H11">
-        <v>63.1442</v>
+        <v>63.4745</v>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">OHY</t>
+          <t xml:space="preserve">ZBB</t>
         </is>
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C12">
@@ -609,30 +609,36 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>11.1626</v>
+        <v>8.9571</v>
       </c>
       <c t="n" r="E12">
-        <v>15.7782</v>
+        <v>12.4084</v>
       </c>
       <c t="n" r="F12">
-        <v>41.0114</v>
+        <v>37.6282</v>
       </c>
       <c t="n" r="G12">
-        <v>31.0889</v>
+        <v>30.3582</v>
       </c>
       <c t="n" r="H12">
-        <v>61.4494</v>
+        <v>59.9851</v>
+      </c>
+      <c t="n" r="I12">
+        <v>207.2410</v>
+      </c>
+      <c t="n" r="J12">
+        <v>1192.5948</v>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">ZBB</t>
+          <t xml:space="preserve">BOE</t>
         </is>
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C13">
@@ -641,36 +647,30 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>10.9399</v>
+        <v>8.4268</v>
       </c>
       <c t="n" r="E13">
-        <v>15.5698</v>
+        <v>11.9808</v>
       </c>
       <c t="n" r="F13">
-        <v>41.2226</v>
+        <v>38.2763</v>
       </c>
       <c t="n" r="G13">
-        <v>31.1475</v>
+        <v>29.6793</v>
       </c>
       <c t="n" r="H13">
-        <v>60.9538</v>
-      </c>
-      <c t="n" r="I13">
-        <v>209.1013</v>
-      </c>
-      <c t="n" r="J13">
-        <v>1215.4689</v>
+        <v>59.5411</v>
       </c>
     </row>
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">BOE</t>
+          <t xml:space="preserve">OHY</t>
         </is>
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">AK PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">OSMANLI PORTFÖY BİST 30 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C14">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>10.7628</v>
+        <v>9.0281</v>
       </c>
       <c t="n" r="E14">
-        <v>15.0058</v>
+        <v>12.2137</v>
       </c>
       <c t="n" r="F14">
-        <v>41.1952</v>
+        <v>36.5034</v>
       </c>
       <c t="n" r="G14">
-        <v>30.6610</v>
+        <v>29.2994</v>
       </c>
       <c t="n" r="H14">
-        <v>60.8783</v>
+        <v>59.2454</v>
       </c>
     </row>
     <row r="15">
@@ -711,74 +711,74 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>11.4207</v>
+        <v>8.1308</v>
       </c>
       <c t="n" r="E15">
-        <v>26.0915</v>
+        <v>21.2244</v>
       </c>
       <c t="n" r="F15">
-        <v>49.4456</v>
+        <v>45.3812</v>
       </c>
       <c t="n" r="G15">
-        <v>41.2107</v>
+        <v>39.8525</v>
       </c>
       <c t="n" r="H15">
-        <v>60.3084</v>
+        <v>59.1873</v>
       </c>
       <c t="n" r="I15">
-        <v>149.8627</v>
+        <v>147.4595</v>
       </c>
       <c t="n" r="J15">
-        <v>979.8220</v>
+        <v>958.7544</v>
       </c>
     </row>
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">FGA</t>
+          <t xml:space="preserve">ZEA</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">Altın Fonu</t>
+          <t xml:space="preserve">Hisse Senedi Yoğun</t>
         </is>
       </c>
       <c t="n" r="D16">
-        <v>-0.6380</v>
+        <v>9.5736</v>
       </c>
       <c t="n" r="E16">
-        <v>-0.1283</v>
+        <v>16.8035</v>
       </c>
       <c t="n" r="F16">
-        <v>17.7657</v>
+        <v>45.0473</v>
       </c>
       <c t="n" r="G16">
-        <v>9.3633</v>
+        <v>34.6518</v>
       </c>
       <c t="n" r="H16">
-        <v>60.0000</v>
+        <v>58.9385</v>
       </c>
       <c t="n" r="I16">
-        <v>391.5825</v>
+        <v>169.6317</v>
       </c>
       <c t="n" r="J16">
-        <v>1306.2124</v>
+        <v>1077.7055</v>
       </c>
     </row>
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">ZEA</t>
+          <t xml:space="preserve">ZBP</t>
         </is>
       </c>
       <c t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST 30 EŞİT AĞIRLIKLI ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C17">
@@ -787,63 +787,63 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>11.2656</v>
+        <v>11.4970</v>
       </c>
       <c t="n" r="E17">
-        <v>21.2489</v>
+        <v>0.7129</v>
       </c>
       <c t="n" r="F17">
-        <v>48.2580</v>
+        <v>30.6412</v>
       </c>
       <c t="n" r="G17">
-        <v>35.2265</v>
+        <v>9.6791</v>
       </c>
       <c t="n" r="H17">
-        <v>59.8721</v>
+        <v>58.7861</v>
       </c>
       <c t="n" r="I17">
-        <v>170.7826</v>
+        <v>316.3065</v>
       </c>
       <c t="n" r="J17">
-        <v>1095.4573</v>
+        <v>1856.6020</v>
       </c>
     </row>
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">ZBP</t>
+          <t xml:space="preserve">FGA</t>
         </is>
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST LİKİT BANKA ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">QNB PORTFÖY ALTIN KATILIM BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">Hisse Senedi Yoğun</t>
+          <t xml:space="preserve">Altın Fonu</t>
         </is>
       </c>
       <c t="n" r="D18">
-        <v>10.2624</v>
+        <v>1.0022</v>
       </c>
       <c t="n" r="E18">
-        <v>1.3856</v>
+        <v>-3.0936</v>
       </c>
       <c t="n" r="F18">
-        <v>32.2943</v>
+        <v>16.3655</v>
       </c>
       <c t="n" r="G18">
-        <v>9.8344</v>
+        <v>8.5206</v>
       </c>
       <c t="n" r="H18">
-        <v>59.1301</v>
+        <v>58.7671</v>
       </c>
       <c t="n" r="I18">
-        <v>316.8959</v>
+        <v>387.7946</v>
       </c>
       <c t="n" r="J18">
-        <v>1875.7914</v>
+        <v>1281.0772</v>
       </c>
     </row>
     <row r="19">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>10.6637</v>
+        <v>9.9107</v>
       </c>
       <c t="n" r="E19">
-        <v>1.3576</v>
+        <v>-0.9256</v>
       </c>
       <c t="n" r="F19">
-        <v>32.0834</v>
+        <v>28.2292</v>
       </c>
       <c t="n" r="G19">
-        <v>10.1762</v>
+        <v>8.4581</v>
       </c>
       <c t="n" r="H19">
-        <v>57.7918</v>
+        <v>55.3312</v>
       </c>
     </row>
     <row r="20">
@@ -895,33 +895,33 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>9.1265</v>
+        <v>7.5569</v>
       </c>
       <c t="n" r="E20">
-        <v>12.6767</v>
+        <v>10.2310</v>
       </c>
       <c t="n" r="F20">
-        <v>36.8765</v>
+        <v>34.4966</v>
       </c>
       <c t="n" r="G20">
-        <v>27.4619</v>
+        <v>27.1574</v>
       </c>
       <c t="n" r="H20">
-        <v>53.6720</v>
+        <v>53.4456</v>
       </c>
       <c t="n" r="I20">
-        <v>221.9231</v>
+        <v>221.1538</v>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">ZPT</t>
+          <t xml:space="preserve">ZTM</t>
         </is>
       </c>
       <c t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY BIST TEMETTÜ 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C21">
@@ -930,33 +930,36 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>14.9975</v>
+        <v>6.6971</v>
       </c>
       <c t="n" r="E21">
-        <v>30.3366</v>
+        <v>8.7424</v>
       </c>
       <c t="n" r="F21">
-        <v>43.0697</v>
+        <v>32.9073</v>
       </c>
       <c t="n" r="G21">
-        <v>41.3177</v>
+        <v>24.7169</v>
       </c>
       <c t="n" r="H21">
-        <v>52.8072</v>
+        <v>52.8787</v>
       </c>
       <c t="n" r="I21">
-        <v>246.5465</v>
+        <v>210.4478</v>
+      </c>
+      <c t="n" r="J21">
+        <v>1020.2873</v>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">ZTM</t>
+          <t xml:space="preserve">ZPT</t>
         </is>
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY BIST TEMETTÜ 25 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YILDIZ PAZAR TEKNOLOJİ VE İLETİŞİM 10 ENDEKSİ HİSSE SENEDİ YOĞUN BORSA YATIRIM FONU</t>
         </is>
       </c>
       <c t="inlineStr" r="C22">
@@ -965,25 +968,22 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>7.3555</v>
+        <v>10.2564</v>
       </c>
       <c t="n" r="E22">
-        <v>12.3054</v>
+        <v>25.2748</v>
       </c>
       <c t="n" r="F22">
-        <v>36.6485</v>
+        <v>41.6232</v>
       </c>
       <c t="n" r="G22">
-        <v>24.9500</v>
+        <v>39.5420</v>
       </c>
       <c t="n" r="H22">
-        <v>52.1704</v>
+        <v>51.9333</v>
       </c>
       <c t="n" r="I22">
-        <v>211.0282</v>
-      </c>
-      <c t="n" r="J22">
-        <v>1035.9782</v>
+        <v>242.1922</v>
       </c>
     </row>
     <row r="23">
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>7.3977</v>
+        <v>5.4205</v>
       </c>
       <c t="n" r="E23">
-        <v>11.9328</v>
+        <v>7.8052</v>
       </c>
       <c t="n" r="F23">
-        <v>34.1052</v>
+        <v>30.0074</v>
       </c>
       <c t="n" r="G23">
-        <v>23.0485</v>
+        <v>22.1709</v>
       </c>
       <c t="n" r="H23">
-        <v>46.2932</v>
+        <v>46.4968</v>
       </c>
     </row>
     <row r="24">
@@ -1035,25 +1035,25 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>13.4956</v>
+        <v>11.4662</v>
       </c>
       <c t="n" r="E24">
-        <v>15.8387</v>
+        <v>15.3323</v>
       </c>
       <c t="n" r="F24">
-        <v>17.7377</v>
+        <v>19.4762</v>
       </c>
       <c t="n" r="G24">
-        <v>24.2561</v>
+        <v>23.1142</v>
       </c>
       <c t="n" r="H24">
-        <v>42.4435</v>
+        <v>43.6415</v>
       </c>
       <c t="n" r="I24">
-        <v>104.9658</v>
+        <v>103.0822</v>
       </c>
       <c t="n" r="J24">
-        <v>782.5264</v>
+        <v>769.9267</v>
       </c>
     </row>
     <row r="25">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>5.8337</v>
+        <v>5.6714</v>
       </c>
       <c t="n" r="E25">
-        <v>6.1851</v>
+        <v>2.3012</v>
       </c>
       <c t="n" r="F25">
-        <v>30.0854</v>
+        <v>27.1067</v>
       </c>
       <c t="n" r="G25">
-        <v>16.8570</v>
+        <v>15.7606</v>
       </c>
       <c t="n" r="H25">
-        <v>30.1384</v>
+        <v>26.7253</v>
       </c>
       <c t="n" r="I25">
-        <v>128.3113</v>
+        <v>126.1692</v>
       </c>
     </row>
     <row r="26">
@@ -1108,25 +1108,25 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.9375</v>
+        <v>1.6187</v>
       </c>
       <c t="n" r="E26">
-        <v>3.9614</v>
+        <v>3.8519</v>
       </c>
       <c t="n" r="F26">
-        <v>7.0082</v>
+        <v>6.9141</v>
       </c>
       <c t="n" r="G26">
-        <v>4.5047</v>
+        <v>4.6789</v>
       </c>
       <c t="n" r="H26">
-        <v>17.4217</v>
+        <v>17.5846</v>
       </c>
       <c t="n" r="I26">
-        <v>105.0193</v>
+        <v>105.3611</v>
       </c>
       <c t="n" r="J26">
-        <v>436.6134</v>
+        <v>430.5247</v>
       </c>
     </row>
     <row r="27">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>-5.2681</v>
+        <v>4.8382</v>
       </c>
     </row>
     <row r="28">
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>7.1687</v>
+        <v>6.6693</v>
       </c>
       <c t="n" r="E28">
-        <v>8.7454</v>
+        <v>5.1485</v>
       </c>
       <c t="n" r="F28">
-        <v>32.9171</v>
+        <v>29.3229</v>
       </c>
       <c t="n" r="G28">
-        <v>22.1202</v>
+        <v>21.8449</v>
       </c>
     </row>
     <row r="29">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>3.1771</v>
+        <v>3.4955</v>
       </c>
       <c t="n" r="E30">
-        <v>9.6163</v>
+        <v>9.5791</v>
       </c>
       <c t="n" r="G30">
-        <v>11.9626</v>
+        <v>12.3595</v>
       </c>
     </row>
     <row r="31">
@@ -1238,16 +1238,16 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>3.3333</v>
+        <v>3.5516</v>
       </c>
       <c t="n" r="E31">
-        <v>9.7993</v>
+        <v>9.6787</v>
       </c>
       <c t="n" r="F31">
-        <v>20.5704</v>
+        <v>20.4389</v>
       </c>
       <c t="n" r="G31">
-        <v>11.7341</v>
+        <v>12.0945</v>
       </c>
     </row>
     <row r="32">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>3.3548</v>
+        <v>3.6082</v>
       </c>
       <c t="n" r="E32">
-        <v>9.8765</v>
+        <v>9.8361</v>
       </c>
       <c t="n" r="G32">
-        <v>11.9236</v>
+        <v>12.3428</v>
       </c>
     </row>
     <row r="33">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>3.3563</v>
+        <v>3.6113</v>
       </c>
       <c t="n" r="E33">
-        <v>9.8811</v>
+        <v>9.8450</v>
       </c>
       <c t="n" r="G33">
-        <v>11.8770</v>
+        <v>12.2497</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>27.04.2026 18:52:06</t>
+    <t>28.04.2026 18:39:02</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.133862</v>
+        <v>0.131332</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.025456</v>
+        <v>-0.01551</v>
       </c>
       <c r="G6" s="7">
-        <v>0.20227499999999998</v>
+        <v>0.21023599999999998</v>
       </c>
       <c r="H6" s="7">
-        <v>0.070925</v>
+        <v>0.062555</v>
       </c>
       <c r="I6" s="7">
-        <v>0.512757</v>
+        <v>0.500933</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.126228</v>
+        <v>0.166516</v>
       </c>
       <c r="F7" s="7">
-        <v>0.146364</v>
+        <v>0.196418</v>
       </c>
       <c r="G7" s="7">
-        <v>0.347702</v>
+        <v>0.39002499999999996</v>
       </c>
       <c r="H7" s="7">
-        <v>0.39388399999999996</v>
+        <v>0.42741300000000004</v>
       </c>
       <c r="I7" s="7">
-        <v>0.641927</v>
+        <v>0.6814239999999999</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.123659</v>
+        <v>0.143466</v>
       </c>
       <c r="F8" s="7">
-        <v>0.105556</v>
+        <v>0.130936</v>
       </c>
       <c r="G8" s="7">
-        <v>0.338715</v>
+        <v>0.373251</v>
       </c>
       <c r="H8" s="7">
-        <v>0.302356</v>
+        <v>0.317081</v>
       </c>
       <c r="I8" s="7">
-        <v>0.576238</v>
+        <v>0.594059</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.031285</v>
+        <v>0.03125</v>
       </c>
       <c r="F9" s="7">
-        <v>0.097103</v>
+        <v>0.096989</v>
       </c>
       <c r="G9" s="7">
-        <v>0.202059</v>
+        <v>0.20205700000000001</v>
       </c>
       <c r="H9" s="7">
-        <v>0.122147</v>
+        <v>0.123348</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.151883</v>
+        <v>0.172081</v>
       </c>
       <c r="F10" s="7">
-        <v>0.16264099999999998</v>
+        <v>0.17359100000000002</v>
       </c>
       <c r="G10" s="7">
-        <v>0.22041899999999998</v>
+        <v>0.22611</v>
       </c>
       <c r="H10" s="7">
-        <v>0.249135</v>
+        <v>0.2609</v>
       </c>
       <c r="I10" s="7">
-        <v>0.445156</v>
+        <v>0.458767</v>
       </c>
       <c r="J10" s="7">
-        <v>1.150089</v>
+        <v>1.163253</v>
       </c>
       <c r="K10" s="7">
-        <v>7.576859</v>
+        <v>7.560019</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.034234</v>
+        <v>0.018851</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.082701</v>
+        <v>-0.073847</v>
       </c>
       <c r="G11" s="7">
-        <v>0.16241399999999998</v>
+        <v>0.192227</v>
       </c>
       <c r="H11" s="7">
-        <v>0.074906</v>
+        <v>0.062734</v>
       </c>
       <c r="I11" s="7">
-        <v>0.656088</v>
+        <v>0.6373340000000001</v>
       </c>
       <c r="J11" s="7">
-        <v>3.612294</v>
+        <v>3.615697</v>
       </c>
       <c r="K11" s="7">
-        <v>12.74192</v>
+        <v>12.701111000000001</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.1036</v>
+        <v>0.071937</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.304688</v>
+        <v>-0.282919</v>
       </c>
       <c r="G12" s="7">
-        <v>0.693885</v>
+        <v>0.7269490000000001</v>
       </c>
       <c r="H12" s="7">
-        <v>0.073123</v>
+        <v>0.054842</v>
       </c>
       <c r="I12" s="7">
-        <v>1.694336</v>
+        <v>1.6484379999999998</v>
       </c>
       <c r="J12" s="7">
-        <v>5.122947</v>
+        <v>5.015972</v>
       </c>
       <c r="K12" s="7">
-        <v>14.10622</v>
+        <v>13.901098999999999</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.016389</v>
+        <v>0.012239</v>
       </c>
       <c r="F13" s="7">
-        <v>0.043037</v>
+        <v>0.04225399999999999</v>
       </c>
       <c r="G13" s="7">
-        <v>0.072755</v>
+        <v>0.074376</v>
       </c>
       <c r="H13" s="7">
-        <v>0.049527</v>
+        <v>0.049776</v>
       </c>
       <c r="I13" s="7">
-        <v>0.173344</v>
+        <v>0.173623</v>
       </c>
       <c r="J13" s="7">
-        <v>1.042131</v>
+        <v>1.0772190000000001</v>
       </c>
       <c r="K13" s="7">
-        <v>4.328532</v>
+        <v>4.391104</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>0.006253999999999999</v>
+        <v>-0.022291</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.04736799999999999</v>
+        <v>-0.05969699999999999</v>
       </c>
       <c r="G14" s="7">
-        <v>0.15655</v>
+        <v>0.168443</v>
       </c>
       <c r="H14" s="7">
-        <v>0.028409</v>
+        <v>0.012428999999999999</v>
       </c>
       <c r="I14" s="7">
-        <v>0.732057</v>
+        <v>0.705144</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>0.076706</v>
+        <v>0.054646999999999994</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.07578299999999999</v>
+        <v>0.07736900000000001</v>
       </c>
       <c r="F17" s="7">
-        <v>0.032410999999999995</v>
+        <v>0.029249</v>
       </c>
       <c r="G17" s="7">
-        <v>0.23674199999999998</v>
+        <v>0.24712599999999998</v>
       </c>
       <c r="H17" s="7">
-        <v>0.198715</v>
+        <v>0.195044</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030219999999999997</v>
+        <v>0.029499</v>
       </c>
       <c r="F18" s="7">
-        <v>0.095698</v>
+        <v>0.095365</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.124587</v>
+        <v>0.125331</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.148666</v>
+        <v>0.17742999999999998</v>
       </c>
       <c r="F19" s="7">
-        <v>0.19532800000000003</v>
+        <v>0.229983</v>
       </c>
       <c r="G19" s="7">
-        <v>0.433327</v>
+        <v>0.474974</v>
       </c>
       <c r="H19" s="7">
-        <v>0.421498</v>
+        <v>0.453301</v>
       </c>
       <c r="I19" s="7">
-        <v>0.753663</v>
+        <v>0.792898</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.128922</v>
+        <v>0.14505</v>
       </c>
       <c r="F20" s="7">
-        <v>0.106746</v>
+        <v>0.131572</v>
       </c>
       <c r="G20" s="7">
-        <v>0.326929</v>
+        <v>0.36166200000000004</v>
       </c>
       <c r="H20" s="7">
-        <v>0.29875599999999997</v>
+        <v>0.312102</v>
       </c>
       <c r="I20" s="7">
-        <v>0.574265</v>
+        <v>0.590441</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.087467</v>
+        <v>0.09483599999999999</v>
       </c>
       <c r="F21" s="7">
-        <v>0.06403500000000001</v>
+        <v>0.079951</v>
       </c>
       <c r="G21" s="7">
-        <v>0.254511</v>
+        <v>0.281483</v>
       </c>
       <c r="H21" s="7">
-        <v>0.220323</v>
+        <v>0.229099</v>
       </c>
       <c r="I21" s="7">
-        <v>0.440174</v>
+        <v>0.450531</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.052518</v>
+        <v>0.090479</v>
       </c>
       <c r="F22" s="7">
-        <v>0.055761000000000005</v>
+        <v>0.06990400000000001</v>
       </c>
       <c r="G22" s="7">
-        <v>0.17363</v>
+        <v>0.194406</v>
       </c>
       <c r="H22" s="7">
-        <v>0.20119199999999998</v>
+        <v>0.212408</v>
       </c>
       <c r="I22" s="7">
-        <v>0.60892</v>
+        <v>0.6239439999999999</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.125393</v>
+        <v>0.143157</v>
       </c>
       <c r="F23" s="7">
-        <v>0.10856099999999999</v>
+        <v>0.12629400000000002</v>
       </c>
       <c r="G23" s="7">
-        <v>0.333023</v>
+        <v>0.368123</v>
       </c>
       <c r="H23" s="7">
-        <v>0.30510000000000004</v>
+        <v>0.32119</v>
       </c>
       <c r="I23" s="7">
-        <v>0.578773</v>
+        <v>0.598237</v>
       </c>
       <c r="J23" s="7">
-        <v>2.236224</v>
+        <v>2.273165</v>
       </c>
       <c r="K23" s="7">
-        <v>11.659011</v>
+        <v>11.688047</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.136986</v>
+        <v>0.151724</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.021688</v>
+        <v>-0.002389</v>
       </c>
       <c r="G24" s="7">
-        <v>0.21238700000000002</v>
+        <v>0.260187</v>
       </c>
       <c r="H24" s="7">
-        <v>0.074017</v>
+        <v>0.080487</v>
       </c>
       <c r="I24" s="7">
-        <v>0.5307999999999999</v>
+        <v>0.540022</v>
       </c>
       <c r="J24" s="7">
-        <v>3.2996269999999996</v>
+        <v>3.275912</v>
       </c>
       <c r="K24" s="7">
-        <v>18.106814</v>
+        <v>18.275162</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.13284100000000001</v>
+        <v>0.142655</v>
       </c>
       <c r="F25" s="7">
-        <v>0.153135</v>
+        <v>0.17518899999999998</v>
       </c>
       <c r="G25" s="7">
-        <v>0.400351</v>
+        <v>0.44001399999999996</v>
       </c>
       <c r="H25" s="7">
-        <v>0.349222</v>
+        <v>0.36747799999999997</v>
       </c>
       <c r="I25" s="7">
-        <v>0.57126</v>
+        <v>0.59252</v>
       </c>
       <c r="J25" s="7">
-        <v>1.860522</v>
+        <v>1.9100720000000002</v>
       </c>
       <c r="K25" s="7">
-        <v>10.574826</v>
+        <v>10.603557</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.070453</v>
+        <v>0.101424</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.014931000000000002</v>
+        <v>0.001177</v>
       </c>
       <c r="G26" s="7">
-        <v>0.22531800000000002</v>
+        <v>0.262117</v>
       </c>
       <c r="H26" s="7">
-        <v>0.145272</v>
+        <v>0.16582899999999998</v>
       </c>
       <c r="I26" s="7">
-        <v>0.267955</v>
+        <v>0.29071400000000003</v>
       </c>
       <c r="J26" s="7">
-        <v>1.350019</v>
+        <v>1.3823750000000001</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>0.014291</v>
+        <v>-0.007249</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.042763</v>
+        <v>-0.043247</v>
       </c>
       <c r="G27" s="7">
-        <v>0.149743</v>
+        <v>0.194848</v>
       </c>
       <c r="H27" s="7">
-        <v>0.041518</v>
+        <v>0.029349</v>
       </c>
       <c r="I27" s="7">
-        <v>0.7202649999999999</v>
+        <v>0.700166</v>
       </c>
       <c r="J27" s="7">
-        <v>4.12685</v>
+        <v>4.135714</v>
       </c>
       <c r="K27" s="7">
-        <v>14.377299</v>
+        <v>14.402742</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.16314</v>
+        <v>0.16344899999999998</v>
       </c>
       <c r="F28" s="7">
-        <v>0.217143</v>
+        <v>0.264472</v>
       </c>
       <c r="G28" s="7">
-        <v>0.45641</v>
+        <v>0.535589</v>
       </c>
       <c r="H28" s="7">
-        <v>0.39500599999999997</v>
+        <v>0.430618</v>
       </c>
       <c r="I28" s="7">
-        <v>0.7177419999999999</v>
+        <v>0.761593</v>
       </c>
       <c r="J28" s="7">
-        <v>2.131202</v>
+        <v>2.20407</v>
       </c>
       <c r="K28" s="7">
-        <v>7.720573000000001</v>
+        <v>7.843623</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.118594</v>
+        <v>0.146953</v>
       </c>
       <c r="F29" s="7">
-        <v>0.16646999999999998</v>
+        <v>0.207547</v>
       </c>
       <c r="G29" s="7">
-        <v>0.388795</v>
+        <v>0.452482</v>
       </c>
       <c r="H29" s="7">
-        <v>0.333243</v>
+        <v>0.383784</v>
       </c>
       <c r="I29" s="7">
-        <v>0.7010339999999999</v>
+        <v>0.765517</v>
       </c>
       <c r="J29" s="7">
-        <v>2.476882</v>
+        <v>2.602589</v>
       </c>
       <c r="K29" s="7">
-        <v>11.661704</v>
+        <v>11.948912</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.138338</v>
+        <v>0.162718</v>
       </c>
       <c r="F30" s="7">
-        <v>0.157156</v>
+        <v>0.19779</v>
       </c>
       <c r="G30" s="7">
-        <v>0.360852</v>
+        <v>0.392771</v>
       </c>
       <c r="H30" s="7">
-        <v>0.404618</v>
+        <v>0.429907</v>
       </c>
       <c r="I30" s="7">
-        <v>0.6601690000000001</v>
+        <v>0.690058</v>
       </c>
       <c r="J30" s="7">
-        <v>2.222755</v>
+        <v>2.306636</v>
       </c>
       <c r="K30" s="7">
-        <v>12.612147</v>
+        <v>12.696682000000001</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.12085800000000001</v>
+        <v>0.150246</v>
       </c>
       <c r="F31" s="7">
-        <v>0.229158</v>
+        <v>0.261617</v>
       </c>
       <c r="G31" s="7">
-        <v>0.39191499999999996</v>
+        <v>0.402908</v>
       </c>
       <c r="H31" s="7">
-        <v>0.40827800000000003</v>
+        <v>0.429709</v>
       </c>
       <c r="I31" s="7">
-        <v>0.52439</v>
+        <v>0.5475869999999999</v>
       </c>
       <c r="J31" s="7">
-        <v>2.6507940000000003</v>
+        <v>2.734805</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.125695</v>
+        <v>0.142461</v>
       </c>
       <c r="F32" s="7">
-        <v>0.202573</v>
+        <v>0.231306</v>
       </c>
       <c r="G32" s="7">
-        <v>0.428292</v>
+        <v>0.463848</v>
       </c>
       <c r="H32" s="7">
-        <v>0.414435</v>
+        <v>0.437718</v>
       </c>
       <c r="I32" s="7">
-        <v>0.575194</v>
+        <v>0.601124</v>
       </c>
       <c r="J32" s="7">
-        <v>1.6245679999999998</v>
+        <v>1.6747040000000002</v>
       </c>
       <c r="K32" s="7">
-        <v>9.510381</v>
+        <v>9.483871</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.106151</v>
+        <v>0.11834199999999999</v>
       </c>
       <c r="F33" s="7">
-        <v>0.079775</v>
+        <v>0.09923299999999999</v>
       </c>
       <c r="G33" s="7">
-        <v>0.285419</v>
+        <v>0.313613</v>
       </c>
       <c r="H33" s="7">
-        <v>0.264213</v>
+        <v>0.27360399999999996</v>
       </c>
       <c r="I33" s="7">
-        <v>0.513062</v>
+        <v>0.524301</v>
       </c>
       <c r="J33" s="7">
-        <v>2.342953</v>
+        <v>2.365526</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,14 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.031637</v>
+        <v>0.03161</v>
       </c>
       <c r="F34" s="7">
-        <v>0.098816</v>
-      </c>
-      <c r="G34" s="7"/>
+        <v>0.09872600000000001</v>
+      </c>
+      <c r="G34" s="7">
+        <v>0.206267</v>
+      </c>
       <c r="H34" s="7">
-        <v>0.123894</v>
+        <v>0.124825</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1696,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.10276</v>
+        <v>0.131749</v>
       </c>
       <c r="F35" s="7">
-        <v>0.082109</v>
+        <v>0.119269</v>
       </c>
       <c r="G35" s="7">
-        <v>0.282349</v>
+        <v>0.34109900000000004</v>
       </c>
       <c r="H35" s="7">
-        <v>0.251166</v>
+        <v>0.28481</v>
       </c>
       <c r="I35" s="7">
-        <v>0.5169630000000001</v>
+        <v>0.557754</v>
       </c>
       <c r="J35" s="7">
-        <v>2.2558949999999998</v>
+        <v>2.338816</v>
       </c>
       <c r="K35" s="7">
-        <v>9.976037</v>
+        <v>10.140959</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1731,14 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.031624</v>
+        <v>0.031157</v>
       </c>
       <c r="F36" s="7">
-        <v>0.098271</v>
-      </c>
-      <c r="G36" s="7"/>
+        <v>0.098681</v>
+      </c>
+      <c r="G36" s="7">
+        <v>0.206752</v>
+      </c>
       <c r="H36" s="7">
-        <v>0.12436</v>
+        <v>0.12529099999999999</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>28.04.2026 18:39:02</t>
+    <t>29.04.2026 18:48:52</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.131332</v>
+        <v>0.111632</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.01551</v>
+        <v>-0.070588</v>
       </c>
       <c r="G6" s="7">
-        <v>0.21023599999999998</v>
+        <v>0.208567</v>
       </c>
       <c r="H6" s="7">
-        <v>0.062555</v>
+        <v>0.044053</v>
       </c>
       <c r="I6" s="7">
-        <v>0.500933</v>
+        <v>0.525097</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.166516</v>
+        <v>0.147546</v>
       </c>
       <c r="F7" s="7">
-        <v>0.196418</v>
+        <v>0.14893</v>
       </c>
       <c r="G7" s="7">
-        <v>0.39002499999999996</v>
+        <v>0.36301900000000004</v>
       </c>
       <c r="H7" s="7">
-        <v>0.42741300000000004</v>
+        <v>0.4042</v>
       </c>
       <c r="I7" s="7">
-        <v>0.6814239999999999</v>
+        <v>0.652645</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.143466</v>
+        <v>0.127557</v>
       </c>
       <c r="F8" s="7">
-        <v>0.130936</v>
+        <v>0.08</v>
       </c>
       <c r="G8" s="7">
-        <v>0.373251</v>
+        <v>0.34816600000000003</v>
       </c>
       <c r="H8" s="7">
-        <v>0.317081</v>
+        <v>0.298757</v>
       </c>
       <c r="I8" s="7">
-        <v>0.594059</v>
+        <v>0.5876</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.03125</v>
+        <v>0.032353</v>
       </c>
       <c r="F9" s="7">
-        <v>0.096989</v>
+        <v>0.09773300000000001</v>
       </c>
       <c r="G9" s="7">
-        <v>0.20205700000000001</v>
+        <v>0.202055</v>
       </c>
       <c r="H9" s="7">
-        <v>0.123348</v>
+        <v>0.124549</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.172081</v>
+        <v>0.14699299999999998</v>
       </c>
       <c r="F10" s="7">
-        <v>0.17359100000000002</v>
+        <v>0.157792</v>
       </c>
       <c r="G10" s="7">
-        <v>0.22611</v>
+        <v>0.179233</v>
       </c>
       <c r="H10" s="7">
-        <v>0.2609</v>
+        <v>0.23390999999999998</v>
       </c>
       <c r="I10" s="7">
-        <v>0.458767</v>
+        <v>0.447828</v>
       </c>
       <c r="J10" s="7">
-        <v>1.163253</v>
+        <v>1.201914</v>
       </c>
       <c r="K10" s="7">
-        <v>7.560019</v>
+        <v>7.434248</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.018851</v>
+        <v>-0.0035909999999999996</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.073847</v>
+        <v>-0.14746499999999998</v>
       </c>
       <c r="G11" s="7">
-        <v>0.192227</v>
+        <v>0.189966</v>
       </c>
       <c r="H11" s="7">
-        <v>0.062734</v>
+        <v>0.039326</v>
       </c>
       <c r="I11" s="7">
-        <v>0.6373340000000001</v>
+        <v>0.571348</v>
       </c>
       <c r="J11" s="7">
-        <v>3.615697</v>
+        <v>3.41879</v>
       </c>
       <c r="K11" s="7">
-        <v>12.701111000000001</v>
+        <v>12.454545000000001</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.071937</v>
+        <v>0.035968</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.282919</v>
+        <v>-0.360732</v>
       </c>
       <c r="G12" s="7">
-        <v>0.7269490000000001</v>
+        <v>0.681422</v>
       </c>
       <c r="H12" s="7">
-        <v>0.054842</v>
+        <v>0.019448</v>
       </c>
       <c r="I12" s="7">
-        <v>1.6484379999999998</v>
+        <v>1.5555770000000002</v>
       </c>
       <c r="J12" s="7">
-        <v>5.015972</v>
+        <v>4.798673</v>
       </c>
       <c r="K12" s="7">
-        <v>13.901098999999999</v>
+        <v>13.714799000000001</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.012239</v>
+        <v>0.016079</v>
       </c>
       <c r="F13" s="7">
-        <v>0.04225399999999999</v>
+        <v>0.043886</v>
       </c>
       <c r="G13" s="7">
-        <v>0.074376</v>
+        <v>0.078726</v>
       </c>
       <c r="H13" s="7">
-        <v>0.049776</v>
+        <v>0.053758</v>
       </c>
       <c r="I13" s="7">
-        <v>0.173623</v>
+        <v>0.177747</v>
       </c>
       <c r="J13" s="7">
-        <v>1.0772190000000001</v>
+        <v>1.13375</v>
       </c>
       <c r="K13" s="7">
-        <v>4.391104</v>
+        <v>4.381975</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.022291</v>
+        <v>-0.041838</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.05969699999999999</v>
+        <v>-0.115823</v>
       </c>
       <c r="G14" s="7">
-        <v>0.168443</v>
+        <v>0.16029900000000002</v>
       </c>
       <c r="H14" s="7">
-        <v>0.012428999999999999</v>
+        <v>-0.007813</v>
       </c>
       <c r="I14" s="7">
-        <v>0.705144</v>
+        <v>0.6619079999999999</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>0.054646999999999994</v>
+        <v>0.0383</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.07736900000000001</v>
+        <v>0.059164</v>
       </c>
       <c r="F17" s="7">
-        <v>0.029249</v>
+        <v>-0.010819</v>
       </c>
       <c r="G17" s="7">
-        <v>0.24712599999999998</v>
+        <v>0.221957</v>
       </c>
       <c r="H17" s="7">
-        <v>0.195044</v>
+        <v>0.17485099999999998</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.029499</v>
+        <v>0.030633</v>
       </c>
       <c r="F18" s="7">
-        <v>0.095365</v>
+        <v>0.09551399999999999</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.125331</v>
+        <v>0.126571</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.17742999999999998</v>
+        <v>0.162753</v>
       </c>
       <c r="F19" s="7">
-        <v>0.229983</v>
+        <v>0.18046399999999999</v>
       </c>
       <c r="G19" s="7">
-        <v>0.474974</v>
+        <v>0.44624699999999995</v>
       </c>
       <c r="H19" s="7">
-        <v>0.453301</v>
+        <v>0.43518500000000004</v>
       </c>
       <c r="I19" s="7">
-        <v>0.792898</v>
+        <v>0.7825</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.14505</v>
+        <v>0.13075699999999998</v>
       </c>
       <c r="F20" s="7">
-        <v>0.131572</v>
+        <v>0.082341</v>
       </c>
       <c r="G20" s="7">
-        <v>0.36166200000000004</v>
+        <v>0.338765</v>
       </c>
       <c r="H20" s="7">
-        <v>0.312102</v>
+        <v>0.29572299999999996</v>
       </c>
       <c r="I20" s="7">
-        <v>0.590441</v>
+        <v>0.582222</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.09483599999999999</v>
+        <v>0.075499</v>
       </c>
       <c r="F21" s="7">
-        <v>0.079951</v>
+        <v>0.026709</v>
       </c>
       <c r="G21" s="7">
-        <v>0.281483</v>
+        <v>0.256127</v>
       </c>
       <c r="H21" s="7">
-        <v>0.229099</v>
+        <v>0.20739000000000002</v>
       </c>
       <c r="I21" s="7">
-        <v>0.450531</v>
+        <v>0.456267</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.090479</v>
+        <v>0.076923</v>
       </c>
       <c r="F22" s="7">
-        <v>0.06990400000000001</v>
+        <v>0.052048</v>
       </c>
       <c r="G22" s="7">
-        <v>0.194406</v>
+        <v>0.168263</v>
       </c>
       <c r="H22" s="7">
-        <v>0.212408</v>
+        <v>0.19733599999999998</v>
       </c>
       <c r="I22" s="7">
-        <v>0.6239439999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.143157</v>
+        <v>0.125033</v>
       </c>
       <c r="F23" s="7">
-        <v>0.12629400000000002</v>
+        <v>0.083207</v>
       </c>
       <c r="G23" s="7">
-        <v>0.368123</v>
+        <v>0.340113</v>
       </c>
       <c r="H23" s="7">
-        <v>0.32119</v>
+        <v>0.300243</v>
       </c>
       <c r="I23" s="7">
-        <v>0.598237</v>
+        <v>0.580443</v>
       </c>
       <c r="J23" s="7">
-        <v>2.273165</v>
+        <v>2.309892</v>
       </c>
       <c r="K23" s="7">
-        <v>11.688047</v>
+        <v>11.567488</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.151724</v>
+        <v>0.115034</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.002389</v>
+        <v>-0.061528</v>
       </c>
       <c r="G24" s="7">
-        <v>0.260187</v>
+        <v>0.214543</v>
       </c>
       <c r="H24" s="7">
-        <v>0.080487</v>
+        <v>0.046066</v>
       </c>
       <c r="I24" s="7">
-        <v>0.540022</v>
+        <v>0.5161290000000001</v>
       </c>
       <c r="J24" s="7">
-        <v>3.275912</v>
+        <v>3.307332</v>
       </c>
       <c r="K24" s="7">
-        <v>18.275162</v>
+        <v>17.609576</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.142655</v>
+        <v>0.118644</v>
       </c>
       <c r="F25" s="7">
-        <v>0.17518899999999998</v>
+        <v>0.122767</v>
       </c>
       <c r="G25" s="7">
-        <v>0.44001399999999996</v>
+        <v>0.405252</v>
       </c>
       <c r="H25" s="7">
-        <v>0.36747799999999997</v>
+        <v>0.33874200000000004</v>
       </c>
       <c r="I25" s="7">
-        <v>0.59252</v>
+        <v>0.573927</v>
       </c>
       <c r="J25" s="7">
-        <v>1.9100720000000002</v>
+        <v>1.9333330000000002</v>
       </c>
       <c r="K25" s="7">
-        <v>10.603557</v>
+        <v>10.392405000000002</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.101424</v>
+        <v>0.071644</v>
       </c>
       <c r="F26" s="7">
-        <v>0.001177</v>
+        <v>-0.030834999999999998</v>
       </c>
       <c r="G26" s="7">
-        <v>0.262117</v>
+        <v>0.23409500000000003</v>
       </c>
       <c r="H26" s="7">
-        <v>0.16582899999999998</v>
+        <v>0.13430799999999998</v>
       </c>
       <c r="I26" s="7">
-        <v>0.29071400000000003</v>
+        <v>0.276475</v>
       </c>
       <c r="J26" s="7">
-        <v>1.3823750000000001</v>
+        <v>1.403213</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.007249</v>
+        <v>-0.020366</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.043247</v>
+        <v>-0.093001</v>
       </c>
       <c r="G27" s="7">
-        <v>0.194848</v>
+        <v>0.208688</v>
       </c>
       <c r="H27" s="7">
-        <v>0.029349</v>
+        <v>0.015747999999999998</v>
       </c>
       <c r="I27" s="7">
-        <v>0.700166</v>
+        <v>0.662761</v>
       </c>
       <c r="J27" s="7">
-        <v>4.135714</v>
+        <v>3.927083</v>
       </c>
       <c r="K27" s="7">
-        <v>14.402742</v>
+        <v>14.231859</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.16344899999999998</v>
+        <v>0.148469</v>
       </c>
       <c r="F28" s="7">
-        <v>0.264472</v>
+        <v>0.216073</v>
       </c>
       <c r="G28" s="7">
-        <v>0.535589</v>
+        <v>0.485788</v>
       </c>
       <c r="H28" s="7">
-        <v>0.430618</v>
+        <v>0.412198</v>
       </c>
       <c r="I28" s="7">
-        <v>0.761593</v>
+        <v>0.759127</v>
       </c>
       <c r="J28" s="7">
-        <v>2.20407</v>
+        <v>2.20632</v>
       </c>
       <c r="K28" s="7">
-        <v>7.843623</v>
+        <v>7.747465</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.146953</v>
+        <v>0.124552</v>
       </c>
       <c r="F29" s="7">
-        <v>0.207547</v>
+        <v>0.15481899999999998</v>
       </c>
       <c r="G29" s="7">
-        <v>0.452482</v>
+        <v>0.40616199999999997</v>
       </c>
       <c r="H29" s="7">
-        <v>0.383784</v>
+        <v>0.356757</v>
       </c>
       <c r="I29" s="7">
-        <v>0.765517</v>
+        <v>0.7394320000000001</v>
       </c>
       <c r="J29" s="7">
-        <v>2.602589</v>
+        <v>2.525281</v>
       </c>
       <c r="K29" s="7">
-        <v>11.948912</v>
+        <v>11.806122</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.162718</v>
+        <v>0.141708</v>
       </c>
       <c r="F30" s="7">
-        <v>0.19779</v>
+        <v>0.155656</v>
       </c>
       <c r="G30" s="7">
-        <v>0.392771</v>
+        <v>0.36032</v>
       </c>
       <c r="H30" s="7">
-        <v>0.429907</v>
+        <v>0.404068</v>
       </c>
       <c r="I30" s="7">
-        <v>0.690058</v>
+        <v>0.6633020000000001</v>
       </c>
       <c r="J30" s="7">
-        <v>2.306636</v>
+        <v>2.351706</v>
       </c>
       <c r="K30" s="7">
-        <v>12.696682000000001</v>
+        <v>12.556263</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.150246</v>
+        <v>0.12315300000000001</v>
       </c>
       <c r="F31" s="7">
-        <v>0.261617</v>
+        <v>0.237248</v>
       </c>
       <c r="G31" s="7">
-        <v>0.402908</v>
+        <v>0.369863</v>
       </c>
       <c r="H31" s="7">
-        <v>0.429709</v>
+        <v>0.396032</v>
       </c>
       <c r="I31" s="7">
-        <v>0.5475869999999999</v>
+        <v>0.506342</v>
       </c>
       <c r="J31" s="7">
-        <v>2.734805</v>
+        <v>2.6007580000000003</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.142461</v>
+        <v>0.113167</v>
       </c>
       <c r="F32" s="7">
-        <v>0.231306</v>
+        <v>0.169799</v>
       </c>
       <c r="G32" s="7">
-        <v>0.463848</v>
+        <v>0.420142</v>
       </c>
       <c r="H32" s="7">
-        <v>0.437718</v>
+        <v>0.400854</v>
       </c>
       <c r="I32" s="7">
-        <v>0.601124</v>
+        <v>0.570931</v>
       </c>
       <c r="J32" s="7">
-        <v>1.6747040000000002</v>
+        <v>1.69403</v>
       </c>
       <c r="K32" s="7">
-        <v>9.483871</v>
+        <v>9.261512</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.11834199999999999</v>
+        <v>0.098507</v>
       </c>
       <c r="F33" s="7">
-        <v>0.09923299999999999</v>
+        <v>0.050959000000000004</v>
       </c>
       <c r="G33" s="7">
-        <v>0.313613</v>
+        <v>0.283928</v>
       </c>
       <c r="H33" s="7">
-        <v>0.27360399999999996</v>
+        <v>0.251015</v>
       </c>
       <c r="I33" s="7">
-        <v>0.524301</v>
+        <v>0.5255340000000001</v>
       </c>
       <c r="J33" s="7">
-        <v>2.365526</v>
+        <v>2.411073</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.03161</v>
+        <v>0.032892000000000005</v>
       </c>
       <c r="F34" s="7">
-        <v>0.09872600000000001</v>
+        <v>0.099091</v>
       </c>
       <c r="G34" s="7">
-        <v>0.206267</v>
+        <v>0.205243</v>
       </c>
       <c r="H34" s="7">
-        <v>0.124825</v>
+        <v>0.126223</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.131749</v>
+        <v>0.08773500000000001</v>
       </c>
       <c r="F35" s="7">
-        <v>0.119269</v>
+        <v>0.04452</v>
       </c>
       <c r="G35" s="7">
-        <v>0.34109900000000004</v>
+        <v>0.2876</v>
       </c>
       <c r="H35" s="7">
-        <v>0.28481</v>
+        <v>0.23484300000000002</v>
       </c>
       <c r="I35" s="7">
-        <v>0.557754</v>
+        <v>0.5149159999999999</v>
       </c>
       <c r="J35" s="7">
-        <v>2.338816</v>
+        <v>2.313371</v>
       </c>
       <c r="K35" s="7">
-        <v>10.140959</v>
+        <v>9.769900999999999</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.031157</v>
+        <v>0.032864</v>
       </c>
       <c r="F36" s="7">
-        <v>0.098681</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="G36" s="7">
-        <v>0.206752</v>
+        <v>0.20619800000000002</v>
       </c>
       <c r="H36" s="7">
-        <v>0.12529099999999999</v>
+        <v>0.12715400000000002</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>29.04.2026 18:48:52</t>
+    <t>30.04.2026 18:45:36</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.111632</v>
+        <v>0.11074099999999999</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.070588</v>
+        <v>-0.14422000000000001</v>
       </c>
       <c r="G6" s="7">
-        <v>0.208567</v>
+        <v>0.18195599999999998</v>
       </c>
       <c r="H6" s="7">
-        <v>0.044053</v>
+        <v>0.027313</v>
       </c>
       <c r="I6" s="7">
-        <v>0.525097</v>
+        <v>0.49967799999999996</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.147546</v>
+        <v>0.150557</v>
       </c>
       <c r="F7" s="7">
-        <v>0.14893</v>
+        <v>0.13585</v>
       </c>
       <c r="G7" s="7">
-        <v>0.36301900000000004</v>
+        <v>0.38996000000000003</v>
       </c>
       <c r="H7" s="7">
-        <v>0.4042</v>
+        <v>0.407885</v>
       </c>
       <c r="I7" s="7">
-        <v>0.652645</v>
+        <v>0.68326</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.127557</v>
+        <v>0.133734</v>
       </c>
       <c r="F8" s="7">
-        <v>0.08</v>
+        <v>0.045971000000000005</v>
       </c>
       <c r="G8" s="7">
-        <v>0.34816600000000003</v>
+        <v>0.355822</v>
       </c>
       <c r="H8" s="7">
-        <v>0.298757</v>
+        <v>0.295484</v>
       </c>
       <c r="I8" s="7">
-        <v>0.5876</v>
+        <v>0.600243</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.032353</v>
+        <v>0.035622</v>
       </c>
       <c r="F9" s="7">
-        <v>0.09773300000000001</v>
+        <v>0.097276</v>
       </c>
       <c r="G9" s="7">
-        <v>0.202055</v>
+        <v>0.20487100000000003</v>
       </c>
       <c r="H9" s="7">
-        <v>0.124549</v>
+        <v>0.129355</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.14699299999999998</v>
+        <v>0.13811500000000002</v>
       </c>
       <c r="F10" s="7">
-        <v>0.157792</v>
+        <v>0.156956</v>
       </c>
       <c r="G10" s="7">
-        <v>0.179233</v>
+        <v>0.189136</v>
       </c>
       <c r="H10" s="7">
-        <v>0.23390999999999998</v>
+        <v>0.257439</v>
       </c>
       <c r="I10" s="7">
-        <v>0.447828</v>
+        <v>0.484477</v>
       </c>
       <c r="J10" s="7">
-        <v>1.201914</v>
+        <v>1.2439019999999998</v>
       </c>
       <c r="K10" s="7">
-        <v>7.434248</v>
+        <v>7.494624</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.0035909999999999996</v>
+        <v>-0.0031530000000000004</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.14746499999999998</v>
+        <v>-0.113026</v>
       </c>
       <c r="G11" s="7">
-        <v>0.189966</v>
+        <v>0.15476900000000002</v>
       </c>
       <c r="H11" s="7">
-        <v>0.039326</v>
+        <v>0.036049000000000005</v>
       </c>
       <c r="I11" s="7">
-        <v>0.571348</v>
+        <v>0.5784590000000001</v>
       </c>
       <c r="J11" s="7">
-        <v>3.41879</v>
+        <v>3.4048570000000002</v>
       </c>
       <c r="K11" s="7">
-        <v>12.454545000000001</v>
+        <v>12.412120999999999</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.035968</v>
+        <v>0.031608</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.360732</v>
+        <v>-0.290489</v>
       </c>
       <c r="G12" s="7">
-        <v>0.681422</v>
+        <v>0.5882000000000001</v>
       </c>
       <c r="H12" s="7">
-        <v>0.019448</v>
+        <v>0.015558</v>
       </c>
       <c r="I12" s="7">
-        <v>1.5555770000000002</v>
+        <v>1.53102</v>
       </c>
       <c r="J12" s="7">
-        <v>4.798673</v>
+        <v>4.776549</v>
       </c>
       <c r="K12" s="7">
-        <v>13.714799000000001</v>
+        <v>13.652076</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.016079</v>
+        <v>0.019</v>
       </c>
       <c r="F13" s="7">
-        <v>0.043886</v>
+        <v>0.0418</v>
       </c>
       <c r="G13" s="7">
-        <v>0.078726</v>
+        <v>0.078941</v>
       </c>
       <c r="H13" s="7">
-        <v>0.053758</v>
+        <v>0.054505</v>
       </c>
       <c r="I13" s="7">
-        <v>0.177747</v>
+        <v>0.17596399999999998</v>
       </c>
       <c r="J13" s="7">
-        <v>1.13375</v>
+        <v>1.135262</v>
       </c>
       <c r="K13" s="7">
-        <v>4.381975</v>
+        <v>4.398828</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.041838</v>
+        <v>-0.032963</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.115823</v>
+        <v>-0.099806</v>
       </c>
       <c r="G14" s="7">
-        <v>0.16029900000000002</v>
+        <v>0.134772</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.007813</v>
+        <v>-0.010298</v>
       </c>
       <c r="I14" s="7">
-        <v>0.6619079999999999</v>
+        <v>0.660906</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>0.0383</v>
+        <v>0.008314</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.059164</v>
+        <v>0.059701000000000004</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.010819</v>
+        <v>-0.042697000000000006</v>
       </c>
       <c r="G17" s="7">
-        <v>0.221957</v>
+        <v>0.227076</v>
       </c>
       <c r="H17" s="7">
-        <v>0.17485099999999998</v>
+        <v>0.173015</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030633</v>
+        <v>0.034467</v>
       </c>
       <c r="F18" s="7">
-        <v>0.09551399999999999</v>
+        <v>0.096108</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.126571</v>
+        <v>0.131532</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.162753</v>
+        <v>0.158438</v>
       </c>
       <c r="F19" s="7">
-        <v>0.18046399999999999</v>
+        <v>0.191108</v>
       </c>
       <c r="G19" s="7">
-        <v>0.44624699999999995</v>
+        <v>0.456389</v>
       </c>
       <c r="H19" s="7">
-        <v>0.43518500000000004</v>
+        <v>0.44525</v>
       </c>
       <c r="I19" s="7">
-        <v>0.7825</v>
+        <v>0.8122159999999999</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.13075699999999998</v>
+        <v>0.1344</v>
       </c>
       <c r="F20" s="7">
-        <v>0.082341</v>
+        <v>0.048558000000000004</v>
       </c>
       <c r="G20" s="7">
-        <v>0.338765</v>
+        <v>0.333124</v>
       </c>
       <c r="H20" s="7">
-        <v>0.29572299999999996</v>
+        <v>0.29026399999999997</v>
       </c>
       <c r="I20" s="7">
-        <v>0.582222</v>
+        <v>0.596847</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.075499</v>
+        <v>0.076478</v>
       </c>
       <c r="F21" s="7">
-        <v>0.026709</v>
+        <v>-0.01401</v>
       </c>
       <c r="G21" s="7">
-        <v>0.256127</v>
+        <v>0.251321</v>
       </c>
       <c r="H21" s="7">
-        <v>0.20739000000000002</v>
+        <v>0.202771</v>
       </c>
       <c r="I21" s="7">
-        <v>0.456267</v>
+        <v>0.458415</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.076923</v>
+        <v>0.086179</v>
       </c>
       <c r="F22" s="7">
-        <v>0.052048</v>
+        <v>0.037816</v>
       </c>
       <c r="G22" s="7">
-        <v>0.168263</v>
+        <v>0.162624</v>
       </c>
       <c r="H22" s="7">
-        <v>0.19733599999999998</v>
+        <v>0.19277999999999998</v>
       </c>
       <c r="I22" s="7">
-        <v>0.6</v>
+        <v>0.606704</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.125033</v>
+        <v>0.136954</v>
       </c>
       <c r="F23" s="7">
-        <v>0.083207</v>
+        <v>0.053251999999999994</v>
       </c>
       <c r="G23" s="7">
-        <v>0.340113</v>
+        <v>0.359088</v>
       </c>
       <c r="H23" s="7">
-        <v>0.300243</v>
+        <v>0.302975</v>
       </c>
       <c r="I23" s="7">
-        <v>0.580443</v>
+        <v>0.6056860000000001</v>
       </c>
       <c r="J23" s="7">
-        <v>2.309892</v>
+        <v>2.316847</v>
       </c>
       <c r="K23" s="7">
-        <v>11.567488</v>
+        <v>11.45502</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.115034</v>
+        <v>0.115536</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.061528</v>
+        <v>-0.141377</v>
       </c>
       <c r="G24" s="7">
-        <v>0.214543</v>
+        <v>0.153712</v>
       </c>
       <c r="H24" s="7">
-        <v>0.046066</v>
+        <v>0.029502999999999998</v>
       </c>
       <c r="I24" s="7">
-        <v>0.5161290000000001</v>
+        <v>0.513123</v>
       </c>
       <c r="J24" s="7">
-        <v>3.307332</v>
+        <v>3.2391300000000003</v>
       </c>
       <c r="K24" s="7">
-        <v>17.609576</v>
+        <v>17.14781</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.118644</v>
+        <v>0.126604</v>
       </c>
       <c r="F25" s="7">
-        <v>0.122767</v>
+        <v>0.08693300000000001</v>
       </c>
       <c r="G25" s="7">
-        <v>0.405252</v>
+        <v>0.402556</v>
       </c>
       <c r="H25" s="7">
-        <v>0.33874200000000004</v>
+        <v>0.3357</v>
       </c>
       <c r="I25" s="7">
-        <v>0.573927</v>
+        <v>0.584838</v>
       </c>
       <c r="J25" s="7">
-        <v>1.9333330000000002</v>
+        <v>1.926667</v>
       </c>
       <c r="K25" s="7">
-        <v>10.392405000000002</v>
+        <v>10.243597</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.071644</v>
+        <v>0.06893500000000001</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.030834999999999998</v>
+        <v>-0.031621</v>
       </c>
       <c r="G26" s="7">
-        <v>0.23409500000000003</v>
+        <v>0.20749099999999998</v>
       </c>
       <c r="H26" s="7">
-        <v>0.13430799999999998</v>
+        <v>0.11923299999999999</v>
       </c>
       <c r="I26" s="7">
-        <v>0.276475</v>
+        <v>0.282723</v>
       </c>
       <c r="J26" s="7">
-        <v>1.403213</v>
+        <v>1.3712739999999999</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.020366</v>
+        <v>-0.016399</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.093001</v>
+        <v>-0.08146</v>
       </c>
       <c r="G27" s="7">
-        <v>0.208688</v>
+        <v>0.16680499999999998</v>
       </c>
       <c r="H27" s="7">
-        <v>0.015747999999999998</v>
+        <v>0.008948000000000001</v>
       </c>
       <c r="I27" s="7">
-        <v>0.662761</v>
+        <v>0.6524030000000001</v>
       </c>
       <c r="J27" s="7">
-        <v>3.927083</v>
+        <v>3.894097</v>
       </c>
       <c r="K27" s="7">
-        <v>14.231859</v>
+        <v>14.136383</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.148469</v>
+        <v>0.13228600000000001</v>
       </c>
       <c r="F28" s="7">
-        <v>0.216073</v>
+        <v>0.23323799999999997</v>
       </c>
       <c r="G28" s="7">
-        <v>0.485788</v>
+        <v>0.480308</v>
       </c>
       <c r="H28" s="7">
-        <v>0.412198</v>
+        <v>0.415473</v>
       </c>
       <c r="I28" s="7">
-        <v>0.759127</v>
+        <v>0.779905</v>
       </c>
       <c r="J28" s="7">
-        <v>2.20632</v>
+        <v>2.213755</v>
       </c>
       <c r="K28" s="7">
-        <v>7.747465</v>
+        <v>7.657987</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.124552</v>
+        <v>0.1341</v>
       </c>
       <c r="F29" s="7">
-        <v>0.15481899999999998</v>
+        <v>0.162125</v>
       </c>
       <c r="G29" s="7">
-        <v>0.40616199999999997</v>
+        <v>0.41269</v>
       </c>
       <c r="H29" s="7">
-        <v>0.356757</v>
+        <v>0.36</v>
       </c>
       <c r="I29" s="7">
-        <v>0.7394320000000001</v>
+        <v>0.759441</v>
       </c>
       <c r="J29" s="7">
-        <v>2.525281</v>
+        <v>2.533708</v>
       </c>
       <c r="K29" s="7">
-        <v>11.806122</v>
+        <v>11.726353</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.141708</v>
+        <v>0.156313</v>
       </c>
       <c r="F30" s="7">
-        <v>0.155656</v>
+        <v>0.14222400000000002</v>
       </c>
       <c r="G30" s="7">
-        <v>0.36032</v>
+        <v>0.403375</v>
       </c>
       <c r="H30" s="7">
-        <v>0.404068</v>
+        <v>0.41726199999999997</v>
       </c>
       <c r="I30" s="7">
-        <v>0.6633020000000001</v>
+        <v>0.7055899999999999</v>
       </c>
       <c r="J30" s="7">
-        <v>2.351706</v>
+        <v>2.383202</v>
       </c>
       <c r="K30" s="7">
-        <v>12.556263</v>
+        <v>12.547030999999999</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.12315300000000001</v>
+        <v>0.147389</v>
       </c>
       <c r="F31" s="7">
-        <v>0.237248</v>
+        <v>0.27356400000000003</v>
       </c>
       <c r="G31" s="7">
-        <v>0.369863</v>
+        <v>0.407447</v>
       </c>
       <c r="H31" s="7">
-        <v>0.396032</v>
+        <v>0.439505</v>
       </c>
       <c r="I31" s="7">
-        <v>0.506342</v>
+        <v>0.5270199999999999</v>
       </c>
       <c r="J31" s="7">
-        <v>2.6007580000000003</v>
+        <v>2.7128870000000003</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.113167</v>
+        <v>0.119055</v>
       </c>
       <c r="F32" s="7">
-        <v>0.169799</v>
+        <v>0.134216</v>
       </c>
       <c r="G32" s="7">
-        <v>0.420142</v>
+        <v>0.422925</v>
       </c>
       <c r="H32" s="7">
-        <v>0.400854</v>
+        <v>0.39697299999999996</v>
       </c>
       <c r="I32" s="7">
-        <v>0.570931</v>
+        <v>0.578947</v>
       </c>
       <c r="J32" s="7">
-        <v>1.69403</v>
+        <v>1.686567</v>
       </c>
       <c r="K32" s="7">
-        <v>9.261512</v>
+        <v>9.123735</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.098507</v>
+        <v>0.103448</v>
       </c>
       <c r="F33" s="7">
-        <v>0.050959000000000004</v>
+        <v>0.015036</v>
       </c>
       <c r="G33" s="7">
-        <v>0.283928</v>
+        <v>0.299578</v>
       </c>
       <c r="H33" s="7">
-        <v>0.251015</v>
+        <v>0.250761</v>
       </c>
       <c r="I33" s="7">
-        <v>0.5255340000000001</v>
+        <v>0.542893</v>
       </c>
       <c r="J33" s="7">
-        <v>2.411073</v>
+        <v>2.4103809999999997</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.032892000000000005</v>
+        <v>0.035836</v>
       </c>
       <c r="F34" s="7">
-        <v>0.099091</v>
+        <v>0.09913999999999999</v>
       </c>
       <c r="G34" s="7">
-        <v>0.205243</v>
+        <v>0.20895600000000003</v>
       </c>
       <c r="H34" s="7">
-        <v>0.126223</v>
+        <v>0.13088</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.08773500000000001</v>
+        <v>0.09351000000000001</v>
       </c>
       <c r="F35" s="7">
-        <v>0.04452</v>
+        <v>0.006790000000000001</v>
       </c>
       <c r="G35" s="7">
-        <v>0.2876</v>
+        <v>0.29344000000000003</v>
       </c>
       <c r="H35" s="7">
         <v>0.23484300000000002</v>
       </c>
       <c r="I35" s="7">
-        <v>0.5149159999999999</v>
+        <v>0.531185</v>
       </c>
       <c r="J35" s="7">
         <v>2.313371</v>
       </c>
       <c r="K35" s="7">
-        <v>9.769900999999999</v>
+        <v>9.689157999999999</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.032864</v>
+        <v>0.035821</v>
       </c>
       <c r="F36" s="7">
-        <v>0.09949999999999999</v>
+        <v>0.098598</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20619800000000002</v>
+        <v>0.209405</v>
       </c>
       <c r="H36" s="7">
-        <v>0.12715400000000002</v>
+        <v>0.13134600000000002</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>30.04.2026 18:45:36</t>
+    <t>04.05.2026 19:03:38</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.11074099999999999</v>
+        <v>0.1</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.14422000000000001</v>
+        <v>-0.109908</v>
       </c>
       <c r="G6" s="7">
-        <v>0.18195599999999998</v>
+        <v>0.186064</v>
       </c>
       <c r="H6" s="7">
-        <v>0.027313</v>
+        <v>0.06850200000000001</v>
       </c>
       <c r="I6" s="7">
-        <v>0.49967799999999996</v>
+        <v>0.544904</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.150557</v>
+        <v>0.147604</v>
       </c>
       <c r="F7" s="7">
-        <v>0.13585</v>
+        <v>0.162992</v>
       </c>
       <c r="G7" s="7">
-        <v>0.38996000000000003</v>
+        <v>0.410043</v>
       </c>
       <c r="H7" s="7">
-        <v>0.407885</v>
+        <v>0.438099</v>
       </c>
       <c r="I7" s="7">
-        <v>0.68326</v>
+        <v>0.7447469999999999</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.133734</v>
+        <v>0.10747</v>
       </c>
       <c r="F8" s="7">
-        <v>0.045971000000000005</v>
+        <v>0.055026</v>
       </c>
       <c r="G8" s="7">
-        <v>0.355822</v>
+        <v>0.338255</v>
       </c>
       <c r="H8" s="7">
-        <v>0.295484</v>
+        <v>0.30497399999999997</v>
       </c>
       <c r="I8" s="7">
-        <v>0.600243</v>
+        <v>0.627091</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.035622</v>
+        <v>0.030292</v>
       </c>
       <c r="F9" s="7">
-        <v>0.097276</v>
+        <v>0.097163</v>
       </c>
       <c r="G9" s="7">
-        <v>0.20487100000000003</v>
+        <v>0.203581</v>
       </c>
       <c r="H9" s="7">
-        <v>0.129355</v>
+        <v>0.130557</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.13811500000000002</v>
+        <v>0.10539</v>
       </c>
       <c r="F10" s="7">
-        <v>0.156956</v>
+        <v>0.168364</v>
       </c>
       <c r="G10" s="7">
-        <v>0.189136</v>
+        <v>0.20203</v>
       </c>
       <c r="H10" s="7">
-        <v>0.257439</v>
+        <v>0.270242</v>
       </c>
       <c r="I10" s="7">
-        <v>0.484477</v>
+        <v>0.531178</v>
       </c>
       <c r="J10" s="7">
-        <v>1.2439019999999998</v>
+        <v>1.299405</v>
       </c>
       <c r="K10" s="7">
-        <v>7.494624</v>
+        <v>7.489824</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.0031530000000000004</v>
+        <v>-0.022609</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.113026</v>
+        <v>-0.069151</v>
       </c>
       <c r="G11" s="7">
-        <v>0.15476900000000002</v>
+        <v>0.175732</v>
       </c>
       <c r="H11" s="7">
-        <v>0.036049000000000005</v>
+        <v>0.052434</v>
       </c>
       <c r="I11" s="7">
-        <v>0.5784590000000001</v>
+        <v>0.608932</v>
       </c>
       <c r="J11" s="7">
-        <v>3.4048570000000002</v>
+        <v>3.572823</v>
       </c>
       <c r="K11" s="7">
-        <v>12.412120999999999</v>
+        <v>12.406488999999999</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.031608</v>
+        <v>0.028163999999999998</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.290489</v>
+        <v>-0.158775</v>
       </c>
       <c r="G12" s="7">
-        <v>0.5882000000000001</v>
+        <v>0.6175039999999999</v>
       </c>
       <c r="H12" s="7">
-        <v>0.015558</v>
+        <v>0.036562000000000004</v>
       </c>
       <c r="I12" s="7">
-        <v>1.53102</v>
+        <v>1.6428</v>
       </c>
       <c r="J12" s="7">
-        <v>4.776549</v>
+        <v>4.844298</v>
       </c>
       <c r="K12" s="7">
-        <v>13.652076</v>
+        <v>13.439748999999999</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.019</v>
+        <v>0.015079</v>
       </c>
       <c r="F13" s="7">
-        <v>0.0418</v>
+        <v>0.043296</v>
       </c>
       <c r="G13" s="7">
-        <v>0.078941</v>
+        <v>0.07831199999999999</v>
       </c>
       <c r="H13" s="7">
-        <v>0.054505</v>
+        <v>0.0555</v>
       </c>
       <c r="I13" s="7">
-        <v>0.17596399999999998</v>
+        <v>0.175118</v>
       </c>
       <c r="J13" s="7">
-        <v>1.135262</v>
+        <v>1.13965</v>
       </c>
       <c r="K13" s="7">
-        <v>4.398828</v>
+        <v>4.374477</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.032963</v>
+        <v>-0.023384000000000002</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.099806</v>
+        <v>-0.100697</v>
       </c>
       <c r="G14" s="7">
-        <v>0.134772</v>
+        <v>0.139647</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.010298</v>
+        <v>0.008523</v>
       </c>
       <c r="I14" s="7">
-        <v>0.660906</v>
+        <v>0.6977519999999999</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>0.008314</v>
+        <v>0.004933</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.059701000000000004</v>
+        <v>0.06675</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.042697000000000006</v>
+        <v>-0.043139000000000004</v>
       </c>
       <c r="G17" s="7">
-        <v>0.227076</v>
+        <v>0.20798100000000003</v>
       </c>
       <c r="H17" s="7">
-        <v>0.173015</v>
+        <v>0.180817</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.034467</v>
+        <v>0.028384999999999997</v>
       </c>
       <c r="F18" s="7">
-        <v>0.096108</v>
+        <v>0.094724</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.131532</v>
+        <v>0.132276</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.158438</v>
+        <v>0.142992</v>
       </c>
       <c r="F19" s="7">
-        <v>0.191108</v>
+        <v>0.218425</v>
       </c>
       <c r="G19" s="7">
-        <v>0.456389</v>
+        <v>0.449582</v>
       </c>
       <c r="H19" s="7">
-        <v>0.44525</v>
+        <v>0.464171</v>
       </c>
       <c r="I19" s="7">
-        <v>0.8122159999999999</v>
+        <v>0.8565590000000001</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.1344</v>
+        <v>0.10376899999999999</v>
       </c>
       <c r="F20" s="7">
-        <v>0.048558000000000004</v>
+        <v>0.053981</v>
       </c>
       <c r="G20" s="7">
-        <v>0.333124</v>
+        <v>0.328363</v>
       </c>
       <c r="H20" s="7">
-        <v>0.29026399999999997</v>
+        <v>0.296937</v>
       </c>
       <c r="I20" s="7">
-        <v>0.596847</v>
+        <v>0.619697</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.076478</v>
+        <v>0.08473900000000001</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.01401</v>
+        <v>-0.0007580000000000001</v>
       </c>
       <c r="G21" s="7">
-        <v>0.251321</v>
+        <v>0.24445499999999998</v>
       </c>
       <c r="H21" s="7">
-        <v>0.202771</v>
+        <v>0.218014</v>
       </c>
       <c r="I21" s="7">
-        <v>0.458415</v>
+        <v>0.478139</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.086179</v>
+        <v>0.066542</v>
       </c>
       <c r="F22" s="7">
-        <v>0.037816</v>
+        <v>0.042236</v>
       </c>
       <c r="G22" s="7">
-        <v>0.162624</v>
+        <v>0.132387</v>
       </c>
       <c r="H22" s="7">
-        <v>0.19277999999999998</v>
+        <v>0.202243</v>
       </c>
       <c r="I22" s="7">
-        <v>0.606704</v>
+        <v>0.595349</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.136954</v>
+        <v>0.11011100000000001</v>
       </c>
       <c r="F23" s="7">
-        <v>0.053251999999999994</v>
+        <v>0.055787</v>
       </c>
       <c r="G23" s="7">
-        <v>0.359088</v>
+        <v>0.340895</v>
       </c>
       <c r="H23" s="7">
-        <v>0.302975</v>
+        <v>0.309957</v>
       </c>
       <c r="I23" s="7">
-        <v>0.6056860000000001</v>
+        <v>0.6221800000000001</v>
       </c>
       <c r="J23" s="7">
-        <v>2.316847</v>
+        <v>2.428957</v>
       </c>
       <c r="K23" s="7">
-        <v>11.45502</v>
+        <v>11.356815999999998</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.115536</v>
+        <v>0.069482</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.141377</v>
+        <v>-0.133766</v>
       </c>
       <c r="G24" s="7">
-        <v>0.153712</v>
+        <v>0.15265</v>
       </c>
       <c r="H24" s="7">
-        <v>0.029502999999999998</v>
+        <v>0.035714</v>
       </c>
       <c r="I24" s="7">
-        <v>0.513123</v>
+        <v>0.5084810000000001</v>
       </c>
       <c r="J24" s="7">
-        <v>3.2391300000000003</v>
+        <v>3.37377</v>
       </c>
       <c r="K24" s="7">
-        <v>17.14781</v>
+        <v>16.978437</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.126604</v>
+        <v>0.10904</v>
       </c>
       <c r="F25" s="7">
-        <v>0.08693300000000001</v>
+        <v>0.087561</v>
       </c>
       <c r="G25" s="7">
-        <v>0.402556</v>
+        <v>0.386783</v>
       </c>
       <c r="H25" s="7">
-        <v>0.3357</v>
+        <v>0.34787</v>
       </c>
       <c r="I25" s="7">
-        <v>0.584838</v>
+        <v>0.609608</v>
       </c>
       <c r="J25" s="7">
-        <v>1.926667</v>
+        <v>2.08305</v>
       </c>
       <c r="K25" s="7">
-        <v>10.243597</v>
+        <v>10.081156</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.06893500000000001</v>
+        <v>0.069354</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.031621</v>
+        <v>-0.031029</v>
       </c>
       <c r="G26" s="7">
-        <v>0.20749099999999998</v>
+        <v>0.182646</v>
       </c>
       <c r="H26" s="7">
-        <v>0.11923299999999999</v>
+        <v>0.126999</v>
       </c>
       <c r="I26" s="7">
-        <v>0.282723</v>
+        <v>0.313352</v>
       </c>
       <c r="J26" s="7">
-        <v>1.3712739999999999</v>
+        <v>1.5323339999999999</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.016399</v>
+        <v>-0.021978</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.08146</v>
+        <v>-0.077421</v>
       </c>
       <c r="G27" s="7">
-        <v>0.16680499999999998</v>
+        <v>0.15490700000000002</v>
       </c>
       <c r="H27" s="7">
-        <v>0.008948000000000001</v>
+        <v>0.019327</v>
       </c>
       <c r="I27" s="7">
-        <v>0.6524030000000001</v>
+        <v>0.6816249999999999</v>
       </c>
       <c r="J27" s="7">
-        <v>3.894097</v>
+        <v>3.9273360000000004</v>
       </c>
       <c r="K27" s="7">
-        <v>14.136383</v>
+        <v>14.014762000000001</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.13228600000000001</v>
+        <v>0.145224</v>
       </c>
       <c r="F28" s="7">
-        <v>0.23323799999999997</v>
+        <v>0.272104</v>
       </c>
       <c r="G28" s="7">
-        <v>0.480308</v>
+        <v>0.48233800000000004</v>
       </c>
       <c r="H28" s="7">
-        <v>0.415473</v>
+        <v>0.442898</v>
       </c>
       <c r="I28" s="7">
-        <v>0.779905</v>
+        <v>0.821894</v>
       </c>
       <c r="J28" s="7">
-        <v>2.213755</v>
+        <v>2.583774</v>
       </c>
       <c r="K28" s="7">
-        <v>7.657987</v>
+        <v>7.690828</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.1341</v>
+        <v>0.123451</v>
       </c>
       <c r="F29" s="7">
-        <v>0.162125</v>
+        <v>0.192019</v>
       </c>
       <c r="G29" s="7">
-        <v>0.41269</v>
+        <v>0.41369700000000004</v>
       </c>
       <c r="H29" s="7">
-        <v>0.36</v>
+        <v>0.37243200000000004</v>
       </c>
       <c r="I29" s="7">
-        <v>0.759441</v>
+        <v>0.794346</v>
       </c>
       <c r="J29" s="7">
-        <v>2.533708</v>
+        <v>2.820343</v>
       </c>
       <c r="K29" s="7">
-        <v>11.726353</v>
+        <v>11.644421999999999</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.156313</v>
+        <v>0.125136</v>
       </c>
       <c r="F30" s="7">
-        <v>0.14222400000000002</v>
+        <v>0.14438</v>
       </c>
       <c r="G30" s="7">
-        <v>0.403375</v>
+        <v>0.38718400000000003</v>
       </c>
       <c r="H30" s="7">
-        <v>0.41726199999999997</v>
+        <v>0.416163</v>
       </c>
       <c r="I30" s="7">
-        <v>0.7055899999999999</v>
+        <v>0.72135</v>
       </c>
       <c r="J30" s="7">
-        <v>2.383202</v>
+        <v>2.423711</v>
       </c>
       <c r="K30" s="7">
-        <v>12.547030999999999</v>
+        <v>11.873562999999999</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.147389</v>
+        <v>0.120419</v>
       </c>
       <c r="F31" s="7">
-        <v>0.27356400000000003</v>
+        <v>0.28718299999999997</v>
       </c>
       <c r="G31" s="7">
-        <v>0.407447</v>
+        <v>0.401858</v>
       </c>
       <c r="H31" s="7">
-        <v>0.439505</v>
+        <v>0.441342</v>
       </c>
       <c r="I31" s="7">
-        <v>0.5270199999999999</v>
+        <v>0.572268</v>
       </c>
       <c r="J31" s="7">
-        <v>2.7128870000000003</v>
+        <v>3.160481</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.119055</v>
+        <v>0.101484</v>
       </c>
       <c r="F32" s="7">
-        <v>0.134216</v>
+        <v>0.13625</v>
       </c>
       <c r="G32" s="7">
-        <v>0.422925</v>
+        <v>0.408756</v>
       </c>
       <c r="H32" s="7">
-        <v>0.39697299999999996</v>
+        <v>0.41094299999999995</v>
       </c>
       <c r="I32" s="7">
-        <v>0.578947</v>
+        <v>0.6074269999999999</v>
       </c>
       <c r="J32" s="7">
-        <v>1.686567</v>
+        <v>1.7986449999999998</v>
       </c>
       <c r="K32" s="7">
-        <v>9.123735</v>
+        <v>9.055309999999999</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.103448</v>
+        <v>0.080044</v>
       </c>
       <c r="F33" s="7">
-        <v>0.015036</v>
+        <v>0.011917</v>
       </c>
       <c r="G33" s="7">
-        <v>0.299578</v>
+        <v>0.279221</v>
       </c>
       <c r="H33" s="7">
-        <v>0.250761</v>
+        <v>0.25</v>
       </c>
       <c r="I33" s="7">
-        <v>0.542893</v>
+        <v>0.5502049999999999</v>
       </c>
       <c r="J33" s="7">
-        <v>2.4103809999999997</v>
+        <v>2.480565</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.035836</v>
+        <v>0.030521</v>
       </c>
       <c r="F34" s="7">
-        <v>0.09913999999999999</v>
+        <v>0.09801299999999999</v>
       </c>
       <c r="G34" s="7">
-        <v>0.20895600000000003</v>
+        <v>0.205329</v>
       </c>
       <c r="H34" s="7">
-        <v>0.13088</v>
+        <v>0.132278</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.09351000000000001</v>
+        <v>0.084275</v>
       </c>
       <c r="F35" s="7">
-        <v>0.006790000000000001</v>
+        <v>0.010526</v>
       </c>
       <c r="G35" s="7">
-        <v>0.29344000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="H35" s="7">
-        <v>0.23484300000000002</v>
+        <v>0.247169</v>
       </c>
       <c r="I35" s="7">
-        <v>0.531185</v>
+        <v>0.554172</v>
       </c>
       <c r="J35" s="7">
-        <v>2.313371</v>
+        <v>2.416058</v>
       </c>
       <c r="K35" s="7">
-        <v>9.689157999999999</v>
+        <v>9.764807</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.035821</v>
+        <v>0.030496</v>
       </c>
       <c r="F36" s="7">
-        <v>0.098598</v>
+        <v>0.098916</v>
       </c>
       <c r="G36" s="7">
-        <v>0.209405</v>
+        <v>0.206283</v>
       </c>
       <c r="H36" s="7">
-        <v>0.13134600000000002</v>
+        <v>0.133209</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>04.05.2026 19:03:38</t>
+    <t>05.05.2026 18:23:36</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.1</v>
+        <v>0.036508</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.109908</v>
+        <v>-0.144968</v>
       </c>
       <c r="G6" s="7">
-        <v>0.186064</v>
+        <v>0.117604</v>
       </c>
       <c r="H6" s="7">
-        <v>0.06850200000000001</v>
+        <v>0.006828</v>
       </c>
       <c r="I6" s="7">
-        <v>0.544904</v>
+        <v>0.455732</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.147604</v>
+        <v>0.12761</v>
       </c>
       <c r="F7" s="7">
-        <v>0.162992</v>
+        <v>0.13933500000000001</v>
       </c>
       <c r="G7" s="7">
-        <v>0.410043</v>
+        <v>0.413043</v>
       </c>
       <c r="H7" s="7">
-        <v>0.438099</v>
+        <v>0.413043</v>
       </c>
       <c r="I7" s="7">
-        <v>0.7447469999999999</v>
+        <v>0.71435</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.10747</v>
+        <v>0.099139</v>
       </c>
       <c r="F8" s="7">
-        <v>0.055026</v>
+        <v>0.049033</v>
       </c>
       <c r="G8" s="7">
-        <v>0.338255</v>
+        <v>0.355479</v>
       </c>
       <c r="H8" s="7">
-        <v>0.30497399999999997</v>
+        <v>0.295157</v>
       </c>
       <c r="I8" s="7">
-        <v>0.627091</v>
+        <v>0.614851</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -871,10 +871,10 @@
         <v>0.030292</v>
       </c>
       <c r="F9" s="7">
-        <v>0.097163</v>
+        <v>0.09545999999999999</v>
       </c>
       <c r="G9" s="7">
-        <v>0.203581</v>
+        <v>0.2023</v>
       </c>
       <c r="H9" s="7">
         <v>0.130557</v>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.10539</v>
+        <v>0.10870200000000001</v>
       </c>
       <c r="F10" s="7">
-        <v>0.168364</v>
+        <v>0.152065</v>
       </c>
       <c r="G10" s="7">
-        <v>0.20203</v>
+        <v>0.215182</v>
       </c>
       <c r="H10" s="7">
-        <v>0.270242</v>
+        <v>0.274048</v>
       </c>
       <c r="I10" s="7">
-        <v>0.531178</v>
+        <v>0.535766</v>
       </c>
       <c r="J10" s="7">
-        <v>1.299405</v>
+        <v>1.320101</v>
       </c>
       <c r="K10" s="7">
-        <v>7.489824</v>
+        <v>7.527096</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.022609</v>
+        <v>-0.034783</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.069151</v>
+        <v>-0.102305</v>
       </c>
       <c r="G11" s="7">
-        <v>0.175732</v>
+        <v>0.197928</v>
       </c>
       <c r="H11" s="7">
-        <v>0.052434</v>
+        <v>0.039326</v>
       </c>
       <c r="I11" s="7">
-        <v>0.608932</v>
+        <v>0.588892</v>
       </c>
       <c r="J11" s="7">
-        <v>3.572823</v>
+        <v>3.5195440000000002</v>
       </c>
       <c r="K11" s="7">
-        <v>12.406488999999999</v>
+        <v>12.182898</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.028163999999999998</v>
+        <v>0.024691</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.158775</v>
+        <v>-0.2202</v>
       </c>
       <c r="G12" s="7">
-        <v>0.6175039999999999</v>
+        <v>0.6509199999999999</v>
       </c>
       <c r="H12" s="7">
-        <v>0.036562000000000004</v>
+        <v>0.033061</v>
       </c>
       <c r="I12" s="7">
-        <v>1.6428</v>
+        <v>1.633875</v>
       </c>
       <c r="J12" s="7">
-        <v>4.844298</v>
+        <v>4.824561</v>
       </c>
       <c r="K12" s="7">
-        <v>13.439748999999999</v>
+        <v>13.294941</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.015079</v>
+        <v>0.0146</v>
       </c>
       <c r="F13" s="7">
-        <v>0.043296</v>
+        <v>0.041523000000000004</v>
       </c>
       <c r="G13" s="7">
-        <v>0.07831199999999999</v>
+        <v>0.076435</v>
       </c>
       <c r="H13" s="7">
-        <v>0.0555</v>
+        <v>0.055002</v>
       </c>
       <c r="I13" s="7">
-        <v>0.175118</v>
+        <v>0.174564</v>
       </c>
       <c r="J13" s="7">
-        <v>1.13965</v>
+        <v>1.129081</v>
       </c>
       <c r="K13" s="7">
-        <v>4.374477</v>
+        <v>4.357685</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.023384000000000002</v>
+        <v>-0.037139000000000005</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.100697</v>
+        <v>-0.14004899999999998</v>
       </c>
       <c r="G14" s="7">
-        <v>0.139647</v>
+        <v>0.146601</v>
       </c>
       <c r="H14" s="7">
-        <v>0.008523</v>
+        <v>-0.005682</v>
       </c>
       <c r="I14" s="7">
-        <v>0.6977519999999999</v>
+        <v>0.67384</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>0.004933</v>
+        <v>-0.007175</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.06675</v>
+        <v>0.058457999999999996</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.043139000000000004</v>
+        <v>-0.05689</v>
       </c>
       <c r="G17" s="7">
-        <v>0.20798100000000003</v>
+        <v>0.225636</v>
       </c>
       <c r="H17" s="7">
-        <v>0.180817</v>
+        <v>0.17163799999999999</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.028384999999999997</v>
+        <v>0.029736</v>
       </c>
       <c r="F18" s="7">
-        <v>0.094724</v>
+        <v>0.09484999999999999</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.132276</v>
+        <v>0.133764</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.142992</v>
+        <v>0.161219</v>
       </c>
       <c r="F19" s="7">
-        <v>0.218425</v>
+        <v>0.228799</v>
       </c>
       <c r="G19" s="7">
-        <v>0.449582</v>
+        <v>0.499899</v>
       </c>
       <c r="H19" s="7">
-        <v>0.464171</v>
+        <v>0.48752</v>
       </c>
       <c r="I19" s="7">
-        <v>0.8565590000000001</v>
+        <v>0.886166</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.10376899999999999</v>
+        <v>0.096541</v>
       </c>
       <c r="F20" s="7">
-        <v>0.053981</v>
+        <v>0.047079</v>
       </c>
       <c r="G20" s="7">
-        <v>0.328363</v>
+        <v>0.34387900000000005</v>
       </c>
       <c r="H20" s="7">
-        <v>0.296937</v>
+        <v>0.288444</v>
       </c>
       <c r="I20" s="7">
-        <v>0.619697</v>
+        <v>0.609091</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.08473900000000001</v>
+        <v>0.076512</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.0007580000000000001</v>
+        <v>-0.006831</v>
       </c>
       <c r="G21" s="7">
-        <v>0.24445499999999998</v>
+        <v>0.264862</v>
       </c>
       <c r="H21" s="7">
-        <v>0.218014</v>
+        <v>0.20877600000000002</v>
       </c>
       <c r="I21" s="7">
-        <v>0.478139</v>
+        <v>0.466928</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.066542</v>
+        <v>0.056592</v>
       </c>
       <c r="F22" s="7">
-        <v>0.042236</v>
+        <v>0.037557</v>
       </c>
       <c r="G22" s="7">
-        <v>0.132387</v>
+        <v>0.131912</v>
       </c>
       <c r="H22" s="7">
-        <v>0.202243</v>
+        <v>0.19102699999999997</v>
       </c>
       <c r="I22" s="7">
-        <v>0.595349</v>
+        <v>0.580465</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.11011100000000001</v>
+        <v>0.101106</v>
       </c>
       <c r="F23" s="7">
-        <v>0.055787</v>
+        <v>0.056528999999999996</v>
       </c>
       <c r="G23" s="7">
-        <v>0.340895</v>
+        <v>0.35314599999999996</v>
       </c>
       <c r="H23" s="7">
-        <v>0.309957</v>
+        <v>0.299332</v>
       </c>
       <c r="I23" s="7">
-        <v>0.6221800000000001</v>
+        <v>0.609023</v>
       </c>
       <c r="J23" s="7">
-        <v>2.428957</v>
+        <v>2.417439</v>
       </c>
       <c r="K23" s="7">
-        <v>11.356815999999998</v>
+        <v>11.291786</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.069482</v>
+        <v>0.049706</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.133766</v>
+        <v>-0.130396</v>
       </c>
       <c r="G24" s="7">
-        <v>0.15265</v>
+        <v>0.136245</v>
       </c>
       <c r="H24" s="7">
-        <v>0.035714</v>
+        <v>0.016563</v>
       </c>
       <c r="I24" s="7">
-        <v>0.5084810000000001</v>
+        <v>0.48058799999999996</v>
       </c>
       <c r="J24" s="7">
-        <v>3.37377</v>
+        <v>3.307018</v>
       </c>
       <c r="K24" s="7">
-        <v>16.978437</v>
+        <v>16.838329</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.10904</v>
+        <v>0.096801</v>
       </c>
       <c r="F25" s="7">
-        <v>0.087561</v>
+        <v>0.076146</v>
       </c>
       <c r="G25" s="7">
-        <v>0.386783</v>
+        <v>0.393286</v>
       </c>
       <c r="H25" s="7">
-        <v>0.34787</v>
+        <v>0.33299500000000004</v>
       </c>
       <c r="I25" s="7">
-        <v>0.609608</v>
+        <v>0.591845</v>
       </c>
       <c r="J25" s="7">
-        <v>2.08305</v>
+        <v>2.0584860000000003</v>
       </c>
       <c r="K25" s="7">
-        <v>10.081156</v>
+        <v>10.020123</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.069354</v>
+        <v>0.059817999999999996</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.031029</v>
+        <v>-0.040047</v>
       </c>
       <c r="G26" s="7">
-        <v>0.182646</v>
+        <v>0.18401900000000002</v>
       </c>
       <c r="H26" s="7">
-        <v>0.126999</v>
+        <v>0.11694800000000001</v>
       </c>
       <c r="I26" s="7">
-        <v>0.313352</v>
+        <v>0.30164</v>
       </c>
       <c r="J26" s="7">
-        <v>1.5323339999999999</v>
+        <v>1.496936</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.021978</v>
+        <v>-0.03228</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.077421</v>
+        <v>-0.096795</v>
       </c>
       <c r="G27" s="7">
-        <v>0.15490700000000002</v>
+        <v>0.172213</v>
       </c>
       <c r="H27" s="7">
-        <v>0.019327</v>
+        <v>0.00859</v>
       </c>
       <c r="I27" s="7">
-        <v>0.6816249999999999</v>
+        <v>0.6639109999999999</v>
       </c>
       <c r="J27" s="7">
-        <v>3.9273360000000004</v>
+        <v>3.82865</v>
       </c>
       <c r="K27" s="7">
-        <v>14.014762000000001</v>
+        <v>13.787992999999998</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.145224</v>
+        <v>0.16179300000000002</v>
       </c>
       <c r="F28" s="7">
-        <v>0.272104</v>
+        <v>0.281261</v>
       </c>
       <c r="G28" s="7">
-        <v>0.48233800000000004</v>
+        <v>0.534764</v>
       </c>
       <c r="H28" s="7">
-        <v>0.442898</v>
+        <v>0.463774</v>
       </c>
       <c r="I28" s="7">
-        <v>0.821894</v>
+        <v>0.848253</v>
       </c>
       <c r="J28" s="7">
-        <v>2.583774</v>
+        <v>2.609205</v>
       </c>
       <c r="K28" s="7">
-        <v>7.690828</v>
+        <v>7.799213</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.123451</v>
+        <v>0.141593</v>
       </c>
       <c r="F29" s="7">
-        <v>0.192019</v>
+        <v>0.202237</v>
       </c>
       <c r="G29" s="7">
-        <v>0.41369700000000004</v>
+        <v>0.449438</v>
       </c>
       <c r="H29" s="7">
-        <v>0.37243200000000004</v>
+        <v>0.394595</v>
       </c>
       <c r="I29" s="7">
-        <v>0.794346</v>
+        <v>0.823322</v>
       </c>
       <c r="J29" s="7">
-        <v>2.820343</v>
+        <v>2.879699</v>
       </c>
       <c r="K29" s="7">
-        <v>11.644421999999999</v>
+        <v>11.848606</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.125136</v>
+        <v>0.1247</v>
       </c>
       <c r="F30" s="7">
-        <v>0.14438</v>
+        <v>0.139381</v>
       </c>
       <c r="G30" s="7">
-        <v>0.38718400000000003</v>
+        <v>0.41444699999999995</v>
       </c>
       <c r="H30" s="7">
-        <v>0.416163</v>
+        <v>0.415613</v>
       </c>
       <c r="I30" s="7">
-        <v>0.72135</v>
+        <v>0.720682</v>
       </c>
       <c r="J30" s="7">
-        <v>2.423711</v>
+        <v>2.464747</v>
       </c>
       <c r="K30" s="7">
-        <v>11.873562999999999</v>
+        <v>12.171355</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.120419</v>
+        <v>0.174203</v>
       </c>
       <c r="F31" s="7">
-        <v>0.28718299999999997</v>
+        <v>0.341928</v>
       </c>
       <c r="G31" s="7">
-        <v>0.401858</v>
+        <v>0.49225700000000006</v>
       </c>
       <c r="H31" s="7">
-        <v>0.441342</v>
+        <v>0.510531</v>
       </c>
       <c r="I31" s="7">
-        <v>0.572268</v>
+        <v>0.6477419999999999</v>
       </c>
       <c r="J31" s="7">
-        <v>3.160481</v>
+        <v>3.378772</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.101484</v>
+        <v>0.09694000000000001</v>
       </c>
       <c r="F32" s="7">
-        <v>0.13625</v>
+        <v>0.126633</v>
       </c>
       <c r="G32" s="7">
-        <v>0.408756</v>
+        <v>0.430095</v>
       </c>
       <c r="H32" s="7">
-        <v>0.41094299999999995</v>
+        <v>0.405122</v>
       </c>
       <c r="I32" s="7">
-        <v>0.6074269999999999</v>
+        <v>0.600796</v>
       </c>
       <c r="J32" s="7">
-        <v>1.7986449999999998</v>
+        <v>1.795707</v>
       </c>
       <c r="K32" s="7">
-        <v>9.055309999999999</v>
+        <v>9.058333</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.080044</v>
+        <v>0.067105</v>
       </c>
       <c r="F33" s="7">
-        <v>0.011917</v>
+        <v>0.004749</v>
       </c>
       <c r="G33" s="7">
-        <v>0.279221</v>
+        <v>0.283905</v>
       </c>
       <c r="H33" s="7">
-        <v>0.25</v>
+        <v>0.235025</v>
       </c>
       <c r="I33" s="7">
-        <v>0.5502049999999999</v>
+        <v>0.531634</v>
       </c>
       <c r="J33" s="7">
-        <v>2.480565</v>
+        <v>2.443737</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.030521</v>
+        <v>0.031369</v>
       </c>
       <c r="F34" s="7">
-        <v>0.09801299999999999</v>
+        <v>0.09842000000000001</v>
       </c>
       <c r="G34" s="7">
-        <v>0.205329</v>
+        <v>0.20504999999999998</v>
       </c>
       <c r="H34" s="7">
-        <v>0.132278</v>
+        <v>0.133209</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.084275</v>
+        <v>0.07327</v>
       </c>
       <c r="F35" s="7">
-        <v>0.010526</v>
+        <v>0.005698999999999999</v>
       </c>
       <c r="G35" s="7">
-        <v>0.28</v>
+        <v>0.289043</v>
       </c>
       <c r="H35" s="7">
-        <v>0.247169</v>
+        <v>0.23451</v>
       </c>
       <c r="I35" s="7">
-        <v>0.554172</v>
+        <v>0.5383979999999999</v>
       </c>
       <c r="J35" s="7">
-        <v>2.416058</v>
+        <v>2.408756</v>
       </c>
       <c r="K35" s="7">
-        <v>9.764807</v>
+        <v>9.704795</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.030496</v>
+        <v>0.031766</v>
       </c>
       <c r="F36" s="7">
-        <v>0.098916</v>
+        <v>0.098287</v>
       </c>
       <c r="G36" s="7">
-        <v>0.206283</v>
+        <v>0.206494</v>
       </c>
       <c r="H36" s="7">
-        <v>0.133209</v>
+        <v>0.134606</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>05.05.2026 18:23:36</t>
+    <t>06.05.2026 18:18:17</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.036508</v>
+        <v>0.035373999999999996</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.144968</v>
+        <v>-0.11716900000000001</v>
       </c>
       <c r="G6" s="7">
-        <v>0.117604</v>
+        <v>0.10771499999999999</v>
       </c>
       <c r="H6" s="7">
-        <v>0.006828</v>
+        <v>0.0057269999999999995</v>
       </c>
       <c r="I6" s="7">
-        <v>0.455732</v>
+        <v>0.47862699999999997</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.12761</v>
+        <v>0.129668</v>
       </c>
       <c r="F7" s="7">
-        <v>0.13933500000000001</v>
+        <v>0.166009</v>
       </c>
       <c r="G7" s="7">
-        <v>0.413043</v>
+        <v>0.415101</v>
       </c>
       <c r="H7" s="7">
-        <v>0.413043</v>
+        <v>0.415623</v>
       </c>
       <c r="I7" s="7">
-        <v>0.71435</v>
+        <v>0.720555</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.099139</v>
+        <v>0.109414</v>
       </c>
       <c r="F8" s="7">
-        <v>0.049033</v>
+        <v>0.086188</v>
       </c>
       <c r="G8" s="7">
-        <v>0.355479</v>
+        <v>0.353778</v>
       </c>
       <c r="H8" s="7">
-        <v>0.295157</v>
+        <v>0.30726400000000004</v>
       </c>
       <c r="I8" s="7">
-        <v>0.614851</v>
+        <v>0.640657</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.030292</v>
+        <v>0.031751999999999996</v>
       </c>
       <c r="F9" s="7">
-        <v>0.09545999999999999</v>
+        <v>0.093617</v>
       </c>
       <c r="G9" s="7">
-        <v>0.2023</v>
+        <v>0.20272300000000001</v>
       </c>
       <c r="H9" s="7">
-        <v>0.130557</v>
+        <v>0.132159</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.10870200000000001</v>
+        <v>0.11683199999999999</v>
       </c>
       <c r="F10" s="7">
-        <v>0.152065</v>
+        <v>0.185363</v>
       </c>
       <c r="G10" s="7">
-        <v>0.215182</v>
+        <v>0.182717</v>
       </c>
       <c r="H10" s="7">
-        <v>0.274048</v>
+        <v>0.283391</v>
       </c>
       <c r="I10" s="7">
-        <v>0.535766</v>
+        <v>0.5522079999999999</v>
       </c>
       <c r="J10" s="7">
-        <v>1.320101</v>
+        <v>1.37452</v>
       </c>
       <c r="K10" s="7">
-        <v>7.527096</v>
+        <v>7.585648</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.034783</v>
+        <v>-0.028696000000000003</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.102305</v>
+        <v>-0.061738999999999995</v>
       </c>
       <c r="G11" s="7">
-        <v>0.197928</v>
+        <v>0.192866</v>
       </c>
       <c r="H11" s="7">
-        <v>0.039326</v>
+        <v>0.045880000000000004</v>
       </c>
       <c r="I11" s="7">
-        <v>0.588892</v>
+        <v>0.571027</v>
       </c>
       <c r="J11" s="7">
-        <v>3.5195440000000002</v>
+        <v>3.634855</v>
       </c>
       <c r="K11" s="7">
-        <v>12.182898</v>
+        <v>12.335721000000001</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.024691</v>
+        <v>0.026234999999999998</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.2202</v>
+        <v>-0.076389</v>
       </c>
       <c r="G12" s="7">
-        <v>0.6509199999999999</v>
+        <v>0.6444110000000001</v>
       </c>
       <c r="H12" s="7">
-        <v>0.033061</v>
+        <v>0.034617</v>
       </c>
       <c r="I12" s="7">
-        <v>1.633875</v>
+        <v>1.62224</v>
       </c>
       <c r="J12" s="7">
-        <v>4.824561</v>
+        <v>4.985599000000001</v>
       </c>
       <c r="K12" s="7">
-        <v>13.294941</v>
+        <v>13.491175</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1005,10 +1005,10 @@
         <v>0.0146</v>
       </c>
       <c r="F13" s="7">
-        <v>0.041523000000000004</v>
+        <v>0.039224999999999996</v>
       </c>
       <c r="G13" s="7">
-        <v>0.076435</v>
+        <v>0.077255</v>
       </c>
       <c r="H13" s="7">
         <v>0.055002</v>
@@ -1017,10 +1017,10 @@
         <v>0.174564</v>
       </c>
       <c r="J13" s="7">
-        <v>1.129081</v>
+        <v>1.106231</v>
       </c>
       <c r="K13" s="7">
-        <v>4.357685</v>
+        <v>4.338791</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.037139000000000005</v>
+        <v>-0.034044</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.14004899999999998</v>
+        <v>-0.09765499999999999</v>
       </c>
       <c r="G14" s="7">
-        <v>0.146601</v>
+        <v>0.14373</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.005682</v>
+        <v>-0.002486</v>
       </c>
       <c r="I14" s="7">
-        <v>0.67384</v>
+        <v>0.636946</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.007175</v>
+        <v>-0.008072000000000001</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.058457999999999996</v>
+        <v>0.077529</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.05689</v>
+        <v>-0.016276</v>
       </c>
       <c r="G17" s="7">
-        <v>0.225636</v>
+        <v>0.21222000000000002</v>
       </c>
       <c r="H17" s="7">
-        <v>0.17163799999999999</v>
+        <v>0.19274899999999998</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.029736</v>
+        <v>0.030411999999999998</v>
       </c>
       <c r="F18" s="7">
-        <v>0.09484999999999999</v>
+        <v>0.09242900000000001</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.133764</v>
+        <v>0.134508</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.161219</v>
+        <v>0.163105</v>
       </c>
       <c r="F19" s="7">
-        <v>0.228799</v>
+        <v>0.256706</v>
       </c>
       <c r="G19" s="7">
-        <v>0.499899</v>
+        <v>0.5023340000000001</v>
       </c>
       <c r="H19" s="7">
-        <v>0.48752</v>
+        <v>0.489936</v>
       </c>
       <c r="I19" s="7">
-        <v>0.886166</v>
+        <v>0.8892289999999999</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.096541</v>
+        <v>0.104285</v>
       </c>
       <c r="F20" s="7">
-        <v>0.047079</v>
+        <v>0.081395</v>
       </c>
       <c r="G20" s="7">
-        <v>0.34387900000000005</v>
+        <v>0.34867600000000004</v>
       </c>
       <c r="H20" s="7">
-        <v>0.288444</v>
+        <v>0.297543</v>
       </c>
       <c r="I20" s="7">
-        <v>0.609091</v>
+        <v>0.6290939999999999</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.076512</v>
+        <v>0.058823999999999994</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.006831</v>
+        <v>-0.0057940000000000005</v>
       </c>
       <c r="G21" s="7">
-        <v>0.264862</v>
+        <v>0.22981400000000002</v>
       </c>
       <c r="H21" s="7">
-        <v>0.20877600000000002</v>
+        <v>0.188915</v>
       </c>
       <c r="I21" s="7">
-        <v>0.466928</v>
+        <v>0.482719</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.056592</v>
+        <v>0.054415</v>
       </c>
       <c r="F22" s="7">
-        <v>0.037557</v>
+        <v>0.05474300000000001</v>
       </c>
       <c r="G22" s="7">
-        <v>0.131912</v>
+        <v>0.118035</v>
       </c>
       <c r="H22" s="7">
-        <v>0.19102699999999997</v>
+        <v>0.188573</v>
       </c>
       <c r="I22" s="7">
-        <v>0.580465</v>
+        <v>0.578678</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.101106</v>
+        <v>0.109596</v>
       </c>
       <c r="F23" s="7">
-        <v>0.056528999999999996</v>
+        <v>0.086946</v>
       </c>
       <c r="G23" s="7">
-        <v>0.35314599999999996</v>
+        <v>0.35885300000000003</v>
       </c>
       <c r="H23" s="7">
-        <v>0.299332</v>
+        <v>0.30935</v>
       </c>
       <c r="I23" s="7">
-        <v>0.609023</v>
+        <v>0.638055</v>
       </c>
       <c r="J23" s="7">
-        <v>2.417439</v>
+        <v>2.512215</v>
       </c>
       <c r="K23" s="7">
-        <v>11.291786</v>
+        <v>11.386559</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.049706</v>
+        <v>0.036611</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.130396</v>
+        <v>-0.11458600000000001</v>
       </c>
       <c r="G24" s="7">
-        <v>0.136245</v>
+        <v>0.112737</v>
       </c>
       <c r="H24" s="7">
-        <v>0.016563</v>
+        <v>0.003882</v>
       </c>
       <c r="I24" s="7">
-        <v>0.48058799999999996</v>
+        <v>0.489631</v>
       </c>
       <c r="J24" s="7">
-        <v>3.307018</v>
+        <v>3.3282749999999997</v>
       </c>
       <c r="K24" s="7">
-        <v>16.838329</v>
+        <v>16.631818</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.096801</v>
+        <v>0.11265599999999999</v>
       </c>
       <c r="F25" s="7">
-        <v>0.076146</v>
+        <v>0.114827</v>
       </c>
       <c r="G25" s="7">
-        <v>0.393286</v>
+        <v>0.401051</v>
       </c>
       <c r="H25" s="7">
-        <v>0.33299500000000004</v>
+        <v>0.352265</v>
       </c>
       <c r="I25" s="7">
-        <v>0.591845</v>
+        <v>0.626016</v>
       </c>
       <c r="J25" s="7">
-        <v>2.0584860000000003</v>
+        <v>2.140704</v>
       </c>
       <c r="K25" s="7">
-        <v>10.020123</v>
+        <v>10.185682</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.059817999999999996</v>
+        <v>0.07629</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.040047</v>
+        <v>-0.0139</v>
       </c>
       <c r="G26" s="7">
-        <v>0.18401900000000002</v>
+        <v>0.186902</v>
       </c>
       <c r="H26" s="7">
-        <v>0.11694800000000001</v>
+        <v>0.13430799999999998</v>
       </c>
       <c r="I26" s="7">
-        <v>0.30164</v>
+        <v>0.329229</v>
       </c>
       <c r="J26" s="7">
-        <v>1.496936</v>
+        <v>1.588616</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.03228</v>
+        <v>-0.033654</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.096795</v>
+        <v>-0.073123</v>
       </c>
       <c r="G27" s="7">
-        <v>0.172213</v>
+        <v>0.16137</v>
       </c>
       <c r="H27" s="7">
-        <v>0.00859</v>
+        <v>0.007158</v>
       </c>
       <c r="I27" s="7">
-        <v>0.6639109999999999</v>
+        <v>0.6269659999999999</v>
       </c>
       <c r="J27" s="7">
-        <v>3.82865</v>
+        <v>3.9247460000000003</v>
       </c>
       <c r="K27" s="7">
-        <v>13.787992999999998</v>
+        <v>13.841772</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.16179300000000002</v>
+        <v>0.155296</v>
       </c>
       <c r="F28" s="7">
-        <v>0.281261</v>
+        <v>0.292621</v>
       </c>
       <c r="G28" s="7">
-        <v>0.534764</v>
+        <v>0.52618</v>
       </c>
       <c r="H28" s="7">
-        <v>0.463774</v>
+        <v>0.455587</v>
       </c>
       <c r="I28" s="7">
-        <v>0.848253</v>
+        <v>0.860611</v>
       </c>
       <c r="J28" s="7">
-        <v>2.609205</v>
+        <v>2.6546760000000003</v>
       </c>
       <c r="K28" s="7">
-        <v>7.799213</v>
+        <v>7.767258000000001</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.141593</v>
+        <v>0.139823</v>
       </c>
       <c r="F29" s="7">
-        <v>0.202237</v>
+        <v>0.220853</v>
       </c>
       <c r="G29" s="7">
-        <v>0.449438</v>
+        <v>0.455778</v>
       </c>
       <c r="H29" s="7">
-        <v>0.394595</v>
+        <v>0.392432</v>
       </c>
       <c r="I29" s="7">
-        <v>0.823322</v>
+        <v>0.828896</v>
       </c>
       <c r="J29" s="7">
-        <v>2.879699</v>
+        <v>2.952133</v>
       </c>
       <c r="K29" s="7">
-        <v>11.848606</v>
+        <v>11.796821</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.1247</v>
+        <v>0.13430899999999998</v>
       </c>
       <c r="F30" s="7">
-        <v>0.139381</v>
+        <v>0.180455</v>
       </c>
       <c r="G30" s="7">
-        <v>0.41444699999999995</v>
+        <v>0.431248</v>
       </c>
       <c r="H30" s="7">
-        <v>0.415613</v>
+        <v>0.42770800000000003</v>
       </c>
       <c r="I30" s="7">
-        <v>0.720682</v>
+        <v>0.739451</v>
       </c>
       <c r="J30" s="7">
-        <v>2.464747</v>
+        <v>2.563392</v>
       </c>
       <c r="K30" s="7">
-        <v>12.171355</v>
+        <v>12.223014000000001</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.174203</v>
+        <v>0.213232</v>
       </c>
       <c r="F31" s="7">
-        <v>0.341928</v>
+        <v>0.412971</v>
       </c>
       <c r="G31" s="7">
-        <v>0.49225700000000006</v>
+        <v>0.49870600000000004</v>
       </c>
       <c r="H31" s="7">
-        <v>0.510531</v>
+        <v>0.56074</v>
       </c>
       <c r="I31" s="7">
-        <v>0.6477419999999999</v>
+        <v>0.720437</v>
       </c>
       <c r="J31" s="7">
-        <v>3.378772</v>
+        <v>3.5828840000000004</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.09694000000000001</v>
+        <v>0.109361</v>
       </c>
       <c r="F32" s="7">
-        <v>0.126633</v>
+        <v>0.161434</v>
       </c>
       <c r="G32" s="7">
-        <v>0.430095</v>
+        <v>0.439465</v>
       </c>
       <c r="H32" s="7">
-        <v>0.405122</v>
+        <v>0.421032</v>
       </c>
       <c r="I32" s="7">
-        <v>0.600796</v>
+        <v>0.6261099999999999</v>
       </c>
       <c r="J32" s="7">
-        <v>1.795707</v>
+        <v>1.8771209999999998</v>
       </c>
       <c r="K32" s="7">
-        <v>9.058333</v>
+        <v>9.166574</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.067105</v>
+        <v>0.074123</v>
       </c>
       <c r="F33" s="7">
-        <v>0.004749</v>
+        <v>0.032462</v>
       </c>
       <c r="G33" s="7">
-        <v>0.283905</v>
+        <v>0.28623899999999997</v>
       </c>
       <c r="H33" s="7">
-        <v>0.235025</v>
+        <v>0.24314699999999997</v>
       </c>
       <c r="I33" s="7">
-        <v>0.531634</v>
+        <v>0.553934</v>
       </c>
       <c r="J33" s="7">
-        <v>2.443737</v>
+        <v>2.508596</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.031369</v>
+        <v>0.032216999999999996</v>
       </c>
       <c r="F34" s="7">
-        <v>0.09842000000000001</v>
+        <v>0.09635300000000001</v>
       </c>
       <c r="G34" s="7">
-        <v>0.20504999999999998</v>
+        <v>0.204767</v>
       </c>
       <c r="H34" s="7">
-        <v>0.133209</v>
+        <v>0.13414099999999998</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.07327</v>
+        <v>0.092963</v>
       </c>
       <c r="F35" s="7">
-        <v>0.005698999999999999</v>
+        <v>0.041391</v>
       </c>
       <c r="G35" s="7">
-        <v>0.289043</v>
+        <v>0.29913900000000004</v>
       </c>
       <c r="H35" s="7">
-        <v>0.23451</v>
+        <v>0.257162</v>
       </c>
       <c r="I35" s="7">
-        <v>0.5383979999999999</v>
+        <v>0.584383</v>
       </c>
       <c r="J35" s="7">
-        <v>2.408756</v>
+        <v>2.531063</v>
       </c>
       <c r="K35" s="7">
-        <v>9.704795</v>
+        <v>9.826162</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.031766</v>
+        <v>0.032612999999999996</v>
       </c>
       <c r="F36" s="7">
-        <v>0.098287</v>
+        <v>0.09622299999999999</v>
       </c>
       <c r="G36" s="7">
-        <v>0.206494</v>
+        <v>0.206206</v>
       </c>
       <c r="H36" s="7">
-        <v>0.134606</v>
+        <v>0.13553800000000002</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>06.05.2026 18:18:17</t>
+    <t>07.05.2026 18:21:20</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.035373999999999996</v>
+        <v>0.081401</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.11716900000000001</v>
+        <v>-0.058811999999999996</v>
       </c>
       <c r="G6" s="7">
-        <v>0.10771499999999999</v>
+        <v>0.156727</v>
       </c>
       <c r="H6" s="7">
-        <v>0.0057269999999999995</v>
+        <v>0.068062</v>
       </c>
       <c r="I6" s="7">
-        <v>0.47862699999999997</v>
+        <v>0.55168</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.129668</v>
+        <v>0.146973</v>
       </c>
       <c r="F7" s="7">
-        <v>0.166009</v>
+        <v>0.194604</v>
       </c>
       <c r="G7" s="7">
-        <v>0.415101</v>
+        <v>0.43674799999999997</v>
       </c>
       <c r="H7" s="7">
-        <v>0.415623</v>
+        <v>0.4521</v>
       </c>
       <c r="I7" s="7">
-        <v>0.720555</v>
+        <v>0.759375</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.109414</v>
+        <v>0.133333</v>
       </c>
       <c r="F8" s="7">
-        <v>0.086188</v>
+        <v>0.122859</v>
       </c>
       <c r="G8" s="7">
-        <v>0.353778</v>
+        <v>0.38299300000000003</v>
       </c>
       <c r="H8" s="7">
-        <v>0.30726400000000004</v>
+        <v>0.35176699999999994</v>
       </c>
       <c r="I8" s="7">
-        <v>0.640657</v>
+        <v>0.68888</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.031751999999999996</v>
+        <v>0.031364</v>
       </c>
       <c r="F9" s="7">
-        <v>0.093617</v>
+        <v>0.09315799999999999</v>
       </c>
       <c r="G9" s="7">
-        <v>0.20272300000000001</v>
+        <v>0.19932099999999997</v>
       </c>
       <c r="H9" s="7">
-        <v>0.132159</v>
+        <v>0.132559</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.11683199999999999</v>
+        <v>0.12319100000000001</v>
       </c>
       <c r="F10" s="7">
-        <v>0.185363</v>
+        <v>0.223688</v>
       </c>
       <c r="G10" s="7">
-        <v>0.182717</v>
+        <v>0.206601</v>
       </c>
       <c r="H10" s="7">
-        <v>0.283391</v>
+        <v>0.315571</v>
       </c>
       <c r="I10" s="7">
-        <v>0.5522079999999999</v>
+        <v>0.569453</v>
       </c>
       <c r="J10" s="7">
-        <v>1.37452</v>
+        <v>1.434059</v>
       </c>
       <c r="K10" s="7">
-        <v>7.585648</v>
+        <v>7.728191000000001</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.028696000000000003</v>
+        <v>-0.00043499999999999995</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.061738999999999995</v>
+        <v>-0.063925</v>
       </c>
       <c r="G11" s="7">
-        <v>0.192866</v>
+        <v>0.21898199999999998</v>
       </c>
       <c r="H11" s="7">
-        <v>0.045880000000000004</v>
+        <v>0.076311</v>
       </c>
       <c r="I11" s="7">
-        <v>0.571027</v>
+        <v>0.588585</v>
       </c>
       <c r="J11" s="7">
-        <v>3.634855</v>
+        <v>3.76971</v>
       </c>
       <c r="K11" s="7">
-        <v>12.335721000000001</v>
+        <v>12.520347999999998</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.026234999999999998</v>
+        <v>0.076596</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.076389</v>
+        <v>-0.023509000000000002</v>
       </c>
       <c r="G12" s="7">
-        <v>0.6444110000000001</v>
+        <v>0.71536</v>
       </c>
       <c r="H12" s="7">
-        <v>0.034617</v>
+        <v>0.08245799999999999</v>
       </c>
       <c r="I12" s="7">
-        <v>1.62224</v>
+        <v>1.6873310000000001</v>
       </c>
       <c r="J12" s="7">
-        <v>4.985599000000001</v>
+        <v>5.262376000000001</v>
       </c>
       <c r="K12" s="7">
-        <v>13.491175</v>
+        <v>13.740466</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.0146</v>
+        <v>0.015576000000000001</v>
       </c>
       <c r="F13" s="7">
-        <v>0.039224999999999996</v>
+        <v>0.039235</v>
       </c>
       <c r="G13" s="7">
-        <v>0.077255</v>
+        <v>0.07481600000000001</v>
       </c>
       <c r="H13" s="7">
-        <v>0.055002</v>
+        <v>0.054754</v>
       </c>
       <c r="I13" s="7">
-        <v>0.174564</v>
+        <v>0.171689</v>
       </c>
       <c r="J13" s="7">
-        <v>1.106231</v>
+        <v>1.105734</v>
       </c>
       <c r="K13" s="7">
-        <v>4.338791</v>
+        <v>4.350335</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.034044</v>
+        <v>-0.010708</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.09765499999999999</v>
+        <v>-0.100503</v>
       </c>
       <c r="G14" s="7">
-        <v>0.14373</v>
+        <v>0.154839</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.002486</v>
+        <v>0.017044999999999998</v>
       </c>
       <c r="I14" s="7">
-        <v>0.636946</v>
+        <v>0.625426</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.008072000000000001</v>
+        <v>0.006646</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.077529</v>
+        <v>0.104727</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.016276</v>
+        <v>0.029233</v>
       </c>
       <c r="G17" s="7">
-        <v>0.21222000000000002</v>
+        <v>0.25858899999999996</v>
       </c>
       <c r="H17" s="7">
-        <v>0.19274899999999998</v>
+        <v>0.244149</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030411999999999998</v>
+        <v>0.030834999999999998</v>
       </c>
       <c r="F18" s="7">
-        <v>0.09242900000000001</v>
+        <v>0.09281800000000001</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.134508</v>
+        <v>0.135996</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.163105</v>
+        <v>0.171375</v>
       </c>
       <c r="F19" s="7">
-        <v>0.256706</v>
+        <v>0.277251</v>
       </c>
       <c r="G19" s="7">
-        <v>0.5023340000000001</v>
+        <v>0.5328050000000001</v>
       </c>
       <c r="H19" s="7">
-        <v>0.489936</v>
+        <v>0.518921</v>
       </c>
       <c r="I19" s="7">
-        <v>0.8892289999999999</v>
+        <v>0.926474</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.104285</v>
+        <v>0.131975</v>
       </c>
       <c r="F20" s="7">
-        <v>0.081395</v>
+        <v>0.133708</v>
       </c>
       <c r="G20" s="7">
-        <v>0.34867600000000004</v>
+        <v>0.38281999999999994</v>
       </c>
       <c r="H20" s="7">
-        <v>0.297543</v>
+        <v>0.347589</v>
       </c>
       <c r="I20" s="7">
-        <v>0.6290939999999999</v>
+        <v>0.689996</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.058823999999999994</v>
+        <v>0.10308400000000001</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.0057940000000000005</v>
+        <v>0.056764999999999996</v>
       </c>
       <c r="G21" s="7">
-        <v>0.22981400000000002</v>
+        <v>0.276956</v>
       </c>
       <c r="H21" s="7">
-        <v>0.188915</v>
+        <v>0.255427</v>
       </c>
       <c r="I21" s="7">
-        <v>0.482719</v>
+        <v>0.548718</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.054415</v>
+        <v>0.073846</v>
       </c>
       <c r="F22" s="7">
-        <v>0.05474300000000001</v>
+        <v>0.086212</v>
       </c>
       <c r="G22" s="7">
-        <v>0.118035</v>
+        <v>0.150676</v>
       </c>
       <c r="H22" s="7">
-        <v>0.188573</v>
+        <v>0.223274</v>
       </c>
       <c r="I22" s="7">
-        <v>0.578678</v>
+        <v>0.6202409999999999</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.109596</v>
+        <v>0.133012</v>
       </c>
       <c r="F23" s="7">
-        <v>0.086946</v>
+        <v>0.129008</v>
       </c>
       <c r="G23" s="7">
-        <v>0.35885300000000003</v>
+        <v>0.392713</v>
       </c>
       <c r="H23" s="7">
-        <v>0.30935</v>
+        <v>0.35762</v>
       </c>
       <c r="I23" s="7">
-        <v>0.638055</v>
+        <v>0.6932980000000001</v>
       </c>
       <c r="J23" s="7">
-        <v>2.512215</v>
+        <v>2.6416939999999998</v>
       </c>
       <c r="K23" s="7">
-        <v>11.386559</v>
+        <v>11.711768</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.036611</v>
+        <v>0.06466</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.11458600000000001</v>
+        <v>-0.067843</v>
       </c>
       <c r="G24" s="7">
-        <v>0.112737</v>
+        <v>0.14660299999999998</v>
       </c>
       <c r="H24" s="7">
-        <v>0.003882</v>
+        <v>0.052536</v>
       </c>
       <c r="I24" s="7">
-        <v>0.489631</v>
+        <v>0.539364</v>
       </c>
       <c r="J24" s="7">
-        <v>3.3282749999999997</v>
+        <v>3.53805</v>
       </c>
       <c r="K24" s="7">
-        <v>16.631818</v>
+        <v>17.336339</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.11265599999999999</v>
+        <v>0.123742</v>
       </c>
       <c r="F25" s="7">
-        <v>0.114827</v>
+        <v>0.156775</v>
       </c>
       <c r="G25" s="7">
-        <v>0.401051</v>
+        <v>0.42926299999999995</v>
       </c>
       <c r="H25" s="7">
-        <v>0.352265</v>
+        <v>0.39689</v>
       </c>
       <c r="I25" s="7">
-        <v>0.626016</v>
+        <v>0.67423</v>
       </c>
       <c r="J25" s="7">
-        <v>2.140704</v>
+        <v>2.244347</v>
       </c>
       <c r="K25" s="7">
-        <v>10.185682</v>
+        <v>10.439646</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.07629</v>
+        <v>0.08734600000000001</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.0139</v>
+        <v>0.016733</v>
       </c>
       <c r="G26" s="7">
-        <v>0.186902</v>
+        <v>0.21177600000000002</v>
       </c>
       <c r="H26" s="7">
-        <v>0.13430799999999998</v>
+        <v>0.16582899999999998</v>
       </c>
       <c r="I26" s="7">
-        <v>0.329229</v>
+        <v>0.356004</v>
       </c>
       <c r="J26" s="7">
-        <v>1.588616</v>
+        <v>1.66055</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.033654</v>
+        <v>-0.018417</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.073123</v>
+        <v>-0.07844999999999999</v>
       </c>
       <c r="G27" s="7">
-        <v>0.16137</v>
+        <v>0.16991900000000001</v>
       </c>
       <c r="H27" s="7">
-        <v>0.007158</v>
+        <v>0.030064</v>
       </c>
       <c r="I27" s="7">
-        <v>0.6269659999999999</v>
+        <v>0.628196</v>
       </c>
       <c r="J27" s="7">
-        <v>3.9247460000000003</v>
+        <v>4.036752</v>
       </c>
       <c r="K27" s="7">
-        <v>13.841772</v>
+        <v>14.002085</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.155296</v>
+        <v>0.15747</v>
       </c>
       <c r="F28" s="7">
-        <v>0.292621</v>
+        <v>0.31875</v>
       </c>
       <c r="G28" s="7">
-        <v>0.52618</v>
+        <v>0.534874</v>
       </c>
       <c r="H28" s="7">
-        <v>0.455587</v>
+        <v>0.468277</v>
       </c>
       <c r="I28" s="7">
-        <v>0.860611</v>
+        <v>0.8760460000000001</v>
       </c>
       <c r="J28" s="7">
-        <v>2.6546760000000003</v>
+        <v>2.686536</v>
       </c>
       <c r="K28" s="7">
-        <v>7.767258000000001</v>
+        <v>7.817601</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.139823</v>
+        <v>0.120334</v>
       </c>
       <c r="F29" s="7">
-        <v>0.220853</v>
+        <v>0.208146</v>
       </c>
       <c r="G29" s="7">
-        <v>0.455778</v>
+        <v>0.441243</v>
       </c>
       <c r="H29" s="7">
-        <v>0.392432</v>
+        <v>0.378919</v>
       </c>
       <c r="I29" s="7">
-        <v>0.828896</v>
+        <v>0.8137220000000001</v>
       </c>
       <c r="J29" s="7">
-        <v>2.952133</v>
+        <v>2.913777</v>
       </c>
       <c r="K29" s="7">
-        <v>11.796821</v>
+        <v>11.560315000000001</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.13430899999999998</v>
+        <v>0.14489000000000002</v>
       </c>
       <c r="F30" s="7">
-        <v>0.180455</v>
+        <v>0.203536</v>
       </c>
       <c r="G30" s="7">
-        <v>0.431248</v>
+        <v>0.45002699999999995</v>
       </c>
       <c r="H30" s="7">
-        <v>0.42770800000000003</v>
+        <v>0.459593</v>
       </c>
       <c r="I30" s="7">
-        <v>0.739451</v>
+        <v>0.77414</v>
       </c>
       <c r="J30" s="7">
-        <v>2.563392</v>
+        <v>2.6429750000000003</v>
       </c>
       <c r="K30" s="7">
-        <v>12.223014000000001</v>
+        <v>12.375315</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.213232</v>
+        <v>0.322474</v>
       </c>
       <c r="F31" s="7">
-        <v>0.412971</v>
+        <v>0.554384</v>
       </c>
       <c r="G31" s="7">
-        <v>0.49870600000000004</v>
+        <v>0.6460980000000001</v>
       </c>
       <c r="H31" s="7">
-        <v>0.56074</v>
+        <v>0.715038</v>
       </c>
       <c r="I31" s="7">
-        <v>0.720437</v>
+        <v>0.853003</v>
       </c>
       <c r="J31" s="7">
-        <v>3.5828840000000004</v>
+        <v>4.035958</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.109361</v>
+        <v>0.128994</v>
       </c>
       <c r="F32" s="7">
-        <v>0.161434</v>
+        <v>0.20108</v>
       </c>
       <c r="G32" s="7">
-        <v>0.439465</v>
+        <v>0.469491</v>
       </c>
       <c r="H32" s="7">
-        <v>0.421032</v>
+        <v>0.46720999999999996</v>
       </c>
       <c r="I32" s="7">
-        <v>0.6261099999999999</v>
+        <v>0.685689</v>
       </c>
       <c r="J32" s="7">
-        <v>1.8771209999999998</v>
+        <v>1.970616</v>
       </c>
       <c r="K32" s="7">
-        <v>9.166574</v>
+        <v>9.404513</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.074123</v>
+        <v>0.09180999999999999</v>
       </c>
       <c r="F33" s="7">
-        <v>0.032462</v>
+        <v>0.06765</v>
       </c>
       <c r="G33" s="7">
-        <v>0.28623899999999997</v>
+        <v>0.311756</v>
       </c>
       <c r="H33" s="7">
-        <v>0.24314699999999997</v>
+        <v>0.285787</v>
       </c>
       <c r="I33" s="7">
-        <v>0.553934</v>
+        <v>0.61389</v>
       </c>
       <c r="J33" s="7">
-        <v>2.508596</v>
+        <v>2.62894</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.032216999999999996</v>
+        <v>0.032176</v>
       </c>
       <c r="F34" s="7">
-        <v>0.09635300000000001</v>
+        <v>0.09573000000000001</v>
       </c>
       <c r="G34" s="7">
-        <v>0.204767</v>
+        <v>0.204976</v>
       </c>
       <c r="H34" s="7">
-        <v>0.13414099999999998</v>
+        <v>0.13553800000000002</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.092963</v>
+        <v>0.111936</v>
       </c>
       <c r="F35" s="7">
-        <v>0.041391</v>
+        <v>0.078969</v>
       </c>
       <c r="G35" s="7">
-        <v>0.29913900000000004</v>
+        <v>0.318213</v>
       </c>
       <c r="H35" s="7">
-        <v>0.257162</v>
+        <v>0.297135</v>
       </c>
       <c r="I35" s="7">
-        <v>0.584383</v>
+        <v>0.634761</v>
       </c>
       <c r="J35" s="7">
-        <v>2.531063</v>
+        <v>2.643338</v>
       </c>
       <c r="K35" s="7">
-        <v>9.826162</v>
+        <v>10.132075</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.032612999999999996</v>
+        <v>0.033446</v>
       </c>
       <c r="F36" s="7">
-        <v>0.09622299999999999</v>
+        <v>0.096586</v>
       </c>
       <c r="G36" s="7">
-        <v>0.206206</v>
+        <v>0.206413</v>
       </c>
       <c r="H36" s="7">
-        <v>0.13553800000000002</v>
+        <v>0.136935</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>07.05.2026 18:21:20</t>
+    <t>08.05.2026 18:18:40</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.081401</v>
+        <v>0.098729</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.058811999999999996</v>
+        <v>-0.060365</v>
       </c>
       <c r="G6" s="7">
-        <v>0.156727</v>
+        <v>0.187102</v>
       </c>
       <c r="H6" s="7">
-        <v>0.068062</v>
+        <v>0.0663</v>
       </c>
       <c r="I6" s="7">
-        <v>0.55168</v>
+        <v>0.553594</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.146973</v>
+        <v>0.15201399999999998</v>
       </c>
       <c r="F7" s="7">
-        <v>0.194604</v>
+        <v>0.18763300000000002</v>
       </c>
       <c r="G7" s="7">
-        <v>0.43674799999999997</v>
+        <v>0.451111</v>
       </c>
       <c r="H7" s="7">
-        <v>0.4521</v>
+        <v>0.443626</v>
       </c>
       <c r="I7" s="7">
-        <v>0.759375</v>
+        <v>0.7569509999999999</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.133333</v>
+        <v>0.146308</v>
       </c>
       <c r="F8" s="7">
-        <v>0.122859</v>
+        <v>0.12231600000000001</v>
       </c>
       <c r="G8" s="7">
-        <v>0.38299300000000003</v>
+        <v>0.412107</v>
       </c>
       <c r="H8" s="7">
-        <v>0.35176699999999994</v>
+        <v>0.351113</v>
       </c>
       <c r="I8" s="7">
-        <v>0.68888</v>
+        <v>0.70268</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.031364</v>
+        <v>0.034232</v>
       </c>
       <c r="F9" s="7">
-        <v>0.09315799999999999</v>
+        <v>0.097797</v>
       </c>
       <c r="G9" s="7">
-        <v>0.19932099999999997</v>
+        <v>0.203135</v>
       </c>
       <c r="H9" s="7">
-        <v>0.132559</v>
+        <v>0.137365</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.12319100000000001</v>
+        <v>0.139005</v>
       </c>
       <c r="F10" s="7">
         <v>0.223688</v>
       </c>
       <c r="G10" s="7">
-        <v>0.206601</v>
+        <v>0.229227</v>
       </c>
       <c r="H10" s="7">
         <v>0.315571</v>
       </c>
       <c r="I10" s="7">
-        <v>0.569453</v>
+        <v>0.580873</v>
       </c>
       <c r="J10" s="7">
         <v>1.434059</v>
       </c>
       <c r="K10" s="7">
-        <v>7.728191000000001</v>
+        <v>7.625227</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.00043499999999999995</v>
+        <v>0.021911</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.063925</v>
+        <v>-0.050489</v>
       </c>
       <c r="G11" s="7">
-        <v>0.21898199999999998</v>
+        <v>0.230737</v>
       </c>
       <c r="H11" s="7">
-        <v>0.076311</v>
+        <v>0.09176000000000001</v>
       </c>
       <c r="I11" s="7">
-        <v>0.588585</v>
+        <v>0.612725</v>
       </c>
       <c r="J11" s="7">
-        <v>3.76971</v>
+        <v>3.8381740000000004</v>
       </c>
       <c r="K11" s="7">
-        <v>12.520347999999998</v>
+        <v>12.701528000000001</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.076596</v>
+        <v>0.164552</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.023509000000000002</v>
+        <v>0.030526</v>
       </c>
       <c r="G12" s="7">
-        <v>0.71536</v>
+        <v>0.7882370000000001</v>
       </c>
       <c r="H12" s="7">
-        <v>0.08245799999999999</v>
+        <v>0.14235699999999998</v>
       </c>
       <c r="I12" s="7">
-        <v>1.6873310000000001</v>
+        <v>1.870407</v>
       </c>
       <c r="J12" s="7">
-        <v>5.262376000000001</v>
+        <v>5.608911000000001</v>
       </c>
       <c r="K12" s="7">
-        <v>13.740466</v>
+        <v>14.682401</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.015576000000000001</v>
+        <v>0.015085999999999999</v>
       </c>
       <c r="F13" s="7">
-        <v>0.039235</v>
+        <v>0.03948</v>
       </c>
       <c r="G13" s="7">
-        <v>0.07481600000000001</v>
+        <v>0.071537</v>
       </c>
       <c r="H13" s="7">
-        <v>0.054754</v>
+        <v>0.055002</v>
       </c>
       <c r="I13" s="7">
-        <v>0.171689</v>
+        <v>0.172939</v>
       </c>
       <c r="J13" s="7">
-        <v>1.105734</v>
+        <v>1.106231</v>
       </c>
       <c r="K13" s="7">
-        <v>4.350335</v>
+        <v>4.389016</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.010708</v>
+        <v>0.016713</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.100503</v>
+        <v>-0.08291499999999999</v>
       </c>
       <c r="G14" s="7">
-        <v>0.154839</v>
+        <v>0.17175</v>
       </c>
       <c r="H14" s="7">
-        <v>0.017044999999999998</v>
+        <v>0.036932</v>
       </c>
       <c r="I14" s="7">
-        <v>0.625426</v>
+        <v>0.6670470000000001</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>0.006646</v>
+        <v>0.038668999999999995</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.104727</v>
+        <v>0.148857</v>
       </c>
       <c r="F17" s="7">
-        <v>0.029233</v>
+        <v>0.048975</v>
       </c>
       <c r="G17" s="7">
-        <v>0.25858899999999996</v>
+        <v>0.302687</v>
       </c>
       <c r="H17" s="7">
-        <v>0.244149</v>
+        <v>0.268013</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030834999999999998</v>
+        <v>0.032824</v>
       </c>
       <c r="F18" s="7">
-        <v>0.09281800000000001</v>
+        <v>0.09615800000000001</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.135996</v>
+        <v>0.13946899999999998</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.171375</v>
+        <v>0.16443100000000002</v>
       </c>
       <c r="F19" s="7">
-        <v>0.277251</v>
+        <v>0.263372</v>
       </c>
       <c r="G19" s="7">
-        <v>0.5328050000000001</v>
+        <v>0.539286</v>
       </c>
       <c r="H19" s="7">
-        <v>0.518921</v>
+        <v>0.5024150000000001</v>
       </c>
       <c r="I19" s="7">
-        <v>0.926474</v>
+        <v>0.918766</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.131975</v>
+        <v>0.152411</v>
       </c>
       <c r="F20" s="7">
-        <v>0.133708</v>
+        <v>0.134473</v>
       </c>
       <c r="G20" s="7">
-        <v>0.38281999999999994</v>
+        <v>0.407853</v>
       </c>
       <c r="H20" s="7">
-        <v>0.347589</v>
+        <v>0.348499</v>
       </c>
       <c r="I20" s="7">
-        <v>0.689996</v>
+        <v>0.702144</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.10308400000000001</v>
+        <v>0.112469</v>
       </c>
       <c r="F21" s="7">
-        <v>0.056764999999999996</v>
+        <v>0.06143099999999999</v>
       </c>
       <c r="G21" s="7">
-        <v>0.276956</v>
+        <v>0.30622</v>
       </c>
       <c r="H21" s="7">
-        <v>0.255427</v>
+        <v>0.26097000000000004</v>
       </c>
       <c r="I21" s="7">
-        <v>0.548718</v>
+        <v>0.5766680000000001</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.073846</v>
+        <v>0.110694</v>
       </c>
       <c r="F22" s="7">
-        <v>0.086212</v>
+        <v>0.105509</v>
       </c>
       <c r="G22" s="7">
-        <v>0.150676</v>
+        <v>0.190748</v>
       </c>
       <c r="H22" s="7">
-        <v>0.223274</v>
+        <v>0.245005</v>
       </c>
       <c r="I22" s="7">
-        <v>0.6202409999999999</v>
+        <v>0.661366</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.133012</v>
+        <v>0.148301</v>
       </c>
       <c r="F23" s="7">
-        <v>0.129008</v>
+        <v>0.125978</v>
       </c>
       <c r="G23" s="7">
-        <v>0.392713</v>
+        <v>0.4105</v>
       </c>
       <c r="H23" s="7">
-        <v>0.35762</v>
+        <v>0.353977</v>
       </c>
       <c r="I23" s="7">
-        <v>0.6932980000000001</v>
+        <v>0.6977540000000001</v>
       </c>
       <c r="J23" s="7">
-        <v>2.6416939999999998</v>
+        <v>2.6319220000000003</v>
       </c>
       <c r="K23" s="7">
-        <v>11.711768</v>
+        <v>11.542182</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.06466</v>
+        <v>0.10329100000000001</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.067843</v>
+        <v>-0.055008</v>
       </c>
       <c r="G24" s="7">
-        <v>0.14660299999999998</v>
+        <v>0.1875</v>
       </c>
       <c r="H24" s="7">
-        <v>0.052536</v>
+        <v>0.06702899999999999</v>
       </c>
       <c r="I24" s="7">
-        <v>0.539364</v>
+        <v>0.563519</v>
       </c>
       <c r="J24" s="7">
-        <v>3.53805</v>
+        <v>3.600536</v>
       </c>
       <c r="K24" s="7">
-        <v>17.336339</v>
+        <v>17.067484999999998</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.123742</v>
+        <v>0.156623</v>
       </c>
       <c r="F25" s="7">
-        <v>0.156775</v>
+        <v>0.166013</v>
       </c>
       <c r="G25" s="7">
-        <v>0.42926299999999995</v>
+        <v>0.462943</v>
       </c>
       <c r="H25" s="7">
-        <v>0.39689</v>
+        <v>0.408046</v>
       </c>
       <c r="I25" s="7">
-        <v>0.67423</v>
+        <v>0.705569</v>
       </c>
       <c r="J25" s="7">
-        <v>2.244347</v>
+        <v>2.270258</v>
       </c>
       <c r="K25" s="7">
-        <v>10.439646</v>
+        <v>10.386003</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.08734600000000001</v>
+        <v>0.130849</v>
       </c>
       <c r="F26" s="7">
-        <v>0.016733</v>
+        <v>0.039841</v>
       </c>
       <c r="G26" s="7">
-        <v>0.21177600000000002</v>
+        <v>0.256015</v>
       </c>
       <c r="H26" s="7">
-        <v>0.16582899999999998</v>
+        <v>0.19232500000000002</v>
       </c>
       <c r="I26" s="7">
-        <v>0.356004</v>
+        <v>0.437225</v>
       </c>
       <c r="J26" s="7">
-        <v>1.66055</v>
+        <v>1.721018</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.018417</v>
+        <v>0.013523</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.07844999999999999</v>
+        <v>-0.064041</v>
       </c>
       <c r="G27" s="7">
-        <v>0.16991900000000001</v>
+        <v>0.182443</v>
       </c>
       <c r="H27" s="7">
-        <v>0.030064</v>
+        <v>0.04617</v>
       </c>
       <c r="I27" s="7">
-        <v>0.628196</v>
+        <v>0.6683790000000001</v>
       </c>
       <c r="J27" s="7">
-        <v>4.036752</v>
+        <v>4.115506</v>
       </c>
       <c r="K27" s="7">
-        <v>14.002085</v>
+        <v>14.176532</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.15747</v>
+        <v>0.19032</v>
       </c>
       <c r="F28" s="7">
-        <v>0.31875</v>
+        <v>0.338235</v>
       </c>
       <c r="G28" s="7">
-        <v>0.534874</v>
+        <v>0.568966</v>
       </c>
       <c r="H28" s="7">
-        <v>0.468277</v>
+        <v>0.48997100000000005</v>
       </c>
       <c r="I28" s="7">
-        <v>0.8760460000000001</v>
+        <v>0.895833</v>
       </c>
       <c r="J28" s="7">
-        <v>2.686536</v>
+        <v>2.741007</v>
       </c>
       <c r="K28" s="7">
-        <v>7.817601</v>
+        <v>7.895406</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.120334</v>
+        <v>0.154967</v>
       </c>
       <c r="F29" s="7">
-        <v>0.208146</v>
+        <v>0.23893</v>
       </c>
       <c r="G29" s="7">
-        <v>0.441243</v>
+        <v>0.505178</v>
       </c>
       <c r="H29" s="7">
-        <v>0.378919</v>
+        <v>0.414054</v>
       </c>
       <c r="I29" s="7">
-        <v>0.8137220000000001</v>
+        <v>0.842254</v>
       </c>
       <c r="J29" s="7">
-        <v>2.913777</v>
+        <v>3.0135009999999998</v>
       </c>
       <c r="K29" s="7">
-        <v>11.560315000000001</v>
+        <v>11.779677999999999</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.14489000000000002</v>
+        <v>0.148148</v>
       </c>
       <c r="F30" s="7">
-        <v>0.203536</v>
+        <v>0.19447</v>
       </c>
       <c r="G30" s="7">
-        <v>0.45002699999999995</v>
+        <v>0.45539900000000005</v>
       </c>
       <c r="H30" s="7">
-        <v>0.459593</v>
+        <v>0.448598</v>
       </c>
       <c r="I30" s="7">
-        <v>0.77414</v>
+        <v>0.764312</v>
       </c>
       <c r="J30" s="7">
-        <v>2.6429750000000003</v>
+        <v>2.615532</v>
       </c>
       <c r="K30" s="7">
-        <v>12.375315</v>
+        <v>12.096421</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.322474</v>
+        <v>0.218347</v>
       </c>
       <c r="F31" s="7">
-        <v>0.554384</v>
+        <v>0.415094</v>
       </c>
       <c r="G31" s="7">
-        <v>0.6460980000000001</v>
+        <v>0.541717</v>
       </c>
       <c r="H31" s="7">
-        <v>0.715038</v>
+        <v>0.561352</v>
       </c>
       <c r="I31" s="7">
-        <v>0.853003</v>
+        <v>0.6798420000000001</v>
       </c>
       <c r="J31" s="7">
-        <v>4.035958</v>
+        <v>3.5846820000000004</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.128994</v>
+        <v>0.158071</v>
       </c>
       <c r="F32" s="7">
-        <v>0.20108</v>
+        <v>0.20552700000000002</v>
       </c>
       <c r="G32" s="7">
-        <v>0.469491</v>
+        <v>0.496451</v>
       </c>
       <c r="H32" s="7">
-        <v>0.46720999999999996</v>
+        <v>0.472643</v>
       </c>
       <c r="I32" s="7">
-        <v>0.685689</v>
+        <v>0.7056180000000001</v>
       </c>
       <c r="J32" s="7">
-        <v>1.970616</v>
+        <v>1.981615</v>
       </c>
       <c r="K32" s="7">
-        <v>9.404513</v>
+        <v>9.374521999999999</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.09180999999999999</v>
+        <v>0.11412900000000001</v>
       </c>
       <c r="F33" s="7">
-        <v>0.06765</v>
+        <v>0.071865</v>
       </c>
       <c r="G33" s="7">
-        <v>0.311756</v>
+        <v>0.33596</v>
       </c>
       <c r="H33" s="7">
-        <v>0.285787</v>
+        <v>0.29086300000000004</v>
       </c>
       <c r="I33" s="7">
-        <v>0.61389</v>
+        <v>0.639059</v>
       </c>
       <c r="J33" s="7">
-        <v>2.62894</v>
+        <v>2.6432659999999997</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.032176</v>
+        <v>0.035548</v>
       </c>
       <c r="F34" s="7">
-        <v>0.09573000000000001</v>
+        <v>0.09977499999999999</v>
       </c>
       <c r="G34" s="7">
-        <v>0.204976</v>
+        <v>0.205605</v>
       </c>
       <c r="H34" s="7">
-        <v>0.13553800000000002</v>
+        <v>0.13973000000000002</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.111936</v>
+        <v>0.136417</v>
       </c>
       <c r="F35" s="7">
-        <v>0.078969</v>
+        <v>0.08257099999999999</v>
       </c>
       <c r="G35" s="7">
-        <v>0.318213</v>
+        <v>0.343535</v>
       </c>
       <c r="H35" s="7">
-        <v>0.297135</v>
+        <v>0.301466</v>
       </c>
       <c r="I35" s="7">
-        <v>0.634761</v>
+        <v>0.6513100000000001</v>
       </c>
       <c r="J35" s="7">
-        <v>2.643338</v>
+        <v>2.6555009999999997</v>
       </c>
       <c r="K35" s="7">
-        <v>10.132075</v>
+        <v>10.105742</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.033446</v>
+        <v>0.03508</v>
       </c>
       <c r="F36" s="7">
-        <v>0.096586</v>
+        <v>0.10018</v>
       </c>
       <c r="G36" s="7">
-        <v>0.206413</v>
+        <v>0.206531</v>
       </c>
       <c r="H36" s="7">
-        <v>0.136935</v>
+        <v>0.140661</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>08.05.2026 18:18:40</t>
+    <t>11.05.2026 18:27:07</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.098729</v>
+        <v>-0.01665</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.060365</v>
+        <v>-0.073996</v>
       </c>
       <c r="G6" s="7">
-        <v>0.187102</v>
+        <v>0.210447</v>
       </c>
       <c r="H6" s="7">
-        <v>0.0663</v>
+        <v>0.06674000000000001</v>
       </c>
       <c r="I6" s="7">
-        <v>0.553594</v>
+        <v>0.525835</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.15201399999999998</v>
+        <v>0.059973</v>
       </c>
       <c r="F7" s="7">
-        <v>0.18763300000000002</v>
+        <v>0.188889</v>
       </c>
       <c r="G7" s="7">
-        <v>0.451111</v>
+        <v>0.481107</v>
       </c>
       <c r="H7" s="7">
-        <v>0.443626</v>
+        <v>0.458732</v>
       </c>
       <c r="I7" s="7">
-        <v>0.7569509999999999</v>
+        <v>0.702064</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.146308</v>
+        <v>0.053670999999999996</v>
       </c>
       <c r="F8" s="7">
-        <v>0.12231600000000001</v>
+        <v>0.116716</v>
       </c>
       <c r="G8" s="7">
-        <v>0.412107</v>
+        <v>0.43964</v>
       </c>
       <c r="H8" s="7">
-        <v>0.351113</v>
+        <v>0.361911</v>
       </c>
       <c r="I8" s="7">
-        <v>0.70268</v>
+        <v>0.6515869999999999</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.034232</v>
+        <v>0.029699</v>
       </c>
       <c r="F9" s="7">
-        <v>0.097797</v>
+        <v>0.096836</v>
       </c>
       <c r="G9" s="7">
-        <v>0.203135</v>
+        <v>0.20313199999999998</v>
       </c>
       <c r="H9" s="7">
-        <v>0.137365</v>
+        <v>0.138566</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.139005</v>
+        <v>0.091655</v>
       </c>
       <c r="F10" s="7">
-        <v>0.223688</v>
+        <v>0.20293</v>
       </c>
       <c r="G10" s="7">
-        <v>0.229227</v>
+        <v>0.262349</v>
       </c>
       <c r="H10" s="7">
-        <v>0.315571</v>
+        <v>0.33529400000000004</v>
       </c>
       <c r="I10" s="7">
-        <v>0.580873</v>
+        <v>0.546074</v>
       </c>
       <c r="J10" s="7">
-        <v>1.434059</v>
+        <v>1.372579</v>
       </c>
       <c r="K10" s="7">
-        <v>7.625227</v>
+        <v>7.623464</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.021911</v>
+        <v>-0.014121</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.050489</v>
+        <v>-0.072837</v>
       </c>
       <c r="G11" s="7">
-        <v>0.230737</v>
+        <v>0.19131299999999998</v>
       </c>
       <c r="H11" s="7">
-        <v>0.09176000000000001</v>
+        <v>0.078652</v>
       </c>
       <c r="I11" s="7">
-        <v>0.612725</v>
+        <v>0.6125419999999999</v>
       </c>
       <c r="J11" s="7">
-        <v>3.8381740000000004</v>
+        <v>3.6227929999999997</v>
       </c>
       <c r="K11" s="7">
-        <v>12.701528000000001</v>
+        <v>12.354973</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.164552</v>
+        <v>0.067847</v>
       </c>
       <c r="F12" s="7">
-        <v>0.030526</v>
+        <v>0.0027700000000000003</v>
       </c>
       <c r="G12" s="7">
-        <v>0.7882370000000001</v>
+        <v>0.714015</v>
       </c>
       <c r="H12" s="7">
-        <v>0.14235699999999998</v>
+        <v>0.12641</v>
       </c>
       <c r="I12" s="7">
-        <v>1.870407</v>
+        <v>1.813836</v>
       </c>
       <c r="J12" s="7">
-        <v>5.608911000000001</v>
+        <v>5.452763</v>
       </c>
       <c r="K12" s="7">
-        <v>14.682401</v>
+        <v>14.277484999999999</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.015085999999999999</v>
+        <v>0.015310999999999998</v>
       </c>
       <c r="F13" s="7">
-        <v>0.03948</v>
+        <v>0.040450999999999994</v>
       </c>
       <c r="G13" s="7">
-        <v>0.071537</v>
+        <v>0.07551999999999999</v>
       </c>
       <c r="H13" s="7">
-        <v>0.055002</v>
+        <v>0.056247</v>
       </c>
       <c r="I13" s="7">
-        <v>0.172939</v>
+        <v>0.171405</v>
       </c>
       <c r="J13" s="7">
-        <v>1.106231</v>
+        <v>1.123593</v>
       </c>
       <c r="K13" s="7">
-        <v>4.389016</v>
+        <v>4.380325</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>0.016713</v>
+        <v>-0.016349</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.08291499999999999</v>
+        <v>-0.097782</v>
       </c>
       <c r="G14" s="7">
-        <v>0.17175</v>
+        <v>0.13925</v>
       </c>
       <c r="H14" s="7">
-        <v>0.036932</v>
+        <v>0.025568</v>
       </c>
       <c r="I14" s="7">
-        <v>0.6670470000000001</v>
+        <v>0.6755629999999999</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>0.038668999999999995</v>
+        <v>0.005242</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.148857</v>
+        <v>0.071975</v>
       </c>
       <c r="F17" s="7">
-        <v>0.048975</v>
+        <v>0.040892</v>
       </c>
       <c r="G17" s="7">
-        <v>0.302687</v>
+        <v>0.32075499999999996</v>
       </c>
       <c r="H17" s="7">
-        <v>0.268013</v>
+        <v>0.284993</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.032824</v>
+        <v>0.028859</v>
       </c>
       <c r="F18" s="7">
-        <v>0.09615800000000001</v>
+        <v>0.095261</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.13946899999999998</v>
+        <v>0.140709</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.16443100000000002</v>
+        <v>0.120071</v>
       </c>
       <c r="F19" s="7">
-        <v>0.263372</v>
+        <v>0.262355</v>
       </c>
       <c r="G19" s="7">
-        <v>0.539286</v>
+        <v>0.573703</v>
       </c>
       <c r="H19" s="7">
-        <v>0.5024150000000001</v>
+        <v>0.532206</v>
       </c>
       <c r="I19" s="7">
-        <v>0.918766</v>
+        <v>0.886026</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.152411</v>
+        <v>0.057474</v>
       </c>
       <c r="F20" s="7">
-        <v>0.134473</v>
+        <v>0.121676</v>
       </c>
       <c r="G20" s="7">
-        <v>0.407853</v>
+        <v>0.435313</v>
       </c>
       <c r="H20" s="7">
-        <v>0.348499</v>
+        <v>0.356081</v>
       </c>
       <c r="I20" s="7">
-        <v>0.702144</v>
+        <v>0.64375</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.112469</v>
+        <v>0.05449</v>
       </c>
       <c r="F21" s="7">
-        <v>0.06143099999999999</v>
+        <v>0.059368</v>
       </c>
       <c r="G21" s="7">
-        <v>0.30622</v>
+        <v>0.325295</v>
       </c>
       <c r="H21" s="7">
-        <v>0.26097000000000004</v>
+        <v>0.269284</v>
       </c>
       <c r="I21" s="7">
-        <v>0.5766680000000001</v>
+        <v>0.545992</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.110694</v>
+        <v>0.06539299999999999</v>
       </c>
       <c r="F22" s="7">
-        <v>0.105509</v>
+        <v>0.08813700000000001</v>
       </c>
       <c r="G22" s="7">
-        <v>0.190748</v>
+        <v>0.21650200000000003</v>
       </c>
       <c r="H22" s="7">
-        <v>0.245005</v>
+        <v>0.250613</v>
       </c>
       <c r="I22" s="7">
-        <v>0.661366</v>
+        <v>0.635947</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.148301</v>
+        <v>0.053433</v>
       </c>
       <c r="F23" s="7">
-        <v>0.125978</v>
+        <v>0.11677</v>
       </c>
       <c r="G23" s="7">
-        <v>0.4105</v>
+        <v>0.44209200000000004</v>
       </c>
       <c r="H23" s="7">
-        <v>0.353977</v>
+        <v>0.364602</v>
       </c>
       <c r="I23" s="7">
-        <v>0.6977540000000001</v>
+        <v>0.64652</v>
       </c>
       <c r="J23" s="7">
-        <v>2.6319220000000003</v>
+        <v>2.5685930000000003</v>
       </c>
       <c r="K23" s="7">
-        <v>11.542182</v>
+        <v>11.437742</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.10329100000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.055008</v>
+        <v>-0.07837</v>
       </c>
       <c r="G24" s="7">
-        <v>0.1875</v>
+        <v>0.224636</v>
       </c>
       <c r="H24" s="7">
-        <v>0.06702899999999999</v>
+        <v>0.065217</v>
       </c>
       <c r="I24" s="7">
-        <v>0.563519</v>
+        <v>0.5318200000000001</v>
       </c>
       <c r="J24" s="7">
-        <v>3.600536</v>
+        <v>3.073634</v>
       </c>
       <c r="K24" s="7">
-        <v>17.067484999999998</v>
+        <v>16.895652</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.156623</v>
+        <v>0.06957200000000001</v>
       </c>
       <c r="F25" s="7">
-        <v>0.166013</v>
+        <v>0.153973</v>
       </c>
       <c r="G25" s="7">
-        <v>0.462943</v>
+        <v>0.49412599999999995</v>
       </c>
       <c r="H25" s="7">
-        <v>0.408046</v>
+        <v>0.418864</v>
       </c>
       <c r="I25" s="7">
-        <v>0.705569</v>
+        <v>0.654316</v>
       </c>
       <c r="J25" s="7">
-        <v>2.270258</v>
+        <v>2.244434</v>
       </c>
       <c r="K25" s="7">
-        <v>10.386003</v>
+        <v>10.294402999999999</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.130849</v>
+        <v>0.032258</v>
       </c>
       <c r="F26" s="7">
-        <v>0.039841</v>
+        <v>-0.010437</v>
       </c>
       <c r="G26" s="7">
-        <v>0.256015</v>
+        <v>0.234925</v>
       </c>
       <c r="H26" s="7">
-        <v>0.19232500000000002</v>
+        <v>0.169484</v>
       </c>
       <c r="I26" s="7">
-        <v>0.437225</v>
+        <v>0.37103700000000006</v>
       </c>
       <c r="J26" s="7">
-        <v>1.721018</v>
+        <v>1.644082</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>0.013523</v>
+        <v>-0.016327</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.064041</v>
+        <v>-0.07069399999999999</v>
       </c>
       <c r="G27" s="7">
-        <v>0.182443</v>
+        <v>0.152191</v>
       </c>
       <c r="H27" s="7">
-        <v>0.04617</v>
+        <v>0.035074999999999995</v>
       </c>
       <c r="I27" s="7">
-        <v>0.6683790000000001</v>
+        <v>0.6786629999999999</v>
       </c>
       <c r="J27" s="7">
-        <v>4.115506</v>
+        <v>3.9301060000000003</v>
       </c>
       <c r="K27" s="7">
-        <v>14.176532</v>
+        <v>13.916443</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.19032</v>
+        <v>0.072701</v>
       </c>
       <c r="F28" s="7">
-        <v>0.338235</v>
+        <v>0.33273800000000003</v>
       </c>
       <c r="G28" s="7">
-        <v>0.568966</v>
+        <v>0.620929</v>
       </c>
       <c r="H28" s="7">
-        <v>0.48997100000000005</v>
+        <v>0.528039</v>
       </c>
       <c r="I28" s="7">
-        <v>0.895833</v>
+        <v>0.885354</v>
       </c>
       <c r="J28" s="7">
-        <v>2.741007</v>
+        <v>2.883687</v>
       </c>
       <c r="K28" s="7">
-        <v>7.895406</v>
+        <v>7.969246000000001</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.154967</v>
+        <v>0.052777000000000004</v>
       </c>
       <c r="F29" s="7">
-        <v>0.23893</v>
+        <v>0.24586300000000003</v>
       </c>
       <c r="G29" s="7">
-        <v>0.505178</v>
+        <v>0.536207</v>
       </c>
       <c r="H29" s="7">
-        <v>0.414054</v>
+        <v>0.444865</v>
       </c>
       <c r="I29" s="7">
-        <v>0.842254</v>
+        <v>0.818367</v>
       </c>
       <c r="J29" s="7">
-        <v>3.0135009999999998</v>
+        <v>3.145471</v>
       </c>
       <c r="K29" s="7">
-        <v>11.779677999999999</v>
+        <v>11.832453000000001</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.148148</v>
+        <v>0.063422</v>
       </c>
       <c r="F30" s="7">
-        <v>0.19447</v>
+        <v>0.189117</v>
       </c>
       <c r="G30" s="7">
-        <v>0.45539900000000005</v>
+        <v>0.499016</v>
       </c>
       <c r="H30" s="7">
-        <v>0.448598</v>
+        <v>0.46564</v>
       </c>
       <c r="I30" s="7">
-        <v>0.764312</v>
+        <v>0.716125</v>
       </c>
       <c r="J30" s="7">
-        <v>2.615532</v>
+        <v>2.639094</v>
       </c>
       <c r="K30" s="7">
-        <v>12.096421</v>
+        <v>11.695238</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.218347</v>
+        <v>0.155556</v>
       </c>
       <c r="F31" s="7">
-        <v>0.415094</v>
+        <v>0.411203</v>
       </c>
       <c r="G31" s="7">
-        <v>0.541717</v>
+        <v>0.56438</v>
       </c>
       <c r="H31" s="7">
-        <v>0.561352</v>
+        <v>0.591967</v>
       </c>
       <c r="I31" s="7">
-        <v>0.6798420000000001</v>
+        <v>0.6594329999999999</v>
       </c>
       <c r="J31" s="7">
-        <v>3.5846820000000004</v>
+        <v>3.722121</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.158071</v>
+        <v>0.074033</v>
       </c>
       <c r="F32" s="7">
-        <v>0.20552700000000002</v>
+        <v>0.20515999999999998</v>
       </c>
       <c r="G32" s="7">
-        <v>0.496451</v>
+        <v>0.5350699999999999</v>
       </c>
       <c r="H32" s="7">
-        <v>0.472643</v>
+        <v>0.486224</v>
       </c>
       <c r="I32" s="7">
-        <v>0.7056180000000001</v>
+        <v>0.64873</v>
       </c>
       <c r="J32" s="7">
-        <v>1.981615</v>
+        <v>1.997808</v>
       </c>
       <c r="K32" s="7">
-        <v>9.374521999999999</v>
+        <v>9.284640000000001</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.11412900000000001</v>
+        <v>0.017166</v>
       </c>
       <c r="F33" s="7">
-        <v>0.071865</v>
+        <v>0.061667</v>
       </c>
       <c r="G33" s="7">
-        <v>0.33596</v>
+        <v>0.35965800000000003</v>
       </c>
       <c r="H33" s="7">
-        <v>0.29086300000000004</v>
+        <v>0.293401</v>
       </c>
       <c r="I33" s="7">
-        <v>0.639059</v>
+        <v>0.5752700000000001</v>
       </c>
       <c r="J33" s="7">
-        <v>2.6432659999999997</v>
+        <v>2.504814</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.035548</v>
+        <v>0.030289999999999997</v>
       </c>
       <c r="F34" s="7">
-        <v>0.09977499999999999</v>
+        <v>0.098699</v>
       </c>
       <c r="G34" s="7">
-        <v>0.205605</v>
+        <v>0.205321</v>
       </c>
       <c r="H34" s="7">
-        <v>0.13973000000000002</v>
+        <v>0.140661</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.136417</v>
+        <v>0.06497700000000001</v>
       </c>
       <c r="F35" s="7">
-        <v>0.08257099999999999</v>
+        <v>0.08248799999999999</v>
       </c>
       <c r="G35" s="7">
-        <v>0.343535</v>
+        <v>0.37439100000000003</v>
       </c>
       <c r="H35" s="7">
-        <v>0.301466</v>
+        <v>0.315789</v>
       </c>
       <c r="I35" s="7">
-        <v>0.6513100000000001</v>
+        <v>0.6175269999999999</v>
       </c>
       <c r="J35" s="7">
-        <v>2.6555009999999997</v>
+        <v>2.615892</v>
       </c>
       <c r="K35" s="7">
-        <v>10.105742</v>
+        <v>10.076837000000001</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.03508</v>
+        <v>0.030265</v>
       </c>
       <c r="F36" s="7">
-        <v>0.10018</v>
+        <v>0.099103</v>
       </c>
       <c r="G36" s="7">
-        <v>0.206531</v>
+        <v>0.20623899999999998</v>
       </c>
       <c r="H36" s="7">
-        <v>0.140661</v>
+        <v>0.141593</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>11.05.2026 18:27:07</t>
+    <t>12.05.2026 14:58:25</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.01665</v>
+        <v>-0.003249</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.073996</v>
+        <v>-0.070617</v>
       </c>
       <c r="G6" s="7">
-        <v>0.210447</v>
+        <v>0.258718</v>
       </c>
       <c r="H6" s="7">
-        <v>0.06674000000000001</v>
+        <v>0.081278</v>
       </c>
       <c r="I6" s="7">
-        <v>0.525835</v>
+        <v>0.546629</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.059973</v>
+        <v>0.060776000000000004</v>
       </c>
       <c r="F7" s="7">
-        <v>0.188889</v>
+        <v>0.17881599999999997</v>
       </c>
       <c r="G7" s="7">
-        <v>0.481107</v>
+        <v>0.507037</v>
       </c>
       <c r="H7" s="7">
-        <v>0.458732</v>
+        <v>0.459838</v>
       </c>
       <c r="I7" s="7">
-        <v>0.702064</v>
+        <v>0.703353</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.053670999999999996</v>
+        <v>0.056708999999999996</v>
       </c>
       <c r="F8" s="7">
-        <v>0.116716</v>
+        <v>0.110106</v>
       </c>
       <c r="G8" s="7">
-        <v>0.43964</v>
+        <v>0.47231</v>
       </c>
       <c r="H8" s="7">
-        <v>0.361911</v>
+        <v>0.36583799999999994</v>
       </c>
       <c r="I8" s="7">
-        <v>0.6515869999999999</v>
+        <v>0.6563490000000001</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.029699</v>
+        <v>0.030424000000000003</v>
       </c>
       <c r="F9" s="7">
-        <v>0.096836</v>
+        <v>0.09633900000000001</v>
       </c>
       <c r="G9" s="7">
-        <v>0.20313199999999998</v>
+        <v>0.20296</v>
       </c>
       <c r="H9" s="7">
-        <v>0.138566</v>
+        <v>0.139367</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.091655</v>
+        <v>0.137482</v>
       </c>
       <c r="F10" s="7">
-        <v>0.20293</v>
+        <v>0.24953399999999998</v>
       </c>
       <c r="G10" s="7">
-        <v>0.262349</v>
+        <v>0.374231</v>
       </c>
       <c r="H10" s="7">
-        <v>0.33529400000000004</v>
+        <v>0.391349</v>
       </c>
       <c r="I10" s="7">
-        <v>0.546074</v>
+        <v>0.610978</v>
       </c>
       <c r="J10" s="7">
-        <v>1.372579</v>
+        <v>1.272393</v>
       </c>
       <c r="K10" s="7">
-        <v>7.623464</v>
+        <v>8.087006</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.014121</v>
+        <v>-0.003423</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.072837</v>
+        <v>-0.062398999999999996</v>
       </c>
       <c r="G11" s="7">
-        <v>0.19131299999999998</v>
+        <v>0.18584499999999998</v>
       </c>
       <c r="H11" s="7">
-        <v>0.078652</v>
+        <v>0.090356</v>
       </c>
       <c r="I11" s="7">
-        <v>0.6125419999999999</v>
+        <v>0.630039</v>
       </c>
       <c r="J11" s="7">
-        <v>3.6227929999999997</v>
+        <v>3.695565</v>
       </c>
       <c r="K11" s="7">
-        <v>12.354973</v>
+        <v>12.512416</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.067847</v>
+        <v>0.11393800000000001</v>
       </c>
       <c r="F12" s="7">
-        <v>0.0027700000000000003</v>
+        <v>0.01206</v>
       </c>
       <c r="G12" s="7">
-        <v>0.714015</v>
+        <v>0.764191</v>
       </c>
       <c r="H12" s="7">
-        <v>0.12641</v>
+        <v>0.175029</v>
       </c>
       <c r="I12" s="7">
-        <v>1.813836</v>
+        <v>1.93529</v>
       </c>
       <c r="J12" s="7">
-        <v>5.452763</v>
+        <v>5.758388999999999</v>
       </c>
       <c r="K12" s="7">
-        <v>14.277484999999999</v>
+        <v>14.896652999999999</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.015310999999999998</v>
+        <v>0.013876</v>
       </c>
       <c r="F13" s="7">
-        <v>0.040450999999999994</v>
+        <v>0.04</v>
       </c>
       <c r="G13" s="7">
-        <v>0.07551999999999999</v>
+        <v>0.072911</v>
       </c>
       <c r="H13" s="7">
-        <v>0.056247</v>
+        <v>0.054754</v>
       </c>
       <c r="I13" s="7">
-        <v>0.171405</v>
+        <v>0.169749</v>
       </c>
       <c r="J13" s="7">
-        <v>1.123593</v>
+        <v>1.062689</v>
       </c>
       <c r="K13" s="7">
-        <v>4.380325</v>
+        <v>4.340222</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.016349</v>
+        <v>-0.023842</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.097782</v>
+        <v>-0.105214</v>
       </c>
       <c r="G14" s="7">
-        <v>0.13925</v>
+        <v>0.118657</v>
       </c>
       <c r="H14" s="7">
-        <v>0.025568</v>
+        <v>0.017756</v>
       </c>
       <c r="I14" s="7">
-        <v>0.6755629999999999</v>
+        <v>0.662799</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>0.005242</v>
+        <v>0.0017469999999999999</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.071975</v>
+        <v>0.058193</v>
       </c>
       <c r="F17" s="7">
-        <v>0.040892</v>
+        <v>0.025602999999999997</v>
       </c>
       <c r="G17" s="7">
-        <v>0.32075499999999996</v>
+        <v>0.341748</v>
       </c>
       <c r="H17" s="7">
-        <v>0.284993</v>
+        <v>0.268472</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.028859</v>
+        <v>0.029529999999999997</v>
       </c>
       <c r="F18" s="7">
-        <v>0.095261</v>
+        <v>0.094672</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.140709</v>
+        <v>0.141453</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.120071</v>
+        <v>0.155091</v>
       </c>
       <c r="F19" s="7">
-        <v>0.262355</v>
+        <v>0.30139299999999997</v>
       </c>
       <c r="G19" s="7">
-        <v>0.573703</v>
+        <v>0.679144</v>
       </c>
       <c r="H19" s="7">
-        <v>0.532206</v>
+        <v>0.580113</v>
       </c>
       <c r="I19" s="7">
-        <v>0.886026</v>
+        <v>0.944995</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.057474</v>
+        <v>0.061967999999999995</v>
       </c>
       <c r="F20" s="7">
-        <v>0.121676</v>
+        <v>0.10919000000000001</v>
       </c>
       <c r="G20" s="7">
-        <v>0.435313</v>
+        <v>0.469241</v>
       </c>
       <c r="H20" s="7">
-        <v>0.356081</v>
+        <v>0.36184399999999994</v>
       </c>
       <c r="I20" s="7">
-        <v>0.64375</v>
+        <v>0.650735</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.05449</v>
+        <v>0.051803999999999996</v>
       </c>
       <c r="F21" s="7">
-        <v>0.059368</v>
+        <v>0.044987000000000006</v>
       </c>
       <c r="G21" s="7">
-        <v>0.325295</v>
+        <v>0.345937</v>
       </c>
       <c r="H21" s="7">
-        <v>0.269284</v>
+        <v>0.266051</v>
       </c>
       <c r="I21" s="7">
-        <v>0.545992</v>
+        <v>0.542053</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.06539299999999999</v>
+        <v>0.064497</v>
       </c>
       <c r="F22" s="7">
-        <v>0.08813700000000001</v>
+        <v>0.08358700000000001</v>
       </c>
       <c r="G22" s="7">
-        <v>0.21650200000000003</v>
+        <v>0.24346</v>
       </c>
       <c r="H22" s="7">
-        <v>0.250613</v>
+        <v>0.24956199999999998</v>
       </c>
       <c r="I22" s="7">
-        <v>0.635947</v>
+        <v>0.634571</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.053433</v>
+        <v>0.058120000000000005</v>
       </c>
       <c r="F23" s="7">
-        <v>0.11677</v>
+        <v>0.11399</v>
       </c>
       <c r="G23" s="7">
-        <v>0.44209200000000004</v>
+        <v>0.45974800000000005</v>
       </c>
       <c r="H23" s="7">
-        <v>0.364602</v>
+        <v>0.370674</v>
       </c>
       <c r="I23" s="7">
-        <v>0.64652</v>
+        <v>0.653846</v>
       </c>
       <c r="J23" s="7">
-        <v>2.5685930000000003</v>
+        <v>2.305271</v>
       </c>
       <c r="K23" s="7">
-        <v>11.437742</v>
+        <v>11.647058999999999</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.02</v>
+        <v>-0.006905</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.07837</v>
+        <v>-0.068973</v>
       </c>
       <c r="G24" s="7">
-        <v>0.224636</v>
+        <v>0.262791</v>
       </c>
       <c r="H24" s="7">
-        <v>0.065217</v>
+        <v>0.079451</v>
       </c>
       <c r="I24" s="7">
-        <v>0.5318200000000001</v>
+        <v>0.552289</v>
       </c>
       <c r="J24" s="7">
-        <v>3.073634</v>
+        <v>2.768522</v>
       </c>
       <c r="K24" s="7">
-        <v>16.895652</v>
+        <v>17.423144999999998</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.06957200000000001</v>
+        <v>0.080785</v>
       </c>
       <c r="F25" s="7">
-        <v>0.153973</v>
+        <v>0.15307199999999999</v>
       </c>
       <c r="G25" s="7">
-        <v>0.49412599999999995</v>
+        <v>0.542182</v>
       </c>
       <c r="H25" s="7">
-        <v>0.418864</v>
+        <v>0.433739</v>
       </c>
       <c r="I25" s="7">
-        <v>0.654316</v>
+        <v>0.6716589999999999</v>
       </c>
       <c r="J25" s="7">
-        <v>2.244434</v>
+        <v>1.9849379999999999</v>
       </c>
       <c r="K25" s="7">
-        <v>10.294402999999999</v>
+        <v>10.543277</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.032258</v>
+        <v>0.054839</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.010437</v>
+        <v>0.0057669999999999996</v>
       </c>
       <c r="G26" s="7">
-        <v>0.234925</v>
+        <v>0.28867</v>
       </c>
       <c r="H26" s="7">
-        <v>0.169484</v>
+        <v>0.195066</v>
       </c>
       <c r="I26" s="7">
-        <v>0.37103700000000006</v>
+        <v>0.401028</v>
       </c>
       <c r="J26" s="7">
-        <v>1.644082</v>
+        <v>1.5280250000000002</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.016327</v>
+        <v>-0.019048</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.07069399999999999</v>
+        <v>-0.078594</v>
       </c>
       <c r="G27" s="7">
-        <v>0.152191</v>
+        <v>0.13364800000000002</v>
       </c>
       <c r="H27" s="7">
-        <v>0.035074999999999995</v>
+        <v>0.032212</v>
       </c>
       <c r="I27" s="7">
-        <v>0.6786629999999999</v>
+        <v>0.6740189999999999</v>
       </c>
       <c r="J27" s="7">
-        <v>3.9301060000000003</v>
+        <v>3.94513</v>
       </c>
       <c r="K27" s="7">
-        <v>13.916443</v>
+        <v>13.823191</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.072701</v>
+        <v>0.08132199999999999</v>
       </c>
       <c r="F28" s="7">
-        <v>0.33273800000000003</v>
+        <v>0.334397</v>
       </c>
       <c r="G28" s="7">
-        <v>0.620929</v>
+        <v>0.646107</v>
       </c>
       <c r="H28" s="7">
-        <v>0.528039</v>
+        <v>0.540319</v>
       </c>
       <c r="I28" s="7">
-        <v>0.885354</v>
+        <v>0.900505</v>
       </c>
       <c r="J28" s="7">
-        <v>2.883687</v>
+        <v>2.6950119999999997</v>
       </c>
       <c r="K28" s="7">
-        <v>7.969246000000001</v>
+        <v>8.142371</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.052777000000000004</v>
+        <v>0.059472</v>
       </c>
       <c r="F29" s="7">
-        <v>0.24586300000000003</v>
+        <v>0.250581</v>
       </c>
       <c r="G29" s="7">
-        <v>0.536207</v>
+        <v>0.565774</v>
       </c>
       <c r="H29" s="7">
-        <v>0.444865</v>
+        <v>0.454054</v>
       </c>
       <c r="I29" s="7">
-        <v>0.818367</v>
+        <v>0.829932</v>
       </c>
       <c r="J29" s="7">
-        <v>3.145471</v>
+        <v>2.903076</v>
       </c>
       <c r="K29" s="7">
-        <v>11.832453000000001</v>
+        <v>12.077297000000002</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.063422</v>
+        <v>0.061428</v>
       </c>
       <c r="F30" s="7">
-        <v>0.189117</v>
+        <v>0.18662199999999998</v>
       </c>
       <c r="G30" s="7">
-        <v>0.499016</v>
+        <v>0.519703</v>
       </c>
       <c r="H30" s="7">
-        <v>0.46564</v>
+        <v>0.462892</v>
       </c>
       <c r="I30" s="7">
-        <v>0.716125</v>
+        <v>0.7129059999999999</v>
       </c>
       <c r="J30" s="7">
-        <v>2.639094</v>
+        <v>2.360697</v>
       </c>
       <c r="K30" s="7">
-        <v>11.695238</v>
+        <v>12.134255000000001</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.155556</v>
+        <v>0.14044399999999999</v>
       </c>
       <c r="F31" s="7">
-        <v>0.411203</v>
+        <v>0.38943</v>
       </c>
       <c r="G31" s="7">
-        <v>0.56438</v>
+        <v>0.594185</v>
       </c>
       <c r="H31" s="7">
-        <v>0.591967</v>
+        <v>0.571149</v>
       </c>
       <c r="I31" s="7">
-        <v>0.6594329999999999</v>
+        <v>0.637733</v>
       </c>
       <c r="J31" s="7">
-        <v>3.722121</v>
+        <v>3.4195659999999997</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.074033</v>
+        <v>0.077117</v>
       </c>
       <c r="F32" s="7">
-        <v>0.20515999999999998</v>
+        <v>0.194712</v>
       </c>
       <c r="G32" s="7">
-        <v>0.5350699999999999</v>
+        <v>0.567115</v>
       </c>
       <c r="H32" s="7">
-        <v>0.486224</v>
+        <v>0.490493</v>
       </c>
       <c r="I32" s="7">
-        <v>0.64873</v>
+        <v>0.6534650000000001</v>
       </c>
       <c r="J32" s="7">
-        <v>1.997808</v>
+        <v>1.788182</v>
       </c>
       <c r="K32" s="7">
-        <v>9.284640000000001</v>
+        <v>9.443176</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.017166</v>
+        <v>0.01477</v>
       </c>
       <c r="F33" s="7">
-        <v>0.061667</v>
+        <v>0.054772</v>
       </c>
       <c r="G33" s="7">
-        <v>0.35965800000000003</v>
+        <v>0.380771</v>
       </c>
       <c r="H33" s="7">
-        <v>0.293401</v>
+        <v>0.290355</v>
       </c>
       <c r="I33" s="7">
-        <v>0.5752700000000001</v>
+        <v>0.571561</v>
       </c>
       <c r="J33" s="7">
-        <v>2.504814</v>
+        <v>2.225888</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.030289999999999997</v>
+        <v>0.031132</v>
       </c>
       <c r="F34" s="7">
-        <v>0.098699</v>
+        <v>0.099103</v>
       </c>
       <c r="G34" s="7">
-        <v>0.205321</v>
+        <v>0.205032</v>
       </c>
       <c r="H34" s="7">
-        <v>0.140661</v>
+        <v>0.141593</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.06497700000000001</v>
+        <v>0.062281</v>
       </c>
       <c r="F35" s="7">
-        <v>0.08248799999999999</v>
+        <v>0.066306</v>
       </c>
       <c r="G35" s="7">
-        <v>0.37439100000000003</v>
+        <v>0.392718</v>
       </c>
       <c r="H35" s="7">
-        <v>0.315789</v>
+        <v>0.312458</v>
       </c>
       <c r="I35" s="7">
-        <v>0.6175269999999999</v>
+        <v>0.613432</v>
       </c>
       <c r="J35" s="7">
-        <v>2.615892</v>
+        <v>2.319852</v>
       </c>
       <c r="K35" s="7">
-        <v>10.076837000000001</v>
+        <v>10.180477</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.030265</v>
+        <v>0.031526</v>
       </c>
       <c r="F36" s="7">
-        <v>0.099103</v>
+        <v>0.09897</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20623899999999998</v>
+        <v>0.20643699999999998</v>
       </c>
       <c r="H36" s="7">
-        <v>0.141593</v>
+        <v>0.14299</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>12.05.2026 14:58:25</t>
+    <t>13.05.2026 10:27:06</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.003249</v>
+        <v>-0.037157</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.070617</v>
+        <v>-0.156228</v>
       </c>
       <c r="G6" s="7">
-        <v>0.258718</v>
+        <v>0.20172299999999999</v>
       </c>
       <c r="H6" s="7">
-        <v>0.081278</v>
+        <v>0.044493</v>
       </c>
       <c r="I6" s="7">
-        <v>0.546629</v>
+        <v>0.427883</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.060776000000000004</v>
+        <v>0.043106</v>
       </c>
       <c r="F7" s="7">
-        <v>0.17881599999999997</v>
+        <v>0.137186</v>
       </c>
       <c r="G7" s="7">
-        <v>0.507037</v>
+        <v>0.483061</v>
       </c>
       <c r="H7" s="7">
-        <v>0.459838</v>
+        <v>0.43552</v>
       </c>
       <c r="I7" s="7">
-        <v>0.703353</v>
+        <v>0.625365</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.056708999999999996</v>
+        <v>0.032152</v>
       </c>
       <c r="F8" s="7">
-        <v>0.110106</v>
+        <v>0.046994999999999995</v>
       </c>
       <c r="G8" s="7">
-        <v>0.47231</v>
+        <v>0.42403100000000005</v>
       </c>
       <c r="H8" s="7">
-        <v>0.36583799999999994</v>
+        <v>0.33409700000000003</v>
       </c>
       <c r="I8" s="7">
-        <v>0.6563490000000001</v>
+        <v>0.55137</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.030424000000000003</v>
+        <v>0.031509999999999996</v>
       </c>
       <c r="F9" s="7">
-        <v>0.09633900000000001</v>
+        <v>0.094122</v>
       </c>
       <c r="G9" s="7">
-        <v>0.20296</v>
+        <v>0.202957</v>
       </c>
       <c r="H9" s="7">
-        <v>0.139367</v>
+        <v>0.140569</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.137482</v>
+        <v>0.150778</v>
       </c>
       <c r="F10" s="7">
-        <v>0.24953399999999998</v>
+        <v>0.26257</v>
       </c>
       <c r="G10" s="7">
-        <v>0.374231</v>
+        <v>0.391721</v>
       </c>
       <c r="H10" s="7">
-        <v>0.391349</v>
+        <v>0.40761200000000003</v>
       </c>
       <c r="I10" s="7">
-        <v>0.610978</v>
+        <v>0.592796</v>
       </c>
       <c r="J10" s="7">
-        <v>1.272393</v>
+        <v>1.3113640000000002</v>
       </c>
       <c r="K10" s="7">
-        <v>8.087006</v>
+        <v>8.230769</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.003423</v>
+        <v>-0.01626</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.062398999999999996</v>
+        <v>-0.060865999999999996</v>
       </c>
       <c r="G11" s="7">
-        <v>0.18584499999999998</v>
+        <v>0.167242</v>
       </c>
       <c r="H11" s="7">
-        <v>0.090356</v>
+        <v>0.076311</v>
       </c>
       <c r="I11" s="7">
-        <v>0.630039</v>
+        <v>0.6737040000000001</v>
       </c>
       <c r="J11" s="7">
-        <v>3.695565</v>
+        <v>3.561508</v>
       </c>
       <c r="K11" s="7">
-        <v>12.512416</v>
+        <v>12.316728000000001</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.11393800000000001</v>
+        <v>0.10730100000000001</v>
       </c>
       <c r="F12" s="7">
-        <v>0.01206</v>
+        <v>0.028425</v>
       </c>
       <c r="G12" s="7">
-        <v>0.764191</v>
+        <v>0.70625</v>
       </c>
       <c r="H12" s="7">
-        <v>0.175029</v>
+        <v>0.168028</v>
       </c>
       <c r="I12" s="7">
-        <v>1.93529</v>
+        <v>1.9638769999999999</v>
       </c>
       <c r="J12" s="7">
-        <v>5.758388999999999</v>
+        <v>5.573993000000001</v>
       </c>
       <c r="K12" s="7">
-        <v>14.896652999999999</v>
+        <v>14.785324000000001</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.013876</v>
+        <v>0.014833</v>
       </c>
       <c r="F13" s="7">
-        <v>0.04</v>
+        <v>0.039961</v>
       </c>
       <c r="G13" s="7">
-        <v>0.072911</v>
+        <v>0.076377</v>
       </c>
       <c r="H13" s="7">
-        <v>0.054754</v>
+        <v>0.05574900000000001</v>
       </c>
       <c r="I13" s="7">
-        <v>0.169749</v>
+        <v>0.171176</v>
       </c>
       <c r="J13" s="7">
-        <v>1.062689</v>
+        <v>0.9713729999999999</v>
       </c>
       <c r="K13" s="7">
-        <v>4.340222</v>
+        <v>4.323127</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.023842</v>
+        <v>-0.028610000000000003</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.105214</v>
+        <v>-0.100883</v>
       </c>
       <c r="G14" s="7">
-        <v>0.118657</v>
+        <v>0.11059200000000001</v>
       </c>
       <c r="H14" s="7">
-        <v>0.017756</v>
+        <v>0.012784</v>
       </c>
       <c r="I14" s="7">
-        <v>0.662799</v>
+        <v>0.731423</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>0.0017469999999999999</v>
+        <v>-0.009174</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.058193</v>
+        <v>0.035605000000000005</v>
       </c>
       <c r="F17" s="7">
-        <v>0.025602999999999997</v>
+        <v>-0.033929</v>
       </c>
       <c r="G17" s="7">
-        <v>0.341748</v>
+        <v>0.305502</v>
       </c>
       <c r="H17" s="7">
-        <v>0.268472</v>
+        <v>0.24139500000000003</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.029529999999999997</v>
+        <v>0.030872</v>
       </c>
       <c r="F18" s="7">
-        <v>0.094672</v>
+        <v>0.092979</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.141453</v>
+        <v>0.142941</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.155091</v>
+        <v>0.124191</v>
       </c>
       <c r="F19" s="7">
-        <v>0.30139299999999997</v>
+        <v>0.23825</v>
       </c>
       <c r="G19" s="7">
-        <v>0.679144</v>
+        <v>0.626224</v>
       </c>
       <c r="H19" s="7">
-        <v>0.580113</v>
+        <v>0.5378419999999999</v>
       </c>
       <c r="I19" s="7">
-        <v>0.944995</v>
+        <v>0.8606919999999999</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.061967999999999995</v>
+        <v>0.042809999999999994</v>
       </c>
       <c r="F20" s="7">
-        <v>0.10919000000000001</v>
+        <v>0.053776000000000004</v>
       </c>
       <c r="G20" s="7">
-        <v>0.469241</v>
+        <v>0.43242400000000003</v>
       </c>
       <c r="H20" s="7">
-        <v>0.36184399999999994</v>
+        <v>0.337276</v>
       </c>
       <c r="I20" s="7">
-        <v>0.650735</v>
+        <v>0.5475610000000001</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.051803999999999996</v>
+        <v>0.04221</v>
       </c>
       <c r="F21" s="7">
-        <v>0.044987000000000006</v>
+        <v>-0.003303</v>
       </c>
       <c r="G21" s="7">
-        <v>0.345937</v>
+        <v>0.32617199999999996</v>
       </c>
       <c r="H21" s="7">
-        <v>0.266051</v>
+        <v>0.254503</v>
       </c>
       <c r="I21" s="7">
-        <v>0.542053</v>
+        <v>0.44969299999999995</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.064497</v>
+        <v>0.047178000000000005</v>
       </c>
       <c r="F22" s="7">
-        <v>0.08358700000000001</v>
+        <v>0.056325</v>
       </c>
       <c r="G22" s="7">
-        <v>0.24346</v>
+        <v>0.227082</v>
       </c>
       <c r="H22" s="7">
-        <v>0.24956199999999998</v>
+        <v>0.22923200000000002</v>
       </c>
       <c r="I22" s="7">
-        <v>0.634571</v>
+        <v>0.571237</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.058120000000000005</v>
+        <v>0.045231</v>
       </c>
       <c r="F23" s="7">
-        <v>0.11399</v>
+        <v>0.059886</v>
       </c>
       <c r="G23" s="7">
-        <v>0.45974800000000005</v>
+        <v>0.448052</v>
       </c>
       <c r="H23" s="7">
-        <v>0.370674</v>
+        <v>0.353977</v>
       </c>
       <c r="I23" s="7">
-        <v>0.653846</v>
+        <v>0.566561</v>
       </c>
       <c r="J23" s="7">
-        <v>2.305271</v>
+        <v>2.275558</v>
       </c>
       <c r="K23" s="7">
-        <v>11.647058999999999</v>
+        <v>11.528089999999999</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.006905</v>
+        <v>-0.030476</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.068973</v>
+        <v>-0.146868</v>
       </c>
       <c r="G24" s="7">
-        <v>0.262791</v>
+        <v>0.218797</v>
       </c>
       <c r="H24" s="7">
-        <v>0.079451</v>
+        <v>0.05383</v>
       </c>
       <c r="I24" s="7">
-        <v>0.552289</v>
+        <v>0.45014200000000004</v>
       </c>
       <c r="J24" s="7">
-        <v>2.768522</v>
+        <v>2.609929</v>
       </c>
       <c r="K24" s="7">
-        <v>17.423144999999998</v>
+        <v>17.001768</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.080785</v>
+        <v>0.051478</v>
       </c>
       <c r="F25" s="7">
-        <v>0.15307199999999999</v>
+        <v>0.050675</v>
       </c>
       <c r="G25" s="7">
-        <v>0.542182</v>
+        <v>0.47832299999999994</v>
       </c>
       <c r="H25" s="7">
-        <v>0.433739</v>
+        <v>0.394861</v>
       </c>
       <c r="I25" s="7">
-        <v>0.6716589999999999</v>
+        <v>0.543007</v>
       </c>
       <c r="J25" s="7">
-        <v>1.9849379999999999</v>
+        <v>1.9881229999999999</v>
       </c>
       <c r="K25" s="7">
-        <v>10.543277</v>
+        <v>10.279387999999999</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.054839</v>
+        <v>0.044355000000000006</v>
       </c>
       <c r="F26" s="7">
-        <v>0.0057669999999999996</v>
+        <v>-0.026316000000000003</v>
       </c>
       <c r="G26" s="7">
-        <v>0.28867</v>
+        <v>0.275234</v>
       </c>
       <c r="H26" s="7">
-        <v>0.195066</v>
+        <v>0.183189</v>
       </c>
       <c r="I26" s="7">
-        <v>0.401028</v>
+        <v>0.335602</v>
       </c>
       <c r="J26" s="7">
-        <v>1.5280250000000002</v>
+        <v>1.540212</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.019048</v>
+        <v>-0.031633</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.078594</v>
+        <v>-0.080426</v>
       </c>
       <c r="G27" s="7">
-        <v>0.13364800000000002</v>
+        <v>0.11384999999999999</v>
       </c>
       <c r="H27" s="7">
-        <v>0.032212</v>
+        <v>0.018969</v>
       </c>
       <c r="I27" s="7">
-        <v>0.6740189999999999</v>
+        <v>0.7212820000000001</v>
       </c>
       <c r="J27" s="7">
-        <v>3.94513</v>
+        <v>3.809122</v>
       </c>
       <c r="K27" s="7">
-        <v>13.823191</v>
+        <v>13.588030000000002</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.08132199999999999</v>
+        <v>0.08045999999999999</v>
       </c>
       <c r="F28" s="7">
-        <v>0.334397</v>
+        <v>0.303293</v>
       </c>
       <c r="G28" s="7">
-        <v>0.646107</v>
+        <v>0.6975169999999999</v>
       </c>
       <c r="H28" s="7">
-        <v>0.540319</v>
+        <v>0.539091</v>
       </c>
       <c r="I28" s="7">
-        <v>0.900505</v>
+        <v>0.8678589999999999</v>
       </c>
       <c r="J28" s="7">
-        <v>2.6950119999999997</v>
+        <v>2.7495010000000004</v>
       </c>
       <c r="K28" s="7">
-        <v>8.142371</v>
+        <v>8.139524</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.059472</v>
+        <v>0.06734899999999999</v>
       </c>
       <c r="F29" s="7">
-        <v>0.250581</v>
+        <v>0.241127</v>
       </c>
       <c r="G29" s="7">
-        <v>0.565774</v>
+        <v>0.60545</v>
       </c>
       <c r="H29" s="7">
-        <v>0.454054</v>
+        <v>0.464865</v>
       </c>
       <c r="I29" s="7">
-        <v>0.829932</v>
+        <v>0.824302</v>
       </c>
       <c r="J29" s="7">
-        <v>2.903076</v>
+        <v>3.00769</v>
       </c>
       <c r="K29" s="7">
-        <v>12.077297000000002</v>
+        <v>12.232422</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.061428</v>
+        <v>0.039489</v>
       </c>
       <c r="F30" s="7">
-        <v>0.18662199999999998</v>
+        <v>0.132797</v>
       </c>
       <c r="G30" s="7">
-        <v>0.519703</v>
+        <v>0.47858199999999995</v>
       </c>
       <c r="H30" s="7">
-        <v>0.462892</v>
+        <v>0.432655</v>
       </c>
       <c r="I30" s="7">
-        <v>0.7129059999999999</v>
+        <v>0.629259</v>
       </c>
       <c r="J30" s="7">
-        <v>2.360697</v>
+        <v>2.353062</v>
       </c>
       <c r="K30" s="7">
-        <v>12.134255000000001</v>
+        <v>11.926587</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.14044399999999999</v>
+        <v>0.108889</v>
       </c>
       <c r="F31" s="7">
-        <v>0.38943</v>
+        <v>0.318432</v>
       </c>
       <c r="G31" s="7">
-        <v>0.594185</v>
+        <v>0.5447</v>
       </c>
       <c r="H31" s="7">
-        <v>0.571149</v>
+        <v>0.527676</v>
       </c>
       <c r="I31" s="7">
-        <v>0.637733</v>
+        <v>0.569577</v>
       </c>
       <c r="J31" s="7">
-        <v>3.4195659999999997</v>
+        <v>3.422191</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.077117</v>
+        <v>0.048794000000000004</v>
       </c>
       <c r="F32" s="7">
-        <v>0.194712</v>
+        <v>0.12244899999999999</v>
       </c>
       <c r="G32" s="7">
-        <v>0.567115</v>
+        <v>0.513557</v>
       </c>
       <c r="H32" s="7">
-        <v>0.490493</v>
+        <v>0.45130000000000003</v>
       </c>
       <c r="I32" s="7">
-        <v>0.6534650000000001</v>
+        <v>0.535304</v>
       </c>
       <c r="J32" s="7">
-        <v>1.788182</v>
+        <v>1.763002</v>
       </c>
       <c r="K32" s="7">
-        <v>9.443176</v>
+        <v>9.196292</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.01477</v>
+        <v>-0.010778000000000001</v>
       </c>
       <c r="F33" s="7">
-        <v>0.054772</v>
+        <v>-0.009592</v>
       </c>
       <c r="G33" s="7">
-        <v>0.380771</v>
+        <v>0.33692999999999995</v>
       </c>
       <c r="H33" s="7">
-        <v>0.290355</v>
+        <v>0.257868</v>
       </c>
       <c r="I33" s="7">
-        <v>0.571561</v>
+        <v>0.45337200000000005</v>
       </c>
       <c r="J33" s="7">
-        <v>2.225888</v>
+        <v>2.168798</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.031132</v>
+        <v>0.032394</v>
       </c>
       <c r="F34" s="7">
-        <v>0.099103</v>
+        <v>0.096515</v>
       </c>
       <c r="G34" s="7">
-        <v>0.205032</v>
+        <v>0.205232</v>
       </c>
       <c r="H34" s="7">
-        <v>0.141593</v>
+        <v>0.14299</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.062281</v>
+        <v>0.032623</v>
       </c>
       <c r="F35" s="7">
-        <v>0.066306</v>
+        <v>-0.001564</v>
       </c>
       <c r="G35" s="7">
-        <v>0.392718</v>
+        <v>0.34527599999999997</v>
       </c>
       <c r="H35" s="7">
-        <v>0.312458</v>
+        <v>0.275816</v>
       </c>
       <c r="I35" s="7">
-        <v>0.613432</v>
+        <v>0.482198</v>
       </c>
       <c r="J35" s="7">
-        <v>2.319852</v>
+        <v>2.297176</v>
       </c>
       <c r="K35" s="7">
-        <v>10.180477</v>
+        <v>9.874502999999999</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.031526</v>
+        <v>0.032787000000000004</v>
       </c>
       <c r="F36" s="7">
-        <v>0.09897</v>
+        <v>0.096875</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20643699999999998</v>
+        <v>0.20663299999999998</v>
       </c>
       <c r="H36" s="7">
-        <v>0.14299</v>
+        <v>0.14438800000000002</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>13.05.2026 10:27:06</t>
+    <t>14.05.2026 21:28:17</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.037157</v>
+        <v>-0.027229</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.156228</v>
+        <v>-0.15370699999999998</v>
       </c>
       <c r="G6" s="7">
-        <v>0.20172299999999999</v>
+        <v>0.18601099999999998</v>
       </c>
       <c r="H6" s="7">
-        <v>0.044493</v>
+        <v>0.030837</v>
       </c>
       <c r="I6" s="7">
-        <v>0.427883</v>
+        <v>0.38789999999999997</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.043106</v>
+        <v>0.018734</v>
       </c>
       <c r="F7" s="7">
-        <v>0.137186</v>
+        <v>0.12173199999999999</v>
       </c>
       <c r="G7" s="7">
-        <v>0.483061</v>
+        <v>0.481013</v>
       </c>
       <c r="H7" s="7">
-        <v>0.43552</v>
+        <v>0.422623</v>
       </c>
       <c r="I7" s="7">
-        <v>0.625365</v>
+        <v>0.625684</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.032152</v>
+        <v>0.01619</v>
       </c>
       <c r="F8" s="7">
-        <v>0.046994999999999995</v>
+        <v>0.031057</v>
       </c>
       <c r="G8" s="7">
-        <v>0.42403100000000005</v>
+        <v>0.407498</v>
       </c>
       <c r="H8" s="7">
-        <v>0.33409700000000003</v>
+        <v>0.314463</v>
       </c>
       <c r="I8" s="7">
-        <v>0.55137</v>
+        <v>0.536138</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.031509999999999996</v>
+        <v>0.031848999999999995</v>
       </c>
       <c r="F9" s="7">
-        <v>0.094122</v>
+        <v>0.094434</v>
       </c>
       <c r="G9" s="7">
-        <v>0.202957</v>
+        <v>0.200674</v>
       </c>
       <c r="H9" s="7">
-        <v>0.140569</v>
+        <v>0.14177</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.150778</v>
+        <v>0.165627</v>
       </c>
       <c r="F10" s="7">
-        <v>0.26257</v>
+        <v>0.266564</v>
       </c>
       <c r="G10" s="7">
-        <v>0.391721</v>
+        <v>0.40129600000000004</v>
       </c>
       <c r="H10" s="7">
-        <v>0.40761200000000003</v>
+        <v>0.422145</v>
       </c>
       <c r="I10" s="7">
-        <v>0.592796</v>
+        <v>0.608611</v>
       </c>
       <c r="J10" s="7">
-        <v>1.3113640000000002</v>
+        <v>1.335227</v>
       </c>
       <c r="K10" s="7">
-        <v>8.230769</v>
+        <v>8.326072</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.01626</v>
+        <v>0.0021709999999999998</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.060865999999999996</v>
+        <v>-0.04113000000000001</v>
       </c>
       <c r="G11" s="7">
-        <v>0.167242</v>
+        <v>0.145978</v>
       </c>
       <c r="H11" s="7">
-        <v>0.076311</v>
+        <v>0.080524</v>
       </c>
       <c r="I11" s="7">
-        <v>0.6737040000000001</v>
+        <v>0.6748909999999999</v>
       </c>
       <c r="J11" s="7">
-        <v>3.561508</v>
+        <v>3.579365</v>
       </c>
       <c r="K11" s="7">
-        <v>12.316728000000001</v>
+        <v>12.36886</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.10730100000000001</v>
+        <v>0.182609</v>
       </c>
       <c r="F12" s="7">
-        <v>0.028425</v>
+        <v>0.126801</v>
       </c>
       <c r="G12" s="7">
-        <v>0.70625</v>
+        <v>0.7424240000000001</v>
       </c>
       <c r="H12" s="7">
-        <v>0.168028</v>
+        <v>0.216647</v>
       </c>
       <c r="I12" s="7">
-        <v>1.9638769999999999</v>
+        <v>2.0606649999999997</v>
       </c>
       <c r="J12" s="7">
-        <v>5.573993000000001</v>
+        <v>5.847636</v>
       </c>
       <c r="K12" s="7">
-        <v>14.785324000000001</v>
+        <v>15.442389</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.014833</v>
+        <v>0.015061</v>
       </c>
       <c r="F13" s="7">
-        <v>0.039961</v>
+        <v>0.038142</v>
       </c>
       <c r="G13" s="7">
-        <v>0.076377</v>
+        <v>0.075754</v>
       </c>
       <c r="H13" s="7">
-        <v>0.05574900000000001</v>
+        <v>0.056745000000000004</v>
       </c>
       <c r="I13" s="7">
-        <v>0.171176</v>
+        <v>0.17228100000000002</v>
       </c>
       <c r="J13" s="7">
-        <v>0.9713729999999999</v>
+        <v>0.973232</v>
       </c>
       <c r="K13" s="7">
-        <v>4.323127</v>
+        <v>4.328147</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.028610000000000003</v>
+        <v>-0.01832</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.100883</v>
+        <v>-0.08799</v>
       </c>
       <c r="G14" s="7">
-        <v>0.11059200000000001</v>
+        <v>0.079437</v>
       </c>
       <c r="H14" s="7">
-        <v>0.012784</v>
+        <v>0.008523</v>
       </c>
       <c r="I14" s="7">
-        <v>0.731423</v>
+        <v>0.706731</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.009174</v>
+        <v>0.0035299999999999997</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.035605000000000005</v>
+        <v>0.039768</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.033929</v>
+        <v>-0.037871</v>
       </c>
       <c r="G17" s="7">
-        <v>0.305502</v>
+        <v>0.302854</v>
       </c>
       <c r="H17" s="7">
-        <v>0.24139500000000003</v>
+        <v>0.235888</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030872</v>
+        <v>0.031299</v>
       </c>
       <c r="F18" s="7">
-        <v>0.092979</v>
+        <v>0.093387</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.142941</v>
+        <v>0.144182</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.124191</v>
+        <v>0.09804500000000001</v>
       </c>
       <c r="F19" s="7">
-        <v>0.23825</v>
+        <v>0.22413799999999998</v>
       </c>
       <c r="G19" s="7">
-        <v>0.626224</v>
+        <v>0.607776</v>
       </c>
       <c r="H19" s="7">
-        <v>0.5378419999999999</v>
+        <v>0.514895</v>
       </c>
       <c r="I19" s="7">
-        <v>0.8606919999999999</v>
+        <v>0.8244849999999999</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.042809999999999994</v>
+        <v>0.022332</v>
       </c>
       <c r="F20" s="7">
-        <v>0.053776000000000004</v>
+        <v>0.039933</v>
       </c>
       <c r="G20" s="7">
-        <v>0.43242400000000003</v>
+        <v>0.40653300000000003</v>
       </c>
       <c r="H20" s="7">
-        <v>0.337276</v>
+        <v>0.31907800000000003</v>
       </c>
       <c r="I20" s="7">
-        <v>0.5475610000000001</v>
+        <v>0.5389240000000001</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.04221</v>
+        <v>0.03268</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.003303</v>
+        <v>-0.013226</v>
       </c>
       <c r="G21" s="7">
-        <v>0.32617199999999996</v>
+        <v>0.310244</v>
       </c>
       <c r="H21" s="7">
-        <v>0.254503</v>
+        <v>0.24064699999999997</v>
       </c>
       <c r="I21" s="7">
-        <v>0.44969299999999995</v>
+        <v>0.41592</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.047178000000000005</v>
+        <v>0.045274999999999996</v>
       </c>
       <c r="F22" s="7">
-        <v>0.056325</v>
+        <v>0.024419</v>
       </c>
       <c r="G22" s="7">
-        <v>0.227082</v>
+        <v>0.215548</v>
       </c>
       <c r="H22" s="7">
-        <v>0.22923200000000002</v>
+        <v>0.205748</v>
       </c>
       <c r="I22" s="7">
-        <v>0.571237</v>
+        <v>0.518764</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.045231</v>
+        <v>0.021871</v>
       </c>
       <c r="F23" s="7">
-        <v>0.059886</v>
+        <v>0.045217</v>
       </c>
       <c r="G23" s="7">
-        <v>0.448052</v>
+        <v>0.43061900000000003</v>
       </c>
       <c r="H23" s="7">
-        <v>0.353977</v>
+        <v>0.333333</v>
       </c>
       <c r="I23" s="7">
-        <v>0.566561</v>
+        <v>0.551943</v>
       </c>
       <c r="J23" s="7">
-        <v>2.275558</v>
+        <v>2.225617</v>
       </c>
       <c r="K23" s="7">
-        <v>11.528089999999999</v>
+        <v>11.337079000000001</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.030476</v>
+        <v>-0.036618</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.146868</v>
+        <v>-0.146425</v>
       </c>
       <c r="G24" s="7">
-        <v>0.218797</v>
+        <v>0.195516</v>
       </c>
       <c r="H24" s="7">
-        <v>0.05383</v>
+        <v>0.034938</v>
       </c>
       <c r="I24" s="7">
-        <v>0.45014200000000004</v>
+        <v>0.40365</v>
       </c>
       <c r="J24" s="7">
-        <v>2.609929</v>
+        <v>2.545213</v>
       </c>
       <c r="K24" s="7">
-        <v>17.001768</v>
+        <v>16.679045000000002</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.051478</v>
+        <v>0.051764000000000004</v>
       </c>
       <c r="F25" s="7">
-        <v>0.050675</v>
+        <v>0.06743299999999999</v>
       </c>
       <c r="G25" s="7">
-        <v>0.47832299999999994</v>
+        <v>0.46222700000000005</v>
       </c>
       <c r="H25" s="7">
-        <v>0.394861</v>
+        <v>0.380663</v>
       </c>
       <c r="I25" s="7">
-        <v>0.543007</v>
+        <v>0.536494</v>
       </c>
       <c r="J25" s="7">
-        <v>1.9881229999999999</v>
+        <v>1.957706</v>
       </c>
       <c r="K25" s="7">
-        <v>10.279387999999999</v>
+        <v>10.164571</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.044355000000000006</v>
+        <v>0.027507999999999998</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.026316000000000003</v>
+        <v>-0.051885</v>
       </c>
       <c r="G26" s="7">
-        <v>0.275234</v>
+        <v>0.24509799999999998</v>
       </c>
       <c r="H26" s="7">
-        <v>0.183189</v>
+        <v>0.16034700000000002</v>
       </c>
       <c r="I26" s="7">
-        <v>0.335602</v>
+        <v>0.300164</v>
       </c>
       <c r="J26" s="7">
-        <v>1.540212</v>
+        <v>1.491173</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.031633</v>
+        <v>-0.018894</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.080426</v>
+        <v>-0.071521</v>
       </c>
       <c r="G27" s="7">
-        <v>0.11384999999999999</v>
+        <v>0.094672</v>
       </c>
       <c r="H27" s="7">
-        <v>0.018969</v>
+        <v>0.022189999999999998</v>
       </c>
       <c r="I27" s="7">
-        <v>0.7212820000000001</v>
+        <v>0.719653</v>
       </c>
       <c r="J27" s="7">
-        <v>3.809122</v>
+        <v>3.824324</v>
       </c>
       <c r="K27" s="7">
-        <v>13.588030000000002</v>
+        <v>13.634146000000001</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.08045999999999999</v>
+        <v>0.157895</v>
       </c>
       <c r="F28" s="7">
-        <v>0.303293</v>
+        <v>0.304955</v>
       </c>
       <c r="G28" s="7">
-        <v>0.6975169999999999</v>
+        <v>0.679389</v>
       </c>
       <c r="H28" s="7">
-        <v>0.539091</v>
+        <v>0.530905</v>
       </c>
       <c r="I28" s="7">
-        <v>0.8678589999999999</v>
+        <v>0.8634780000000001</v>
       </c>
       <c r="J28" s="7">
-        <v>2.7495010000000004</v>
+        <v>2.729557</v>
       </c>
       <c r="K28" s="7">
-        <v>8.139524</v>
+        <v>8.090909</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.06734899999999999</v>
+        <v>0.07177399999999999</v>
       </c>
       <c r="F29" s="7">
-        <v>0.241127</v>
+        <v>0.208182</v>
       </c>
       <c r="G29" s="7">
-        <v>0.60545</v>
+        <v>0.592093</v>
       </c>
       <c r="H29" s="7">
-        <v>0.464865</v>
+        <v>0.436757</v>
       </c>
       <c r="I29" s="7">
-        <v>0.824302</v>
+        <v>0.7911050000000001</v>
       </c>
       <c r="J29" s="7">
-        <v>3.00769</v>
+        <v>2.93079</v>
       </c>
       <c r="K29" s="7">
-        <v>12.232422</v>
+        <v>11.978515999999999</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,19 +1533,19 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.039489</v>
+        <v>0.026793</v>
       </c>
       <c r="F30" s="7">
-        <v>0.132797</v>
+        <v>0.124245</v>
       </c>
       <c r="G30" s="7">
-        <v>0.47858199999999995</v>
+        <v>0.4917</v>
       </c>
       <c r="H30" s="7">
         <v>0.432655</v>
       </c>
       <c r="I30" s="7">
-        <v>0.629259</v>
+        <v>0.638478</v>
       </c>
       <c r="J30" s="7">
         <v>2.353062</v>
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.108889</v>
+        <v>0.09694599999999999</v>
       </c>
       <c r="F31" s="7">
-        <v>0.318432</v>
+        <v>0.28314</v>
       </c>
       <c r="G31" s="7">
-        <v>0.5447</v>
+        <v>0.542196</v>
       </c>
       <c r="H31" s="7">
-        <v>0.527676</v>
+        <v>0.517267</v>
       </c>
       <c r="I31" s="7">
-        <v>0.569577</v>
+        <v>0.574733</v>
       </c>
       <c r="J31" s="7">
-        <v>3.422191</v>
+        <v>3.3920600000000003</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.048794000000000004</v>
+        <v>0.046893000000000004</v>
       </c>
       <c r="F32" s="7">
-        <v>0.12244899999999999</v>
+        <v>0.10232</v>
       </c>
       <c r="G32" s="7">
-        <v>0.513557</v>
+        <v>0.501013</v>
       </c>
       <c r="H32" s="7">
-        <v>0.45130000000000003</v>
+        <v>0.438106</v>
       </c>
       <c r="I32" s="7">
-        <v>0.535304</v>
+        <v>0.525731</v>
       </c>
       <c r="J32" s="7">
-        <v>1.763002</v>
+        <v>1.737884</v>
       </c>
       <c r="K32" s="7">
-        <v>9.196292</v>
+        <v>9.103599</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.010778000000000001</v>
+        <v>-0.011215999999999999</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.009592</v>
+        <v>-0.01575</v>
       </c>
       <c r="G33" s="7">
-        <v>0.33692999999999995</v>
+        <v>0.332164</v>
       </c>
       <c r="H33" s="7">
-        <v>0.257868</v>
+        <v>0.253046</v>
       </c>
       <c r="I33" s="7">
-        <v>0.45337200000000005</v>
+        <v>0.445681</v>
       </c>
       <c r="J33" s="7">
-        <v>2.168798</v>
+        <v>2.15665</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.032394</v>
+        <v>0.032787000000000004</v>
       </c>
       <c r="F34" s="7">
-        <v>0.096515</v>
+        <v>0.096875</v>
       </c>
       <c r="G34" s="7">
-        <v>0.205232</v>
+        <v>0.20543</v>
       </c>
       <c r="H34" s="7">
-        <v>0.14299</v>
+        <v>0.14438800000000002</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,19 +1698,19 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.032623</v>
+        <v>0.036816</v>
       </c>
       <c r="F35" s="7">
-        <v>-0.001564</v>
+        <v>-0.0013039999999999998</v>
       </c>
       <c r="G35" s="7">
-        <v>0.34527599999999997</v>
+        <v>0.346695</v>
       </c>
       <c r="H35" s="7">
         <v>0.275816</v>
       </c>
       <c r="I35" s="7">
-        <v>0.482198</v>
+        <v>0.479907</v>
       </c>
       <c r="J35" s="7">
         <v>2.297176</v>
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.032787000000000004</v>
+        <v>0.032759</v>
       </c>
       <c r="F36" s="7">
-        <v>0.096875</v>
+        <v>0.096789</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20663299999999998</v>
+        <v>0.20634</v>
       </c>
       <c r="H36" s="7">
-        <v>0.14438800000000002</v>
+        <v>0.145319</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>14.05.2026 21:28:17</t>
+    <t>15.05.2026 18:50:41</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.027229</v>
+        <v>-0.034328</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.15370699999999998</v>
+        <v>-0.145389</v>
       </c>
       <c r="G6" s="7">
-        <v>0.18601099999999998</v>
+        <v>0.202545</v>
       </c>
       <c r="H6" s="7">
-        <v>0.030837</v>
+        <v>0.040969</v>
       </c>
       <c r="I6" s="7">
-        <v>0.38789999999999997</v>
+        <v>0.394923</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.018734</v>
+        <v>0.020959</v>
       </c>
       <c r="F7" s="7">
-        <v>0.12173199999999999</v>
+        <v>0.132191</v>
       </c>
       <c r="G7" s="7">
-        <v>0.481013</v>
+        <v>0.516933</v>
       </c>
       <c r="H7" s="7">
-        <v>0.422623</v>
+        <v>0.435888</v>
       </c>
       <c r="I7" s="7">
-        <v>0.625684</v>
+        <v>0.6505719999999999</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.01619</v>
+        <v>0.024605000000000002</v>
       </c>
       <c r="F8" s="7">
-        <v>0.031057</v>
+        <v>0.047485</v>
       </c>
       <c r="G8" s="7">
-        <v>0.407498</v>
+        <v>0.43899900000000003</v>
       </c>
       <c r="H8" s="7">
-        <v>0.314463</v>
+        <v>0.335406</v>
       </c>
       <c r="I8" s="7">
-        <v>0.536138</v>
+        <v>0.562404</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.031848999999999995</v>
+        <v>0.034346</v>
       </c>
       <c r="F9" s="7">
-        <v>0.094434</v>
+        <v>0.098273</v>
       </c>
       <c r="G9" s="7">
-        <v>0.200674</v>
+        <v>0.203618</v>
       </c>
       <c r="H9" s="7">
-        <v>0.14177</v>
+        <v>0.14577500000000002</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.165627</v>
+        <v>0.151959</v>
       </c>
       <c r="F10" s="7">
-        <v>0.266564</v>
+        <v>0.259168</v>
       </c>
       <c r="G10" s="7">
-        <v>0.40129600000000004</v>
+        <v>0.381806</v>
       </c>
       <c r="H10" s="7">
-        <v>0.422145</v>
+        <v>0.41384099999999996</v>
       </c>
       <c r="I10" s="7">
-        <v>0.608611</v>
+        <v>0.603611</v>
       </c>
       <c r="J10" s="7">
-        <v>1.335227</v>
+        <v>1.321591</v>
       </c>
       <c r="K10" s="7">
-        <v>8.326072</v>
+        <v>8.271613</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.0021709999999999998</v>
+        <v>-0.017123</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.04113000000000001</v>
+        <v>-0.046115</v>
       </c>
       <c r="G11" s="7">
-        <v>0.145978</v>
+        <v>0.16312100000000002</v>
       </c>
       <c r="H11" s="7">
-        <v>0.080524</v>
+        <v>0.074906</v>
       </c>
       <c r="I11" s="7">
-        <v>0.6748909999999999</v>
+        <v>0.6942149999999999</v>
       </c>
       <c r="J11" s="7">
-        <v>3.579365</v>
+        <v>3.555556</v>
       </c>
       <c r="K11" s="7">
-        <v>12.36886</v>
+        <v>12.299351</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.182609</v>
+        <v>0.083571</v>
       </c>
       <c r="F12" s="7">
-        <v>0.126801</v>
+        <v>0.09293900000000001</v>
       </c>
       <c r="G12" s="7">
-        <v>0.7424240000000001</v>
+        <v>0.7521370000000001</v>
       </c>
       <c r="H12" s="7">
-        <v>0.216647</v>
+        <v>0.18008600000000002</v>
       </c>
       <c r="I12" s="7">
-        <v>2.0606649999999997</v>
+        <v>2.031575</v>
       </c>
       <c r="J12" s="7">
-        <v>5.847636</v>
+        <v>5.641856000000001</v>
       </c>
       <c r="K12" s="7">
-        <v>15.442389</v>
+        <v>14.948276</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.015061</v>
+        <v>0.017733000000000002</v>
       </c>
       <c r="F13" s="7">
-        <v>0.038142</v>
+        <v>0.038386</v>
       </c>
       <c r="G13" s="7">
-        <v>0.075754</v>
+        <v>0.074646</v>
       </c>
       <c r="H13" s="7">
-        <v>0.056745000000000004</v>
+        <v>0.056993999999999996</v>
       </c>
       <c r="I13" s="7">
-        <v>0.17228100000000002</v>
+        <v>0.17352900000000002</v>
       </c>
       <c r="J13" s="7">
-        <v>0.973232</v>
+        <v>0.973696</v>
       </c>
       <c r="K13" s="7">
-        <v>4.328147</v>
+        <v>4.329401</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.01832</v>
+        <v>-0.035518999999999995</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.08799</v>
+        <v>-0.09312799999999999</v>
       </c>
       <c r="G14" s="7">
-        <v>0.079437</v>
+        <v>0.08699</v>
       </c>
       <c r="H14" s="7">
-        <v>0.008523</v>
+        <v>0.002841</v>
       </c>
       <c r="I14" s="7">
-        <v>0.706731</v>
+        <v>0.721951</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>0.0035299999999999997</v>
+        <v>-0.012675</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.039768</v>
+        <v>0.033105</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.037871</v>
+        <v>-0.030011</v>
       </c>
       <c r="G17" s="7">
-        <v>0.302854</v>
+        <v>0.317322</v>
       </c>
       <c r="H17" s="7">
-        <v>0.235888</v>
+        <v>0.245984</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.031299</v>
+        <v>0.033274</v>
       </c>
       <c r="F18" s="7">
-        <v>0.093387</v>
+        <v>0.096705</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.144182</v>
+        <v>0.147654</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.09804500000000001</v>
+        <v>0.099162</v>
       </c>
       <c r="F19" s="7">
-        <v>0.22413799999999998</v>
+        <v>0.236825</v>
       </c>
       <c r="G19" s="7">
-        <v>0.607776</v>
+        <v>0.6448189999999999</v>
       </c>
       <c r="H19" s="7">
-        <v>0.514895</v>
+        <v>0.5305960000000001</v>
       </c>
       <c r="I19" s="7">
-        <v>0.8244849999999999</v>
+        <v>0.8384910000000001</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.022332</v>
+        <v>0.017899</v>
       </c>
       <c r="F20" s="7">
-        <v>0.039933</v>
+        <v>0.047107</v>
       </c>
       <c r="G20" s="7">
-        <v>0.40653300000000003</v>
+        <v>0.434797</v>
       </c>
       <c r="H20" s="7">
-        <v>0.31907800000000003</v>
+        <v>0.328177</v>
       </c>
       <c r="I20" s="7">
-        <v>0.5389240000000001</v>
+        <v>0.553388</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.03268</v>
+        <v>0.023909</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.013226</v>
+        <v>-0.008817</v>
       </c>
       <c r="G21" s="7">
-        <v>0.310244</v>
+        <v>0.325473</v>
       </c>
       <c r="H21" s="7">
-        <v>0.24064699999999997</v>
+        <v>0.246189</v>
       </c>
       <c r="I21" s="7">
-        <v>0.41592</v>
+        <v>0.435106</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.045274999999999996</v>
+        <v>0.033591</v>
       </c>
       <c r="F22" s="7">
-        <v>0.024419</v>
+        <v>0.035438</v>
       </c>
       <c r="G22" s="7">
-        <v>0.215548</v>
+        <v>0.223865</v>
       </c>
       <c r="H22" s="7">
-        <v>0.205748</v>
+        <v>0.218717</v>
       </c>
       <c r="I22" s="7">
-        <v>0.518764</v>
+        <v>0.511739</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.021871</v>
+        <v>0.014227</v>
       </c>
       <c r="F23" s="7">
-        <v>0.045217</v>
+        <v>0.051879999999999996</v>
       </c>
       <c r="G23" s="7">
-        <v>0.43061900000000003</v>
+        <v>0.450607</v>
       </c>
       <c r="H23" s="7">
-        <v>0.333333</v>
+        <v>0.34183399999999997</v>
       </c>
       <c r="I23" s="7">
-        <v>0.551943</v>
+        <v>0.563495</v>
       </c>
       <c r="J23" s="7">
-        <v>2.225617</v>
+        <v>2.246181</v>
       </c>
       <c r="K23" s="7">
-        <v>11.337079000000001</v>
+        <v>11.415730000000002</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.036618</v>
+        <v>-0.039656</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.146425</v>
+        <v>-0.141942</v>
       </c>
       <c r="G24" s="7">
-        <v>0.195516</v>
+        <v>0.20829599999999998</v>
       </c>
       <c r="H24" s="7">
-        <v>0.034938</v>
+        <v>0.040373</v>
       </c>
       <c r="I24" s="7">
-        <v>0.40365</v>
+        <v>0.403631</v>
       </c>
       <c r="J24" s="7">
-        <v>2.545213</v>
+        <v>2.56383</v>
       </c>
       <c r="K24" s="7">
-        <v>16.679045000000002</v>
+        <v>16.771883</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.051764000000000004</v>
+        <v>0.038931</v>
       </c>
       <c r="F25" s="7">
-        <v>0.06743299999999999</v>
+        <v>0.067172</v>
       </c>
       <c r="G25" s="7">
-        <v>0.46222700000000005</v>
+        <v>0.463966</v>
       </c>
       <c r="H25" s="7">
-        <v>0.380663</v>
+        <v>0.38032499999999997</v>
       </c>
       <c r="I25" s="7">
-        <v>0.536494</v>
+        <v>0.5366960000000001</v>
       </c>
       <c r="J25" s="7">
-        <v>1.957706</v>
+        <v>1.956981</v>
       </c>
       <c r="K25" s="7">
-        <v>10.164571</v>
+        <v>10.161837</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.027507999999999998</v>
+        <v>0.0204</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.051885</v>
+        <v>-0.047778999999999995</v>
       </c>
       <c r="G26" s="7">
-        <v>0.24509799999999998</v>
+        <v>0.267893</v>
       </c>
       <c r="H26" s="7">
-        <v>0.16034700000000002</v>
+        <v>0.165372</v>
       </c>
       <c r="I26" s="7">
-        <v>0.300164</v>
+        <v>0.31305299999999997</v>
       </c>
       <c r="J26" s="7">
-        <v>1.491173</v>
+        <v>1.501962</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.018894</v>
+        <v>-0.033593000000000005</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.071521</v>
+        <v>-0.07412200000000001</v>
       </c>
       <c r="G27" s="7">
-        <v>0.094672</v>
+        <v>0.10387600000000001</v>
       </c>
       <c r="H27" s="7">
-        <v>0.022189999999999998</v>
+        <v>0.019327</v>
       </c>
       <c r="I27" s="7">
-        <v>0.719653</v>
+        <v>0.7340479999999999</v>
       </c>
       <c r="J27" s="7">
-        <v>3.824324</v>
+        <v>3.8108109999999997</v>
       </c>
       <c r="K27" s="7">
-        <v>13.634146000000001</v>
+        <v>13.593154</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.157895</v>
+        <v>0.126602</v>
       </c>
       <c r="F28" s="7">
-        <v>0.304955</v>
+        <v>0.288555</v>
       </c>
       <c r="G28" s="7">
-        <v>0.679389</v>
+        <v>0.6695300000000001</v>
       </c>
       <c r="H28" s="7">
-        <v>0.530905</v>
+        <v>0.5116660000000001</v>
       </c>
       <c r="I28" s="7">
-        <v>0.8634780000000001</v>
+        <v>0.828218</v>
       </c>
       <c r="J28" s="7">
-        <v>2.729557</v>
+        <v>2.682688</v>
       </c>
       <c r="K28" s="7">
-        <v>8.090909</v>
+        <v>7.976665000000001</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.07177399999999999</v>
+        <v>0.084871</v>
       </c>
       <c r="F29" s="7">
-        <v>0.208182</v>
+        <v>0.202727</v>
       </c>
       <c r="G29" s="7">
-        <v>0.592093</v>
+        <v>0.593976</v>
       </c>
       <c r="H29" s="7">
-        <v>0.436757</v>
+        <v>0.43027</v>
       </c>
       <c r="I29" s="7">
-        <v>0.7911050000000001</v>
+        <v>0.78362</v>
       </c>
       <c r="J29" s="7">
-        <v>2.93079</v>
+        <v>2.913043</v>
       </c>
       <c r="K29" s="7">
-        <v>11.978515999999999</v>
+        <v>11.919922</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.026793</v>
+        <v>0.022665</v>
       </c>
       <c r="F30" s="7">
-        <v>0.124245</v>
+        <v>0.128991</v>
       </c>
       <c r="G30" s="7">
-        <v>0.4917</v>
+        <v>0.505321</v>
       </c>
       <c r="H30" s="7">
-        <v>0.432655</v>
+        <v>0.438703</v>
       </c>
       <c r="I30" s="7">
-        <v>0.638478</v>
+        <v>0.6537120000000001</v>
       </c>
       <c r="J30" s="7">
-        <v>2.353062</v>
+        <v>2.367216</v>
       </c>
       <c r="K30" s="7">
-        <v>11.926587</v>
+        <v>11.981151</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.09694599999999999</v>
+        <v>0.11582700000000001</v>
       </c>
       <c r="F31" s="7">
-        <v>0.28314</v>
+        <v>0.30695900000000004</v>
       </c>
       <c r="G31" s="7">
-        <v>0.542196</v>
+        <v>0.58185</v>
       </c>
       <c r="H31" s="7">
-        <v>0.517267</v>
+        <v>0.545432</v>
       </c>
       <c r="I31" s="7">
-        <v>0.574733</v>
+        <v>0.603558</v>
       </c>
       <c r="J31" s="7">
-        <v>3.3920600000000003</v>
+        <v>3.4735910000000003</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.046893000000000004</v>
+        <v>0.022407</v>
       </c>
       <c r="F32" s="7">
-        <v>0.10232</v>
+        <v>0.09934599999999999</v>
       </c>
       <c r="G32" s="7">
-        <v>0.501013</v>
+        <v>0.501829</v>
       </c>
       <c r="H32" s="7">
-        <v>0.438106</v>
+        <v>0.434226</v>
       </c>
       <c r="I32" s="7">
-        <v>0.525731</v>
+        <v>0.528536</v>
       </c>
       <c r="J32" s="7">
-        <v>1.737884</v>
+        <v>1.730496</v>
       </c>
       <c r="K32" s="7">
-        <v>9.103599</v>
+        <v>9.076336</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.011215999999999999</v>
+        <v>-0.012702999999999999</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.01575</v>
+        <v>-0.008373</v>
       </c>
       <c r="G33" s="7">
-        <v>0.332164</v>
+        <v>0.35199800000000003</v>
       </c>
       <c r="H33" s="7">
-        <v>0.253046</v>
+        <v>0.26243700000000003</v>
       </c>
       <c r="I33" s="7">
-        <v>0.445681</v>
+        <v>0.460364</v>
       </c>
       <c r="J33" s="7">
-        <v>2.15665</v>
+        <v>2.180307</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.032787000000000004</v>
+        <v>0.034845</v>
       </c>
       <c r="F34" s="7">
-        <v>0.096875</v>
+        <v>0.10044600000000001</v>
       </c>
       <c r="G34" s="7">
-        <v>0.20543</v>
+        <v>0.205533</v>
       </c>
       <c r="H34" s="7">
-        <v>0.14438800000000002</v>
+        <v>0.148114</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.036816</v>
+        <v>0.028022000000000002</v>
       </c>
       <c r="F35" s="7">
-        <v>-0.0013039999999999998</v>
+        <v>0.004433</v>
       </c>
       <c r="G35" s="7">
-        <v>0.346695</v>
+        <v>0.359689</v>
       </c>
       <c r="H35" s="7">
-        <v>0.275816</v>
+        <v>0.283145</v>
       </c>
       <c r="I35" s="7">
-        <v>0.479907</v>
+        <v>0.488983</v>
       </c>
       <c r="J35" s="7">
-        <v>2.297176</v>
+        <v>2.316116</v>
       </c>
       <c r="K35" s="7">
-        <v>9.874502999999999</v>
+        <v>9.936968</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.032759</v>
+        <v>0.034815</v>
       </c>
       <c r="F36" s="7">
-        <v>0.096789</v>
+        <v>0.100357</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20634</v>
+        <v>0.20642700000000003</v>
       </c>
       <c r="H36" s="7">
-        <v>0.145319</v>
+        <v>0.149045</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>15.05.2026 18:50:41</t>
+    <t>18.05.2026 12:24:43</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.034328</v>
+        <v>-0.097847</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.145389</v>
+        <v>-0.167269</v>
       </c>
       <c r="G6" s="7">
-        <v>0.202545</v>
+        <v>0.17243099999999997</v>
       </c>
       <c r="H6" s="7">
-        <v>0.040969</v>
+        <v>0.015419</v>
       </c>
       <c r="I6" s="7">
-        <v>0.394923</v>
+        <v>0.352303</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.020959</v>
+        <v>0.001041</v>
       </c>
       <c r="F7" s="7">
-        <v>0.132191</v>
+        <v>0.119977</v>
       </c>
       <c r="G7" s="7">
-        <v>0.516933</v>
+        <v>0.459029</v>
       </c>
       <c r="H7" s="7">
-        <v>0.435888</v>
+        <v>0.417097</v>
       </c>
       <c r="I7" s="7">
-        <v>0.6505719999999999</v>
+        <v>0.628281</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.024605000000000002</v>
+        <v>-0.032528</v>
       </c>
       <c r="F8" s="7">
-        <v>0.047485</v>
+        <v>0.027954</v>
       </c>
       <c r="G8" s="7">
-        <v>0.43899900000000003</v>
+        <v>0.39917</v>
       </c>
       <c r="H8" s="7">
-        <v>0.335406</v>
+        <v>0.323626</v>
       </c>
       <c r="I8" s="7">
-        <v>0.562404</v>
+        <v>0.554573</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.034346</v>
+        <v>0.030924</v>
       </c>
       <c r="F9" s="7">
-        <v>0.098273</v>
+        <v>0.098888</v>
       </c>
       <c r="G9" s="7">
-        <v>0.203618</v>
+        <v>0.204875</v>
       </c>
       <c r="H9" s="7">
-        <v>0.14577500000000002</v>
+        <v>0.148178</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.151959</v>
+        <v>0.091713</v>
       </c>
       <c r="F10" s="7">
-        <v>0.259168</v>
+        <v>0.20231200000000002</v>
       </c>
       <c r="G10" s="7">
-        <v>0.381806</v>
+        <v>0.29066</v>
       </c>
       <c r="H10" s="7">
-        <v>0.41384099999999996</v>
+        <v>0.36747399999999997</v>
       </c>
       <c r="I10" s="7">
-        <v>0.603611</v>
+        <v>0.541943</v>
       </c>
       <c r="J10" s="7">
-        <v>1.321591</v>
+        <v>1.4075540000000002</v>
       </c>
       <c r="K10" s="7">
-        <v>8.271613</v>
+        <v>7.884892</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.017123</v>
+        <v>-0.07104300000000001</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.046115</v>
+        <v>-0.052542</v>
       </c>
       <c r="G11" s="7">
-        <v>0.16312100000000002</v>
+        <v>0.137798</v>
       </c>
       <c r="H11" s="7">
-        <v>0.074906</v>
+        <v>0.046816</v>
       </c>
       <c r="I11" s="7">
-        <v>0.6942149999999999</v>
+        <v>0.654336</v>
       </c>
       <c r="J11" s="7">
-        <v>3.555556</v>
+        <v>3.713322</v>
       </c>
       <c r="K11" s="7">
-        <v>12.299351</v>
+        <v>11.704545000000001</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.083571</v>
+        <v>-0.043892</v>
       </c>
       <c r="F12" s="7">
-        <v>0.09293900000000001</v>
+        <v>0.08536099999999999</v>
       </c>
       <c r="G12" s="7">
-        <v>0.7521370000000001</v>
+        <v>0.622027</v>
       </c>
       <c r="H12" s="7">
-        <v>0.18008600000000002</v>
+        <v>0.09295999999999999</v>
       </c>
       <c r="I12" s="7">
-        <v>2.031575</v>
+        <v>1.8066319999999998</v>
       </c>
       <c r="J12" s="7">
-        <v>5.641856000000001</v>
+        <v>5.658768</v>
       </c>
       <c r="K12" s="7">
-        <v>14.948276</v>
+        <v>13.496492</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.017733000000000002</v>
+        <v>0.015039</v>
       </c>
       <c r="F13" s="7">
-        <v>0.038386</v>
+        <v>0.038086</v>
       </c>
       <c r="G13" s="7">
-        <v>0.074646</v>
+        <v>0.07754699999999999</v>
       </c>
       <c r="H13" s="7">
-        <v>0.056993999999999996</v>
+        <v>0.058238000000000005</v>
       </c>
       <c r="I13" s="7">
-        <v>0.17352900000000002</v>
+        <v>0.17102699999999998</v>
       </c>
       <c r="J13" s="7">
-        <v>0.973696</v>
+        <v>1.129194</v>
       </c>
       <c r="K13" s="7">
-        <v>4.329401</v>
+        <v>4.33233</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.035518999999999995</v>
+        <v>-0.08227000000000001</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.09312799999999999</v>
+        <v>-0.098615</v>
       </c>
       <c r="G14" s="7">
-        <v>0.08699</v>
+        <v>0.064667</v>
       </c>
       <c r="H14" s="7">
-        <v>0.002841</v>
+        <v>-0.029474</v>
       </c>
       <c r="I14" s="7">
-        <v>0.721951</v>
+        <v>0.666057</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.012675</v>
+        <v>-0.050427</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.033105</v>
+        <v>-0.024751</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.030011</v>
+        <v>-0.051724</v>
       </c>
       <c r="G17" s="7">
-        <v>0.317322</v>
+        <v>0.269841</v>
       </c>
       <c r="H17" s="7">
-        <v>0.245984</v>
+        <v>0.211565</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.033274</v>
+        <v>0.029758</v>
       </c>
       <c r="F18" s="7">
-        <v>0.096705</v>
+        <v>0.096996</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.147654</v>
+        <v>0.15013400000000002</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.099162</v>
+        <v>0.064873</v>
       </c>
       <c r="F19" s="7">
-        <v>0.236825</v>
+        <v>0.22642700000000002</v>
       </c>
       <c r="G19" s="7">
-        <v>0.6448189999999999</v>
+        <v>0.588422</v>
       </c>
       <c r="H19" s="7">
-        <v>0.5305960000000001</v>
+        <v>0.513285</v>
       </c>
       <c r="I19" s="7">
-        <v>0.8384910000000001</v>
+        <v>0.819898</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.017899</v>
+        <v>-0.015093</v>
       </c>
       <c r="F20" s="7">
-        <v>0.047107</v>
+        <v>0.033845</v>
       </c>
       <c r="G20" s="7">
-        <v>0.434797</v>
+        <v>0.395206</v>
       </c>
       <c r="H20" s="7">
-        <v>0.328177</v>
+        <v>0.30633900000000003</v>
       </c>
       <c r="I20" s="7">
-        <v>0.553388</v>
+        <v>0.534925</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.023909</v>
+        <v>0.001119</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.008817</v>
+        <v>-0.011049999999999999</v>
       </c>
       <c r="G21" s="7">
-        <v>0.325473</v>
+        <v>0.311035</v>
       </c>
       <c r="H21" s="7">
-        <v>0.246189</v>
+        <v>0.24018499999999998</v>
       </c>
       <c r="I21" s="7">
-        <v>0.435106</v>
+        <v>0.43391199999999996</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.033591</v>
+        <v>-0.024418000000000002</v>
       </c>
       <c r="F22" s="7">
-        <v>0.035438</v>
+        <v>0.002334</v>
       </c>
       <c r="G22" s="7">
-        <v>0.223865</v>
+        <v>0.198047</v>
       </c>
       <c r="H22" s="7">
-        <v>0.218717</v>
+        <v>0.204346</v>
       </c>
       <c r="I22" s="7">
-        <v>0.511739</v>
+        <v>0.52847</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.014227</v>
+        <v>-0.017934000000000002</v>
       </c>
       <c r="F23" s="7">
-        <v>0.051879999999999996</v>
+        <v>0.035176</v>
       </c>
       <c r="G23" s="7">
-        <v>0.450607</v>
+        <v>0.395934</v>
       </c>
       <c r="H23" s="7">
-        <v>0.34183399999999997</v>
+        <v>0.313297</v>
       </c>
       <c r="I23" s="7">
-        <v>0.563495</v>
+        <v>0.529162</v>
       </c>
       <c r="J23" s="7">
-        <v>2.246181</v>
+        <v>2.3256460000000003</v>
       </c>
       <c r="K23" s="7">
-        <v>11.415730000000002</v>
+        <v>11.036728</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.039656</v>
+        <v>-0.099634</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.141942</v>
+        <v>-0.159504</v>
       </c>
       <c r="G24" s="7">
-        <v>0.20829599999999998</v>
+        <v>0.18047999999999997</v>
       </c>
       <c r="H24" s="7">
-        <v>0.040373</v>
+        <v>0.01734</v>
       </c>
       <c r="I24" s="7">
-        <v>0.403631</v>
+        <v>0.36115</v>
       </c>
       <c r="J24" s="7">
-        <v>2.56383</v>
+        <v>3.2178109999999998</v>
       </c>
       <c r="K24" s="7">
-        <v>16.771883</v>
+        <v>16.046834</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.038931</v>
+        <v>-0.017717</v>
       </c>
       <c r="F25" s="7">
-        <v>0.067172</v>
+        <v>0.04257</v>
       </c>
       <c r="G25" s="7">
-        <v>0.463966</v>
+        <v>0.416105</v>
       </c>
       <c r="H25" s="7">
-        <v>0.38032499999999997</v>
+        <v>0.349561</v>
       </c>
       <c r="I25" s="7">
-        <v>0.5366960000000001</v>
+        <v>0.509834</v>
       </c>
       <c r="J25" s="7">
-        <v>1.956981</v>
+        <v>1.9430850000000002</v>
       </c>
       <c r="K25" s="7">
-        <v>10.161837</v>
+        <v>9.765912</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.0204</v>
+        <v>-0.0387</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.047778999999999995</v>
+        <v>-0.076237</v>
       </c>
       <c r="G26" s="7">
-        <v>0.267893</v>
+        <v>0.21052600000000002</v>
       </c>
       <c r="H26" s="7">
-        <v>0.165372</v>
+        <v>0.134765</v>
       </c>
       <c r="I26" s="7">
-        <v>0.31305299999999997</v>
+        <v>0.293211</v>
       </c>
       <c r="J26" s="7">
-        <v>1.501962</v>
+        <v>1.4711500000000002</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.033593000000000005</v>
+        <v>-0.076821</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.07412200000000001</v>
+        <v>-0.046838</v>
       </c>
       <c r="G27" s="7">
-        <v>0.10387600000000001</v>
+        <v>0.083139</v>
       </c>
       <c r="H27" s="7">
-        <v>0.019327</v>
+        <v>-0.002147</v>
       </c>
       <c r="I27" s="7">
-        <v>0.7340479999999999</v>
+        <v>0.697103</v>
       </c>
       <c r="J27" s="7">
-        <v>3.8108109999999997</v>
+        <v>3.867318</v>
       </c>
       <c r="K27" s="7">
-        <v>13.593154</v>
+        <v>13.080808</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.126602</v>
+        <v>0.083532</v>
       </c>
       <c r="F28" s="7">
-        <v>0.288555</v>
+        <v>0.24982800000000002</v>
       </c>
       <c r="G28" s="7">
-        <v>0.6695300000000001</v>
+        <v>0.6286999999999999</v>
       </c>
       <c r="H28" s="7">
-        <v>0.5116660000000001</v>
+        <v>0.486697</v>
       </c>
       <c r="I28" s="7">
-        <v>0.828218</v>
+        <v>0.7891630000000001</v>
       </c>
       <c r="J28" s="7">
-        <v>2.682688</v>
+        <v>2.490965</v>
       </c>
       <c r="K28" s="7">
-        <v>7.976665000000001</v>
+        <v>7.768711</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.084871</v>
+        <v>0.0424</v>
       </c>
       <c r="F29" s="7">
-        <v>0.202727</v>
+        <v>0.185354</v>
       </c>
       <c r="G29" s="7">
-        <v>0.593976</v>
+        <v>0.537463</v>
       </c>
       <c r="H29" s="7">
-        <v>0.43027</v>
+        <v>0.408649</v>
       </c>
       <c r="I29" s="7">
-        <v>0.78362</v>
+        <v>0.7484069999999999</v>
       </c>
       <c r="J29" s="7">
-        <v>2.913043</v>
+        <v>2.74964</v>
       </c>
       <c r="K29" s="7">
-        <v>11.919922</v>
+        <v>11.662779</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.022665</v>
+        <v>0.000385</v>
       </c>
       <c r="F30" s="7">
-        <v>0.128991</v>
+        <v>0.132882</v>
       </c>
       <c r="G30" s="7">
-        <v>0.505321</v>
+        <v>0.469989</v>
       </c>
       <c r="H30" s="7">
-        <v>0.438703</v>
+        <v>0.42715800000000004</v>
       </c>
       <c r="I30" s="7">
-        <v>0.6537120000000001</v>
+        <v>0.643038</v>
       </c>
       <c r="J30" s="7">
-        <v>2.367216</v>
+        <v>2.301119</v>
       </c>
       <c r="K30" s="7">
-        <v>11.981151</v>
+        <v>11.651072</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.11582700000000001</v>
+        <v>0.058394</v>
       </c>
       <c r="F31" s="7">
-        <v>0.30695900000000004</v>
+        <v>0.207741</v>
       </c>
       <c r="G31" s="7">
-        <v>0.58185</v>
+        <v>0.49538899999999997</v>
       </c>
       <c r="H31" s="7">
-        <v>0.545432</v>
+        <v>0.5093070000000001</v>
       </c>
       <c r="I31" s="7">
-        <v>0.603558</v>
+        <v>0.553441</v>
       </c>
       <c r="J31" s="7">
-        <v>3.4735910000000003</v>
+        <v>3.269138</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.022407</v>
+        <v>-0.018428</v>
       </c>
       <c r="F32" s="7">
-        <v>0.09934599999999999</v>
+        <v>0.077655</v>
       </c>
       <c r="G32" s="7">
-        <v>0.501829</v>
+        <v>0.45637300000000003</v>
       </c>
       <c r="H32" s="7">
-        <v>0.434226</v>
+        <v>0.40551000000000004</v>
       </c>
       <c r="I32" s="7">
-        <v>0.528536</v>
+        <v>0.512949</v>
       </c>
       <c r="J32" s="7">
-        <v>1.730496</v>
+        <v>1.674247</v>
       </c>
       <c r="K32" s="7">
-        <v>9.076336</v>
+        <v>8.799783999999999</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.012702999999999999</v>
+        <v>-0.049474</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.008373</v>
+        <v>-0.017911</v>
       </c>
       <c r="G33" s="7">
-        <v>0.35199800000000003</v>
+        <v>0.315364</v>
       </c>
       <c r="H33" s="7">
-        <v>0.26243700000000003</v>
+        <v>0.238579</v>
       </c>
       <c r="I33" s="7">
-        <v>0.460364</v>
+        <v>0.442933</v>
       </c>
       <c r="J33" s="7">
-        <v>2.180307</v>
+        <v>2.344757</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.034845</v>
+        <v>0.031315</v>
       </c>
       <c r="F34" s="7">
-        <v>0.10044600000000001</v>
+        <v>0.10071300000000001</v>
       </c>
       <c r="G34" s="7">
-        <v>0.205533</v>
+        <v>0.20671399999999998</v>
       </c>
       <c r="H34" s="7">
-        <v>0.148114</v>
+        <v>0.150442</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.028022000000000002</v>
+        <v>-0.009958</v>
       </c>
       <c r="F35" s="7">
-        <v>0.004433</v>
+        <v>-0.008399</v>
       </c>
       <c r="G35" s="7">
-        <v>0.359689</v>
+        <v>0.329346</v>
       </c>
       <c r="H35" s="7">
-        <v>0.283145</v>
+        <v>0.258494</v>
       </c>
       <c r="I35" s="7">
-        <v>0.488983</v>
+        <v>0.467754</v>
       </c>
       <c r="J35" s="7">
-        <v>2.316116</v>
+        <v>2.397482</v>
       </c>
       <c r="K35" s="7">
-        <v>9.936968</v>
+        <v>9.720772</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.034815</v>
+        <v>0.031706</v>
       </c>
       <c r="F36" s="7">
-        <v>0.100357</v>
+        <v>0.10155900000000001</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20642700000000003</v>
+        <v>0.20808900000000002</v>
       </c>
       <c r="H36" s="7">
-        <v>0.149045</v>
+        <v>0.15184</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>18.05.2026 12:24:43</t>
+    <t>20.05.2026 16:09:52</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.097847</v>
+        <v>-0.10254400000000001</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.167269</v>
+        <v>-0.140555</v>
       </c>
       <c r="G6" s="7">
-        <v>0.17243099999999997</v>
+        <v>0.12099700000000001</v>
       </c>
       <c r="H6" s="7">
-        <v>0.015419</v>
+        <v>0.010132</v>
       </c>
       <c r="I6" s="7">
-        <v>0.352303</v>
+        <v>0.345263</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.001041</v>
+        <v>-0.016137</v>
       </c>
       <c r="F7" s="7">
-        <v>0.119977</v>
+        <v>0.128021</v>
       </c>
       <c r="G7" s="7">
-        <v>0.459029</v>
+        <v>0.409396</v>
       </c>
       <c r="H7" s="7">
-        <v>0.417097</v>
+        <v>0.392778</v>
       </c>
       <c r="I7" s="7">
-        <v>0.628281</v>
+        <v>0.6003390000000001</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.032528</v>
+        <v>-0.062664</v>
       </c>
       <c r="F8" s="7">
-        <v>0.027954</v>
+        <v>0.038696</v>
       </c>
       <c r="G8" s="7">
-        <v>0.39917</v>
+        <v>0.337086</v>
       </c>
       <c r="H8" s="7">
-        <v>0.323626</v>
+        <v>0.282395</v>
       </c>
       <c r="I8" s="7">
-        <v>0.554573</v>
+        <v>0.506149</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.030924</v>
+        <v>0.032003</v>
       </c>
       <c r="F9" s="7">
-        <v>0.098888</v>
+        <v>0.09542</v>
       </c>
       <c r="G9" s="7">
-        <v>0.204875</v>
+        <v>0.203607</v>
       </c>
       <c r="H9" s="7">
-        <v>0.148178</v>
+        <v>0.149379</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.091713</v>
+        <v>0.048619</v>
       </c>
       <c r="F10" s="7">
-        <v>0.20231200000000002</v>
+        <v>0.23326799999999998</v>
       </c>
       <c r="G10" s="7">
-        <v>0.29066</v>
+        <v>0.271266</v>
       </c>
       <c r="H10" s="7">
-        <v>0.36747399999999997</v>
+        <v>0.31349499999999997</v>
       </c>
       <c r="I10" s="7">
-        <v>0.541943</v>
+        <v>0.48107700000000003</v>
       </c>
       <c r="J10" s="7">
-        <v>1.4075540000000002</v>
+        <v>1.397221</v>
       </c>
       <c r="K10" s="7">
-        <v>7.884892</v>
+        <v>7.50168</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.07104300000000001</v>
+        <v>-0.07312</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.052542</v>
+        <v>-0.117484</v>
       </c>
       <c r="G11" s="7">
-        <v>0.137798</v>
+        <v>0.120655</v>
       </c>
       <c r="H11" s="7">
-        <v>0.046816</v>
+        <v>0.044476</v>
       </c>
       <c r="I11" s="7">
-        <v>0.654336</v>
+        <v>0.650636</v>
       </c>
       <c r="J11" s="7">
-        <v>3.713322</v>
+        <v>3.683039</v>
       </c>
       <c r="K11" s="7">
-        <v>11.704545000000001</v>
+        <v>11.650261</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.043892</v>
+        <v>-0.043212</v>
       </c>
       <c r="F12" s="7">
-        <v>0.08536099999999999</v>
+        <v>-0.0007109999999999999</v>
       </c>
       <c r="G12" s="7">
-        <v>0.622027</v>
+        <v>0.597001</v>
       </c>
       <c r="H12" s="7">
-        <v>0.09295999999999999</v>
+        <v>0.09373799999999999</v>
       </c>
       <c r="I12" s="7">
-        <v>1.8066319999999998</v>
+        <v>1.80863</v>
       </c>
       <c r="J12" s="7">
-        <v>5.658768</v>
+        <v>5.692051</v>
       </c>
       <c r="K12" s="7">
-        <v>13.496492</v>
+        <v>13.355728</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.015039</v>
+        <v>0.016949000000000002</v>
       </c>
       <c r="F13" s="7">
-        <v>0.038086</v>
+        <v>0.038771</v>
       </c>
       <c r="G13" s="7">
-        <v>0.07754699999999999</v>
+        <v>0.079027</v>
       </c>
       <c r="H13" s="7">
-        <v>0.058238000000000005</v>
+        <v>0.060229</v>
       </c>
       <c r="I13" s="7">
-        <v>0.17102699999999998</v>
+        <v>0.173231</v>
       </c>
       <c r="J13" s="7">
-        <v>1.129194</v>
+        <v>1.109015</v>
       </c>
       <c r="K13" s="7">
-        <v>4.33233</v>
+        <v>4.322339</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.08227000000000001</v>
+        <v>-0.08529199999999999</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.098615</v>
+        <v>-0.142047</v>
       </c>
       <c r="G14" s="7">
-        <v>0.064667</v>
+        <v>0.048095</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.029474</v>
+        <v>-0.03267</v>
       </c>
       <c r="I14" s="7">
-        <v>0.666057</v>
+        <v>0.660571</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.050427</v>
+        <v>-0.053419</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.024751</v>
+        <v>-0.045807</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.051724</v>
+        <v>-0.037989</v>
       </c>
       <c r="G17" s="7">
-        <v>0.269841</v>
+        <v>0.217822</v>
       </c>
       <c r="H17" s="7">
-        <v>0.211565</v>
+        <v>0.18540600000000002</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.029758</v>
+        <v>0.030868000000000003</v>
       </c>
       <c r="F18" s="7">
-        <v>0.096996</v>
+        <v>0.093522</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.15013400000000002</v>
+        <v>0.15137499999999998</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.064873</v>
+        <v>0.041075999999999994</v>
       </c>
       <c r="F19" s="7">
-        <v>0.22642700000000002</v>
+        <v>0.22663599999999998</v>
       </c>
       <c r="G19" s="7">
-        <v>0.588422</v>
+        <v>0.543469</v>
       </c>
       <c r="H19" s="7">
-        <v>0.513285</v>
+        <v>0.479469</v>
       </c>
       <c r="I19" s="7">
-        <v>0.819898</v>
+        <v>0.77923</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.015093</v>
+        <v>-0.031786</v>
       </c>
       <c r="F20" s="7">
-        <v>0.033845</v>
+        <v>0.049058000000000004</v>
       </c>
       <c r="G20" s="7">
-        <v>0.395206</v>
+        <v>0.336068</v>
       </c>
       <c r="H20" s="7">
-        <v>0.30633900000000003</v>
+        <v>0.284198</v>
       </c>
       <c r="I20" s="7">
-        <v>0.534925</v>
+        <v>0.5089090000000001</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.001119</v>
+        <v>-0.032066</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.011049999999999999</v>
+        <v>-0.011800999999999999</v>
       </c>
       <c r="G21" s="7">
-        <v>0.311035</v>
+        <v>0.23766400000000001</v>
       </c>
       <c r="H21" s="7">
-        <v>0.24018499999999998</v>
+        <v>0.19907599999999998</v>
       </c>
       <c r="I21" s="7">
-        <v>0.43391199999999996</v>
+        <v>0.386382</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.024418000000000002</v>
+        <v>-0.047984</v>
       </c>
       <c r="F22" s="7">
-        <v>0.002334</v>
+        <v>0.034238</v>
       </c>
       <c r="G22" s="7">
-        <v>0.198047</v>
+        <v>0.16910699999999998</v>
       </c>
       <c r="H22" s="7">
-        <v>0.204346</v>
+        <v>0.17525400000000002</v>
       </c>
       <c r="I22" s="7">
-        <v>0.52847</v>
+        <v>0.49154800000000004</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.017934000000000002</v>
+        <v>-0.036322</v>
       </c>
       <c r="F23" s="7">
-        <v>0.035176</v>
+        <v>0.046340000000000006</v>
       </c>
       <c r="G23" s="7">
-        <v>0.395934</v>
+        <v>0.34292900000000004</v>
       </c>
       <c r="H23" s="7">
-        <v>0.313297</v>
+        <v>0.288707</v>
       </c>
       <c r="I23" s="7">
-        <v>0.529162</v>
+        <v>0.5005299999999999</v>
       </c>
       <c r="J23" s="7">
-        <v>2.3256460000000003</v>
+        <v>2.386248</v>
       </c>
       <c r="K23" s="7">
-        <v>11.036728</v>
+        <v>10.745988</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.099634</v>
+        <v>-0.102153</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.159504</v>
+        <v>-0.13351000000000002</v>
       </c>
       <c r="G24" s="7">
-        <v>0.18047999999999997</v>
+        <v>0.129358</v>
       </c>
       <c r="H24" s="7">
-        <v>0.01734</v>
+        <v>0.014493</v>
       </c>
       <c r="I24" s="7">
-        <v>0.36115</v>
+        <v>0.35734099999999996</v>
       </c>
       <c r="J24" s="7">
-        <v>3.2178109999999998</v>
+        <v>3.335324</v>
       </c>
       <c r="K24" s="7">
-        <v>16.046834</v>
+        <v>15.709292</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.017717</v>
+        <v>-0.037894000000000004</v>
       </c>
       <c r="F25" s="7">
-        <v>0.04257</v>
+        <v>0.06830599999999999</v>
       </c>
       <c r="G25" s="7">
-        <v>0.416105</v>
+        <v>0.35200600000000004</v>
       </c>
       <c r="H25" s="7">
-        <v>0.349561</v>
+        <v>0.321839</v>
       </c>
       <c r="I25" s="7">
-        <v>0.509834</v>
+        <v>0.47881999999999997</v>
       </c>
       <c r="J25" s="7">
-        <v>1.9430850000000002</v>
+        <v>1.938082</v>
       </c>
       <c r="K25" s="7">
-        <v>9.765912</v>
+        <v>9.493827</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.0387</v>
+        <v>-0.059985</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.076237</v>
+        <v>-0.058162000000000005</v>
       </c>
       <c r="G26" s="7">
-        <v>0.21052600000000002</v>
+        <v>0.16835</v>
       </c>
       <c r="H26" s="7">
-        <v>0.134765</v>
+        <v>0.109639</v>
       </c>
       <c r="I26" s="7">
-        <v>0.293211</v>
+        <v>0.264577</v>
       </c>
       <c r="J26" s="7">
-        <v>1.4711500000000002</v>
+        <v>1.48975</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.076821</v>
+        <v>-0.08476800000000001</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.046838</v>
+        <v>-0.10230600000000001</v>
       </c>
       <c r="G27" s="7">
-        <v>0.083139</v>
+        <v>0.053755</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.002147</v>
+        <v>-0.010737000000000002</v>
       </c>
       <c r="I27" s="7">
-        <v>0.697103</v>
+        <v>0.682493</v>
       </c>
       <c r="J27" s="7">
-        <v>3.867318</v>
+        <v>3.7969459999999997</v>
       </c>
       <c r="K27" s="7">
-        <v>13.080808</v>
+        <v>12.864366</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.083532</v>
+        <v>0.087112</v>
       </c>
       <c r="F28" s="7">
-        <v>0.24982800000000002</v>
+        <v>0.310791</v>
       </c>
       <c r="G28" s="7">
-        <v>0.6286999999999999</v>
+        <v>0.609541</v>
       </c>
       <c r="H28" s="7">
-        <v>0.486697</v>
+        <v>0.49160899999999996</v>
       </c>
       <c r="I28" s="7">
-        <v>0.7891630000000001</v>
+        <v>0.7950740000000001</v>
       </c>
       <c r="J28" s="7">
-        <v>2.490965</v>
+        <v>2.5725490000000004</v>
       </c>
       <c r="K28" s="7">
-        <v>7.768711</v>
+        <v>7.801932000000001</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.0424</v>
+        <v>0.026000000000000002</v>
       </c>
       <c r="F29" s="7">
-        <v>0.185354</v>
+        <v>0.171233</v>
       </c>
       <c r="G29" s="7">
-        <v>0.537463</v>
+        <v>0.482659</v>
       </c>
       <c r="H29" s="7">
-        <v>0.408649</v>
+        <v>0.386486</v>
       </c>
       <c r="I29" s="7">
-        <v>0.7484069999999999</v>
+        <v>0.720899</v>
       </c>
       <c r="J29" s="7">
-        <v>2.74964</v>
+        <v>2.8203750000000003</v>
       </c>
       <c r="K29" s="7">
-        <v>11.662779</v>
+        <v>11.445415</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.000385</v>
+        <v>-0.025048</v>
       </c>
       <c r="F30" s="7">
-        <v>0.132882</v>
+        <v>0.122698</v>
       </c>
       <c r="G30" s="7">
-        <v>0.469989</v>
+        <v>0.412224</v>
       </c>
       <c r="H30" s="7">
-        <v>0.42715800000000004</v>
+        <v>0.390874</v>
       </c>
       <c r="I30" s="7">
-        <v>0.643038</v>
+        <v>0.6012660000000001</v>
       </c>
       <c r="J30" s="7">
-        <v>2.301119</v>
+        <v>2.33597</v>
       </c>
       <c r="K30" s="7">
-        <v>11.651072</v>
+        <v>11.245886</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.058394</v>
+        <v>0.04079</v>
       </c>
       <c r="F31" s="7">
-        <v>0.207741</v>
+        <v>0.24002500000000002</v>
       </c>
       <c r="G31" s="7">
-        <v>0.49538899999999997</v>
+        <v>0.48565800000000003</v>
       </c>
       <c r="H31" s="7">
-        <v>0.5093070000000001</v>
+        <v>0.484203</v>
       </c>
       <c r="I31" s="7">
-        <v>0.553441</v>
+        <v>0.527603</v>
       </c>
       <c r="J31" s="7">
-        <v>3.269138</v>
+        <v>3.3223970000000005</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.018428</v>
+        <v>-0.040650000000000006</v>
       </c>
       <c r="F32" s="7">
-        <v>0.077655</v>
+        <v>0.081907</v>
       </c>
       <c r="G32" s="7">
-        <v>0.45637300000000003</v>
+        <v>0.39315199999999995</v>
       </c>
       <c r="H32" s="7">
-        <v>0.40551000000000004</v>
+        <v>0.37369</v>
       </c>
       <c r="I32" s="7">
-        <v>0.512949</v>
+        <v>0.47869700000000004</v>
       </c>
       <c r="J32" s="7">
-        <v>1.674247</v>
+        <v>1.71639</v>
       </c>
       <c r="K32" s="7">
-        <v>8.799783999999999</v>
+        <v>8.541779</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.049474</v>
+        <v>-0.065056</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.017911</v>
+        <v>0.000834</v>
       </c>
       <c r="G33" s="7">
-        <v>0.315364</v>
+        <v>0.265823</v>
       </c>
       <c r="H33" s="7">
-        <v>0.238579</v>
+        <v>0.218274</v>
       </c>
       <c r="I33" s="7">
-        <v>0.442933</v>
+        <v>0.419279</v>
       </c>
       <c r="J33" s="7">
-        <v>2.344757</v>
+        <v>2.4066710000000002</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.031315</v>
+        <v>0.032568</v>
       </c>
       <c r="F34" s="7">
-        <v>0.10071300000000001</v>
+        <v>0.097648</v>
       </c>
       <c r="G34" s="7">
-        <v>0.20671399999999998</v>
+        <v>0.20562899999999998</v>
       </c>
       <c r="H34" s="7">
-        <v>0.150442</v>
+        <v>0.15184</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.009958</v>
+        <v>-0.026992</v>
       </c>
       <c r="F35" s="7">
-        <v>-0.008399</v>
+        <v>0.006233</v>
       </c>
       <c r="G35" s="7">
-        <v>0.329346</v>
+        <v>0.275945</v>
       </c>
       <c r="H35" s="7">
-        <v>0.258494</v>
+        <v>0.236842</v>
       </c>
       <c r="I35" s="7">
-        <v>0.467754</v>
+        <v>0.442502</v>
       </c>
       <c r="J35" s="7">
-        <v>2.397482</v>
+        <v>2.444341</v>
       </c>
       <c r="K35" s="7">
-        <v>9.720772</v>
+        <v>9.470953</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.031706</v>
+        <v>0.032541</v>
       </c>
       <c r="F36" s="7">
-        <v>0.10155900000000001</v>
+        <v>0.098048</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20808900000000002</v>
+        <v>0.206508</v>
       </c>
       <c r="H36" s="7">
-        <v>0.15184</v>
+        <v>0.15277100000000002</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>20.05.2026 16:09:52</t>
+    <t>21.05.2026 16:40:59</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.10254400000000001</v>
+        <v>-0.10396000000000001</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.140555</v>
+        <v>-0.165437</v>
       </c>
       <c r="G6" s="7">
-        <v>0.12099700000000001</v>
+        <v>0.09405200000000001</v>
       </c>
       <c r="H6" s="7">
-        <v>0.010132</v>
+        <v>-0.003304</v>
       </c>
       <c r="I6" s="7">
-        <v>0.345263</v>
+        <v>0.309317</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.016137</v>
+        <v>-0.023772</v>
       </c>
       <c r="F7" s="7">
-        <v>0.128021</v>
+        <v>0.108902</v>
       </c>
       <c r="G7" s="7">
-        <v>0.409396</v>
+        <v>0.394923</v>
       </c>
       <c r="H7" s="7">
-        <v>0.392778</v>
+        <v>0.376934</v>
       </c>
       <c r="I7" s="7">
-        <v>0.6003390000000001</v>
+        <v>0.617749</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.062664</v>
+        <v>-0.021307999999999997</v>
       </c>
       <c r="F8" s="7">
-        <v>0.038696</v>
+        <v>0.036745</v>
       </c>
       <c r="G8" s="7">
-        <v>0.337086</v>
+        <v>0.340346</v>
       </c>
       <c r="H8" s="7">
-        <v>0.282395</v>
+        <v>0.292539</v>
       </c>
       <c r="I8" s="7">
-        <v>0.506149</v>
+        <v>0.539961</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.032003</v>
+        <v>0.031968</v>
       </c>
       <c r="F9" s="7">
-        <v>0.09542</v>
+        <v>0.09572800000000001</v>
       </c>
       <c r="G9" s="7">
-        <v>0.203607</v>
+        <v>0.201087</v>
       </c>
       <c r="H9" s="7">
-        <v>0.149379</v>
+        <v>0.150581</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.048619</v>
+        <v>0.054741</v>
       </c>
       <c r="F10" s="7">
-        <v>0.23326799999999998</v>
+        <v>0.23703</v>
       </c>
       <c r="G10" s="7">
-        <v>0.271266</v>
+        <v>0.257416</v>
       </c>
       <c r="H10" s="7">
-        <v>0.31349499999999997</v>
+        <v>0.320069</v>
       </c>
       <c r="I10" s="7">
-        <v>0.48107700000000003</v>
+        <v>0.490817</v>
       </c>
       <c r="J10" s="7">
-        <v>1.397221</v>
+        <v>1.40922</v>
       </c>
       <c r="K10" s="7">
-        <v>7.50168</v>
+        <v>7.5923419999999995</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.07312</v>
+        <v>-0.056732</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.117484</v>
+        <v>-0.119368</v>
       </c>
       <c r="G11" s="7">
-        <v>0.120655</v>
+        <v>0.128444</v>
       </c>
       <c r="H11" s="7">
-        <v>0.044476</v>
+        <v>0.043071</v>
       </c>
       <c r="I11" s="7">
-        <v>0.650636</v>
+        <v>0.595989</v>
       </c>
       <c r="J11" s="7">
-        <v>3.683039</v>
+        <v>3.676742</v>
       </c>
       <c r="K11" s="7">
-        <v>11.650261</v>
+        <v>11.533752999999999</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.043212</v>
+        <v>-0.017977</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.0007109999999999999</v>
+        <v>-0.065101</v>
       </c>
       <c r="G12" s="7">
-        <v>0.597001</v>
+        <v>0.604839</v>
       </c>
       <c r="H12" s="7">
-        <v>0.09373799999999999</v>
+        <v>0.083625</v>
       </c>
       <c r="I12" s="7">
-        <v>1.80863</v>
+        <v>1.732444</v>
       </c>
       <c r="J12" s="7">
-        <v>5.692051</v>
+        <v>5.6301760000000005</v>
       </c>
       <c r="K12" s="7">
-        <v>13.355728</v>
+        <v>13.278393000000001</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.016949000000000002</v>
+        <v>0.015495000000000002</v>
       </c>
       <c r="F13" s="7">
-        <v>0.038771</v>
+        <v>0.034985</v>
       </c>
       <c r="G13" s="7">
-        <v>0.079027</v>
+        <v>0.077118</v>
       </c>
       <c r="H13" s="7">
         <v>0.060229</v>
       </c>
       <c r="I13" s="7">
-        <v>0.173231</v>
+        <v>0.17420100000000002</v>
       </c>
       <c r="J13" s="7">
         <v>1.109015</v>
       </c>
       <c r="K13" s="7">
-        <v>4.322339</v>
+        <v>4.316361</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.08529199999999999</v>
+        <v>-0.061796</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.142047</v>
+        <v>-0.146053</v>
       </c>
       <c r="G14" s="7">
-        <v>0.048095</v>
+        <v>0.067184</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.03267</v>
+        <v>-0.024148</v>
       </c>
       <c r="I14" s="7">
-        <v>0.660571</v>
+        <v>0.637664</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.053419</v>
+        <v>-0.043742</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.045807</v>
+        <v>-0.0233</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.037989</v>
+        <v>-0.042373</v>
       </c>
       <c r="G17" s="7">
-        <v>0.217822</v>
+        <v>0.220188</v>
       </c>
       <c r="H17" s="7">
-        <v>0.18540600000000002</v>
+        <v>0.19274899999999998</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030868000000000003</v>
+        <v>0.030840999999999997</v>
       </c>
       <c r="F18" s="7">
-        <v>0.093522</v>
+        <v>0.093434</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.15137499999999998</v>
+        <v>0.152367</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.041075999999999994</v>
+        <v>0.032312</v>
       </c>
       <c r="F19" s="7">
-        <v>0.22663599999999998</v>
+        <v>0.220193</v>
       </c>
       <c r="G19" s="7">
-        <v>0.543469</v>
+        <v>0.531791</v>
       </c>
       <c r="H19" s="7">
-        <v>0.479469</v>
+        <v>0.479066</v>
       </c>
       <c r="I19" s="7">
-        <v>0.77923</v>
+        <v>0.795699</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.031786</v>
+        <v>-0.029262999999999997</v>
       </c>
       <c r="F20" s="7">
-        <v>0.049058000000000004</v>
+        <v>0.033104</v>
       </c>
       <c r="G20" s="7">
-        <v>0.336068</v>
+        <v>0.334918</v>
       </c>
       <c r="H20" s="7">
-        <v>0.284198</v>
+        <v>0.277828</v>
       </c>
       <c r="I20" s="7">
-        <v>0.5089090000000001</v>
+        <v>0.516559</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.032066</v>
+        <v>-0.027402000000000003</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.011800999999999999</v>
+        <v>-0.018561</v>
       </c>
       <c r="G21" s="7">
-        <v>0.23766400000000001</v>
+        <v>0.23381</v>
       </c>
       <c r="H21" s="7">
-        <v>0.19907599999999998</v>
+        <v>0.196767</v>
       </c>
       <c r="I21" s="7">
-        <v>0.386382</v>
+        <v>0.39488599999999996</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.047984</v>
+        <v>-0.022091</v>
       </c>
       <c r="F22" s="7">
-        <v>0.034238</v>
+        <v>0.024375</v>
       </c>
       <c r="G22" s="7">
-        <v>0.16910699999999998</v>
+        <v>0.163687</v>
       </c>
       <c r="H22" s="7">
-        <v>0.17525400000000002</v>
+        <v>0.163687</v>
       </c>
       <c r="I22" s="7">
-        <v>0.49154800000000004</v>
+        <v>0.48082099999999994</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.036322</v>
+        <v>-0.024329</v>
       </c>
       <c r="F23" s="7">
-        <v>0.046340000000000006</v>
+        <v>0.034558</v>
       </c>
       <c r="G23" s="7">
-        <v>0.34292900000000004</v>
+        <v>0.338055</v>
       </c>
       <c r="H23" s="7">
-        <v>0.288707</v>
+        <v>0.290528</v>
       </c>
       <c r="I23" s="7">
-        <v>0.5005299999999999</v>
+        <v>0.53355</v>
       </c>
       <c r="J23" s="7">
-        <v>2.386248</v>
+        <v>2.391034</v>
       </c>
       <c r="K23" s="7">
-        <v>10.745988</v>
+        <v>10.841225999999999</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.102153</v>
+        <v>-0.09696300000000001</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.13351000000000002</v>
+        <v>-0.16033</v>
       </c>
       <c r="G24" s="7">
-        <v>0.129358</v>
+        <v>0.10114000000000001</v>
       </c>
       <c r="H24" s="7">
-        <v>0.014493</v>
+        <v>0.000259</v>
       </c>
       <c r="I24" s="7">
-        <v>0.35734099999999996</v>
+        <v>0.324084</v>
       </c>
       <c r="J24" s="7">
-        <v>3.335324</v>
+        <v>3.274497</v>
       </c>
       <c r="K24" s="7">
-        <v>15.709292</v>
+        <v>15.294266</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.037894000000000004</v>
+        <v>-0.037221000000000004</v>
       </c>
       <c r="F25" s="7">
-        <v>0.06830599999999999</v>
+        <v>0.029724</v>
       </c>
       <c r="G25" s="7">
-        <v>0.35200600000000004</v>
+        <v>0.32785800000000004</v>
       </c>
       <c r="H25" s="7">
-        <v>0.321839</v>
+        <v>0.311697</v>
       </c>
       <c r="I25" s="7">
-        <v>0.47881999999999997</v>
+        <v>0.488872</v>
       </c>
       <c r="J25" s="7">
-        <v>1.938082</v>
+        <v>1.91554</v>
       </c>
       <c r="K25" s="7">
-        <v>9.493827</v>
+        <v>9.418904</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.059985</v>
+        <v>-0.039132</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.058162000000000005</v>
+        <v>-0.049080000000000006</v>
       </c>
       <c r="G26" s="7">
-        <v>0.16835</v>
+        <v>0.18151499999999998</v>
       </c>
       <c r="H26" s="7">
-        <v>0.109639</v>
+        <v>0.132937</v>
       </c>
       <c r="I26" s="7">
-        <v>0.264577</v>
+        <v>0.30389099999999997</v>
       </c>
       <c r="J26" s="7">
-        <v>1.48975</v>
+        <v>1.5420249999999998</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.08476800000000001</v>
+        <v>-0.068052</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.10230600000000001</v>
+        <v>-0.112955</v>
       </c>
       <c r="G27" s="7">
-        <v>0.053755</v>
+        <v>0.062691</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.010737000000000002</v>
+        <v>-0.005011</v>
       </c>
       <c r="I27" s="7">
-        <v>0.682493</v>
+        <v>0.650831</v>
       </c>
       <c r="J27" s="7">
-        <v>3.7969459999999997</v>
+        <v>3.824714</v>
       </c>
       <c r="K27" s="7">
-        <v>12.864366</v>
+        <v>12.800635</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.087112</v>
+        <v>0.060965</v>
       </c>
       <c r="F28" s="7">
-        <v>0.310791</v>
+        <v>0.283107</v>
       </c>
       <c r="G28" s="7">
-        <v>0.609541</v>
+        <v>0.576517</v>
       </c>
       <c r="H28" s="7">
-        <v>0.49160899999999996</v>
+        <v>0.46745800000000004</v>
       </c>
       <c r="I28" s="7">
-        <v>0.7950740000000001</v>
+        <v>0.777392</v>
       </c>
       <c r="J28" s="7">
-        <v>2.5725490000000004</v>
+        <v>2.514706</v>
       </c>
       <c r="K28" s="7">
-        <v>7.801932000000001</v>
+        <v>7.7268740000000005</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.026000000000000002</v>
+        <v>0.016407</v>
       </c>
       <c r="F29" s="7">
-        <v>0.171233</v>
+        <v>0.145434</v>
       </c>
       <c r="G29" s="7">
-        <v>0.482659</v>
+        <v>0.478033</v>
       </c>
       <c r="H29" s="7">
-        <v>0.386486</v>
+        <v>0.372973</v>
       </c>
       <c r="I29" s="7">
-        <v>0.720899</v>
+        <v>0.692205</v>
       </c>
       <c r="J29" s="7">
-        <v>2.8203750000000003</v>
+        <v>2.7831400000000004</v>
       </c>
       <c r="K29" s="7">
-        <v>11.445415</v>
+        <v>11.438786</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.025048</v>
+        <v>-0.021012</v>
       </c>
       <c r="F30" s="7">
-        <v>0.122698</v>
+        <v>0.107638</v>
       </c>
       <c r="G30" s="7">
-        <v>0.412224</v>
+        <v>0.40206200000000003</v>
       </c>
       <c r="H30" s="7">
-        <v>0.390874</v>
+        <v>0.38317799999999996</v>
       </c>
       <c r="I30" s="7">
-        <v>0.6012660000000001</v>
+        <v>0.63059</v>
       </c>
       <c r="J30" s="7">
-        <v>2.33597</v>
+        <v>2.317511</v>
       </c>
       <c r="K30" s="7">
-        <v>11.245886</v>
+        <v>11.225462</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.04079</v>
+        <v>0.032850000000000004</v>
       </c>
       <c r="F31" s="7">
-        <v>0.24002500000000002</v>
+        <v>0.21244</v>
       </c>
       <c r="G31" s="7">
-        <v>0.48565800000000003</v>
+        <v>0.488198</v>
       </c>
       <c r="H31" s="7">
-        <v>0.484203</v>
+        <v>0.482366</v>
       </c>
       <c r="I31" s="7">
-        <v>0.527603</v>
+        <v>0.537338</v>
       </c>
       <c r="J31" s="7">
-        <v>3.3223970000000005</v>
+        <v>3.317047</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.040650000000000006</v>
+        <v>-0.033986</v>
       </c>
       <c r="F32" s="7">
-        <v>0.081907</v>
+        <v>0.071795</v>
       </c>
       <c r="G32" s="7">
-        <v>0.39315199999999995</v>
+        <v>0.389519</v>
       </c>
       <c r="H32" s="7">
-        <v>0.37369</v>
+        <v>0.378735</v>
       </c>
       <c r="I32" s="7">
-        <v>0.47869700000000004</v>
+        <v>0.515139</v>
       </c>
       <c r="J32" s="7">
-        <v>1.71639</v>
+        <v>1.7263659999999998</v>
       </c>
       <c r="K32" s="7">
-        <v>8.541779</v>
+        <v>8.644408</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,19 +1636,19 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.065056</v>
+        <v>-0.054374000000000006</v>
       </c>
       <c r="F33" s="7">
-        <v>0.000834</v>
+        <v>-0.010308999999999999</v>
       </c>
       <c r="G33" s="7">
-        <v>0.265823</v>
+        <v>0.260504</v>
       </c>
       <c r="H33" s="7">
         <v>0.218274</v>
       </c>
       <c r="I33" s="7">
-        <v>0.419279</v>
+        <v>0.431554</v>
       </c>
       <c r="J33" s="7">
         <v>2.4066710000000002</v>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.032568</v>
+        <v>0.032958</v>
       </c>
       <c r="F34" s="7">
-        <v>0.097648</v>
+        <v>0.097518</v>
       </c>
       <c r="G34" s="7">
-        <v>0.20562899999999998</v>
+        <v>0.20727399999999999</v>
       </c>
       <c r="H34" s="7">
-        <v>0.15184</v>
+        <v>0.153237</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.026992</v>
+        <v>-0.019038</v>
       </c>
       <c r="F35" s="7">
-        <v>0.006233</v>
+        <v>-0.002688</v>
       </c>
       <c r="G35" s="7">
-        <v>0.275945</v>
+        <v>0.269244</v>
       </c>
       <c r="H35" s="7">
-        <v>0.236842</v>
+        <v>0.235843</v>
       </c>
       <c r="I35" s="7">
-        <v>0.442502</v>
+        <v>0.461205</v>
       </c>
       <c r="J35" s="7">
-        <v>2.444341</v>
+        <v>2.441558</v>
       </c>
       <c r="K35" s="7">
-        <v>9.470953</v>
+        <v>9.606061</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.032541</v>
+        <v>0.032514</v>
       </c>
       <c r="F36" s="7">
-        <v>0.098048</v>
+        <v>0.097475</v>
       </c>
       <c r="G36" s="7">
-        <v>0.206508</v>
+        <v>0.207474</v>
       </c>
       <c r="H36" s="7">
-        <v>0.15277100000000002</v>
+        <v>0.153703</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>21.05.2026 16:40:59</t>
+    <t>22.05.2026 17:21:46</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.10396000000000001</v>
+        <v>-0.133347</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.165437</v>
+        <v>-0.20048</v>
       </c>
       <c r="G6" s="7">
-        <v>0.09405200000000001</v>
+        <v>0.056802</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.003304</v>
+        <v>-0.045154</v>
       </c>
       <c r="I6" s="7">
-        <v>0.309317</v>
+        <v>0.270144</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.023772</v>
+        <v>-0.079432</v>
       </c>
       <c r="F7" s="7">
-        <v>0.108902</v>
+        <v>0.038576</v>
       </c>
       <c r="G7" s="7">
-        <v>0.394923</v>
+        <v>0.31678</v>
       </c>
       <c r="H7" s="7">
-        <v>0.376934</v>
+        <v>0.289609</v>
       </c>
       <c r="I7" s="7">
-        <v>0.617749</v>
+        <v>0.531729</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.021307999999999997</v>
+        <v>-0.073629</v>
       </c>
       <c r="F8" s="7">
-        <v>0.036745</v>
+        <v>-0.029134000000000004</v>
       </c>
       <c r="G8" s="7">
-        <v>0.340346</v>
+        <v>0.253473</v>
       </c>
       <c r="H8" s="7">
-        <v>0.292539</v>
+        <v>0.210406</v>
       </c>
       <c r="I8" s="7">
-        <v>0.539961</v>
+        <v>0.459172</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.031968</v>
+        <v>0.032616</v>
       </c>
       <c r="F9" s="7">
-        <v>0.09572800000000001</v>
+        <v>0.09878</v>
       </c>
       <c r="G9" s="7">
-        <v>0.201087</v>
+        <v>0.203174</v>
       </c>
       <c r="H9" s="7">
-        <v>0.150581</v>
+        <v>0.153785</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.054741</v>
+        <v>-0.025341</v>
       </c>
       <c r="F10" s="7">
-        <v>0.23703</v>
+        <v>0.13489</v>
       </c>
       <c r="G10" s="7">
-        <v>0.257416</v>
+        <v>0.161248</v>
       </c>
       <c r="H10" s="7">
-        <v>0.320069</v>
+        <v>0.21107299999999998</v>
       </c>
       <c r="I10" s="7">
-        <v>0.490817</v>
+        <v>0.373626</v>
       </c>
       <c r="J10" s="7">
-        <v>1.40922</v>
+        <v>1.210294</v>
       </c>
       <c r="K10" s="7">
-        <v>7.5923419999999995</v>
+        <v>6.854578</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.056732</v>
+        <v>-0.049229</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.119368</v>
+        <v>-0.122134</v>
       </c>
       <c r="G11" s="7">
-        <v>0.128444</v>
+        <v>0.14202</v>
       </c>
       <c r="H11" s="7">
-        <v>0.043071</v>
+        <v>0.039794</v>
       </c>
       <c r="I11" s="7">
-        <v>0.595989</v>
+        <v>0.5787599999999999</v>
       </c>
       <c r="J11" s="7">
-        <v>3.676742</v>
+        <v>3.662049</v>
       </c>
       <c r="K11" s="7">
-        <v>11.533752999999999</v>
+        <v>11.488753999999998</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.017977</v>
+        <v>-0.002545</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.065101</v>
+        <v>-0.079195</v>
       </c>
       <c r="G12" s="7">
-        <v>0.604839</v>
+        <v>0.613358</v>
       </c>
       <c r="H12" s="7">
-        <v>0.083625</v>
+        <v>0.067289</v>
       </c>
       <c r="I12" s="7">
-        <v>1.732444</v>
+        <v>1.654799</v>
       </c>
       <c r="J12" s="7">
-        <v>5.6301760000000005</v>
+        <v>5.530224</v>
       </c>
       <c r="K12" s="7">
-        <v>13.278393000000001</v>
+        <v>13.217617</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.015495000000000002</v>
+        <v>0.020005000000000002</v>
       </c>
       <c r="F13" s="7">
-        <v>0.034985</v>
+        <v>0.040573</v>
       </c>
       <c r="G13" s="7">
-        <v>0.077118</v>
+        <v>0.082386</v>
       </c>
       <c r="H13" s="7">
-        <v>0.060229</v>
+        <v>0.065953</v>
       </c>
       <c r="I13" s="7">
-        <v>0.17420100000000002</v>
+        <v>0.180866</v>
       </c>
       <c r="J13" s="7">
-        <v>1.109015</v>
+        <v>1.120402</v>
       </c>
       <c r="K13" s="7">
-        <v>4.316361</v>
+        <v>4.335077</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.061796</v>
+        <v>-0.048147</v>
       </c>
       <c r="F14" s="7">
         <v>-0.146053</v>
       </c>
       <c r="G14" s="7">
-        <v>0.067184</v>
+        <v>0.087455</v>
       </c>
       <c r="H14" s="7">
         <v>-0.024148</v>
       </c>
       <c r="I14" s="7">
-        <v>0.637664</v>
+        <v>0.632993</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.043742</v>
+        <v>-0.030423</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.0233</v>
+        <v>-0.060128</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.042373</v>
+        <v>-0.078482</v>
       </c>
       <c r="G17" s="7">
-        <v>0.220188</v>
+        <v>0.189819</v>
       </c>
       <c r="H17" s="7">
-        <v>0.19274899999999998</v>
+        <v>0.147774</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030840999999999997</v>
+        <v>0.032344</v>
       </c>
       <c r="F18" s="7">
-        <v>0.093434</v>
+        <v>0.09672900000000001</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.152367</v>
+        <v>0.155839</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.032312</v>
+        <v>-0.003691</v>
       </c>
       <c r="F19" s="7">
-        <v>0.220193</v>
+        <v>0.165394</v>
       </c>
       <c r="G19" s="7">
-        <v>0.531791</v>
+        <v>0.47097</v>
       </c>
       <c r="H19" s="7">
-        <v>0.479066</v>
+        <v>0.412641</v>
       </c>
       <c r="I19" s="7">
-        <v>0.795699</v>
+        <v>0.7213639999999999</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.029262999999999997</v>
+        <v>-0.040952999999999996</v>
       </c>
       <c r="F20" s="7">
-        <v>0.033104</v>
+        <v>0.01643</v>
       </c>
       <c r="G20" s="7">
-        <v>0.334918</v>
+        <v>0.319223</v>
       </c>
       <c r="H20" s="7">
-        <v>0.277828</v>
+        <v>0.257204</v>
       </c>
       <c r="I20" s="7">
-        <v>0.516559</v>
+        <v>0.506177</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.027402000000000003</v>
+        <v>-0.072072</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.018561</v>
+        <v>-0.063636</v>
       </c>
       <c r="G21" s="7">
-        <v>0.23381</v>
+        <v>0.191325</v>
       </c>
       <c r="H21" s="7">
-        <v>0.196767</v>
+        <v>0.14180099999999998</v>
       </c>
       <c r="I21" s="7">
-        <v>0.39488599999999996</v>
+        <v>0.35452100000000003</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.022091</v>
+        <v>-0.035788</v>
       </c>
       <c r="F22" s="7">
-        <v>0.024375</v>
+        <v>0.005862000000000001</v>
       </c>
       <c r="G22" s="7">
-        <v>0.163687</v>
+        <v>0.138666</v>
       </c>
       <c r="H22" s="7">
-        <v>0.163687</v>
+        <v>0.142657</v>
       </c>
       <c r="I22" s="7">
-        <v>0.48082099999999994</v>
+        <v>0.441202</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.024329</v>
+        <v>-0.074074</v>
       </c>
       <c r="F23" s="7">
-        <v>0.034558</v>
+        <v>-0.026527</v>
       </c>
       <c r="G23" s="7">
-        <v>0.338055</v>
+        <v>0.26782900000000004</v>
       </c>
       <c r="H23" s="7">
-        <v>0.290528</v>
+        <v>0.214329</v>
       </c>
       <c r="I23" s="7">
-        <v>0.53355</v>
+        <v>0.461988</v>
       </c>
       <c r="J23" s="7">
-        <v>2.391034</v>
+        <v>2.19081</v>
       </c>
       <c r="K23" s="7">
-        <v>10.841225999999999</v>
+        <v>10.123471</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.09696300000000001</v>
+        <v>-0.18025400000000003</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.16033</v>
+        <v>-0.24418900000000002</v>
       </c>
       <c r="G24" s="7">
-        <v>0.10114000000000001</v>
+        <v>0.000288</v>
       </c>
       <c r="H24" s="7">
-        <v>0.000259</v>
+        <v>-0.099638</v>
       </c>
       <c r="I24" s="7">
-        <v>0.324084</v>
+        <v>0.20505700000000002</v>
       </c>
       <c r="J24" s="7">
-        <v>3.274497</v>
+        <v>2.8476</v>
       </c>
       <c r="K24" s="7">
-        <v>15.294266</v>
+        <v>13.791667</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.037221000000000004</v>
+        <v>-0.08074999999999999</v>
       </c>
       <c r="F25" s="7">
-        <v>0.029724</v>
+        <v>-0.024151</v>
       </c>
       <c r="G25" s="7">
-        <v>0.32785800000000004</v>
+        <v>0.263574</v>
       </c>
       <c r="H25" s="7">
-        <v>0.311697</v>
+        <v>0.24306999999999998</v>
       </c>
       <c r="I25" s="7">
-        <v>0.488872</v>
+        <v>0.43073900000000004</v>
       </c>
       <c r="J25" s="7">
-        <v>1.91554</v>
+        <v>1.7630000000000001</v>
       </c>
       <c r="K25" s="7">
-        <v>9.418904</v>
+        <v>8.857909</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.039132</v>
+        <v>-0.069977</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.049080000000000006</v>
+        <v>-0.087807</v>
       </c>
       <c r="G26" s="7">
-        <v>0.18151499999999998</v>
+        <v>0.137733</v>
       </c>
       <c r="H26" s="7">
-        <v>0.132937</v>
+        <v>0.086798</v>
       </c>
       <c r="I26" s="7">
-        <v>0.30389099999999997</v>
+        <v>0.273555</v>
       </c>
       <c r="J26" s="7">
-        <v>1.5420249999999998</v>
+        <v>1.438499</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.068052</v>
+        <v>-0.052488</v>
       </c>
       <c r="F27" s="7">
         <v>-0.112955</v>
       </c>
       <c r="G27" s="7">
-        <v>0.062691</v>
+        <v>0.080031</v>
       </c>
       <c r="H27" s="7">
         <v>-0.005011</v>
       </c>
       <c r="I27" s="7">
-        <v>0.650831</v>
+        <v>0.64497</v>
       </c>
       <c r="J27" s="7">
         <v>3.824714</v>
       </c>
       <c r="K27" s="7">
-        <v>12.800635</v>
+        <v>12.773286</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.060965</v>
+        <v>0.027458</v>
       </c>
       <c r="F28" s="7">
-        <v>0.283107</v>
+        <v>0.24552600000000002</v>
       </c>
       <c r="G28" s="7">
-        <v>0.576517</v>
+        <v>0.583978</v>
       </c>
       <c r="H28" s="7">
-        <v>0.46745800000000004</v>
+        <v>0.424478</v>
       </c>
       <c r="I28" s="7">
-        <v>0.777392</v>
+        <v>0.74</v>
       </c>
       <c r="J28" s="7">
-        <v>2.514706</v>
+        <v>2.411765</v>
       </c>
       <c r="K28" s="7">
-        <v>7.7268740000000005</v>
+        <v>7.479532000000001</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.016407</v>
+        <v>-0.0516</v>
       </c>
       <c r="F29" s="7">
-        <v>0.145434</v>
+        <v>0.069222</v>
       </c>
       <c r="G29" s="7">
-        <v>0.478033</v>
+        <v>0.38695500000000005</v>
       </c>
       <c r="H29" s="7">
-        <v>0.372973</v>
+        <v>0.281622</v>
       </c>
       <c r="I29" s="7">
-        <v>0.692205</v>
+        <v>0.591275</v>
       </c>
       <c r="J29" s="7">
-        <v>2.7831400000000004</v>
+        <v>2.531427</v>
       </c>
       <c r="K29" s="7">
-        <v>11.438786</v>
+        <v>10.639666</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.021012</v>
+        <v>-0.064764</v>
       </c>
       <c r="F30" s="7">
-        <v>0.107638</v>
+        <v>0.045785</v>
       </c>
       <c r="G30" s="7">
-        <v>0.40206200000000003</v>
+        <v>0.332305</v>
       </c>
       <c r="H30" s="7">
-        <v>0.38317799999999996</v>
+        <v>0.30593699999999996</v>
       </c>
       <c r="I30" s="7">
-        <v>0.63059</v>
+        <v>0.5582159999999999</v>
       </c>
       <c r="J30" s="7">
-        <v>2.317511</v>
+        <v>2.132252</v>
       </c>
       <c r="K30" s="7">
-        <v>11.225462</v>
+        <v>10.481392000000001</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.032850000000000004</v>
+        <v>-0.005633</v>
       </c>
       <c r="F31" s="7">
-        <v>0.21244</v>
+        <v>0.149339</v>
       </c>
       <c r="G31" s="7">
-        <v>0.488198</v>
+        <v>0.43473399999999995</v>
       </c>
       <c r="H31" s="7">
-        <v>0.482366</v>
+        <v>0.40521700000000005</v>
       </c>
       <c r="I31" s="7">
-        <v>0.537338</v>
+        <v>0.47153100000000003</v>
       </c>
       <c r="J31" s="7">
-        <v>3.317047</v>
+        <v>3.092368</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.033986</v>
+        <v>-0.052211999999999995</v>
       </c>
       <c r="F32" s="7">
-        <v>0.071795</v>
+        <v>0.040422</v>
       </c>
       <c r="G32" s="7">
-        <v>0.389519</v>
+        <v>0.352549</v>
       </c>
       <c r="H32" s="7">
-        <v>0.378735</v>
+        <v>0.338378</v>
       </c>
       <c r="I32" s="7">
-        <v>0.515139</v>
+        <v>0.49372</v>
       </c>
       <c r="J32" s="7">
-        <v>1.7263659999999998</v>
+        <v>1.646562</v>
       </c>
       <c r="K32" s="7">
-        <v>8.644408</v>
+        <v>8.331710000000001</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.054374000000000006</v>
+        <v>-0.074671</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.010308999999999999</v>
+        <v>-0.041856</v>
       </c>
       <c r="G33" s="7">
-        <v>0.260504</v>
+        <v>0.228066</v>
       </c>
       <c r="H33" s="7">
-        <v>0.218274</v>
+        <v>0.179442</v>
       </c>
       <c r="I33" s="7">
-        <v>0.431554</v>
+        <v>0.409463</v>
       </c>
       <c r="J33" s="7">
-        <v>2.4066710000000002</v>
+        <v>2.2980840000000002</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.032958</v>
+        <v>0.034138</v>
       </c>
       <c r="F34" s="7">
-        <v>0.097518</v>
+        <v>0.101064</v>
       </c>
       <c r="G34" s="7">
-        <v>0.20727399999999999</v>
+        <v>0.20752500000000002</v>
       </c>
       <c r="H34" s="7">
-        <v>0.153237</v>
+        <v>0.15696300000000002</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.019038</v>
+        <v>-0.069315</v>
       </c>
       <c r="F35" s="7">
-        <v>-0.002688</v>
+        <v>-0.061559</v>
       </c>
       <c r="G35" s="7">
-        <v>0.269244</v>
+        <v>0.205872</v>
       </c>
       <c r="H35" s="7">
-        <v>0.235843</v>
+        <v>0.162891</v>
       </c>
       <c r="I35" s="7">
-        <v>0.461205</v>
+        <v>0.393613</v>
       </c>
       <c r="J35" s="7">
-        <v>2.441558</v>
+        <v>2.238404</v>
       </c>
       <c r="K35" s="7">
-        <v>9.606061</v>
+        <v>8.979989</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.032514</v>
+        <v>0.03454</v>
       </c>
       <c r="F36" s="7">
-        <v>0.097475</v>
+        <v>0.101462</v>
       </c>
       <c r="G36" s="7">
-        <v>0.207474</v>
+        <v>0.20817699999999997</v>
       </c>
       <c r="H36" s="7">
-        <v>0.153703</v>
+        <v>0.157895</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>22.05.2026 17:21:46</t>
+    <t>25.05.2026 13:26:03</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.133347</v>
+        <v>-0.125874</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.20048</v>
+        <v>-0.238078</v>
       </c>
       <c r="G6" s="7">
-        <v>0.056802</v>
+        <v>0.01772</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.045154</v>
+        <v>-0.063877</v>
       </c>
       <c r="I6" s="7">
-        <v>0.270144</v>
+        <v>0.25221</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.079432</v>
+        <v>-0.01401</v>
       </c>
       <c r="F7" s="7">
-        <v>0.038576</v>
+        <v>0.106168</v>
       </c>
       <c r="G7" s="7">
-        <v>0.31678</v>
+        <v>0.420952</v>
       </c>
       <c r="H7" s="7">
-        <v>0.289609</v>
+        <v>0.374355</v>
       </c>
       <c r="I7" s="7">
-        <v>0.531729</v>
+        <v>0.630245</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.073629</v>
+        <v>-0.035176</v>
       </c>
       <c r="F8" s="7">
-        <v>-0.029134000000000004</v>
+        <v>0.00026</v>
       </c>
       <c r="G8" s="7">
-        <v>0.253473</v>
+        <v>0.312821</v>
       </c>
       <c r="H8" s="7">
-        <v>0.210406</v>
+        <v>0.25654499999999997</v>
       </c>
       <c r="I8" s="7">
-        <v>0.459172</v>
+        <v>0.523205</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.032616</v>
+        <v>0.036403</v>
       </c>
       <c r="F9" s="7">
-        <v>0.09878</v>
+        <v>0.105443</v>
       </c>
       <c r="G9" s="7">
-        <v>0.203174</v>
+        <v>0.21151399999999998</v>
       </c>
       <c r="H9" s="7">
-        <v>0.153785</v>
+        <v>0.16299600000000003</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.025341</v>
+        <v>0.008864</v>
       </c>
       <c r="F10" s="7">
-        <v>0.13489</v>
+        <v>0.158029</v>
       </c>
       <c r="G10" s="7">
-        <v>0.161248</v>
+        <v>0.205561</v>
       </c>
       <c r="H10" s="7">
-        <v>0.21107299999999998</v>
+        <v>0.260208</v>
       </c>
       <c r="I10" s="7">
-        <v>0.373626</v>
+        <v>0.46382599999999996</v>
       </c>
       <c r="J10" s="7">
-        <v>1.210294</v>
+        <v>1.356519</v>
       </c>
       <c r="K10" s="7">
-        <v>6.854578</v>
+        <v>7.175084000000001</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.049229</v>
+        <v>-0.020905999999999998</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.122134</v>
+        <v>-0.10687300000000001</v>
       </c>
       <c r="G11" s="7">
-        <v>0.14202</v>
+        <v>0.15519</v>
       </c>
       <c r="H11" s="7">
-        <v>0.039794</v>
+        <v>0.052434</v>
       </c>
       <c r="I11" s="7">
-        <v>0.5787599999999999</v>
+        <v>0.562848</v>
       </c>
       <c r="J11" s="7">
-        <v>3.662049</v>
+        <v>3.5691059999999997</v>
       </c>
       <c r="K11" s="7">
-        <v>11.488753999999998</v>
+        <v>11.536248</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.002545</v>
+        <v>0.011597999999999999</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.079195</v>
+        <v>-0.09500600000000001</v>
       </c>
       <c r="G12" s="7">
-        <v>0.613358</v>
+        <v>0.624942</v>
       </c>
       <c r="H12" s="7">
-        <v>0.067289</v>
+        <v>0.08557000000000001</v>
       </c>
       <c r="I12" s="7">
-        <v>1.654799</v>
+        <v>1.683654</v>
       </c>
       <c r="J12" s="7">
-        <v>5.530224</v>
+        <v>5.539363</v>
       </c>
       <c r="K12" s="7">
-        <v>13.217617</v>
+        <v>13.321634</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.020005000000000002</v>
+        <v>0.028456000000000002</v>
       </c>
       <c r="F13" s="7">
-        <v>0.040573</v>
+        <v>0.054973999999999995</v>
       </c>
       <c r="G13" s="7">
-        <v>0.082386</v>
+        <v>0.096864</v>
       </c>
       <c r="H13" s="7">
-        <v>0.065953</v>
+        <v>0.079393</v>
       </c>
       <c r="I13" s="7">
-        <v>0.180866</v>
+        <v>0.186918</v>
       </c>
       <c r="J13" s="7">
-        <v>1.120402</v>
+        <v>1.10534</v>
       </c>
       <c r="K13" s="7">
-        <v>4.335077</v>
+        <v>4.400996</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.048147</v>
+        <v>-0.046961</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.146053</v>
+        <v>-0.156479</v>
       </c>
       <c r="G14" s="7">
-        <v>0.087455</v>
+        <v>0.090478</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.024148</v>
+        <v>-0.019886</v>
       </c>
       <c r="I14" s="7">
-        <v>0.632993</v>
+        <v>0.589862</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.030423</v>
+        <v>-0.029283</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.060128</v>
+        <v>-0.018376999999999998</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.078482</v>
+        <v>-0.061837</v>
       </c>
       <c r="G17" s="7">
-        <v>0.189819</v>
+        <v>0.223866</v>
       </c>
       <c r="H17" s="7">
-        <v>0.147774</v>
+        <v>0.176687</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.032344</v>
+        <v>0.035289</v>
       </c>
       <c r="F18" s="7">
-        <v>0.09672900000000001</v>
+        <v>0.103173</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.155839</v>
+        <v>0.164272</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.003691</v>
+        <v>0.015576000000000001</v>
       </c>
       <c r="F19" s="7">
-        <v>0.165394</v>
+        <v>0.177668</v>
       </c>
       <c r="G19" s="7">
-        <v>0.47097</v>
+        <v>0.503879</v>
       </c>
       <c r="H19" s="7">
-        <v>0.412641</v>
+        <v>0.443639</v>
       </c>
       <c r="I19" s="7">
-        <v>0.7213639999999999</v>
+        <v>0.762162</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.040952999999999996</v>
+        <v>-0.033863</v>
       </c>
       <c r="F20" s="7">
-        <v>0.01643</v>
+        <v>0.004614</v>
       </c>
       <c r="G20" s="7">
-        <v>0.319223</v>
+        <v>0.318356</v>
       </c>
       <c r="H20" s="7">
-        <v>0.257204</v>
+        <v>0.254777</v>
       </c>
       <c r="I20" s="7">
-        <v>0.506177</v>
+        <v>0.512061</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.072072</v>
+        <v>-0.03028</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.063636</v>
+        <v>-0.039009999999999996</v>
       </c>
       <c r="G21" s="7">
-        <v>0.191325</v>
+        <v>0.233213</v>
       </c>
       <c r="H21" s="7">
-        <v>0.14180099999999998</v>
+        <v>0.18337199999999998</v>
       </c>
       <c r="I21" s="7">
-        <v>0.35452100000000003</v>
+        <v>0.411959</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.035788</v>
+        <v>-0.044062000000000004</v>
       </c>
       <c r="F22" s="7">
-        <v>0.005862000000000001</v>
+        <v>0.015184</v>
       </c>
       <c r="G22" s="7">
-        <v>0.138666</v>
+        <v>0.141463</v>
       </c>
       <c r="H22" s="7">
-        <v>0.142657</v>
+        <v>0.14826499999999998</v>
       </c>
       <c r="I22" s="7">
-        <v>0.441202</v>
+        <v>0.479675</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.074074</v>
+        <v>-0.023959</v>
       </c>
       <c r="F23" s="7">
-        <v>-0.026527</v>
+        <v>0.015489</v>
       </c>
       <c r="G23" s="7">
-        <v>0.26782900000000004</v>
+        <v>0.33291</v>
       </c>
       <c r="H23" s="7">
-        <v>0.214329</v>
+        <v>0.273831</v>
       </c>
       <c r="I23" s="7">
-        <v>0.461988</v>
+        <v>0.539817</v>
       </c>
       <c r="J23" s="7">
-        <v>2.19081</v>
+        <v>2.393724</v>
       </c>
       <c r="K23" s="7">
-        <v>10.123471</v>
+        <v>10.629712</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.18025400000000003</v>
+        <v>-0.125542</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.24418900000000002</v>
+        <v>-0.23228300000000002</v>
       </c>
       <c r="G24" s="7">
-        <v>0.000288</v>
+        <v>0.023118</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.099638</v>
+        <v>-0.060818000000000004</v>
       </c>
       <c r="I24" s="7">
-        <v>0.20505700000000002</v>
+        <v>0.26446000000000003</v>
       </c>
       <c r="J24" s="7">
-        <v>2.8476</v>
+        <v>3.237506</v>
       </c>
       <c r="K24" s="7">
-        <v>13.791667</v>
+        <v>14.442553</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.08074999999999999</v>
+        <v>-0.029817</v>
       </c>
       <c r="F25" s="7">
-        <v>-0.024151</v>
+        <v>0.009385</v>
       </c>
       <c r="G25" s="7">
-        <v>0.263574</v>
+        <v>0.32150199999999995</v>
       </c>
       <c r="H25" s="7">
-        <v>0.24306999999999998</v>
+        <v>0.308993</v>
       </c>
       <c r="I25" s="7">
-        <v>0.43073900000000004</v>
+        <v>0.517836</v>
       </c>
       <c r="J25" s="7">
-        <v>1.7630000000000001</v>
+        <v>1.9848910000000002</v>
       </c>
       <c r="K25" s="7">
-        <v>8.857909</v>
+        <v>9.369577</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.069977</v>
+        <v>-0.030714</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.087807</v>
+        <v>-0.068966</v>
       </c>
       <c r="G26" s="7">
-        <v>0.137733</v>
+        <v>0.153299</v>
       </c>
       <c r="H26" s="7">
-        <v>0.086798</v>
+        <v>0.11009600000000001</v>
       </c>
       <c r="I26" s="7">
-        <v>0.273555</v>
+        <v>0.306452</v>
       </c>
       <c r="J26" s="7">
-        <v>1.438499</v>
+        <v>1.541309</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.052488</v>
+        <v>-0.039175</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.112955</v>
+        <v>-0.11294399999999999</v>
       </c>
       <c r="G27" s="7">
-        <v>0.080031</v>
+        <v>0.086247</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.005011</v>
+        <v>0.000716</v>
       </c>
       <c r="I27" s="7">
-        <v>0.64497</v>
+        <v>0.600641</v>
       </c>
       <c r="J27" s="7">
-        <v>3.824714</v>
+        <v>3.75672</v>
       </c>
       <c r="K27" s="7">
-        <v>12.773286</v>
+        <v>12.759843</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.027458</v>
+        <v>0.056338</v>
       </c>
       <c r="F28" s="7">
-        <v>0.24552600000000002</v>
+        <v>0.28113900000000003</v>
       </c>
       <c r="G28" s="7">
-        <v>0.583978</v>
+        <v>0.59292</v>
       </c>
       <c r="H28" s="7">
-        <v>0.424478</v>
+        <v>0.473598</v>
       </c>
       <c r="I28" s="7">
-        <v>0.74</v>
+        <v>0.777778</v>
       </c>
       <c r="J28" s="7">
-        <v>2.411765</v>
+        <v>2.550296</v>
       </c>
       <c r="K28" s="7">
-        <v>7.479532000000001</v>
+        <v>7.789063</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.0516</v>
+        <v>0.023312</v>
       </c>
       <c r="F29" s="7">
-        <v>0.069222</v>
+        <v>0.15251099999999998</v>
       </c>
       <c r="G29" s="7">
-        <v>0.38695500000000005</v>
+        <v>0.476023</v>
       </c>
       <c r="H29" s="7">
-        <v>0.281622</v>
+        <v>0.36432400000000004</v>
       </c>
       <c r="I29" s="7">
-        <v>0.591275</v>
+        <v>0.7175910000000001</v>
       </c>
       <c r="J29" s="7">
-        <v>2.531427</v>
+        <v>2.734833</v>
       </c>
       <c r="K29" s="7">
-        <v>10.639666</v>
+        <v>11.360431</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.064764</v>
+        <v>-0.009785</v>
       </c>
       <c r="F30" s="7">
-        <v>0.045785</v>
+        <v>0.11946899999999999</v>
       </c>
       <c r="G30" s="7">
-        <v>0.332305</v>
+        <v>0.442006</v>
       </c>
       <c r="H30" s="7">
-        <v>0.30593699999999996</v>
+        <v>0.390874</v>
       </c>
       <c r="I30" s="7">
-        <v>0.5582159999999999</v>
+        <v>0.650897</v>
       </c>
       <c r="J30" s="7">
-        <v>2.132252</v>
+        <v>2.406031</v>
       </c>
       <c r="K30" s="7">
-        <v>10.481392000000001</v>
+        <v>11.18103</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.005633</v>
+        <v>0.039565</v>
       </c>
       <c r="F31" s="7">
-        <v>0.149339</v>
+        <v>0.213213</v>
       </c>
       <c r="G31" s="7">
-        <v>0.43473399999999995</v>
+        <v>0.5</v>
       </c>
       <c r="H31" s="7">
-        <v>0.40521700000000005</v>
+        <v>0.46399700000000005</v>
       </c>
       <c r="I31" s="7">
-        <v>0.47153100000000003</v>
+        <v>0.525651</v>
       </c>
       <c r="J31" s="7">
-        <v>3.092368</v>
+        <v>3.375915</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.052211999999999995</v>
+        <v>-0.034294</v>
       </c>
       <c r="F32" s="7">
-        <v>0.040422</v>
+        <v>0.025341999999999996</v>
       </c>
       <c r="G32" s="7">
-        <v>0.352549</v>
+        <v>0.38364800000000004</v>
       </c>
       <c r="H32" s="7">
-        <v>0.338378</v>
+        <v>0.365929</v>
       </c>
       <c r="I32" s="7">
-        <v>0.49372</v>
+        <v>0.540481</v>
       </c>
       <c r="J32" s="7">
-        <v>1.646562</v>
+        <v>1.7244579999999998</v>
       </c>
       <c r="K32" s="7">
-        <v>8.331710000000001</v>
+        <v>8.508374</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.074671</v>
+        <v>-0.07368000000000001</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.041856</v>
+        <v>-0.048659999999999995</v>
       </c>
       <c r="G33" s="7">
-        <v>0.228066</v>
+        <v>0.22517299999999998</v>
       </c>
       <c r="H33" s="7">
-        <v>0.179442</v>
+        <v>0.171066</v>
       </c>
       <c r="I33" s="7">
-        <v>0.409463</v>
+        <v>0.411441</v>
       </c>
       <c r="J33" s="7">
-        <v>2.2980840000000002</v>
+        <v>2.390154</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.034138</v>
+        <v>0.036884</v>
       </c>
       <c r="F34" s="7">
-        <v>0.101064</v>
+        <v>0.10708000000000001</v>
       </c>
       <c r="G34" s="7">
-        <v>0.20752500000000002</v>
+        <v>0.215051</v>
       </c>
       <c r="H34" s="7">
-        <v>0.15696300000000002</v>
+        <v>0.16534700000000002</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.069315</v>
+        <v>-0.021831999999999997</v>
       </c>
       <c r="F35" s="7">
-        <v>-0.061559</v>
+        <v>-0.019743999999999998</v>
       </c>
       <c r="G35" s="7">
-        <v>0.205872</v>
+        <v>0.270401</v>
       </c>
       <c r="H35" s="7">
-        <v>0.162891</v>
+        <v>0.22385100000000002</v>
       </c>
       <c r="I35" s="7">
-        <v>0.393613</v>
+        <v>0.47787599999999997</v>
       </c>
       <c r="J35" s="7">
-        <v>2.238404</v>
+        <v>2.5477019999999997</v>
       </c>
       <c r="K35" s="7">
-        <v>8.979989</v>
+        <v>9.473203999999999</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.03454</v>
+        <v>0.037697</v>
       </c>
       <c r="F36" s="7">
-        <v>0.101462</v>
+        <v>0.107917</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20817699999999997</v>
+        <v>0.216175</v>
       </c>
       <c r="H36" s="7">
-        <v>0.157895</v>
+        <v>0.16674399999999998</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>25.05.2026 13:26:03</t>
+    <t>26.05.2026 11:05:03</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.125874</v>
+        <v>-0.105306</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.238078</v>
+        <v>-0.21706299999999998</v>
       </c>
       <c r="G6" s="7">
-        <v>0.01772</v>
+        <v>0.030806</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.063877</v>
+        <v>-0.04185</v>
       </c>
       <c r="I6" s="7">
-        <v>0.25221</v>
+        <v>0.281674</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.01401</v>
+        <v>-0.023526</v>
       </c>
       <c r="F7" s="7">
-        <v>0.106168</v>
+        <v>0.10930899999999999</v>
       </c>
       <c r="G7" s="7">
-        <v>0.420952</v>
+        <v>0.413701</v>
       </c>
       <c r="H7" s="7">
-        <v>0.374355</v>
+        <v>0.361091</v>
       </c>
       <c r="I7" s="7">
-        <v>0.630245</v>
+        <v>0.61451</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.035176</v>
+        <v>-0.034925000000000005</v>
       </c>
       <c r="F8" s="7">
-        <v>0.00026</v>
+        <v>0.011588000000000001</v>
       </c>
       <c r="G8" s="7">
-        <v>0.312821</v>
+        <v>0.314061</v>
       </c>
       <c r="H8" s="7">
-        <v>0.25654499999999997</v>
+        <v>0.256872</v>
       </c>
       <c r="I8" s="7">
-        <v>0.523205</v>
+        <v>0.523602</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.036403</v>
+        <v>0.036759</v>
       </c>
       <c r="F9" s="7">
-        <v>0.105443</v>
+        <v>0.104563</v>
       </c>
       <c r="G9" s="7">
-        <v>0.21151399999999998</v>
+        <v>0.210669</v>
       </c>
       <c r="H9" s="7">
-        <v>0.16299600000000003</v>
+        <v>0.163396</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.008864</v>
+        <v>0.044321</v>
       </c>
       <c r="F10" s="7">
-        <v>0.158029</v>
+        <v>0.21927600000000003</v>
       </c>
       <c r="G10" s="7">
-        <v>0.205561</v>
+        <v>0.275804</v>
       </c>
       <c r="H10" s="7">
-        <v>0.260208</v>
+        <v>0.304498</v>
       </c>
       <c r="I10" s="7">
-        <v>0.46382599999999996</v>
+        <v>0.515273</v>
       </c>
       <c r="J10" s="7">
-        <v>1.356519</v>
+        <v>1.440919</v>
       </c>
       <c r="K10" s="7">
-        <v>7.175084000000001</v>
+        <v>7.7107209999999995</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.020905999999999998</v>
+        <v>-0.004791</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.10687300000000001</v>
+        <v>-0.104273</v>
       </c>
       <c r="G11" s="7">
-        <v>0.15519</v>
+        <v>0.16820000000000002</v>
       </c>
       <c r="H11" s="7">
-        <v>0.052434</v>
+        <v>0.069757</v>
       </c>
       <c r="I11" s="7">
-        <v>0.562848</v>
+        <v>0.5885710000000001</v>
       </c>
       <c r="J11" s="7">
-        <v>3.5691059999999997</v>
+        <v>3.663265</v>
       </c>
       <c r="K11" s="7">
-        <v>11.536248</v>
+        <v>11.527412</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.011597999999999999</v>
+        <v>0.045306</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.09500600000000001</v>
+        <v>-0.106844</v>
       </c>
       <c r="G12" s="7">
-        <v>0.624942</v>
+        <v>0.673242</v>
       </c>
       <c r="H12" s="7">
-        <v>0.08557000000000001</v>
+        <v>0.121743</v>
       </c>
       <c r="I12" s="7">
-        <v>1.683654</v>
+        <v>1.773077</v>
       </c>
       <c r="J12" s="7">
-        <v>5.539363</v>
+        <v>5.8083100000000005</v>
       </c>
       <c r="K12" s="7">
-        <v>13.321634</v>
+        <v>13.518726999999998</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.028456000000000002</v>
+        <v>0.020868</v>
       </c>
       <c r="F13" s="7">
-        <v>0.054973999999999995</v>
+        <v>0.04897700000000001</v>
       </c>
       <c r="G13" s="7">
-        <v>0.096864</v>
+        <v>0.089046</v>
       </c>
       <c r="H13" s="7">
-        <v>0.079393</v>
+        <v>0.071429</v>
       </c>
       <c r="I13" s="7">
-        <v>0.186918</v>
+        <v>0.17816099999999999</v>
       </c>
       <c r="J13" s="7">
-        <v>1.10534</v>
+        <v>1.112365</v>
       </c>
       <c r="K13" s="7">
-        <v>4.400996</v>
+        <v>4.301724</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.046961</v>
+        <v>-0.033149000000000005</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.156479</v>
+        <v>-0.146341</v>
       </c>
       <c r="G14" s="7">
-        <v>0.090478</v>
+        <v>0.092044</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.019886</v>
+        <v>-0.005682</v>
       </c>
       <c r="I14" s="7">
-        <v>0.589862</v>
+        <v>0.612903</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.029283</v>
+        <v>-0.021852999999999997</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.018376999999999998</v>
+        <v>-0.022205</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.061837</v>
+        <v>-0.050205</v>
       </c>
       <c r="G17" s="7">
-        <v>0.223866</v>
+        <v>0.22670500000000002</v>
       </c>
       <c r="H17" s="7">
-        <v>0.176687</v>
+        <v>0.17209700000000003</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.035289</v>
+        <v>0.036392</v>
       </c>
       <c r="F18" s="7">
-        <v>0.103173</v>
+        <v>0.102793</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.164272</v>
+        <v>0.16551300000000002</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.015576000000000001</v>
+        <v>0.027471000000000002</v>
       </c>
       <c r="F19" s="7">
-        <v>0.177668</v>
+        <v>0.205716</v>
       </c>
       <c r="G19" s="7">
-        <v>0.503879</v>
+        <v>0.533066</v>
       </c>
       <c r="H19" s="7">
-        <v>0.443639</v>
+        <v>0.460548</v>
       </c>
       <c r="I19" s="7">
-        <v>0.762162</v>
+        <v>0.7828010000000001</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.033863</v>
+        <v>-0.032461000000000004</v>
       </c>
       <c r="F20" s="7">
-        <v>0.004614</v>
+        <v>0.015441</v>
       </c>
       <c r="G20" s="7">
-        <v>0.318356</v>
+        <v>0.321531</v>
       </c>
       <c r="H20" s="7">
-        <v>0.254777</v>
+        <v>0.256597</v>
       </c>
       <c r="I20" s="7">
-        <v>0.512061</v>
+        <v>0.514254</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.03028</v>
+        <v>-0.038986</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.039009999999999996</v>
+        <v>-0.036798000000000004</v>
       </c>
       <c r="G21" s="7">
-        <v>0.233213</v>
+        <v>0.223614</v>
       </c>
       <c r="H21" s="7">
-        <v>0.18337199999999998</v>
+        <v>0.17274799999999998</v>
       </c>
       <c r="I21" s="7">
-        <v>0.411959</v>
+        <v>0.39928400000000003</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.044062000000000004</v>
+        <v>-0.036475</v>
       </c>
       <c r="F22" s="7">
-        <v>0.015184</v>
+        <v>0.03706</v>
       </c>
       <c r="G22" s="7">
-        <v>0.141463</v>
+        <v>0.15859600000000001</v>
       </c>
       <c r="H22" s="7">
-        <v>0.14826499999999998</v>
+        <v>0.157378</v>
       </c>
       <c r="I22" s="7">
-        <v>0.479675</v>
+        <v>0.491418</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.023959</v>
+        <v>-0.033264</v>
       </c>
       <c r="F23" s="7">
-        <v>0.015489</v>
+        <v>0.01564</v>
       </c>
       <c r="G23" s="7">
-        <v>0.33291</v>
+        <v>0.325255</v>
       </c>
       <c r="H23" s="7">
-        <v>0.273831</v>
+        <v>0.26168800000000003</v>
       </c>
       <c r="I23" s="7">
-        <v>0.539817</v>
+        <v>0.525138</v>
       </c>
       <c r="J23" s="7">
-        <v>2.393724</v>
+        <v>2.371188</v>
       </c>
       <c r="K23" s="7">
-        <v>10.629712</v>
+        <v>10.847206000000002</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.125542</v>
+        <v>-0.11084300000000001</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.23228300000000002</v>
+        <v>-0.225115</v>
       </c>
       <c r="G24" s="7">
-        <v>0.023118</v>
+        <v>0.025285000000000002</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.060818000000000004</v>
+        <v>-0.045031</v>
       </c>
       <c r="I24" s="7">
-        <v>0.26446000000000003</v>
+        <v>0.285714</v>
       </c>
       <c r="J24" s="7">
-        <v>3.237506</v>
+        <v>3.1931819999999997</v>
       </c>
       <c r="K24" s="7">
-        <v>14.442553</v>
+        <v>15.155867</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.029817</v>
+        <v>-0.028815</v>
       </c>
       <c r="F25" s="7">
-        <v>0.009385</v>
+        <v>0.025939999999999998</v>
       </c>
       <c r="G25" s="7">
-        <v>0.32150199999999995</v>
+        <v>0.339786</v>
       </c>
       <c r="H25" s="7">
-        <v>0.308993</v>
+        <v>0.31034500000000004</v>
       </c>
       <c r="I25" s="7">
-        <v>0.517836</v>
+        <v>0.519404</v>
       </c>
       <c r="J25" s="7">
-        <v>1.9848910000000002</v>
+        <v>1.9907409999999999</v>
       </c>
       <c r="K25" s="7">
-        <v>9.369577</v>
+        <v>9.754717000000001</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1398,10 +1398,10 @@
         <v>-0.030714</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.068966</v>
+        <v>-0.064305</v>
       </c>
       <c r="G26" s="7">
-        <v>0.153299</v>
+        <v>0.158246</v>
       </c>
       <c r="H26" s="7">
         <v>0.11009600000000001</v>
@@ -1410,7 +1410,7 @@
         <v>0.306452</v>
       </c>
       <c r="J26" s="7">
-        <v>1.541309</v>
+        <v>1.50309</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.039175</v>
+        <v>-0.020274999999999998</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.11294399999999999</v>
+        <v>-0.092038</v>
       </c>
       <c r="G27" s="7">
-        <v>0.086247</v>
+        <v>0.107615</v>
       </c>
       <c r="H27" s="7">
-        <v>0.000716</v>
+        <v>0.020401</v>
       </c>
       <c r="I27" s="7">
-        <v>0.600641</v>
+        <v>0.632127</v>
       </c>
       <c r="J27" s="7">
-        <v>3.75672</v>
+        <v>3.8354820000000003</v>
       </c>
       <c r="K27" s="7">
-        <v>12.759843</v>
+        <v>12.775609</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.056338</v>
+        <v>0.074824</v>
       </c>
       <c r="F28" s="7">
-        <v>0.28113900000000003</v>
+        <v>0.31762599999999996</v>
       </c>
       <c r="G28" s="7">
-        <v>0.59292</v>
+        <v>0.628724</v>
       </c>
       <c r="H28" s="7">
-        <v>0.473598</v>
+        <v>0.499386</v>
       </c>
       <c r="I28" s="7">
-        <v>0.777778</v>
+        <v>0.8088890000000001</v>
       </c>
       <c r="J28" s="7">
-        <v>2.550296</v>
+        <v>2.584149</v>
       </c>
       <c r="K28" s="7">
-        <v>7.789063</v>
+        <v>8.31587</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.023312</v>
+        <v>0.020069</v>
       </c>
       <c r="F29" s="7">
-        <v>0.15251099999999998</v>
+        <v>0.165894</v>
       </c>
       <c r="G29" s="7">
-        <v>0.476023</v>
+        <v>0.488317</v>
       </c>
       <c r="H29" s="7">
-        <v>0.36432400000000004</v>
+        <v>0.36</v>
       </c>
       <c r="I29" s="7">
-        <v>0.7175910000000001</v>
+        <v>0.712147</v>
       </c>
       <c r="J29" s="7">
-        <v>2.734833</v>
+        <v>2.7263029999999997</v>
       </c>
       <c r="K29" s="7">
-        <v>11.360431</v>
+        <v>11.836735000000001</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.009785</v>
+        <v>-0.013699</v>
       </c>
       <c r="F30" s="7">
-        <v>0.11946899999999999</v>
+        <v>0.127769</v>
       </c>
       <c r="G30" s="7">
-        <v>0.442006</v>
+        <v>0.445369</v>
       </c>
       <c r="H30" s="7">
-        <v>0.390874</v>
+        <v>0.385377</v>
       </c>
       <c r="I30" s="7">
-        <v>0.650897</v>
+        <v>0.6443720000000001</v>
       </c>
       <c r="J30" s="7">
-        <v>2.406031</v>
+        <v>2.386187</v>
       </c>
       <c r="K30" s="7">
-        <v>11.18103</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.039565</v>
+        <v>0.063478</v>
       </c>
       <c r="F31" s="7">
-        <v>0.213213</v>
+        <v>0.235104</v>
       </c>
       <c r="G31" s="7">
-        <v>0.5</v>
+        <v>0.557565</v>
       </c>
       <c r="H31" s="7">
-        <v>0.46399700000000005</v>
+        <v>0.497673</v>
       </c>
       <c r="I31" s="7">
-        <v>0.525651</v>
+        <v>0.560745</v>
       </c>
       <c r="J31" s="7">
-        <v>3.375915</v>
+        <v>3.4295549999999997</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.034294</v>
+        <v>-0.027984</v>
       </c>
       <c r="F32" s="7">
-        <v>0.025341999999999996</v>
+        <v>0.071364</v>
       </c>
       <c r="G32" s="7">
-        <v>0.38364800000000004</v>
+        <v>0.394882</v>
       </c>
       <c r="H32" s="7">
-        <v>0.365929</v>
+        <v>0.37485399999999997</v>
       </c>
       <c r="I32" s="7">
-        <v>0.540481</v>
+        <v>0.550547</v>
       </c>
       <c r="J32" s="7">
-        <v>1.7244579999999998</v>
+        <v>1.755912</v>
       </c>
       <c r="K32" s="7">
-        <v>8.508374</v>
+        <v>8.869081</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.07368000000000001</v>
+        <v>-0.065047</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.048659999999999995</v>
+        <v>-0.032010000000000004</v>
       </c>
       <c r="G33" s="7">
-        <v>0.22517299999999998</v>
+        <v>0.232989</v>
       </c>
       <c r="H33" s="7">
-        <v>0.171066</v>
+        <v>0.18198</v>
       </c>
       <c r="I33" s="7">
-        <v>0.411441</v>
+        <v>0.424595</v>
       </c>
       <c r="J33" s="7">
-        <v>2.390154</v>
+        <v>2.434366</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.036884</v>
+        <v>0.037711999999999996</v>
       </c>
       <c r="F34" s="7">
-        <v>0.10708000000000001</v>
+        <v>0.107475</v>
       </c>
       <c r="G34" s="7">
-        <v>0.215051</v>
+        <v>0.21479800000000002</v>
       </c>
       <c r="H34" s="7">
-        <v>0.16534700000000002</v>
+        <v>0.166279</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.021831999999999997</v>
+        <v>-0.033546</v>
       </c>
       <c r="F35" s="7">
-        <v>-0.019743999999999998</v>
+        <v>-0.020772</v>
       </c>
       <c r="G35" s="7">
-        <v>0.270401</v>
+        <v>0.256055</v>
       </c>
       <c r="H35" s="7">
-        <v>0.22385100000000002</v>
+        <v>0.209194</v>
       </c>
       <c r="I35" s="7">
-        <v>0.47787599999999997</v>
+        <v>0.460177</v>
       </c>
       <c r="J35" s="7">
-        <v>2.5477019999999997</v>
+        <v>2.522904</v>
       </c>
       <c r="K35" s="7">
-        <v>9.473203999999999</v>
+        <v>9.663925</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.037697</v>
+        <v>0.038525000000000004</v>
       </c>
       <c r="F36" s="7">
-        <v>0.107917</v>
+        <v>0.107332</v>
       </c>
       <c r="G36" s="7">
-        <v>0.216175</v>
+        <v>0.21590900000000002</v>
       </c>
       <c r="H36" s="7">
-        <v>0.16674399999999998</v>
+        <v>0.16767600000000002</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>26.05.2026 11:05:03</t>
+    <t>01.06.2026 17:40:14</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.105306</v>
+        <v>-0.111111</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.21706299999999998</v>
+        <v>-0.222783</v>
       </c>
       <c r="G6" s="7">
-        <v>0.030806</v>
+        <v>-0.008052</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.04185</v>
+        <v>-0.05022</v>
       </c>
       <c r="I6" s="7">
-        <v>0.281674</v>
+        <v>0.311436</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.023526</v>
+        <v>-0.067384</v>
       </c>
       <c r="F7" s="7">
-        <v>0.10930899999999999</v>
+        <v>0.089168</v>
       </c>
       <c r="G7" s="7">
-        <v>0.413701</v>
+        <v>0.380356</v>
       </c>
       <c r="H7" s="7">
-        <v>0.361091</v>
+        <v>0.341194</v>
       </c>
       <c r="I7" s="7">
-        <v>0.61451</v>
+        <v>0.642599</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.034925000000000005</v>
+        <v>-0.048144</v>
       </c>
       <c r="F8" s="7">
-        <v>0.011588000000000001</v>
+        <v>0.002112</v>
       </c>
       <c r="G8" s="7">
-        <v>0.314061</v>
+        <v>0.291156</v>
       </c>
       <c r="H8" s="7">
-        <v>0.256872</v>
+        <v>0.242147</v>
       </c>
       <c r="I8" s="7">
-        <v>0.523602</v>
+        <v>0.560214</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.036759</v>
+        <v>0.029756</v>
       </c>
       <c r="F9" s="7">
-        <v>0.104563</v>
+        <v>0.101136</v>
       </c>
       <c r="G9" s="7">
-        <v>0.210669</v>
+        <v>0.20522400000000002</v>
       </c>
       <c r="H9" s="7">
-        <v>0.163396</v>
+        <v>0.16419699999999998</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.044321</v>
+        <v>0.017979000000000002</v>
       </c>
       <c r="F10" s="7">
-        <v>0.21927600000000003</v>
+        <v>0.220444</v>
       </c>
       <c r="G10" s="7">
-        <v>0.275804</v>
+        <v>0.289065</v>
       </c>
       <c r="H10" s="7">
-        <v>0.304498</v>
+        <v>0.29308</v>
       </c>
       <c r="I10" s="7">
-        <v>0.515273</v>
+        <v>0.56885</v>
       </c>
       <c r="J10" s="7">
-        <v>1.440919</v>
+        <v>1.20537</v>
       </c>
       <c r="K10" s="7">
-        <v>7.7107209999999995</v>
+        <v>7.483541</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.004791</v>
+        <v>0.006228</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.104273</v>
+        <v>-0.126978</v>
       </c>
       <c r="G11" s="7">
-        <v>0.16820000000000002</v>
+        <v>0.147757</v>
       </c>
       <c r="H11" s="7">
-        <v>0.069757</v>
+        <v>0.058989</v>
       </c>
       <c r="I11" s="7">
-        <v>0.5885710000000001</v>
+        <v>0.604711</v>
       </c>
       <c r="J11" s="7">
-        <v>3.663265</v>
+        <v>3.623876</v>
       </c>
       <c r="K11" s="7">
-        <v>11.527412</v>
+        <v>11.352556</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.045306</v>
+        <v>0.061538</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.106844</v>
+        <v>-0.148405</v>
       </c>
       <c r="G12" s="7">
-        <v>0.673242</v>
+        <v>0.522933</v>
       </c>
       <c r="H12" s="7">
-        <v>0.121743</v>
+        <v>0.10035</v>
       </c>
       <c r="I12" s="7">
-        <v>1.773077</v>
+        <v>1.730695</v>
       </c>
       <c r="J12" s="7">
-        <v>5.8083100000000005</v>
+        <v>5.5064400000000004</v>
       </c>
       <c r="K12" s="7">
-        <v>13.518726999999998</v>
+        <v>13.196106</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.020868</v>
+        <v>0.018392</v>
       </c>
       <c r="F13" s="7">
-        <v>0.04897700000000001</v>
+        <v>0.049574999999999994</v>
       </c>
       <c r="G13" s="7">
-        <v>0.089046</v>
+        <v>0.090381</v>
       </c>
       <c r="H13" s="7">
-        <v>0.071429</v>
+        <v>0.074913</v>
       </c>
       <c r="I13" s="7">
-        <v>0.17816099999999999</v>
+        <v>0.17619800000000002</v>
       </c>
       <c r="J13" s="7">
-        <v>1.112365</v>
+        <v>1.113014</v>
       </c>
       <c r="K13" s="7">
-        <v>4.301724</v>
+        <v>4.320276</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.033149000000000005</v>
+        <v>-0.026761</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.146341</v>
+        <v>-0.157317</v>
       </c>
       <c r="G14" s="7">
-        <v>0.092044</v>
+        <v>0.066358</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.005682</v>
+        <v>-0.018466</v>
       </c>
       <c r="I14" s="7">
-        <v>0.612903</v>
+        <v>0.629333</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.021852999999999997</v>
+        <v>-0.00357</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.022205</v>
+        <v>-0.015545999999999999</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.050205</v>
+        <v>-0.043429</v>
       </c>
       <c r="G17" s="7">
-        <v>0.22670500000000002</v>
+        <v>0.21486799999999998</v>
       </c>
       <c r="H17" s="7">
-        <v>0.17209700000000003</v>
+        <v>0.16246</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,10 +1139,10 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.036392</v>
+        <v>0.029354</v>
       </c>
       <c r="F18" s="7">
-        <v>0.102793</v>
+        <v>0.09841</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.027471000000000002</v>
+        <v>-0.014846999999999999</v>
       </c>
       <c r="F19" s="7">
-        <v>0.205716</v>
+        <v>0.182899</v>
       </c>
       <c r="G19" s="7">
-        <v>0.533066</v>
+        <v>0.516935</v>
       </c>
       <c r="H19" s="7">
-        <v>0.460548</v>
+        <v>0.442432</v>
       </c>
       <c r="I19" s="7">
-        <v>0.7828010000000001</v>
+        <v>0.8469070000000001</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.032461000000000004</v>
+        <v>-0.042563000000000004</v>
       </c>
       <c r="F20" s="7">
-        <v>0.015441</v>
+        <v>0.014874</v>
       </c>
       <c r="G20" s="7">
-        <v>0.321531</v>
+        <v>0.291483</v>
       </c>
       <c r="H20" s="7">
-        <v>0.256597</v>
+        <v>0.241735</v>
       </c>
       <c r="I20" s="7">
-        <v>0.514254</v>
+        <v>0.5525220000000001</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.038986</v>
+        <v>-0.047402</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.036798000000000004</v>
+        <v>-0.031238000000000002</v>
       </c>
       <c r="G21" s="7">
-        <v>0.223614</v>
+        <v>0.199904</v>
       </c>
       <c r="H21" s="7">
-        <v>0.17274799999999998</v>
+        <v>0.160277</v>
       </c>
       <c r="I21" s="7">
-        <v>0.39928400000000003</v>
+        <v>0.431747</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.036475</v>
+        <v>-0.027697</v>
       </c>
       <c r="F22" s="7">
-        <v>0.03706</v>
+        <v>0.048412</v>
       </c>
       <c r="G22" s="7">
-        <v>0.15859600000000001</v>
+        <v>0.168535</v>
       </c>
       <c r="H22" s="7">
-        <v>0.157378</v>
+        <v>0.168945</v>
       </c>
       <c r="I22" s="7">
-        <v>0.491418</v>
+        <v>0.558411</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.033264</v>
+        <v>-0.049131</v>
       </c>
       <c r="F23" s="7">
-        <v>0.01564</v>
+        <v>0.004652</v>
       </c>
       <c r="G23" s="7">
-        <v>0.325255</v>
+        <v>0.28863099999999997</v>
       </c>
       <c r="H23" s="7">
-        <v>0.26168800000000003</v>
+        <v>0.24559799999999998</v>
       </c>
       <c r="I23" s="7">
-        <v>0.525138</v>
+        <v>0.561858</v>
       </c>
       <c r="J23" s="7">
-        <v>2.371188</v>
+        <v>2.016025</v>
       </c>
       <c r="K23" s="7">
-        <v>10.847206000000002</v>
+        <v>10.512346</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.11084300000000001</v>
+        <v>-0.08520699999999999</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.225115</v>
+        <v>-0.220732</v>
       </c>
       <c r="G24" s="7">
-        <v>0.025285000000000002</v>
+        <v>0.003014</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.045031</v>
+        <v>-0.052536</v>
       </c>
       <c r="I24" s="7">
-        <v>0.285714</v>
+        <v>0.31596</v>
       </c>
       <c r="J24" s="7">
-        <v>3.1931819999999997</v>
+        <v>2.741823</v>
       </c>
       <c r="K24" s="7">
-        <v>15.155867</v>
+        <v>14.712446</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.028815</v>
+        <v>-0.046902</v>
       </c>
       <c r="F25" s="7">
-        <v>0.025939999999999998</v>
+        <v>0.0052910000000000006</v>
       </c>
       <c r="G25" s="7">
-        <v>0.339786</v>
+        <v>0.30809000000000003</v>
       </c>
       <c r="H25" s="7">
-        <v>0.31034500000000004</v>
+        <v>0.284652</v>
       </c>
       <c r="I25" s="7">
-        <v>0.519404</v>
+        <v>0.5605749999999999</v>
       </c>
       <c r="J25" s="7">
-        <v>1.9907409999999999</v>
+        <v>1.6235849999999998</v>
       </c>
       <c r="K25" s="7">
-        <v>9.754717000000001</v>
+        <v>9.371179</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.030714</v>
+        <v>-0.033644</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.064305</v>
+        <v>-0.064731</v>
       </c>
       <c r="G26" s="7">
-        <v>0.158246</v>
+        <v>0.141216</v>
       </c>
       <c r="H26" s="7">
-        <v>0.11009600000000001</v>
+        <v>0.08908200000000001</v>
       </c>
       <c r="I26" s="7">
-        <v>0.306452</v>
+        <v>0.36073099999999997</v>
       </c>
       <c r="J26" s="7">
-        <v>1.50309</v>
+        <v>1.2363979999999999</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.020274999999999998</v>
+        <v>-0.014045</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.092038</v>
+        <v>-0.140759</v>
       </c>
       <c r="G27" s="7">
-        <v>0.107615</v>
+        <v>0.08837199999999999</v>
       </c>
       <c r="H27" s="7">
-        <v>0.020401</v>
+        <v>0.005011</v>
       </c>
       <c r="I27" s="7">
-        <v>0.632127</v>
+        <v>0.636364</v>
       </c>
       <c r="J27" s="7">
-        <v>3.8354820000000003</v>
+        <v>3.8016419999999997</v>
       </c>
       <c r="K27" s="7">
-        <v>12.775609</v>
+        <v>12.463751</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.074824</v>
+        <v>0.015035</v>
       </c>
       <c r="F28" s="7">
-        <v>0.31762599999999996</v>
+        <v>0.28335699999999997</v>
       </c>
       <c r="G28" s="7">
-        <v>0.628724</v>
+        <v>0.597321</v>
       </c>
       <c r="H28" s="7">
-        <v>0.499386</v>
+        <v>0.464593</v>
       </c>
       <c r="I28" s="7">
-        <v>0.8088890000000001</v>
+        <v>0.879992</v>
       </c>
       <c r="J28" s="7">
-        <v>2.584149</v>
+        <v>2.139698</v>
       </c>
       <c r="K28" s="7">
-        <v>8.31587</v>
+        <v>8.090447000000001</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.020069</v>
+        <v>-0.014573000000000001</v>
       </c>
       <c r="F29" s="7">
-        <v>0.165894</v>
+        <v>0.15459199999999998</v>
       </c>
       <c r="G29" s="7">
-        <v>0.488317</v>
+        <v>0.456345</v>
       </c>
       <c r="H29" s="7">
-        <v>0.36</v>
+        <v>0.352432</v>
       </c>
       <c r="I29" s="7">
-        <v>0.712147</v>
+        <v>0.772582</v>
       </c>
       <c r="J29" s="7">
-        <v>2.7263029999999997</v>
+        <v>2.356587</v>
       </c>
       <c r="K29" s="7">
-        <v>11.836735000000001</v>
+        <v>11.48503</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.013699</v>
+        <v>-0.05066</v>
       </c>
       <c r="F30" s="7">
-        <v>0.127769</v>
+        <v>0.088098</v>
       </c>
       <c r="G30" s="7">
-        <v>0.445369</v>
+        <v>0.392257</v>
       </c>
       <c r="H30" s="7">
-        <v>0.385377</v>
+        <v>0.34442</v>
       </c>
       <c r="I30" s="7">
-        <v>0.6443720000000001</v>
+        <v>0.649022</v>
       </c>
       <c r="J30" s="7">
-        <v>2.386187</v>
+        <v>1.975061</v>
       </c>
       <c r="K30" s="7">
-        <v>11.6</v>
+        <v>11.190926999999999</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.063478</v>
+        <v>0.07094299999999999</v>
       </c>
       <c r="F31" s="7">
-        <v>0.235104</v>
+        <v>0.271948</v>
       </c>
       <c r="G31" s="7">
-        <v>0.557565</v>
+        <v>0.624774</v>
       </c>
       <c r="H31" s="7">
-        <v>0.497673</v>
+        <v>0.5435949999999999</v>
       </c>
       <c r="I31" s="7">
-        <v>0.560745</v>
+        <v>0.706145</v>
       </c>
       <c r="J31" s="7">
-        <v>3.4295549999999997</v>
+        <v>3.1314319999999998</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.027984</v>
+        <v>-0.043178999999999995</v>
       </c>
       <c r="F32" s="7">
-        <v>0.071364</v>
+        <v>0.055522</v>
       </c>
       <c r="G32" s="7">
-        <v>0.394882</v>
+        <v>0.361644</v>
       </c>
       <c r="H32" s="7">
-        <v>0.37485399999999997</v>
+        <v>0.35001899999999997</v>
       </c>
       <c r="I32" s="7">
-        <v>0.550547</v>
+        <v>0.582803</v>
       </c>
       <c r="J32" s="7">
-        <v>1.755912</v>
+        <v>1.432867</v>
       </c>
       <c r="K32" s="7">
-        <v>8.869081</v>
+        <v>8.573473</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.065047</v>
+        <v>-0.068629</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.032010000000000004</v>
+        <v>-0.037154</v>
       </c>
       <c r="G33" s="7">
-        <v>0.232989</v>
+        <v>0.204253</v>
       </c>
       <c r="H33" s="7">
-        <v>0.18198</v>
+        <v>0.164213</v>
       </c>
       <c r="I33" s="7">
-        <v>0.424595</v>
+        <v>0.45388300000000004</v>
       </c>
       <c r="J33" s="7">
-        <v>2.434366</v>
+        <v>2.082661</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.037711999999999996</v>
+        <v>0.030440000000000002</v>
       </c>
       <c r="F34" s="7">
-        <v>0.107475</v>
+        <v>0.103038</v>
       </c>
       <c r="G34" s="7">
-        <v>0.21479800000000002</v>
+        <v>0.207229</v>
       </c>
       <c r="H34" s="7">
-        <v>0.166279</v>
+        <v>0.16674399999999998</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.033546</v>
+        <v>-0.045406</v>
       </c>
       <c r="F35" s="7">
-        <v>-0.020772</v>
+        <v>-0.019479</v>
       </c>
       <c r="G35" s="7">
-        <v>0.256055</v>
+        <v>0.22817900000000002</v>
       </c>
       <c r="H35" s="7">
-        <v>0.209194</v>
+        <v>0.19054</v>
       </c>
       <c r="I35" s="7">
-        <v>0.460177</v>
+        <v>0.490409</v>
       </c>
       <c r="J35" s="7">
-        <v>2.522904</v>
+        <v>2.170688</v>
       </c>
       <c r="K35" s="7">
-        <v>9.663925</v>
+        <v>9.159181</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.038525000000000004</v>
+        <v>0.030004</v>
       </c>
       <c r="F36" s="7">
-        <v>0.107332</v>
+        <v>0.102508</v>
       </c>
       <c r="G36" s="7">
-        <v>0.21590900000000002</v>
+        <v>0.207711</v>
       </c>
       <c r="H36" s="7">
-        <v>0.16767600000000002</v>
+        <v>0.16721</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>01.06.2026 17:40:14</t>
+    <t>02.06.2026 11:23:08</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.111111</v>
+        <v>-0.11028700000000001</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.222783</v>
+        <v>-0.22206199999999998</v>
       </c>
       <c r="G6" s="7">
-        <v>-0.008052</v>
+        <v>-0.041953</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.05022</v>
+        <v>-0.049339</v>
       </c>
       <c r="I6" s="7">
-        <v>0.311436</v>
+        <v>0.312652</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.067384</v>
+        <v>-0.068409</v>
       </c>
       <c r="F7" s="7">
-        <v>0.089168</v>
+        <v>0.08797100000000001</v>
       </c>
       <c r="G7" s="7">
-        <v>0.380356</v>
+        <v>0.36384099999999997</v>
       </c>
       <c r="H7" s="7">
-        <v>0.341194</v>
+        <v>0.33972</v>
       </c>
       <c r="I7" s="7">
-        <v>0.642599</v>
+        <v>0.6407940000000001</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.048144</v>
+        <v>-0.05015</v>
       </c>
       <c r="F8" s="7">
-        <v>0.002112</v>
+        <v>0</v>
       </c>
       <c r="G8" s="7">
-        <v>0.291156</v>
+        <v>0.263509</v>
       </c>
       <c r="H8" s="7">
-        <v>0.242147</v>
+        <v>0.239529</v>
       </c>
       <c r="I8" s="7">
-        <v>0.560214</v>
+        <v>0.556926</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.029756</v>
+        <v>0.030464</v>
       </c>
       <c r="F9" s="7">
-        <v>0.101136</v>
+        <v>0.10189399999999998</v>
       </c>
       <c r="G9" s="7">
-        <v>0.20522400000000002</v>
+        <v>0.20480399999999999</v>
       </c>
       <c r="H9" s="7">
-        <v>0.16419699999999998</v>
+        <v>0.164998</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.017979000000000002</v>
+        <v>0.052029</v>
       </c>
       <c r="F10" s="7">
-        <v>0.220444</v>
+        <v>0.26126699999999997</v>
       </c>
       <c r="G10" s="7">
-        <v>0.289065</v>
+        <v>0.308266</v>
       </c>
       <c r="H10" s="7">
-        <v>0.29308</v>
+        <v>0.336332</v>
       </c>
       <c r="I10" s="7">
-        <v>0.56885</v>
+        <v>0.621327</v>
       </c>
       <c r="J10" s="7">
-        <v>1.20537</v>
+        <v>1.244696</v>
       </c>
       <c r="K10" s="7">
-        <v>7.483541</v>
+        <v>7.651434</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.006228</v>
+        <v>-0.011121</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.126978</v>
+        <v>-0.14203</v>
       </c>
       <c r="G11" s="7">
-        <v>0.147757</v>
+        <v>0.106521</v>
       </c>
       <c r="H11" s="7">
-        <v>0.058989</v>
+        <v>0.04073</v>
       </c>
       <c r="I11" s="7">
-        <v>0.604711</v>
+        <v>0.5770430000000001</v>
       </c>
       <c r="J11" s="7">
-        <v>3.623876</v>
+        <v>3.5571960000000002</v>
       </c>
       <c r="K11" s="7">
-        <v>11.352556</v>
+        <v>11.179487</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.061538</v>
+        <v>0.039024</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.148405</v>
+        <v>-0.166466</v>
       </c>
       <c r="G12" s="7">
-        <v>0.522933</v>
+        <v>0.415934</v>
       </c>
       <c r="H12" s="7">
-        <v>0.10035</v>
+        <v>0.077013</v>
       </c>
       <c r="I12" s="7">
-        <v>1.730695</v>
+        <v>1.67278</v>
       </c>
       <c r="J12" s="7">
-        <v>5.5064400000000004</v>
+        <v>5.293182000000001</v>
       </c>
       <c r="K12" s="7">
-        <v>13.196106</v>
+        <v>12.856085</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.018392</v>
+        <v>0.015091</v>
       </c>
       <c r="F13" s="7">
-        <v>0.049574999999999994</v>
+        <v>0.046173</v>
       </c>
       <c r="G13" s="7">
-        <v>0.090381</v>
+        <v>0.089322</v>
       </c>
       <c r="H13" s="7">
-        <v>0.074913</v>
+        <v>0.071429</v>
       </c>
       <c r="I13" s="7">
-        <v>0.17619800000000002</v>
+        <v>0.172386</v>
       </c>
       <c r="J13" s="7">
-        <v>1.113014</v>
+        <v>1.119645</v>
       </c>
       <c r="K13" s="7">
-        <v>4.320276</v>
+        <v>4.299114</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.026761</v>
+        <v>-0.028169</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.157317</v>
+        <v>-0.158537</v>
       </c>
       <c r="G14" s="7">
-        <v>0.066358</v>
+        <v>0.050228</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.018466</v>
+        <v>-0.019886</v>
       </c>
       <c r="I14" s="7">
-        <v>0.629333</v>
+        <v>0.626975</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.00357</v>
+        <v>-0.018742</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.015545999999999999</v>
+        <v>-0.014379999999999999</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.043429</v>
+        <v>-0.04229599999999999</v>
       </c>
       <c r="G17" s="7">
-        <v>0.21486799999999998</v>
+        <v>0.19061</v>
       </c>
       <c r="H17" s="7">
-        <v>0.16246</v>
+        <v>0.163837</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.029354</v>
+        <v>0.030449</v>
       </c>
       <c r="F18" s="7">
-        <v>0.09841</v>
+        <v>0.099579</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.16551300000000002</v>
+        <v>0.166753</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.014846999999999999</v>
+        <v>-0.004399</v>
       </c>
       <c r="F19" s="7">
-        <v>0.182899</v>
+        <v>0.195444</v>
       </c>
       <c r="G19" s="7">
-        <v>0.516935</v>
+        <v>0.50875</v>
       </c>
       <c r="H19" s="7">
-        <v>0.442432</v>
+        <v>0.457729</v>
       </c>
       <c r="I19" s="7">
-        <v>0.8469070000000001</v>
+        <v>0.866495</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.042563000000000004</v>
+        <v>-0.042329</v>
       </c>
       <c r="F20" s="7">
-        <v>0.014874</v>
+        <v>0.015121</v>
       </c>
       <c r="G20" s="7">
-        <v>0.291483</v>
+        <v>0.270555</v>
       </c>
       <c r="H20" s="7">
-        <v>0.241735</v>
+        <v>0.242038</v>
       </c>
       <c r="I20" s="7">
-        <v>0.5525220000000001</v>
+        <v>0.552901</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.047402</v>
+        <v>-0.046265</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.031238000000000002</v>
+        <v>-0.030081000000000004</v>
       </c>
       <c r="G21" s="7">
-        <v>0.199904</v>
+        <v>0.176883</v>
       </c>
       <c r="H21" s="7">
-        <v>0.160277</v>
+        <v>0.161663</v>
       </c>
       <c r="I21" s="7">
-        <v>0.431747</v>
+        <v>0.433457</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.027697</v>
+        <v>-0.033819</v>
       </c>
       <c r="F22" s="7">
-        <v>0.048412</v>
+        <v>0.041811</v>
       </c>
       <c r="G22" s="7">
-        <v>0.168535</v>
+        <v>0.14592</v>
       </c>
       <c r="H22" s="7">
-        <v>0.168945</v>
+        <v>0.161584</v>
       </c>
       <c r="I22" s="7">
-        <v>0.558411</v>
+        <v>0.548598</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.049131</v>
+        <v>-0.051448</v>
       </c>
       <c r="F23" s="7">
-        <v>0.004652</v>
+        <v>0.0022040000000000002</v>
       </c>
       <c r="G23" s="7">
-        <v>0.28863099999999997</v>
+        <v>0.262103</v>
       </c>
       <c r="H23" s="7">
-        <v>0.24559799999999998</v>
+        <v>0.242562</v>
       </c>
       <c r="I23" s="7">
-        <v>0.561858</v>
+        <v>0.5580510000000001</v>
       </c>
       <c r="J23" s="7">
-        <v>2.016025</v>
+        <v>1.9702469999999999</v>
       </c>
       <c r="K23" s="7">
-        <v>10.512346</v>
+        <v>10.350527</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.08520699999999999</v>
+        <v>-0.08620699999999999</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.220732</v>
+        <v>-0.221584</v>
       </c>
       <c r="G24" s="7">
-        <v>0.003014</v>
+        <v>-0.045668</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.052536</v>
+        <v>-0.053571</v>
       </c>
       <c r="I24" s="7">
-        <v>0.31596</v>
+        <v>0.314522</v>
       </c>
       <c r="J24" s="7">
-        <v>2.741823</v>
+        <v>2.700668</v>
       </c>
       <c r="K24" s="7">
-        <v>14.712446</v>
+        <v>14.404381</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.046902</v>
+        <v>-0.043391</v>
       </c>
       <c r="F25" s="7">
-        <v>0.0052910000000000006</v>
+        <v>0.008995</v>
       </c>
       <c r="G25" s="7">
-        <v>0.30809000000000003</v>
+        <v>0.289385</v>
       </c>
       <c r="H25" s="7">
-        <v>0.284652</v>
+        <v>0.289385</v>
       </c>
       <c r="I25" s="7">
-        <v>0.5605749999999999</v>
+        <v>0.5663239999999999</v>
       </c>
       <c r="J25" s="7">
-        <v>1.6235849999999998</v>
+        <v>1.605903</v>
       </c>
       <c r="K25" s="7">
-        <v>9.371179</v>
+        <v>9.285868</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.033644</v>
+        <v>-0.023105</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.064731</v>
+        <v>-0.054531</v>
       </c>
       <c r="G26" s="7">
-        <v>0.141216</v>
+        <v>0.119888</v>
       </c>
       <c r="H26" s="7">
-        <v>0.08908200000000001</v>
+        <v>0.10095900000000001</v>
       </c>
       <c r="I26" s="7">
-        <v>0.36073099999999997</v>
+        <v>0.375571</v>
       </c>
       <c r="J26" s="7">
-        <v>1.2363979999999999</v>
+        <v>1.202925</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.014045</v>
+        <v>-0.029845999999999998</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.140759</v>
+        <v>-0.154529</v>
       </c>
       <c r="G27" s="7">
-        <v>0.08837199999999999</v>
+        <v>0.052973</v>
       </c>
       <c r="H27" s="7">
-        <v>0.005011</v>
+        <v>-0.011094999999999999</v>
       </c>
       <c r="I27" s="7">
-        <v>0.636364</v>
+        <v>0.61014</v>
       </c>
       <c r="J27" s="7">
-        <v>3.8016419999999997</v>
+        <v>3.7490550000000002</v>
       </c>
       <c r="K27" s="7">
-        <v>12.463751</v>
+        <v>12.412621</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.015035</v>
+        <v>0.026949999999999998</v>
       </c>
       <c r="F28" s="7">
-        <v>0.28335699999999997</v>
+        <v>0.29842199999999997</v>
       </c>
       <c r="G28" s="7">
-        <v>0.597321</v>
+        <v>0.59894</v>
       </c>
       <c r="H28" s="7">
-        <v>0.464593</v>
+        <v>0.481785</v>
       </c>
       <c r="I28" s="7">
-        <v>0.879992</v>
+        <v>0.9020600000000001</v>
       </c>
       <c r="J28" s="7">
-        <v>2.139698</v>
+        <v>2.116391</v>
       </c>
       <c r="K28" s="7">
-        <v>8.090447000000001</v>
+        <v>8.150657</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.014573000000000001</v>
+        <v>-0.003545</v>
       </c>
       <c r="F29" s="7">
-        <v>0.15459199999999998</v>
+        <v>0.167513</v>
       </c>
       <c r="G29" s="7">
-        <v>0.456345</v>
+        <v>0.467092</v>
       </c>
       <c r="H29" s="7">
-        <v>0.352432</v>
+        <v>0.367568</v>
       </c>
       <c r="I29" s="7">
-        <v>0.772582</v>
+        <v>0.792419</v>
       </c>
       <c r="J29" s="7">
-        <v>2.356587</v>
+        <v>2.3474459999999997</v>
       </c>
       <c r="K29" s="7">
-        <v>11.48503</v>
+        <v>11.568306</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.05066</v>
+        <v>-0.051436</v>
       </c>
       <c r="F30" s="7">
-        <v>0.088098</v>
+        <v>0.08720800000000001</v>
       </c>
       <c r="G30" s="7">
-        <v>0.392257</v>
+        <v>0.365847</v>
       </c>
       <c r="H30" s="7">
-        <v>0.34442</v>
+        <v>0.343321</v>
       </c>
       <c r="I30" s="7">
-        <v>0.649022</v>
+        <v>0.647674</v>
       </c>
       <c r="J30" s="7">
-        <v>1.975061</v>
+        <v>1.942558</v>
       </c>
       <c r="K30" s="7">
-        <v>11.190926999999999</v>
+        <v>11.078596</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.07094299999999999</v>
+        <v>0.060747999999999996</v>
       </c>
       <c r="F31" s="7">
-        <v>0.271948</v>
+        <v>0.259839</v>
       </c>
       <c r="G31" s="7">
-        <v>0.624774</v>
+        <v>0.581581</v>
       </c>
       <c r="H31" s="7">
-        <v>0.5435949999999999</v>
+        <v>0.5289</v>
       </c>
       <c r="I31" s="7">
-        <v>0.706145</v>
+        <v>0.689903</v>
       </c>
       <c r="J31" s="7">
-        <v>3.1314319999999998</v>
+        <v>3.018346</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.043178999999999995</v>
+        <v>-0.043454</v>
       </c>
       <c r="F32" s="7">
-        <v>0.055522</v>
+        <v>0.055217999999999996</v>
       </c>
       <c r="G32" s="7">
-        <v>0.361644</v>
+        <v>0.337692</v>
       </c>
       <c r="H32" s="7">
-        <v>0.35001899999999997</v>
+        <v>0.34963099999999997</v>
       </c>
       <c r="I32" s="7">
-        <v>0.582803</v>
+        <v>0.582348</v>
       </c>
       <c r="J32" s="7">
-        <v>1.432867</v>
+        <v>1.412597</v>
       </c>
       <c r="K32" s="7">
-        <v>8.573473</v>
+        <v>8.466522</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.068629</v>
+        <v>-0.067817</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.037154</v>
+        <v>-0.036314</v>
       </c>
       <c r="G33" s="7">
-        <v>0.204253</v>
+        <v>0.181117</v>
       </c>
       <c r="H33" s="7">
-        <v>0.164213</v>
+        <v>0.165228</v>
       </c>
       <c r="I33" s="7">
-        <v>0.45388300000000004</v>
+        <v>0.455151</v>
       </c>
       <c r="J33" s="7">
-        <v>2.082661</v>
+        <v>2.034369</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.030440000000000002</v>
+        <v>0.031263</v>
       </c>
       <c r="F34" s="7">
-        <v>0.103038</v>
+        <v>0.103919</v>
       </c>
       <c r="G34" s="7">
-        <v>0.207229</v>
+        <v>0.207611</v>
       </c>
       <c r="H34" s="7">
-        <v>0.16674399999999998</v>
+        <v>0.16767600000000002</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.045406</v>
+        <v>-0.041666999999999996</v>
       </c>
       <c r="F35" s="7">
-        <v>-0.019479</v>
+        <v>-0.015638</v>
       </c>
       <c r="G35" s="7">
-        <v>0.22817900000000002</v>
+        <v>0.207268</v>
       </c>
       <c r="H35" s="7">
-        <v>0.19054</v>
+        <v>0.195203</v>
       </c>
       <c r="I35" s="7">
-        <v>0.490409</v>
+        <v>0.496247</v>
       </c>
       <c r="J35" s="7">
-        <v>2.170688</v>
+        <v>2.145161</v>
       </c>
       <c r="K35" s="7">
-        <v>9.159181</v>
+        <v>9.135593</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.030004</v>
+        <v>0.031648</v>
       </c>
       <c r="F36" s="7">
-        <v>0.102508</v>
+        <v>0.104267</v>
       </c>
       <c r="G36" s="7">
-        <v>0.207711</v>
+        <v>0.208474</v>
       </c>
       <c r="H36" s="7">
-        <v>0.16721</v>
+        <v>0.169073</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>02.06.2026 11:23:08</t>
+    <t>03.06.2026 17:43:43</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.11028700000000001</v>
+        <v>-0.071119</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.22206199999999998</v>
+        <v>-0.123346</v>
       </c>
       <c r="G6" s="7">
-        <v>-0.041953</v>
+        <v>0.0067020000000000005</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.049339</v>
+        <v>-0.007489</v>
       </c>
       <c r="I6" s="7">
-        <v>0.312652</v>
+        <v>0.359276</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.068409</v>
+        <v>-0.038432</v>
       </c>
       <c r="F7" s="7">
-        <v>0.08797100000000001</v>
+        <v>0.120633</v>
       </c>
       <c r="G7" s="7">
-        <v>0.36384099999999997</v>
+        <v>0.396205</v>
       </c>
       <c r="H7" s="7">
-        <v>0.33972</v>
+        <v>0.38283</v>
       </c>
       <c r="I7" s="7">
-        <v>0.6407940000000001</v>
+        <v>0.685227</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.05015</v>
+        <v>-0.013791</v>
       </c>
       <c r="F8" s="7">
-        <v>0</v>
+        <v>0.062398999999999996</v>
       </c>
       <c r="G8" s="7">
-        <v>0.263509</v>
+        <v>0.306645</v>
       </c>
       <c r="H8" s="7">
-        <v>0.239529</v>
+        <v>0.286976</v>
       </c>
       <c r="I8" s="7">
-        <v>0.556926</v>
+        <v>0.6099060000000001</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.030464</v>
+        <v>0.031527</v>
       </c>
       <c r="F9" s="7">
-        <v>0.10189399999999998</v>
+        <v>0.101778</v>
       </c>
       <c r="G9" s="7">
-        <v>0.20480399999999999</v>
+        <v>0.204799</v>
       </c>
       <c r="H9" s="7">
-        <v>0.164998</v>
+        <v>0.166199</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.052029</v>
+        <v>0.09452500000000001</v>
       </c>
       <c r="F10" s="7">
-        <v>0.26126699999999997</v>
+        <v>0.38360900000000003</v>
       </c>
       <c r="G10" s="7">
-        <v>0.308266</v>
+        <v>0.367597</v>
       </c>
       <c r="H10" s="7">
-        <v>0.336332</v>
+        <v>0.390311</v>
       </c>
       <c r="I10" s="7">
-        <v>0.621327</v>
+        <v>0.7007410000000001</v>
       </c>
       <c r="J10" s="7">
-        <v>1.244696</v>
+        <v>1.244693</v>
       </c>
       <c r="K10" s="7">
-        <v>7.651434</v>
+        <v>8.029213</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.011121</v>
+        <v>-0.0026690000000000004</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.14203</v>
+        <v>-0.15746000000000002</v>
       </c>
       <c r="G11" s="7">
-        <v>0.106521</v>
+        <v>0.115978</v>
       </c>
       <c r="H11" s="7">
-        <v>0.04073</v>
+        <v>0.049625</v>
       </c>
       <c r="I11" s="7">
-        <v>0.5770430000000001</v>
+        <v>0.547915</v>
       </c>
       <c r="J11" s="7">
-        <v>3.5571960000000002</v>
+        <v>3.6360629999999996</v>
       </c>
       <c r="K11" s="7">
-        <v>11.179487</v>
+        <v>11.160988999999999</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.039024</v>
+        <v>0.050656999999999994</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.166466</v>
+        <v>-0.151258</v>
       </c>
       <c r="G12" s="7">
-        <v>0.415934</v>
+        <v>0.419878</v>
       </c>
       <c r="H12" s="7">
-        <v>0.077013</v>
+        <v>0.08907</v>
       </c>
       <c r="I12" s="7">
-        <v>1.67278</v>
+        <v>1.6138910000000002</v>
       </c>
       <c r="J12" s="7">
-        <v>5.293182000000001</v>
+        <v>5.4220180000000004</v>
       </c>
       <c r="K12" s="7">
-        <v>12.856085</v>
+        <v>12.955343000000001</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.015091</v>
+        <v>0.015798</v>
       </c>
       <c r="F13" s="7">
-        <v>0.046173</v>
+        <v>0.049451999999999996</v>
       </c>
       <c r="G13" s="7">
-        <v>0.089322</v>
+        <v>0.09008100000000001</v>
       </c>
       <c r="H13" s="7">
-        <v>0.071429</v>
+        <v>0.072175</v>
       </c>
       <c r="I13" s="7">
-        <v>0.172386</v>
+        <v>0.17737100000000003</v>
       </c>
       <c r="J13" s="7">
-        <v>1.119645</v>
+        <v>1.1159139999999999</v>
       </c>
       <c r="K13" s="7">
-        <v>4.299114</v>
+        <v>4.2607159999999995</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1040,16 +1040,16 @@
         <v>-0.028169</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.158537</v>
+        <v>-0.18246400000000002</v>
       </c>
       <c r="G14" s="7">
-        <v>0.050228</v>
+        <v>0.061538</v>
       </c>
       <c r="H14" s="7">
         <v>-0.019886</v>
       </c>
       <c r="I14" s="7">
-        <v>0.626975</v>
+        <v>0.593533</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.018742</v>
+        <v>-0.013833</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.014379999999999999</v>
+        <v>0.007383999999999999</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.04229599999999999</v>
+        <v>0.0062109999999999995</v>
       </c>
       <c r="G17" s="7">
-        <v>0.19061</v>
+        <v>0.21462</v>
       </c>
       <c r="H17" s="7">
-        <v>0.163837</v>
+        <v>0.189536</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030449</v>
+        <v>0.031543999999999996</v>
       </c>
       <c r="F18" s="7">
-        <v>0.099579</v>
+        <v>0.099977</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.166753</v>
+        <v>0.16799299999999998</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.004399</v>
+        <v>0.017597</v>
       </c>
       <c r="F19" s="7">
-        <v>0.195444</v>
+        <v>0.24153</v>
       </c>
       <c r="G19" s="7">
-        <v>0.50875</v>
+        <v>0.537279</v>
       </c>
       <c r="H19" s="7">
-        <v>0.457729</v>
+        <v>0.489936</v>
       </c>
       <c r="I19" s="7">
-        <v>0.866495</v>
+        <v>0.912661</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.042329</v>
+        <v>-0.0037419999999999997</v>
       </c>
       <c r="F20" s="7">
-        <v>0.015121</v>
+        <v>0.075486</v>
       </c>
       <c r="G20" s="7">
-        <v>0.270555</v>
+        <v>0.316033</v>
       </c>
       <c r="H20" s="7">
-        <v>0.242038</v>
+        <v>0.292084</v>
       </c>
       <c r="I20" s="7">
-        <v>0.552901</v>
+        <v>0.603916</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.046265</v>
+        <v>-0.025787</v>
       </c>
       <c r="F21" s="7">
-        <v>-0.030081000000000004</v>
+        <v>0.018231999999999998</v>
       </c>
       <c r="G21" s="7">
-        <v>0.176883</v>
+        <v>0.19962599999999997</v>
       </c>
       <c r="H21" s="7">
-        <v>0.161663</v>
+        <v>0.186605</v>
       </c>
       <c r="I21" s="7">
-        <v>0.433457</v>
+        <v>0.463401</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.033819</v>
+        <v>-0.01895</v>
       </c>
       <c r="F22" s="7">
-        <v>0.041811</v>
+        <v>0.099314</v>
       </c>
       <c r="G22" s="7">
-        <v>0.14592</v>
+        <v>0.157153</v>
       </c>
       <c r="H22" s="7">
-        <v>0.161584</v>
+        <v>0.17946</v>
       </c>
       <c r="I22" s="7">
-        <v>0.548598</v>
+        <v>0.5731649999999999</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.051448</v>
+        <v>-0.012978</v>
       </c>
       <c r="F23" s="7">
-        <v>0.0022040000000000002</v>
+        <v>0.065816</v>
       </c>
       <c r="G23" s="7">
-        <v>0.262103</v>
+        <v>0.311268</v>
       </c>
       <c r="H23" s="7">
-        <v>0.242562</v>
+        <v>0.292957</v>
       </c>
       <c r="I23" s="7">
-        <v>0.5580510000000001</v>
+        <v>0.6047480000000001</v>
       </c>
       <c r="J23" s="7">
-        <v>1.9702469999999999</v>
+        <v>1.979989</v>
       </c>
       <c r="K23" s="7">
-        <v>10.350527</v>
+        <v>10.817425</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.08620699999999999</v>
+        <v>-0.036982</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.221584</v>
+        <v>-0.11585200000000001</v>
       </c>
       <c r="G24" s="7">
-        <v>-0.045668</v>
+        <v>0.01341</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.053571</v>
+        <v>-0.0025879999999999996</v>
       </c>
       <c r="I24" s="7">
-        <v>0.314522</v>
+        <v>0.36087600000000003</v>
       </c>
       <c r="J24" s="7">
-        <v>2.700668</v>
+        <v>2.6385950000000005</v>
       </c>
       <c r="K24" s="7">
-        <v>14.404381</v>
+        <v>15.302876000000001</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.043391</v>
+        <v>-0.0037619999999999997</v>
       </c>
       <c r="F25" s="7">
-        <v>0.008995</v>
+        <v>0.08287900000000001</v>
       </c>
       <c r="G25" s="7">
-        <v>0.289385</v>
+        <v>0.344617</v>
       </c>
       <c r="H25" s="7">
-        <v>0.289385</v>
+        <v>0.34279899999999996</v>
       </c>
       <c r="I25" s="7">
-        <v>0.5663239999999999</v>
+        <v>0.623876</v>
       </c>
       <c r="J25" s="7">
-        <v>1.605903</v>
+        <v>1.622821</v>
       </c>
       <c r="K25" s="7">
-        <v>9.285868</v>
+        <v>9.717755</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.023105</v>
+        <v>0.009728</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.054531</v>
+        <v>0.012602</v>
       </c>
       <c r="G26" s="7">
-        <v>0.119888</v>
+        <v>0.15057700000000002</v>
       </c>
       <c r="H26" s="7">
-        <v>0.10095900000000001</v>
+        <v>0.137963</v>
       </c>
       <c r="I26" s="7">
-        <v>0.375571</v>
+        <v>0.437226</v>
       </c>
       <c r="J26" s="7">
-        <v>1.202925</v>
+        <v>1.228883</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.029845999999999998</v>
+        <v>-0.023174</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.154529</v>
+        <v>-0.17935099999999998</v>
       </c>
       <c r="G27" s="7">
-        <v>0.052973</v>
+        <v>0.065084</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.011094999999999999</v>
+        <v>-0.004295</v>
       </c>
       <c r="I27" s="7">
-        <v>0.61014</v>
+        <v>0.591533</v>
       </c>
       <c r="J27" s="7">
-        <v>3.7490550000000002</v>
+        <v>3.799862</v>
       </c>
       <c r="K27" s="7">
-        <v>12.412621</v>
+        <v>12.298279</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.026949999999999998</v>
+        <v>0.060993000000000006</v>
       </c>
       <c r="F28" s="7">
-        <v>0.29842199999999997</v>
+        <v>0.38827</v>
       </c>
       <c r="G28" s="7">
-        <v>0.59894</v>
+        <v>0.626087</v>
       </c>
       <c r="H28" s="7">
-        <v>0.481785</v>
+        <v>0.530905</v>
       </c>
       <c r="I28" s="7">
-        <v>0.9020600000000001</v>
+        <v>0.964286</v>
       </c>
       <c r="J28" s="7">
-        <v>2.116391</v>
+        <v>2.155586</v>
       </c>
       <c r="K28" s="7">
-        <v>8.150657</v>
+        <v>8.506863</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.003545</v>
+        <v>0.014178999999999999</v>
       </c>
       <c r="F29" s="7">
-        <v>0.167513</v>
+        <v>0.207786</v>
       </c>
       <c r="G29" s="7">
-        <v>0.467092</v>
+        <v>0.480736</v>
       </c>
       <c r="H29" s="7">
-        <v>0.367568</v>
+        <v>0.391892</v>
       </c>
       <c r="I29" s="7">
-        <v>0.792419</v>
+        <v>0.812104</v>
       </c>
       <c r="J29" s="7">
-        <v>2.3474459999999997</v>
+        <v>2.316589</v>
       </c>
       <c r="K29" s="7">
-        <v>11.568306</v>
+        <v>11.849301</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.051436</v>
+        <v>-0.017081</v>
       </c>
       <c r="F30" s="7">
-        <v>0.08720800000000001</v>
+        <v>0.125083</v>
       </c>
       <c r="G30" s="7">
-        <v>0.365847</v>
+        <v>0.40901499999999996</v>
       </c>
       <c r="H30" s="7">
-        <v>0.343321</v>
+        <v>0.39197400000000004</v>
       </c>
       <c r="I30" s="7">
-        <v>0.647674</v>
+        <v>0.69762</v>
       </c>
       <c r="J30" s="7">
-        <v>1.942558</v>
+        <v>1.9837379999999998</v>
       </c>
       <c r="K30" s="7">
-        <v>11.078596</v>
+        <v>11.442260000000001</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.060747999999999996</v>
+        <v>0.110875</v>
       </c>
       <c r="F31" s="7">
-        <v>0.259839</v>
+        <v>0.308547</v>
       </c>
       <c r="G31" s="7">
-        <v>0.581581</v>
+        <v>0.647971</v>
       </c>
       <c r="H31" s="7">
-        <v>0.5289</v>
+        <v>0.601151</v>
       </c>
       <c r="I31" s="7">
-        <v>0.689903</v>
+        <v>0.784739</v>
       </c>
       <c r="J31" s="7">
-        <v>3.018346</v>
+        <v>3.088493</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.043454</v>
+        <v>-0.006876</v>
       </c>
       <c r="F32" s="7">
-        <v>0.055217999999999996</v>
+        <v>0.115884</v>
       </c>
       <c r="G32" s="7">
-        <v>0.337692</v>
+        <v>0.392059</v>
       </c>
       <c r="H32" s="7">
-        <v>0.34963099999999997</v>
+        <v>0.40124200000000004</v>
       </c>
       <c r="I32" s="7">
-        <v>0.582348</v>
+        <v>0.647354</v>
       </c>
       <c r="J32" s="7">
-        <v>1.412597</v>
+        <v>1.4118350000000002</v>
       </c>
       <c r="K32" s="7">
-        <v>8.466522</v>
+        <v>8.839237</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.067817</v>
+        <v>-0.034112</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.036314</v>
+        <v>0.024332</v>
       </c>
       <c r="G33" s="7">
-        <v>0.181117</v>
+        <v>0.221623</v>
       </c>
       <c r="H33" s="7">
-        <v>0.165228</v>
+        <v>0.20736000000000002</v>
       </c>
       <c r="I33" s="7">
-        <v>0.455151</v>
+        <v>0.501578</v>
       </c>
       <c r="J33" s="7">
-        <v>2.034369</v>
+        <v>2.0396170000000002</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.031263</v>
+        <v>0.032497</v>
       </c>
       <c r="F34" s="7">
-        <v>0.103919</v>
+        <v>0.104267</v>
       </c>
       <c r="G34" s="7">
-        <v>0.207611</v>
+        <v>0.20731100000000002</v>
       </c>
       <c r="H34" s="7">
-        <v>0.16767600000000002</v>
+        <v>0.169073</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.041666999999999996</v>
+        <v>-0.003205</v>
       </c>
       <c r="F35" s="7">
-        <v>-0.015638</v>
+        <v>0.053047000000000004</v>
       </c>
       <c r="G35" s="7">
-        <v>0.207268</v>
+        <v>0.252769</v>
       </c>
       <c r="H35" s="7">
-        <v>0.195203</v>
+        <v>0.243171</v>
       </c>
       <c r="I35" s="7">
-        <v>0.496247</v>
+        <v>0.551767</v>
       </c>
       <c r="J35" s="7">
-        <v>2.145161</v>
+        <v>2.188653</v>
       </c>
       <c r="K35" s="7">
-        <v>9.135593</v>
+        <v>9.560272</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.031648</v>
+        <v>0.032059000000000004</v>
       </c>
       <c r="F36" s="7">
-        <v>0.104267</v>
+        <v>0.10325100000000001</v>
       </c>
       <c r="G36" s="7">
-        <v>0.208474</v>
+        <v>0.208373</v>
       </c>
       <c r="H36" s="7">
-        <v>0.169073</v>
+        <v>0.169539</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>03.06.2026 17:43:43</t>
+    <t>04.06.2026 10:49:04</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.071119</v>
+        <v>-0.08740500000000001</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.123346</v>
+        <v>-0.08400600000000001</v>
       </c>
       <c r="G6" s="7">
-        <v>0.0067020000000000005</v>
+        <v>-0.021657000000000003</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.007489</v>
+        <v>-0.02489</v>
       </c>
       <c r="I6" s="7">
-        <v>0.359276</v>
+        <v>0.253398</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.038432</v>
+        <v>-0.06226</v>
       </c>
       <c r="F7" s="7">
-        <v>0.120633</v>
+        <v>0.119951</v>
       </c>
       <c r="G7" s="7">
-        <v>0.396205</v>
+        <v>0.37439</v>
       </c>
       <c r="H7" s="7">
-        <v>0.38283</v>
+        <v>0.34856299999999996</v>
       </c>
       <c r="I7" s="7">
-        <v>0.685227</v>
+        <v>0.608791</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.013791</v>
+        <v>-0.036610000000000004</v>
       </c>
       <c r="F8" s="7">
-        <v>0.062398999999999996</v>
+        <v>0.073784</v>
       </c>
       <c r="G8" s="7">
-        <v>0.306645</v>
+        <v>0.283233</v>
       </c>
       <c r="H8" s="7">
-        <v>0.286976</v>
+        <v>0.257199</v>
       </c>
       <c r="I8" s="7">
-        <v>0.6099060000000001</v>
+        <v>0.517977</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.031527</v>
+        <v>0.032589</v>
       </c>
       <c r="F9" s="7">
-        <v>0.101778</v>
+        <v>0.101663</v>
       </c>
       <c r="G9" s="7">
-        <v>0.204799</v>
+        <v>0.20479399999999998</v>
       </c>
       <c r="H9" s="7">
-        <v>0.166199</v>
+        <v>0.16740100000000002</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.09452500000000001</v>
+        <v>0.049305</v>
       </c>
       <c r="F10" s="7">
-        <v>0.38360900000000003</v>
+        <v>0.343096</v>
       </c>
       <c r="G10" s="7">
-        <v>0.367597</v>
+        <v>0.277188</v>
       </c>
       <c r="H10" s="7">
-        <v>0.390311</v>
+        <v>0.332872</v>
       </c>
       <c r="I10" s="7">
-        <v>0.7007410000000001</v>
+        <v>0.610368</v>
       </c>
       <c r="J10" s="7">
-        <v>1.244693</v>
+        <v>1.151955</v>
       </c>
       <c r="K10" s="7">
-        <v>8.029213</v>
+        <v>7.693297</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.0026690000000000004</v>
+        <v>-0.017794</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.15746000000000002</v>
+        <v>-0.120669</v>
       </c>
       <c r="G11" s="7">
-        <v>0.115978</v>
+        <v>0.100149</v>
       </c>
       <c r="H11" s="7">
-        <v>0.049625</v>
+        <v>0.033708</v>
       </c>
       <c r="I11" s="7">
-        <v>0.547915</v>
+        <v>0.540179</v>
       </c>
       <c r="J11" s="7">
-        <v>3.6360629999999996</v>
+        <v>3.5657569999999996</v>
       </c>
       <c r="K11" s="7">
-        <v>11.160988999999999</v>
+        <v>11.028764</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.050656999999999994</v>
+        <v>0.022139000000000002</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.151258</v>
+        <v>-0.080351</v>
       </c>
       <c r="G12" s="7">
-        <v>0.419878</v>
+        <v>0.365824</v>
       </c>
       <c r="H12" s="7">
-        <v>0.08907</v>
+        <v>0.05950999999999999</v>
       </c>
       <c r="I12" s="7">
-        <v>1.6138910000000002</v>
+        <v>1.5231569999999999</v>
       </c>
       <c r="J12" s="7">
-        <v>5.4220180000000004</v>
+        <v>5.247705999999999</v>
       </c>
       <c r="K12" s="7">
-        <v>12.955343000000001</v>
+        <v>12.886623</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.015798</v>
+        <v>0.013675999999999999</v>
       </c>
       <c r="F13" s="7">
-        <v>0.049451999999999996</v>
+        <v>0.041929</v>
       </c>
       <c r="G13" s="7">
-        <v>0.09008100000000001</v>
+        <v>0.08780400000000001</v>
       </c>
       <c r="H13" s="7">
-        <v>0.072175</v>
+        <v>0.069935</v>
       </c>
       <c r="I13" s="7">
-        <v>0.17737100000000003</v>
+        <v>0.171709</v>
       </c>
       <c r="J13" s="7">
-        <v>1.1159139999999999</v>
+        <v>1.111493</v>
       </c>
       <c r="K13" s="7">
-        <v>4.2607159999999995</v>
+        <v>4.191402</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.028169</v>
+        <v>-0.048239000000000004</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.18246400000000002</v>
+        <v>-0.16753900000000002</v>
       </c>
       <c r="G14" s="7">
-        <v>0.061538</v>
+        <v>0.046053</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.019886</v>
+        <v>-0.040128000000000004</v>
       </c>
       <c r="I14" s="7">
-        <v>0.593533</v>
+        <v>0.575175</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.013833</v>
+        <v>-0.018295</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.007383999999999999</v>
+        <v>-0.013603</v>
       </c>
       <c r="F17" s="7">
-        <v>0.0062109999999999995</v>
+        <v>0.026699</v>
       </c>
       <c r="G17" s="7">
-        <v>0.21462</v>
+        <v>0.196605</v>
       </c>
       <c r="H17" s="7">
-        <v>0.189536</v>
+        <v>0.164754</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.031543999999999996</v>
+        <v>0.032859</v>
       </c>
       <c r="F18" s="7">
-        <v>0.099977</v>
+        <v>0.09958</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.16799299999999998</v>
+        <v>0.169481</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.017597</v>
+        <v>0.009348</v>
       </c>
       <c r="F19" s="7">
-        <v>0.24153</v>
+        <v>0.25162</v>
       </c>
       <c r="G19" s="7">
-        <v>0.537279</v>
+        <v>0.533737</v>
       </c>
       <c r="H19" s="7">
-        <v>0.489936</v>
+        <v>0.477858</v>
       </c>
       <c r="I19" s="7">
-        <v>0.912661</v>
+        <v>0.87105</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.0037419999999999997</v>
+        <v>-0.030636</v>
       </c>
       <c r="F20" s="7">
-        <v>0.075486</v>
+        <v>0.078304</v>
       </c>
       <c r="G20" s="7">
-        <v>0.316033</v>
+        <v>0.281694</v>
       </c>
       <c r="H20" s="7">
-        <v>0.292084</v>
+        <v>0.257204</v>
       </c>
       <c r="I20" s="7">
-        <v>0.603916</v>
+        <v>0.513879</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.025787</v>
+        <v>-0.037163</v>
       </c>
       <c r="F21" s="7">
-        <v>0.018231999999999998</v>
+        <v>0.035692</v>
       </c>
       <c r="G21" s="7">
-        <v>0.19962599999999997</v>
+        <v>0.192299</v>
       </c>
       <c r="H21" s="7">
-        <v>0.186605</v>
+        <v>0.17274799999999998</v>
       </c>
       <c r="I21" s="7">
-        <v>0.463401</v>
+        <v>0.403538</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.01895</v>
+        <v>-0.041983</v>
       </c>
       <c r="F22" s="7">
-        <v>0.099314</v>
+        <v>0.079501</v>
       </c>
       <c r="G22" s="7">
-        <v>0.157153</v>
+        <v>0.127273</v>
       </c>
       <c r="H22" s="7">
-        <v>0.17946</v>
+        <v>0.15177</v>
       </c>
       <c r="I22" s="7">
-        <v>0.5731649999999999</v>
+        <v>0.489574</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.012978</v>
+        <v>-0.037774999999999996</v>
       </c>
       <c r="F23" s="7">
-        <v>0.065816</v>
+        <v>0.073423</v>
       </c>
       <c r="G23" s="7">
-        <v>0.311268</v>
+        <v>0.283859</v>
       </c>
       <c r="H23" s="7">
-        <v>0.292957</v>
+        <v>0.260474</v>
       </c>
       <c r="I23" s="7">
-        <v>0.6047480000000001</v>
+        <v>0.5186540000000001</v>
       </c>
       <c r="J23" s="7">
-        <v>1.979989</v>
+        <v>1.905122</v>
       </c>
       <c r="K23" s="7">
-        <v>10.817425</v>
+        <v>10.533333</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.036982</v>
+        <v>-0.06097</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.11585200000000001</v>
+        <v>-0.084977</v>
       </c>
       <c r="G24" s="7">
-        <v>0.01341</v>
+        <v>-0.027684</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.0025879999999999996</v>
+        <v>-0.027433</v>
       </c>
       <c r="I24" s="7">
-        <v>0.36087600000000003</v>
+        <v>0.25854</v>
       </c>
       <c r="J24" s="7">
-        <v>2.6385950000000005</v>
+        <v>2.547961</v>
       </c>
       <c r="K24" s="7">
-        <v>15.302876000000001</v>
+        <v>14.910245999999999</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.0037619999999999997</v>
+        <v>-0.02157</v>
       </c>
       <c r="F25" s="7">
-        <v>0.08287900000000001</v>
+        <v>0.095787</v>
       </c>
       <c r="G25" s="7">
-        <v>0.344617</v>
+        <v>0.33185400000000004</v>
       </c>
       <c r="H25" s="7">
-        <v>0.34279899999999996</v>
+        <v>0.318796</v>
       </c>
       <c r="I25" s="7">
-        <v>0.623876</v>
+        <v>0.5431170000000001</v>
       </c>
       <c r="J25" s="7">
-        <v>1.622821</v>
+        <v>1.5759379999999998</v>
       </c>
       <c r="K25" s="7">
-        <v>9.717755</v>
+        <v>9.509159</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.009728</v>
+        <v>-0.00527</v>
       </c>
       <c r="F26" s="7">
-        <v>0.012602</v>
+        <v>0.027638</v>
       </c>
       <c r="G26" s="7">
-        <v>0.15057700000000002</v>
+        <v>0.13506</v>
       </c>
       <c r="H26" s="7">
-        <v>0.137963</v>
+        <v>0.12106</v>
       </c>
       <c r="I26" s="7">
-        <v>0.437226</v>
+        <v>0.374944</v>
       </c>
       <c r="J26" s="7">
-        <v>1.228883</v>
+        <v>1.1957769999999999</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.023174</v>
+        <v>-0.043890000000000005</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.17935099999999998</v>
+        <v>-0.16163799999999998</v>
       </c>
       <c r="G27" s="7">
-        <v>0.065084</v>
+        <v>0.054201</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.004295</v>
+        <v>-0.025412</v>
       </c>
       <c r="I27" s="7">
-        <v>0.591533</v>
+        <v>0.57581</v>
       </c>
       <c r="J27" s="7">
-        <v>3.799862</v>
+        <v>3.698068</v>
       </c>
       <c r="K27" s="7">
-        <v>12.298279</v>
+        <v>12.071237000000002</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.060993000000000006</v>
+        <v>0.055319</v>
       </c>
       <c r="F28" s="7">
-        <v>0.38827</v>
+        <v>0.391695</v>
       </c>
       <c r="G28" s="7">
-        <v>0.626087</v>
+        <v>0.643836</v>
       </c>
       <c r="H28" s="7">
-        <v>0.530905</v>
+        <v>0.522718</v>
       </c>
       <c r="I28" s="7">
-        <v>0.964286</v>
+        <v>0.9703390000000001</v>
       </c>
       <c r="J28" s="7">
-        <v>2.155586</v>
+        <v>2.1387110000000003</v>
       </c>
       <c r="K28" s="7">
-        <v>8.506863</v>
+        <v>8.489796</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.014178999999999999</v>
+        <v>0.024024999999999998</v>
       </c>
       <c r="F29" s="7">
-        <v>0.207786</v>
+        <v>0.235154</v>
       </c>
       <c r="G29" s="7">
-        <v>0.480736</v>
+        <v>0.516035</v>
       </c>
       <c r="H29" s="7">
-        <v>0.391892</v>
+        <v>0.405405</v>
       </c>
       <c r="I29" s="7">
-        <v>0.812104</v>
+        <v>0.838755</v>
       </c>
       <c r="J29" s="7">
-        <v>2.316589</v>
+        <v>2.348789</v>
       </c>
       <c r="K29" s="7">
-        <v>11.849301</v>
+        <v>12.006503</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.017081</v>
+        <v>-0.044255</v>
       </c>
       <c r="F30" s="7">
-        <v>0.125083</v>
+        <v>0.12087400000000001</v>
       </c>
       <c r="G30" s="7">
-        <v>0.40901499999999996</v>
+        <v>0.385871</v>
       </c>
       <c r="H30" s="7">
-        <v>0.39197400000000004</v>
+        <v>0.353491</v>
       </c>
       <c r="I30" s="7">
-        <v>0.69762</v>
+        <v>0.616016</v>
       </c>
       <c r="J30" s="7">
-        <v>1.9837379999999998</v>
+        <v>1.901249</v>
       </c>
       <c r="K30" s="7">
-        <v>11.442260000000001</v>
+        <v>11.009756</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.110875</v>
+        <v>0.07689</v>
       </c>
       <c r="F31" s="7">
-        <v>0.308547</v>
+        <v>0.294688</v>
       </c>
       <c r="G31" s="7">
-        <v>0.647971</v>
+        <v>0.599975</v>
       </c>
       <c r="H31" s="7">
-        <v>0.601151</v>
+        <v>0.552168</v>
       </c>
       <c r="I31" s="7">
-        <v>0.784739</v>
+        <v>0.699062</v>
       </c>
       <c r="J31" s="7">
-        <v>3.088493</v>
+        <v>2.963415</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.006876</v>
+        <v>-0.020076999999999998</v>
       </c>
       <c r="F32" s="7">
-        <v>0.115884</v>
+        <v>0.127889</v>
       </c>
       <c r="G32" s="7">
-        <v>0.392059</v>
+        <v>0.38962600000000003</v>
       </c>
       <c r="H32" s="7">
-        <v>0.40124200000000004</v>
+        <v>0.382615</v>
       </c>
       <c r="I32" s="7">
-        <v>0.647354</v>
+        <v>0.577945</v>
       </c>
       <c r="J32" s="7">
-        <v>1.4118350000000002</v>
+        <v>1.379776</v>
       </c>
       <c r="K32" s="7">
-        <v>8.839237</v>
+        <v>8.68733</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.034112</v>
+        <v>-0.056853</v>
       </c>
       <c r="F33" s="7">
-        <v>0.024332</v>
+        <v>0.025386000000000002</v>
       </c>
       <c r="G33" s="7">
-        <v>0.221623</v>
+        <v>0.19500900000000002</v>
       </c>
       <c r="H33" s="7">
-        <v>0.20736000000000002</v>
+        <v>0.178934</v>
       </c>
       <c r="I33" s="7">
-        <v>0.501578</v>
+        <v>0.41572699999999996</v>
       </c>
       <c r="J33" s="7">
-        <v>2.0396170000000002</v>
+        <v>1.968051</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.032497</v>
+        <v>0.033319999999999995</v>
       </c>
       <c r="F34" s="7">
-        <v>0.104267</v>
+        <v>0.104176</v>
       </c>
       <c r="G34" s="7">
-        <v>0.20731100000000002</v>
+        <v>0.20711200000000002</v>
       </c>
       <c r="H34" s="7">
-        <v>0.169073</v>
+        <v>0.170005</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.003205</v>
+        <v>-0.029647</v>
       </c>
       <c r="F35" s="7">
-        <v>0.053047000000000004</v>
+        <v>0.057026</v>
       </c>
       <c r="G35" s="7">
-        <v>0.252769</v>
+        <v>0.224057</v>
       </c>
       <c r="H35" s="7">
-        <v>0.243171</v>
+        <v>0.21019300000000002</v>
       </c>
       <c r="I35" s="7">
-        <v>0.551767</v>
+        <v>0.45728</v>
       </c>
       <c r="J35" s="7">
-        <v>2.188653</v>
+        <v>2.104067</v>
       </c>
       <c r="K35" s="7">
-        <v>9.560272</v>
+        <v>9.285957</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.032059000000000004</v>
+        <v>0.033292</v>
       </c>
       <c r="F36" s="7">
-        <v>0.10325100000000001</v>
+        <v>0.10408400000000001</v>
       </c>
       <c r="G36" s="7">
-        <v>0.208373</v>
+        <v>0.208073</v>
       </c>
       <c r="H36" s="7">
-        <v>0.169539</v>
+        <v>0.17093599999999998</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>04.06.2026 10:49:04</t>
+    <t>05.06.2026 11:19:13</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.08740500000000001</v>
+        <v>-0.011375999999999999</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.08400600000000001</v>
+        <v>-0.08688599999999999</v>
       </c>
       <c r="G6" s="7">
-        <v>-0.021657000000000003</v>
+        <v>0.036230000000000005</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.02489</v>
+        <v>-0.004626</v>
       </c>
       <c r="I6" s="7">
-        <v>0.253398</v>
+        <v>0.270096</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.06226</v>
+        <v>-0.059192</v>
       </c>
       <c r="F7" s="7">
-        <v>0.119951</v>
+        <v>0.091679</v>
       </c>
       <c r="G7" s="7">
-        <v>0.37439</v>
+        <v>0.367703</v>
       </c>
       <c r="H7" s="7">
-        <v>0.34856299999999996</v>
+        <v>0.329403</v>
       </c>
       <c r="I7" s="7">
-        <v>0.608791</v>
+        <v>0.554502</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.036610000000000004</v>
+        <v>-0.040677000000000005</v>
       </c>
       <c r="F8" s="7">
-        <v>0.073784</v>
+        <v>0.057955</v>
       </c>
       <c r="G8" s="7">
-        <v>0.283233</v>
+        <v>0.287119</v>
       </c>
       <c r="H8" s="7">
-        <v>0.257199</v>
+        <v>0.242474</v>
       </c>
       <c r="I8" s="7">
-        <v>0.517977</v>
+        <v>0.474563</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.032589</v>
+        <v>0.036132</v>
       </c>
       <c r="F9" s="7">
-        <v>0.101663</v>
+        <v>0.10419</v>
       </c>
       <c r="G9" s="7">
-        <v>0.20479399999999998</v>
+        <v>0.204943</v>
       </c>
       <c r="H9" s="7">
-        <v>0.16740100000000002</v>
+        <v>0.171406</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.049305</v>
+        <v>0.020913</v>
       </c>
       <c r="F10" s="7">
-        <v>0.343096</v>
+        <v>0.289979</v>
       </c>
       <c r="G10" s="7">
-        <v>0.277188</v>
+        <v>0.236107</v>
       </c>
       <c r="H10" s="7">
-        <v>0.332872</v>
+        <v>0.30069199999999996</v>
       </c>
       <c r="I10" s="7">
-        <v>0.610368</v>
+        <v>0.547869</v>
       </c>
       <c r="J10" s="7">
-        <v>1.151955</v>
+        <v>1.1</v>
       </c>
       <c r="K10" s="7">
-        <v>7.693297</v>
+        <v>7.409396</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.017794</v>
+        <v>-0.003604</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.120669</v>
+        <v>-0.128448</v>
       </c>
       <c r="G11" s="7">
-        <v>0.100149</v>
+        <v>0.10544700000000001</v>
       </c>
       <c r="H11" s="7">
-        <v>0.033708</v>
+        <v>0.035581</v>
       </c>
       <c r="I11" s="7">
-        <v>0.540179</v>
+        <v>0.527624</v>
       </c>
       <c r="J11" s="7">
-        <v>3.5657569999999996</v>
+        <v>3.574028</v>
       </c>
       <c r="K11" s="7">
-        <v>11.028764</v>
+        <v>10.951588999999998</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.022139000000000002</v>
+        <v>0.027860999999999997</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.080351</v>
+        <v>-0.100494</v>
       </c>
       <c r="G12" s="7">
-        <v>0.365824</v>
+        <v>0.407507</v>
       </c>
       <c r="H12" s="7">
-        <v>0.05950999999999999</v>
+        <v>0.061844</v>
       </c>
       <c r="I12" s="7">
-        <v>1.5231569999999999</v>
+        <v>1.5036680000000002</v>
       </c>
       <c r="J12" s="7">
-        <v>5.247705999999999</v>
+        <v>5.261468</v>
       </c>
       <c r="K12" s="7">
-        <v>12.886623</v>
+        <v>12.671875</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.013675999999999999</v>
+        <v>0.01439</v>
       </c>
       <c r="F13" s="7">
-        <v>0.041929</v>
+        <v>0.043943</v>
       </c>
       <c r="G13" s="7">
-        <v>0.08780400000000001</v>
+        <v>0.08668200000000001</v>
       </c>
       <c r="H13" s="7">
-        <v>0.069935</v>
+        <v>0.070184</v>
       </c>
       <c r="I13" s="7">
-        <v>0.171709</v>
+        <v>0.17102399999999998</v>
       </c>
       <c r="J13" s="7">
-        <v>1.111493</v>
+        <v>1.111984</v>
       </c>
       <c r="K13" s="7">
-        <v>4.191402</v>
+        <v>4.213385</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.048239000000000004</v>
+        <v>-0.04</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.16753900000000002</v>
+        <v>-0.17241399999999998</v>
       </c>
       <c r="G14" s="7">
-        <v>0.046053</v>
+        <v>0.048771</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.040128000000000004</v>
+        <v>-0.045454999999999995</v>
       </c>
       <c r="I14" s="7">
-        <v>0.575175</v>
+        <v>0.539519</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.018295</v>
+        <v>-0.006323</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.013603</v>
+        <v>-0.006659000000000001</v>
       </c>
       <c r="F17" s="7">
-        <v>0.026699</v>
+        <v>0.035102</v>
       </c>
       <c r="G17" s="7">
-        <v>0.196605</v>
+        <v>0.209924</v>
       </c>
       <c r="H17" s="7">
-        <v>0.164754</v>
+        <v>0.163837</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.032859</v>
+        <v>0.034346999999999996</v>
       </c>
       <c r="F18" s="7">
-        <v>0.09958</v>
+        <v>0.102098</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.169481</v>
+        <v>0.17270600000000003</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.009348</v>
+        <v>-0.014343999999999999</v>
       </c>
       <c r="F19" s="7">
-        <v>0.25162</v>
+        <v>0.23165400000000003</v>
       </c>
       <c r="G19" s="7">
-        <v>0.533737</v>
+        <v>0.531861</v>
       </c>
       <c r="H19" s="7">
-        <v>0.477858</v>
+        <v>0.466184</v>
       </c>
       <c r="I19" s="7">
-        <v>0.87105</v>
+        <v>0.8164589999999999</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.030636</v>
+        <v>-0.032014999999999995</v>
       </c>
       <c r="F20" s="7">
-        <v>0.078304</v>
+        <v>0.071391</v>
       </c>
       <c r="G20" s="7">
-        <v>0.281694</v>
+        <v>0.288624</v>
       </c>
       <c r="H20" s="7">
-        <v>0.257204</v>
+        <v>0.247194</v>
       </c>
       <c r="I20" s="7">
-        <v>0.513879</v>
+        <v>0.473835</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.037163</v>
+        <v>-0.030569000000000002</v>
       </c>
       <c r="F21" s="7">
-        <v>0.035692</v>
+        <v>0.042531</v>
       </c>
       <c r="G21" s="7">
-        <v>0.192299</v>
+        <v>0.20694600000000002</v>
       </c>
       <c r="H21" s="7">
-        <v>0.17274799999999998</v>
+        <v>0.171824</v>
       </c>
       <c r="I21" s="7">
-        <v>0.403538</v>
+        <v>0.37917900000000004</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.041983</v>
+        <v>-0.028546000000000002</v>
       </c>
       <c r="F22" s="7">
-        <v>0.079501</v>
+        <v>0.08265</v>
       </c>
       <c r="G22" s="7">
-        <v>0.127273</v>
+        <v>0.155812</v>
       </c>
       <c r="H22" s="7">
-        <v>0.15177</v>
+        <v>0.157028</v>
       </c>
       <c r="I22" s="7">
-        <v>0.489574</v>
+        <v>0.48493</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.037774999999999996</v>
+        <v>-0.041121</v>
       </c>
       <c r="F23" s="7">
-        <v>0.073423</v>
+        <v>0.061562</v>
       </c>
       <c r="G23" s="7">
-        <v>0.283859</v>
+        <v>0.291785</v>
       </c>
       <c r="H23" s="7">
-        <v>0.260474</v>
+        <v>0.24590199999999998</v>
       </c>
       <c r="I23" s="7">
-        <v>0.5186540000000001</v>
+        <v>0.470968</v>
       </c>
       <c r="J23" s="7">
-        <v>1.905122</v>
+        <v>1.8715369999999998</v>
       </c>
       <c r="K23" s="7">
-        <v>10.533333</v>
+        <v>10.355838</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.06097</v>
+        <v>-0.022912</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.084977</v>
+        <v>-0.054447</v>
       </c>
       <c r="G24" s="7">
-        <v>-0.027684</v>
+        <v>0.027852000000000002</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.027433</v>
+        <v>-0.006729000000000001</v>
       </c>
       <c r="I24" s="7">
-        <v>0.25854</v>
+        <v>0.27508299999999997</v>
       </c>
       <c r="J24" s="7">
-        <v>2.547961</v>
+        <v>2.623489</v>
       </c>
       <c r="K24" s="7">
-        <v>14.910245999999999</v>
+        <v>15.139612999999999</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.02157</v>
+        <v>-0.015978000000000003</v>
       </c>
       <c r="F25" s="7">
-        <v>0.095787</v>
+        <v>0.090194</v>
       </c>
       <c r="G25" s="7">
-        <v>0.33185400000000004</v>
+        <v>0.339779</v>
       </c>
       <c r="H25" s="7">
-        <v>0.318796</v>
+        <v>0.311697</v>
       </c>
       <c r="I25" s="7">
-        <v>0.5431170000000001</v>
+        <v>0.505627</v>
       </c>
       <c r="J25" s="7">
-        <v>1.5759379999999998</v>
+        <v>1.562071</v>
       </c>
       <c r="K25" s="7">
-        <v>9.509159</v>
+        <v>9.385439</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.00527</v>
+        <v>-0.004499</v>
       </c>
       <c r="F26" s="7">
-        <v>0.027638</v>
+        <v>0.023549</v>
       </c>
       <c r="G26" s="7">
-        <v>0.13506</v>
+        <v>0.13898</v>
       </c>
       <c r="H26" s="7">
-        <v>0.12106</v>
+        <v>0.111923</v>
       </c>
       <c r="I26" s="7">
-        <v>0.374944</v>
+        <v>0.337951</v>
       </c>
       <c r="J26" s="7">
-        <v>1.1957769999999999</v>
+        <v>1.177881</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.043890000000000005</v>
+        <v>-0.035486</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.16163799999999998</v>
+        <v>-0.163177</v>
       </c>
       <c r="G27" s="7">
-        <v>0.054201</v>
+        <v>0.060062</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.025412</v>
+        <v>-0.027201</v>
       </c>
       <c r="I27" s="7">
-        <v>0.57581</v>
+        <v>0.553853</v>
       </c>
       <c r="J27" s="7">
-        <v>3.698068</v>
+        <v>3.689441</v>
       </c>
       <c r="K27" s="7">
-        <v>12.071237000000002</v>
+        <v>11.982422999999999</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.055319</v>
+        <v>0.029083</v>
       </c>
       <c r="F28" s="7">
-        <v>0.391695</v>
+        <v>0.34847900000000004</v>
       </c>
       <c r="G28" s="7">
-        <v>0.643836</v>
+        <v>0.602787</v>
       </c>
       <c r="H28" s="7">
-        <v>0.522718</v>
+        <v>0.506345</v>
       </c>
       <c r="I28" s="7">
-        <v>0.9703390000000001</v>
+        <v>0.887179</v>
       </c>
       <c r="J28" s="7">
-        <v>2.1387110000000003</v>
+        <v>2.1049610000000003</v>
       </c>
       <c r="K28" s="7">
-        <v>8.489796</v>
+        <v>8.402146</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.024024999999999998</v>
+        <v>-0.011628000000000001</v>
       </c>
       <c r="F29" s="7">
-        <v>0.235154</v>
+        <v>0.200565</v>
       </c>
       <c r="G29" s="7">
-        <v>0.516035</v>
+        <v>0.473988</v>
       </c>
       <c r="H29" s="7">
-        <v>0.405405</v>
+        <v>0.378378</v>
       </c>
       <c r="I29" s="7">
-        <v>0.838755</v>
+        <v>0.734694</v>
       </c>
       <c r="J29" s="7">
-        <v>2.348789</v>
+        <v>2.284389</v>
       </c>
       <c r="K29" s="7">
-        <v>12.006503</v>
+        <v>11.730904</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.044255</v>
+        <v>-0.063495</v>
       </c>
       <c r="F30" s="7">
-        <v>0.12087400000000001</v>
+        <v>0.09093</v>
       </c>
       <c r="G30" s="7">
-        <v>0.385871</v>
+        <v>0.372119</v>
       </c>
       <c r="H30" s="7">
-        <v>0.353491</v>
+        <v>0.325728</v>
       </c>
       <c r="I30" s="7">
-        <v>0.616016</v>
+        <v>0.546329</v>
       </c>
       <c r="J30" s="7">
-        <v>1.901249</v>
+        <v>1.841739</v>
       </c>
       <c r="K30" s="7">
-        <v>11.009756</v>
+        <v>10.723384000000001</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.07689</v>
+        <v>0.010944</v>
       </c>
       <c r="F31" s="7">
-        <v>0.294688</v>
+        <v>0.26599</v>
       </c>
       <c r="G31" s="7">
-        <v>0.599975</v>
+        <v>0.574097</v>
       </c>
       <c r="H31" s="7">
-        <v>0.552168</v>
+        <v>0.527063</v>
       </c>
       <c r="I31" s="7">
-        <v>0.699062</v>
+        <v>0.613613</v>
       </c>
       <c r="J31" s="7">
-        <v>2.963415</v>
+        <v>2.899312</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.020076999999999998</v>
+        <v>-0.024579</v>
       </c>
       <c r="F32" s="7">
-        <v>0.127889</v>
+        <v>0.112791</v>
       </c>
       <c r="G32" s="7">
-        <v>0.38962600000000003</v>
+        <v>0.39055100000000004</v>
       </c>
       <c r="H32" s="7">
-        <v>0.382615</v>
+        <v>0.37058599999999997</v>
       </c>
       <c r="I32" s="7">
-        <v>0.577945</v>
+        <v>0.531657</v>
       </c>
       <c r="J32" s="7">
-        <v>1.379776</v>
+        <v>1.35907</v>
       </c>
       <c r="K32" s="7">
-        <v>8.68733</v>
+        <v>8.571816</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.056853</v>
+        <v>-0.047882999999999995</v>
       </c>
       <c r="F33" s="7">
-        <v>0.025386000000000002</v>
+        <v>0.019586</v>
       </c>
       <c r="G33" s="7">
-        <v>0.19500900000000002</v>
+        <v>0.214099</v>
       </c>
       <c r="H33" s="7">
-        <v>0.178934</v>
+        <v>0.175888</v>
       </c>
       <c r="I33" s="7">
-        <v>0.41572699999999996</v>
+        <v>0.387126</v>
       </c>
       <c r="J33" s="7">
-        <v>1.968051</v>
+        <v>1.960383</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.033319999999999995</v>
+        <v>0.036169</v>
       </c>
       <c r="F34" s="7">
-        <v>0.104176</v>
+        <v>0.106187</v>
       </c>
       <c r="G34" s="7">
-        <v>0.20711200000000002</v>
+        <v>0.207954</v>
       </c>
       <c r="H34" s="7">
-        <v>0.170005</v>
+        <v>0.174197</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.029647</v>
+        <v>-0.021856</v>
       </c>
       <c r="F35" s="7">
-        <v>0.057026</v>
+        <v>0.061804</v>
       </c>
       <c r="G35" s="7">
-        <v>0.224057</v>
+        <v>0.23846900000000001</v>
       </c>
       <c r="H35" s="7">
-        <v>0.21019300000000002</v>
+        <v>0.20752800000000002</v>
       </c>
       <c r="I35" s="7">
-        <v>0.45728</v>
+        <v>0.427727</v>
       </c>
       <c r="J35" s="7">
-        <v>2.104067</v>
+        <v>2.097232</v>
       </c>
       <c r="K35" s="7">
-        <v>9.285957</v>
+        <v>9.211268</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.033292</v>
+        <v>0.035714</v>
       </c>
       <c r="F36" s="7">
-        <v>0.10408400000000001</v>
+        <v>0.10609400000000001</v>
       </c>
       <c r="G36" s="7">
-        <v>0.208073</v>
+        <v>0.21239799999999998</v>
       </c>
       <c r="H36" s="7">
-        <v>0.17093599999999998</v>
+        <v>0.17512799999999998</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>05.06.2026 11:19:13</t>
+    <t>08.06.2026 10:35:47</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.011375999999999999</v>
+        <v>-0.09936</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.08688599999999999</v>
+        <v>-0.052792000000000006</v>
       </c>
       <c r="G6" s="7">
-        <v>0.036230000000000005</v>
+        <v>-0.026134</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.004626</v>
+        <v>-0.039647999999999996</v>
       </c>
       <c r="I6" s="7">
-        <v>0.270096</v>
+        <v>0.226097</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.059192</v>
+        <v>-0.08626899999999998</v>
       </c>
       <c r="F7" s="7">
-        <v>0.091679</v>
+        <v>0.092796</v>
       </c>
       <c r="G7" s="7">
-        <v>0.367703</v>
+        <v>0.36432899999999996</v>
       </c>
       <c r="H7" s="7">
-        <v>0.329403</v>
+        <v>0.319086</v>
       </c>
       <c r="I7" s="7">
-        <v>0.554502</v>
+        <v>0.524053</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.040677000000000005</v>
+        <v>-0.092274</v>
       </c>
       <c r="F8" s="7">
-        <v>0.057955</v>
+        <v>0.062358000000000004</v>
       </c>
       <c r="G8" s="7">
-        <v>0.287119</v>
+        <v>0.262378</v>
       </c>
       <c r="H8" s="7">
-        <v>0.242474</v>
+        <v>0.22643999999999997</v>
       </c>
       <c r="I8" s="7">
-        <v>0.474563</v>
+        <v>0.448223</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.036132</v>
+        <v>0.030986</v>
       </c>
       <c r="F9" s="7">
-        <v>0.10419</v>
+        <v>0.10075200000000001</v>
       </c>
       <c r="G9" s="7">
-        <v>0.204943</v>
+        <v>0.204938</v>
       </c>
       <c r="H9" s="7">
-        <v>0.171406</v>
+        <v>0.172607</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>0.020913</v>
+        <v>-0.020516</v>
       </c>
       <c r="F10" s="7">
-        <v>0.289979</v>
+        <v>0.26194500000000004</v>
       </c>
       <c r="G10" s="7">
-        <v>0.236107</v>
+        <v>0.210663</v>
       </c>
       <c r="H10" s="7">
-        <v>0.30069199999999996</v>
+        <v>0.288581</v>
       </c>
       <c r="I10" s="7">
-        <v>0.547869</v>
+        <v>0.515053</v>
       </c>
       <c r="J10" s="7">
-        <v>1.1</v>
+        <v>0.88557</v>
       </c>
       <c r="K10" s="7">
-        <v>7.409396</v>
+        <v>7.224382</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.003604</v>
+        <v>-0.06518</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.128448</v>
+        <v>-0.13834</v>
       </c>
       <c r="G11" s="7">
-        <v>0.10544700000000001</v>
+        <v>0.071253</v>
       </c>
       <c r="H11" s="7">
-        <v>0.035581</v>
+        <v>0.020599</v>
       </c>
       <c r="I11" s="7">
-        <v>0.527624</v>
+        <v>0.494379</v>
       </c>
       <c r="J11" s="7">
-        <v>3.574028</v>
+        <v>3.169855</v>
       </c>
       <c r="K11" s="7">
-        <v>10.951588999999998</v>
+        <v>10.865882999999998</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0.027860999999999997</v>
+        <v>-0.104869</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.100494</v>
+        <v>-0.132916</v>
       </c>
       <c r="G12" s="7">
-        <v>0.407507</v>
+        <v>0.315289</v>
       </c>
       <c r="H12" s="7">
-        <v>0.061844</v>
+        <v>0.022559</v>
       </c>
       <c r="I12" s="7">
-        <v>1.5036680000000002</v>
+        <v>1.3389680000000002</v>
       </c>
       <c r="J12" s="7">
-        <v>5.261468</v>
+        <v>4.7351659999999995</v>
       </c>
       <c r="K12" s="7">
-        <v>12.671875</v>
+        <v>12.251007999999999</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.01439</v>
+        <v>0.020524</v>
       </c>
       <c r="F13" s="7">
-        <v>0.043943</v>
+        <v>0.047965</v>
       </c>
       <c r="G13" s="7">
-        <v>0.08668200000000001</v>
+        <v>0.09297599999999999</v>
       </c>
       <c r="H13" s="7">
-        <v>0.070184</v>
+        <v>0.076655</v>
       </c>
       <c r="I13" s="7">
-        <v>0.17102399999999998</v>
+        <v>0.17299299999999998</v>
       </c>
       <c r="J13" s="7">
-        <v>1.111984</v>
+        <v>0.8982009999999999</v>
       </c>
       <c r="K13" s="7">
-        <v>4.213385</v>
+        <v>4.272395</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.04</v>
+        <v>-0.090753</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.17241399999999998</v>
+        <v>-0.17443999999999998</v>
       </c>
       <c r="G14" s="7">
-        <v>0.048771</v>
+        <v>0.033879</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.045454999999999995</v>
+        <v>-0.057173</v>
       </c>
       <c r="I14" s="7">
-        <v>0.539519</v>
+        <v>0.518879</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.006323</v>
+        <v>-0.065801</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.006659000000000001</v>
+        <v>-0.08613799999999999</v>
       </c>
       <c r="F17" s="7">
-        <v>0.035102</v>
+        <v>0.054720000000000005</v>
       </c>
       <c r="G17" s="7">
-        <v>0.209924</v>
+        <v>0.196682</v>
       </c>
       <c r="H17" s="7">
-        <v>0.163837</v>
+        <v>0.158788</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.034346999999999996</v>
+        <v>0.030692</v>
       </c>
       <c r="F18" s="7">
-        <v>0.102098</v>
+        <v>0.098863</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.17270600000000003</v>
+        <v>0.17444199999999999</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.014343999999999999</v>
+        <v>-0.030815000000000002</v>
       </c>
       <c r="F19" s="7">
-        <v>0.23165400000000003</v>
+        <v>0.201661</v>
       </c>
       <c r="G19" s="7">
-        <v>0.531861</v>
+        <v>0.513073</v>
       </c>
       <c r="H19" s="7">
-        <v>0.466184</v>
+        <v>0.456119</v>
       </c>
       <c r="I19" s="7">
-        <v>0.8164589999999999</v>
+        <v>0.7923690000000001</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.032014999999999995</v>
+        <v>-0.087269</v>
       </c>
       <c r="F20" s="7">
-        <v>0.071391</v>
+        <v>0.075252</v>
       </c>
       <c r="G20" s="7">
-        <v>0.288624</v>
+        <v>0.268918</v>
       </c>
       <c r="H20" s="7">
-        <v>0.247194</v>
+        <v>0.23081600000000002</v>
       </c>
       <c r="I20" s="7">
-        <v>0.473835</v>
+        <v>0.451878</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.030569000000000002</v>
+        <v>-0.081319</v>
       </c>
       <c r="F21" s="7">
-        <v>0.042531</v>
+        <v>0.038509</v>
       </c>
       <c r="G21" s="7">
-        <v>0.20694600000000002</v>
+        <v>0.147563</v>
       </c>
       <c r="H21" s="7">
-        <v>0.171824</v>
+        <v>0.15843</v>
       </c>
       <c r="I21" s="7">
-        <v>0.37917900000000004</v>
+        <v>0.35751</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.028546000000000002</v>
+        <v>-0.080518</v>
       </c>
       <c r="F22" s="7">
-        <v>0.08265</v>
+        <v>0.073636</v>
       </c>
       <c r="G22" s="7">
-        <v>0.155812</v>
+        <v>0.13917</v>
       </c>
       <c r="H22" s="7">
-        <v>0.157028</v>
+        <v>0.14476</v>
       </c>
       <c r="I22" s="7">
-        <v>0.48493</v>
+        <v>0.45803600000000005</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.041121</v>
+        <v>-0.091256</v>
       </c>
       <c r="F23" s="7">
-        <v>0.061562</v>
+        <v>0.060439999999999994</v>
       </c>
       <c r="G23" s="7">
-        <v>0.291785</v>
+        <v>0.26616700000000004</v>
       </c>
       <c r="H23" s="7">
-        <v>0.24590199999999998</v>
+        <v>0.23041899999999998</v>
       </c>
       <c r="I23" s="7">
-        <v>0.470968</v>
+        <v>0.450608</v>
       </c>
       <c r="J23" s="7">
-        <v>1.8715369999999998</v>
+        <v>1.559358</v>
       </c>
       <c r="K23" s="7">
-        <v>10.355838</v>
+        <v>10.085886</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.022912</v>
+        <v>-0.103323</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.054447</v>
+        <v>-0.054717</v>
       </c>
       <c r="G24" s="7">
-        <v>0.027852000000000002</v>
+        <v>-0.025823</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.006729000000000001</v>
+        <v>-0.043219</v>
       </c>
       <c r="I24" s="7">
-        <v>0.27508299999999997</v>
+        <v>0.231512</v>
       </c>
       <c r="J24" s="7">
-        <v>2.623489</v>
+        <v>2.302072</v>
       </c>
       <c r="K24" s="7">
-        <v>15.139612999999999</v>
+        <v>14.25165</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.015978000000000003</v>
+        <v>-0.08715500000000001</v>
       </c>
       <c r="F25" s="7">
-        <v>0.090194</v>
+        <v>0.08072800000000001</v>
       </c>
       <c r="G25" s="7">
-        <v>0.339779</v>
+        <v>0.304736</v>
       </c>
       <c r="H25" s="7">
-        <v>0.311697</v>
+        <v>0.285328</v>
       </c>
       <c r="I25" s="7">
-        <v>0.505627</v>
+        <v>0.476505</v>
       </c>
       <c r="J25" s="7">
-        <v>1.562071</v>
+        <v>1.3104040000000001</v>
       </c>
       <c r="K25" s="7">
-        <v>9.385439</v>
+        <v>9.047569</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.004499</v>
+        <v>-0.08084300000000001</v>
       </c>
       <c r="F26" s="7">
-        <v>0.023549</v>
+        <v>0.015235</v>
       </c>
       <c r="G26" s="7">
-        <v>0.13898</v>
+        <v>0.11322499999999999</v>
       </c>
       <c r="H26" s="7">
-        <v>0.111923</v>
+        <v>0.095934</v>
       </c>
       <c r="I26" s="7">
-        <v>0.337951</v>
+        <v>0.31813199999999997</v>
       </c>
       <c r="J26" s="7">
-        <v>1.177881</v>
+        <v>1.046928</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.035486</v>
+        <v>-0.08450200000000001</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.163177</v>
+        <v>-0.159019</v>
       </c>
       <c r="G27" s="7">
-        <v>0.060062</v>
+        <v>0.02765</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.027201</v>
+        <v>-0.042233</v>
       </c>
       <c r="I27" s="7">
-        <v>0.553853</v>
+        <v>0.510158</v>
       </c>
       <c r="J27" s="7">
-        <v>3.689441</v>
+        <v>3.399868</v>
       </c>
       <c r="K27" s="7">
-        <v>11.982422999999999</v>
+        <v>11.835764</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.029083</v>
+        <v>0.0041210000000000005</v>
       </c>
       <c r="F28" s="7">
-        <v>0.34847900000000004</v>
+        <v>0.32667900000000005</v>
       </c>
       <c r="G28" s="7">
-        <v>0.602787</v>
+        <v>0.548729</v>
       </c>
       <c r="H28" s="7">
-        <v>0.506345</v>
+        <v>0.496111</v>
       </c>
       <c r="I28" s="7">
-        <v>0.887179</v>
+        <v>0.8640349999999999</v>
       </c>
       <c r="J28" s="7">
-        <v>2.1049610000000003</v>
+        <v>1.90633</v>
       </c>
       <c r="K28" s="7">
-        <v>8.402146</v>
+        <v>8.295524</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.011628000000000001</v>
+        <v>-0.032875</v>
       </c>
       <c r="F29" s="7">
-        <v>0.200565</v>
+        <v>0.17729199999999998</v>
       </c>
       <c r="G29" s="7">
-        <v>0.473988</v>
+        <v>0.429379</v>
       </c>
       <c r="H29" s="7">
-        <v>0.378378</v>
+        <v>0.367568</v>
       </c>
       <c r="I29" s="7">
-        <v>0.734694</v>
+        <v>0.732877</v>
       </c>
       <c r="J29" s="7">
-        <v>2.284389</v>
+        <v>1.9997630000000002</v>
       </c>
       <c r="K29" s="7">
-        <v>11.730904</v>
+        <v>11.555831000000001</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.063495</v>
+        <v>-0.08538899999999999</v>
       </c>
       <c r="F30" s="7">
-        <v>0.09093</v>
+        <v>0.095953</v>
       </c>
       <c r="G30" s="7">
-        <v>0.372119</v>
+        <v>0.37087600000000004</v>
       </c>
       <c r="H30" s="7">
-        <v>0.325728</v>
+        <v>0.324904</v>
       </c>
       <c r="I30" s="7">
-        <v>0.546329</v>
+        <v>0.5325909999999999</v>
       </c>
       <c r="J30" s="7">
-        <v>1.841739</v>
+        <v>1.572038</v>
       </c>
       <c r="K30" s="7">
-        <v>10.723384000000001</v>
+        <v>10.580971</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.010944</v>
+        <v>-0.036078</v>
       </c>
       <c r="F31" s="7">
-        <v>0.26599</v>
+        <v>0.26570499999999997</v>
       </c>
       <c r="G31" s="7">
-        <v>0.574097</v>
+        <v>0.540486</v>
       </c>
       <c r="H31" s="7">
-        <v>0.527063</v>
+        <v>0.5050209999999999</v>
       </c>
       <c r="I31" s="7">
-        <v>0.613613</v>
+        <v>0.572416</v>
       </c>
       <c r="J31" s="7">
-        <v>2.899312</v>
+        <v>2.541787</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.024579</v>
+        <v>-0.08274</v>
       </c>
       <c r="F32" s="7">
-        <v>0.112791</v>
+        <v>0.104378</v>
       </c>
       <c r="G32" s="7">
-        <v>0.39055100000000004</v>
+        <v>0.382446</v>
       </c>
       <c r="H32" s="7">
-        <v>0.37058599999999997</v>
+        <v>0.350795</v>
       </c>
       <c r="I32" s="7">
-        <v>0.531657</v>
+        <v>0.518099</v>
       </c>
       <c r="J32" s="7">
-        <v>1.35907</v>
+        <v>1.118943</v>
       </c>
       <c r="K32" s="7">
-        <v>8.571816</v>
+        <v>8.327437999999999</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.047882999999999995</v>
+        <v>-0.09909599999999999</v>
       </c>
       <c r="F33" s="7">
-        <v>0.019586</v>
+        <v>0.025974</v>
       </c>
       <c r="G33" s="7">
-        <v>0.214099</v>
+        <v>0.190439</v>
       </c>
       <c r="H33" s="7">
-        <v>0.175888</v>
+        <v>0.162944</v>
       </c>
       <c r="I33" s="7">
-        <v>0.387126</v>
+        <v>0.37515</v>
       </c>
       <c r="J33" s="7">
-        <v>1.960383</v>
+        <v>1.657773</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.036169</v>
+        <v>0.031467</v>
       </c>
       <c r="F34" s="7">
-        <v>0.106187</v>
+        <v>0.102665</v>
       </c>
       <c r="G34" s="7">
-        <v>0.207954</v>
+        <v>0.208812</v>
       </c>
       <c r="H34" s="7">
-        <v>0.174197</v>
+        <v>0.175594</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.021856</v>
+        <v>-0.08088</v>
       </c>
       <c r="F35" s="7">
-        <v>0.061804</v>
+        <v>0.06274</v>
       </c>
       <c r="G35" s="7">
-        <v>0.23846900000000001</v>
+        <v>0.214817</v>
       </c>
       <c r="H35" s="7">
-        <v>0.20752800000000002</v>
+        <v>0.19620300000000002</v>
       </c>
       <c r="I35" s="7">
-        <v>0.427727</v>
+        <v>0.411557</v>
       </c>
       <c r="J35" s="7">
-        <v>2.097232</v>
+        <v>1.8266689999999999</v>
       </c>
       <c r="K35" s="7">
-        <v>9.211268</v>
+        <v>9.041946000000001</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.035714</v>
+        <v>0.031441</v>
       </c>
       <c r="F36" s="7">
-        <v>0.10609400000000001</v>
+        <v>0.102575</v>
       </c>
       <c r="G36" s="7">
-        <v>0.21239799999999998</v>
+        <v>0.208612</v>
       </c>
       <c r="H36" s="7">
-        <v>0.17512799999999998</v>
+        <v>0.176525</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>08.06.2026 10:35:47</t>
+    <t>09.06.2026 10:03:03</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.09936</v>
+        <v>-0.06442300000000001</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.052792000000000006</v>
+        <v>-0.015642</v>
       </c>
       <c r="G6" s="7">
-        <v>-0.026134</v>
+        <v>0.003988</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.039647999999999996</v>
+        <v>-0.001982</v>
       </c>
       <c r="I6" s="7">
-        <v>0.226097</v>
+        <v>0.274184</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.08626899999999998</v>
+        <v>-0.086638</v>
       </c>
       <c r="F7" s="7">
-        <v>0.092796</v>
+        <v>0.103785</v>
       </c>
       <c r="G7" s="7">
-        <v>0.36432899999999996</v>
+        <v>0.351776</v>
       </c>
       <c r="H7" s="7">
-        <v>0.319086</v>
+        <v>0.332351</v>
       </c>
       <c r="I7" s="7">
-        <v>0.524053</v>
+        <v>0.539378</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.092274</v>
+        <v>-0.087218</v>
       </c>
       <c r="F8" s="7">
-        <v>0.062358000000000004</v>
+        <v>0.076814</v>
       </c>
       <c r="G8" s="7">
-        <v>0.262378</v>
+        <v>0.25214200000000003</v>
       </c>
       <c r="H8" s="7">
-        <v>0.22643999999999997</v>
+        <v>0.24312799999999998</v>
       </c>
       <c r="I8" s="7">
-        <v>0.448223</v>
+        <v>0.46792900000000004</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.030986</v>
+        <v>0.030952999999999998</v>
       </c>
       <c r="F9" s="7">
-        <v>0.10075200000000001</v>
+        <v>0.10188000000000001</v>
       </c>
       <c r="G9" s="7">
-        <v>0.204938</v>
+        <v>0.204933</v>
       </c>
       <c r="H9" s="7">
-        <v>0.172607</v>
+        <v>0.173809</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.020516</v>
+        <v>-0.048976</v>
       </c>
       <c r="F10" s="7">
-        <v>0.26194500000000004</v>
+        <v>0.243646</v>
       </c>
       <c r="G10" s="7">
-        <v>0.210663</v>
+        <v>0.182345</v>
       </c>
       <c r="H10" s="7">
-        <v>0.288581</v>
+        <v>0.26989599999999997</v>
       </c>
       <c r="I10" s="7">
-        <v>0.515053</v>
+        <v>0.49308399999999997</v>
       </c>
       <c r="J10" s="7">
-        <v>0.88557</v>
+        <v>0.861055</v>
       </c>
       <c r="K10" s="7">
-        <v>7.224382</v>
+        <v>7.115878</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.06518</v>
+        <v>-0.064236</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.13834</v>
+        <v>-0.147826</v>
       </c>
       <c r="G11" s="7">
-        <v>0.071253</v>
+        <v>0.08016</v>
       </c>
       <c r="H11" s="7">
-        <v>0.020599</v>
+        <v>0.009363</v>
       </c>
       <c r="I11" s="7">
-        <v>0.494379</v>
+        <v>0.47792700000000005</v>
       </c>
       <c r="J11" s="7">
-        <v>3.169855</v>
+        <v>3.074074</v>
       </c>
       <c r="K11" s="7">
-        <v>10.865882999999998</v>
+        <v>10.735249</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.104869</v>
+        <v>-0.118785</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.132916</v>
+        <v>-0.15831099999999998</v>
       </c>
       <c r="G12" s="7">
-        <v>0.315289</v>
+        <v>0.280096</v>
       </c>
       <c r="H12" s="7">
-        <v>0.022559</v>
+        <v>-0.00739</v>
       </c>
       <c r="I12" s="7">
-        <v>1.3389680000000002</v>
+        <v>1.2704630000000001</v>
       </c>
       <c r="J12" s="7">
-        <v>4.7351659999999995</v>
+        <v>4.3953489999999995</v>
       </c>
       <c r="K12" s="7">
-        <v>12.251007999999999</v>
+        <v>11.928064999999998</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.020524</v>
+        <v>0.014844</v>
       </c>
       <c r="F13" s="7">
-        <v>0.047965</v>
+        <v>0.043362</v>
       </c>
       <c r="G13" s="7">
-        <v>0.09297599999999999</v>
+        <v>0.08434</v>
       </c>
       <c r="H13" s="7">
-        <v>0.076655</v>
+        <v>0.07192599999999999</v>
       </c>
       <c r="I13" s="7">
-        <v>0.17299299999999998</v>
+        <v>0.167842</v>
       </c>
       <c r="J13" s="7">
-        <v>0.8982009999999999</v>
+        <v>0.8948529999999999</v>
       </c>
       <c r="K13" s="7">
-        <v>4.272395</v>
+        <v>4.244125</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.090753</v>
+        <v>-0.085873</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.17443999999999998</v>
+        <v>-0.17910399999999999</v>
       </c>
       <c r="G14" s="7">
-        <v>0.033879</v>
+        <v>0.026439</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.057173</v>
+        <v>-0.0625</v>
       </c>
       <c r="I14" s="7">
-        <v>0.518879</v>
+        <v>0.510297</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.065801</v>
+        <v>-0.0691</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.08613799999999999</v>
+        <v>-0.098571</v>
       </c>
       <c r="F17" s="7">
-        <v>0.054720000000000005</v>
+        <v>0.054302</v>
       </c>
       <c r="G17" s="7">
-        <v>0.196682</v>
+        <v>0.166359</v>
       </c>
       <c r="H17" s="7">
-        <v>0.158788</v>
+        <v>0.15833</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030692</v>
+        <v>0.030224</v>
       </c>
       <c r="F18" s="7">
-        <v>0.098863</v>
+        <v>0.099559</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.17444199999999999</v>
+        <v>0.17518599999999998</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.030815000000000002</v>
+        <v>-0.027851</v>
       </c>
       <c r="F19" s="7">
-        <v>0.201661</v>
+        <v>0.229236</v>
       </c>
       <c r="G19" s="7">
-        <v>0.513073</v>
+        <v>0.5226339999999999</v>
       </c>
       <c r="H19" s="7">
-        <v>0.456119</v>
+        <v>0.489533</v>
       </c>
       <c r="I19" s="7">
-        <v>0.7923690000000001</v>
+        <v>0.8334990000000001</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.087269</v>
+        <v>-0.083427</v>
       </c>
       <c r="F20" s="7">
-        <v>0.075252</v>
+        <v>0.08585100000000001</v>
       </c>
       <c r="G20" s="7">
-        <v>0.268918</v>
+        <v>0.25168</v>
       </c>
       <c r="H20" s="7">
-        <v>0.23081600000000002</v>
+        <v>0.242948</v>
       </c>
       <c r="I20" s="7">
-        <v>0.451878</v>
+        <v>0.46619</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.081319</v>
+        <v>-0.07278</v>
       </c>
       <c r="F21" s="7">
-        <v>0.038509</v>
+        <v>0.055072</v>
       </c>
       <c r="G21" s="7">
-        <v>0.147563</v>
+        <v>0.174735</v>
       </c>
       <c r="H21" s="7">
-        <v>0.15843</v>
+        <v>0.176905</v>
       </c>
       <c r="I21" s="7">
-        <v>0.35751</v>
+        <v>0.379161</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.080518</v>
+        <v>-0.079036</v>
       </c>
       <c r="F22" s="7">
-        <v>0.073636</v>
+        <v>0.08021</v>
       </c>
       <c r="G22" s="7">
-        <v>0.13917</v>
+        <v>0.14018</v>
       </c>
       <c r="H22" s="7">
-        <v>0.14476</v>
+        <v>0.15177</v>
       </c>
       <c r="I22" s="7">
-        <v>0.45803600000000005</v>
+        <v>0.466964</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.091256</v>
+        <v>-0.08676299999999999</v>
       </c>
       <c r="F23" s="7">
-        <v>0.060439999999999994</v>
+        <v>0.074045</v>
       </c>
       <c r="G23" s="7">
-        <v>0.26616700000000004</v>
+        <v>0.25496800000000003</v>
       </c>
       <c r="H23" s="7">
-        <v>0.23041899999999998</v>
+        <v>0.246205</v>
       </c>
       <c r="I23" s="7">
-        <v>0.450608</v>
+        <v>0.46921999999999997</v>
       </c>
       <c r="J23" s="7">
-        <v>1.559358</v>
+        <v>1.611988</v>
       </c>
       <c r="K23" s="7">
-        <v>10.085886</v>
+        <v>10.215847</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.103323</v>
+        <v>-0.066812</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.054717</v>
+        <v>-0.017898</v>
       </c>
       <c r="G24" s="7">
-        <v>-0.025823</v>
+        <v>0.000521</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.043219</v>
+        <v>-0.005952</v>
       </c>
       <c r="I24" s="7">
-        <v>0.231512</v>
+        <v>0.27948</v>
       </c>
       <c r="J24" s="7">
-        <v>2.302072</v>
+        <v>2.441756</v>
       </c>
       <c r="K24" s="7">
-        <v>14.25165</v>
+        <v>14.819605</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.08715500000000001</v>
+        <v>-0.08101000000000001</v>
       </c>
       <c r="F25" s="7">
-        <v>0.08072800000000001</v>
+        <v>0.096362</v>
       </c>
       <c r="G25" s="7">
-        <v>0.304736</v>
+        <v>0.293427</v>
       </c>
       <c r="H25" s="7">
-        <v>0.285328</v>
+        <v>0.30392199999999997</v>
       </c>
       <c r="I25" s="7">
-        <v>0.476505</v>
+        <v>0.49786400000000003</v>
       </c>
       <c r="J25" s="7">
-        <v>1.3104040000000001</v>
+        <v>1.3478210000000002</v>
       </c>
       <c r="K25" s="7">
-        <v>9.047569</v>
+        <v>9.182154</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.08084300000000001</v>
+        <v>-0.052733999999999996</v>
       </c>
       <c r="F26" s="7">
-        <v>0.015235</v>
+        <v>0.026238</v>
       </c>
       <c r="G26" s="7">
-        <v>0.11322499999999999</v>
+        <v>0.10984</v>
       </c>
       <c r="H26" s="7">
-        <v>0.095934</v>
+        <v>0.107812</v>
       </c>
       <c r="I26" s="7">
-        <v>0.31813199999999997</v>
+        <v>0.332418</v>
       </c>
       <c r="J26" s="7">
-        <v>1.046928</v>
+        <v>1.0963</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.08450200000000001</v>
+        <v>-0.081604</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.159019</v>
+        <v>-0.165305</v>
       </c>
       <c r="G27" s="7">
-        <v>0.02765</v>
+        <v>0.031056</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.042233</v>
+        <v>-0.049392</v>
       </c>
       <c r="I27" s="7">
-        <v>0.510158</v>
+        <v>0.49887099999999995</v>
       </c>
       <c r="J27" s="7">
-        <v>3.399868</v>
+        <v>3.301911</v>
       </c>
       <c r="K27" s="7">
-        <v>11.835764</v>
+        <v>11.759416000000002</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.0041210000000000005</v>
+        <v>-0.035092</v>
       </c>
       <c r="F28" s="7">
-        <v>0.32667900000000005</v>
+        <v>0.307441</v>
       </c>
       <c r="G28" s="7">
-        <v>0.548729</v>
+        <v>0.559983</v>
       </c>
       <c r="H28" s="7">
-        <v>0.496111</v>
+        <v>0.474417</v>
       </c>
       <c r="I28" s="7">
-        <v>0.8640349999999999</v>
+        <v>0.837005</v>
       </c>
       <c r="J28" s="7">
-        <v>1.90633</v>
+        <v>1.901095</v>
       </c>
       <c r="K28" s="7">
-        <v>8.295524</v>
+        <v>8.156075</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.032875</v>
+        <v>-0.055743</v>
       </c>
       <c r="F29" s="7">
-        <v>0.17729199999999998</v>
+        <v>0.1745</v>
       </c>
       <c r="G29" s="7">
-        <v>0.429379</v>
+        <v>0.44974200000000003</v>
       </c>
       <c r="H29" s="7">
-        <v>0.367568</v>
+        <v>0.36432400000000004</v>
       </c>
       <c r="I29" s="7">
-        <v>0.732877</v>
+        <v>0.7287669999999999</v>
       </c>
       <c r="J29" s="7">
-        <v>1.9997630000000002</v>
+        <v>2.001189</v>
       </c>
       <c r="K29" s="7">
-        <v>11.555831000000001</v>
+        <v>11.519841</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.08538899999999999</v>
+        <v>-0.086272</v>
       </c>
       <c r="F30" s="7">
-        <v>0.095953</v>
+        <v>0.107776</v>
       </c>
       <c r="G30" s="7">
-        <v>0.37087600000000004</v>
+        <v>0.358996</v>
       </c>
       <c r="H30" s="7">
-        <v>0.324904</v>
+        <v>0.33919699999999997</v>
       </c>
       <c r="I30" s="7">
-        <v>0.5325909999999999</v>
+        <v>0.549126</v>
       </c>
       <c r="J30" s="7">
-        <v>1.572038</v>
+        <v>1.621046</v>
       </c>
       <c r="K30" s="7">
-        <v>10.580971</v>
+        <v>10.683453</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.036078</v>
+        <v>-0.046154</v>
       </c>
       <c r="F31" s="7">
-        <v>0.26570499999999997</v>
+        <v>0.277034</v>
       </c>
       <c r="G31" s="7">
-        <v>0.540486</v>
+        <v>0.534653</v>
       </c>
       <c r="H31" s="7">
-        <v>0.5050209999999999</v>
+        <v>0.518491</v>
       </c>
       <c r="I31" s="7">
-        <v>0.572416</v>
+        <v>0.5864889999999999</v>
       </c>
       <c r="J31" s="7">
-        <v>2.541787</v>
+        <v>2.54387</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.08274</v>
+        <v>-0.085117</v>
       </c>
       <c r="F32" s="7">
-        <v>0.104378</v>
+        <v>0.11167500000000001</v>
       </c>
       <c r="G32" s="7">
-        <v>0.382446</v>
+        <v>0.361305</v>
       </c>
       <c r="H32" s="7">
-        <v>0.350795</v>
+        <v>0.35972099999999996</v>
       </c>
       <c r="I32" s="7">
-        <v>0.518099</v>
+        <v>0.528129</v>
       </c>
       <c r="J32" s="7">
-        <v>1.118943</v>
+        <v>1.142857</v>
       </c>
       <c r="K32" s="7">
-        <v>8.327437999999999</v>
+        <v>8.368984000000001</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.09909599999999999</v>
+        <v>-0.089482</v>
       </c>
       <c r="F33" s="7">
-        <v>0.025974</v>
+        <v>0.038961</v>
       </c>
       <c r="G33" s="7">
-        <v>0.190439</v>
+        <v>0.18337199999999998</v>
       </c>
       <c r="H33" s="7">
-        <v>0.162944</v>
+        <v>0.17766500000000002</v>
       </c>
       <c r="I33" s="7">
-        <v>0.37515</v>
+        <v>0.392557</v>
       </c>
       <c r="J33" s="7">
-        <v>1.657773</v>
+        <v>1.682081</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.031467</v>
+        <v>0.03185</v>
       </c>
       <c r="F34" s="7">
-        <v>0.102665</v>
+        <v>0.10397600000000001</v>
       </c>
       <c r="G34" s="7">
-        <v>0.208812</v>
+        <v>0.209091</v>
       </c>
       <c r="H34" s="7">
-        <v>0.175594</v>
+        <v>0.176991</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.08088</v>
+        <v>-0.079747</v>
       </c>
       <c r="F35" s="7">
-        <v>0.06274</v>
+        <v>0.075762</v>
       </c>
       <c r="G35" s="7">
-        <v>0.214817</v>
+        <v>0.205239</v>
       </c>
       <c r="H35" s="7">
-        <v>0.19620300000000002</v>
+        <v>0.210859</v>
       </c>
       <c r="I35" s="7">
-        <v>0.411557</v>
+        <v>0.42885199999999996</v>
       </c>
       <c r="J35" s="7">
-        <v>1.8266689999999999</v>
+        <v>1.8785239999999999</v>
       </c>
       <c r="K35" s="7">
-        <v>9.041946000000001</v>
+        <v>9.170677</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.031441</v>
+        <v>0.031416</v>
       </c>
       <c r="F36" s="7">
-        <v>0.102575</v>
+        <v>0.103448</v>
       </c>
       <c r="G36" s="7">
-        <v>0.208612</v>
+        <v>0.20841300000000001</v>
       </c>
       <c r="H36" s="7">
-        <v>0.176525</v>
+        <v>0.177457</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>09.06.2026 10:03:03</t>
+    <t>10.06.2026 10:56:56</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.06442300000000001</v>
+        <v>-0.059674</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.015642</v>
+        <v>-0.010215</v>
       </c>
       <c r="G6" s="7">
-        <v>0.003988</v>
+        <v>0.00021999999999999998</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.001982</v>
+        <v>0.003084</v>
       </c>
       <c r="I6" s="7">
-        <v>0.274184</v>
+        <v>0.280652</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.086638</v>
+        <v>-0.095731</v>
       </c>
       <c r="F7" s="7">
-        <v>0.103785</v>
+        <v>0.105962</v>
       </c>
       <c r="G7" s="7">
-        <v>0.351776</v>
+        <v>0.335323</v>
       </c>
       <c r="H7" s="7">
-        <v>0.332351</v>
+        <v>0.319086</v>
       </c>
       <c r="I7" s="7">
-        <v>0.539378</v>
+        <v>0.524053</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.087218</v>
+        <v>-0.09706899999999999</v>
       </c>
       <c r="F8" s="7">
-        <v>0.076814</v>
+        <v>0.071266</v>
       </c>
       <c r="G8" s="7">
-        <v>0.25214200000000003</v>
+        <v>0.235778</v>
       </c>
       <c r="H8" s="7">
-        <v>0.24312799999999998</v>
+        <v>0.229712</v>
       </c>
       <c r="I8" s="7">
-        <v>0.46792900000000004</v>
+        <v>0.452087</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.030952999999999998</v>
+        <v>0.03236</v>
       </c>
       <c r="F9" s="7">
-        <v>0.10188000000000001</v>
+        <v>0.10255399999999999</v>
       </c>
       <c r="G9" s="7">
-        <v>0.204933</v>
+        <v>0.205339</v>
       </c>
       <c r="H9" s="7">
-        <v>0.173809</v>
+        <v>0.17541</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.048976</v>
+        <v>-0.076186</v>
       </c>
       <c r="F10" s="7">
-        <v>0.243646</v>
+        <v>0.19031700000000001</v>
       </c>
       <c r="G10" s="7">
-        <v>0.182345</v>
+        <v>0.124961</v>
       </c>
       <c r="H10" s="7">
-        <v>0.26989599999999997</v>
+        <v>0.233564</v>
       </c>
       <c r="I10" s="7">
-        <v>0.49308399999999997</v>
+        <v>0.450366</v>
       </c>
       <c r="J10" s="7">
-        <v>0.861055</v>
+        <v>0.77983</v>
       </c>
       <c r="K10" s="7">
-        <v>7.115878</v>
+        <v>6.848965</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.064236</v>
+        <v>-0.074653</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.147826</v>
+        <v>-0.14136100000000001</v>
       </c>
       <c r="G11" s="7">
-        <v>0.08016</v>
+        <v>0.073947</v>
       </c>
       <c r="H11" s="7">
-        <v>0.009363</v>
+        <v>-0.0018729999999999999</v>
       </c>
       <c r="I11" s="7">
-        <v>0.47792700000000005</v>
+        <v>0.461475</v>
       </c>
       <c r="J11" s="7">
-        <v>3.074074</v>
+        <v>3.0563170000000004</v>
       </c>
       <c r="K11" s="7">
-        <v>10.735249</v>
+        <v>10.660468000000002</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.118785</v>
+        <v>-0.16022099999999997</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.15831099999999998</v>
+        <v>-0.18004</v>
       </c>
       <c r="G12" s="7">
-        <v>0.280096</v>
+        <v>0.193327</v>
       </c>
       <c r="H12" s="7">
-        <v>-0.00739</v>
+        <v>-0.054065</v>
       </c>
       <c r="I12" s="7">
-        <v>1.2704630000000001</v>
+        <v>1.1637009999999999</v>
       </c>
       <c r="J12" s="7">
-        <v>4.3953489999999995</v>
+        <v>4.14818</v>
       </c>
       <c r="K12" s="7">
-        <v>11.928064999999998</v>
+        <v>11.325156999999999</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.014844</v>
+        <v>0.014609</v>
       </c>
       <c r="F13" s="7">
-        <v>0.043362</v>
+        <v>0.04211</v>
       </c>
       <c r="G13" s="7">
-        <v>0.08434</v>
+        <v>0.08436199999999999</v>
       </c>
       <c r="H13" s="7">
-        <v>0.07192599999999999</v>
+        <v>0.071677</v>
       </c>
       <c r="I13" s="7">
-        <v>0.167842</v>
+        <v>0.16757000000000002</v>
       </c>
       <c r="J13" s="7">
-        <v>0.8948529999999999</v>
+        <v>0.929211</v>
       </c>
       <c r="K13" s="7">
-        <v>4.244125</v>
+        <v>4.267278</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.085873</v>
+        <v>-0.099723</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.17910399999999999</v>
+        <v>-0.1875</v>
       </c>
       <c r="G14" s="7">
-        <v>0.026439</v>
+        <v>0.015625</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.0625</v>
+        <v>-0.076705</v>
       </c>
       <c r="I14" s="7">
-        <v>0.510297</v>
+        <v>0.487414</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.0691</v>
+        <v>-0.073881</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1110,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.098571</v>
+        <v>-0.09285700000000001</v>
       </c>
       <c r="F17" s="7">
-        <v>0.054302</v>
+        <v>0.067675</v>
       </c>
       <c r="G17" s="7">
-        <v>0.166359</v>
+        <v>0.17701599999999998</v>
       </c>
       <c r="H17" s="7">
-        <v>0.15833</v>
+        <v>0.16567199999999999</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1139,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030224</v>
+        <v>0.031745999999999996</v>
       </c>
       <c r="F18" s="7">
-        <v>0.099559</v>
+        <v>0.100162</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.17518599999999998</v>
+        <v>0.176922</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1166,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.027851</v>
+        <v>-0.047031</v>
       </c>
       <c r="F19" s="7">
-        <v>0.229236</v>
+        <v>0.20819500000000002</v>
       </c>
       <c r="G19" s="7">
-        <v>0.5226339999999999</v>
+        <v>0.48040799999999995</v>
       </c>
       <c r="H19" s="7">
-        <v>0.489533</v>
+        <v>0.46014499999999997</v>
       </c>
       <c r="I19" s="7">
-        <v>0.8334990000000001</v>
+        <v>0.797324</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1197,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.083427</v>
+        <v>-0.09192600000000001</v>
       </c>
       <c r="F20" s="7">
-        <v>0.08585100000000001</v>
+        <v>0.091398</v>
       </c>
       <c r="G20" s="7">
-        <v>0.25168</v>
+        <v>0.237428</v>
       </c>
       <c r="H20" s="7">
-        <v>0.242948</v>
+        <v>0.231423</v>
       </c>
       <c r="I20" s="7">
-        <v>0.46619</v>
+        <v>0.452594</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1228,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.07278</v>
+        <v>-0.077875</v>
       </c>
       <c r="F21" s="7">
-        <v>0.055072</v>
+        <v>0.054735</v>
       </c>
       <c r="G21" s="7">
-        <v>0.174735</v>
+        <v>0.17125</v>
       </c>
       <c r="H21" s="7">
-        <v>0.176905</v>
+        <v>0.170439</v>
       </c>
       <c r="I21" s="7">
-        <v>0.379161</v>
+        <v>0.371583</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1259,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.079036</v>
+        <v>-0.07595299999999999</v>
       </c>
       <c r="F22" s="7">
-        <v>0.08021</v>
+        <v>0.091722</v>
       </c>
       <c r="G22" s="7">
-        <v>0.14018</v>
+        <v>0.152394</v>
       </c>
       <c r="H22" s="7">
-        <v>0.15177</v>
+        <v>0.155626</v>
       </c>
       <c r="I22" s="7">
-        <v>0.466964</v>
+        <v>0.471875</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1290,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.08676299999999999</v>
+        <v>-0.096774</v>
       </c>
       <c r="F23" s="7">
-        <v>0.074045</v>
+        <v>0.073506</v>
       </c>
       <c r="G23" s="7">
-        <v>0.25496800000000003</v>
+        <v>0.235921</v>
       </c>
       <c r="H23" s="7">
-        <v>0.246205</v>
+        <v>0.232544</v>
       </c>
       <c r="I23" s="7">
-        <v>0.46921999999999997</v>
+        <v>0.453114</v>
       </c>
       <c r="J23" s="7">
-        <v>1.611988</v>
+        <v>1.553459</v>
       </c>
       <c r="K23" s="7">
-        <v>10.215847</v>
+        <v>10.074741</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1325,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.066812</v>
+        <v>-0.061952999999999994</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.017898</v>
+        <v>-0.013289</v>
       </c>
       <c r="G24" s="7">
-        <v>0.000521</v>
+        <v>-0.001552</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.005952</v>
+        <v>-0.000776</v>
       </c>
       <c r="I24" s="7">
-        <v>0.27948</v>
+        <v>0.286143</v>
       </c>
       <c r="J24" s="7">
-        <v>2.441756</v>
+        <v>2.426518</v>
       </c>
       <c r="K24" s="7">
-        <v>14.819605</v>
+        <v>14.82377</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1360,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.08101000000000001</v>
+        <v>-0.089588</v>
       </c>
       <c r="F25" s="7">
-        <v>0.096362</v>
+        <v>0.092651</v>
       </c>
       <c r="G25" s="7">
-        <v>0.293427</v>
+        <v>0.284802</v>
       </c>
       <c r="H25" s="7">
-        <v>0.30392199999999997</v>
+        <v>0.291751</v>
       </c>
       <c r="I25" s="7">
-        <v>0.49786400000000003</v>
+        <v>0.483883</v>
       </c>
       <c r="J25" s="7">
-        <v>1.3478210000000002</v>
+        <v>1.291317</v>
       </c>
       <c r="K25" s="7">
-        <v>9.182154</v>
+        <v>9.071165</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1395,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.052733999999999996</v>
+        <v>-0.060156</v>
       </c>
       <c r="F26" s="7">
-        <v>0.026238</v>
+        <v>0.018197</v>
       </c>
       <c r="G26" s="7">
-        <v>0.10984</v>
+        <v>0.122201</v>
       </c>
       <c r="H26" s="7">
-        <v>0.107812</v>
+        <v>0.099132</v>
       </c>
       <c r="I26" s="7">
-        <v>0.332418</v>
+        <v>0.321978</v>
       </c>
       <c r="J26" s="7">
-        <v>1.0963</v>
+        <v>1.026617</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1428,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.081604</v>
+        <v>-0.08540800000000001</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.165305</v>
+        <v>-0.157106</v>
       </c>
       <c r="G27" s="7">
-        <v>0.031056</v>
+        <v>0.032397</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.049392</v>
+        <v>-0.053329</v>
       </c>
       <c r="I27" s="7">
-        <v>0.49887099999999995</v>
+        <v>0.492664</v>
       </c>
       <c r="J27" s="7">
-        <v>3.301911</v>
+        <v>3.2306459999999997</v>
       </c>
       <c r="K27" s="7">
-        <v>11.759416000000002</v>
+        <v>11.740848000000002</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1463,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.035092</v>
+        <v>-0.056791</v>
       </c>
       <c r="F28" s="7">
-        <v>0.307441</v>
+        <v>0.252134</v>
       </c>
       <c r="G28" s="7">
-        <v>0.559983</v>
+        <v>0.532202</v>
       </c>
       <c r="H28" s="7">
-        <v>0.474417</v>
+        <v>0.441261</v>
       </c>
       <c r="I28" s="7">
-        <v>0.837005</v>
+        <v>0.795696</v>
       </c>
       <c r="J28" s="7">
-        <v>1.901095</v>
+        <v>1.793558</v>
       </c>
       <c r="K28" s="7">
-        <v>8.156075</v>
+        <v>7.95473</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1498,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.055743</v>
+        <v>-0.063973</v>
       </c>
       <c r="F29" s="7">
-        <v>0.1745</v>
+        <v>0.169159</v>
       </c>
       <c r="G29" s="7">
-        <v>0.44974200000000003</v>
+        <v>0.439172</v>
       </c>
       <c r="H29" s="7">
-        <v>0.36432400000000004</v>
+        <v>0.352432</v>
       </c>
       <c r="I29" s="7">
-        <v>0.7287669999999999</v>
+        <v>0.713699</v>
       </c>
       <c r="J29" s="7">
-        <v>2.001189</v>
+        <v>1.9393799999999999</v>
       </c>
       <c r="K29" s="7">
-        <v>11.519841</v>
+        <v>11.373887</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1533,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.086272</v>
+        <v>-0.104276</v>
       </c>
       <c r="F30" s="7">
-        <v>0.107776</v>
+        <v>0.09466</v>
       </c>
       <c r="G30" s="7">
-        <v>0.358996</v>
+        <v>0.32556199999999996</v>
       </c>
       <c r="H30" s="7">
-        <v>0.33919699999999997</v>
+        <v>0.312809</v>
       </c>
       <c r="I30" s="7">
-        <v>0.549126</v>
+        <v>0.518601</v>
       </c>
       <c r="J30" s="7">
-        <v>1.621046</v>
+        <v>1.512098</v>
       </c>
       <c r="K30" s="7">
-        <v>10.683453</v>
+        <v>10.480769</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1568,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.046154</v>
+        <v>-0.062308</v>
       </c>
       <c r="F31" s="7">
-        <v>0.277034</v>
+        <v>0.274038</v>
       </c>
       <c r="G31" s="7">
-        <v>0.534653</v>
+        <v>0.465497</v>
       </c>
       <c r="H31" s="7">
-        <v>0.518491</v>
+        <v>0.492775</v>
       </c>
       <c r="I31" s="7">
-        <v>0.5864889999999999</v>
+        <v>0.559621</v>
       </c>
       <c r="J31" s="7">
-        <v>2.54387</v>
+        <v>2.414566</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1601,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.085117</v>
+        <v>-0.091906</v>
       </c>
       <c r="F32" s="7">
-        <v>0.11167500000000001</v>
+        <v>0.115101</v>
       </c>
       <c r="G32" s="7">
-        <v>0.361305</v>
+        <v>0.35172899999999996</v>
       </c>
       <c r="H32" s="7">
-        <v>0.35972099999999996</v>
+        <v>0.34963099999999997</v>
       </c>
       <c r="I32" s="7">
-        <v>0.528129</v>
+        <v>0.51679</v>
       </c>
       <c r="J32" s="7">
-        <v>1.142857</v>
+        <v>1.1078789999999998</v>
       </c>
       <c r="K32" s="7">
-        <v>8.368984000000001</v>
+        <v>8.294495</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1636,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.089482</v>
+        <v>-0.08928599999999999</v>
       </c>
       <c r="F33" s="7">
-        <v>0.038961</v>
+        <v>0.045270000000000005</v>
       </c>
       <c r="G33" s="7">
-        <v>0.18337199999999998</v>
+        <v>0.17762</v>
       </c>
       <c r="H33" s="7">
-        <v>0.17766500000000002</v>
+        <v>0.177919</v>
       </c>
       <c r="I33" s="7">
-        <v>0.392557</v>
+        <v>0.392857</v>
       </c>
       <c r="J33" s="7">
-        <v>1.682081</v>
+        <v>1.653516</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1669,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.03185</v>
+        <v>0.032666</v>
       </c>
       <c r="F34" s="7">
-        <v>0.10397600000000001</v>
+        <v>0.104367</v>
       </c>
       <c r="G34" s="7">
-        <v>0.209091</v>
+        <v>0.208313</v>
       </c>
       <c r="H34" s="7">
-        <v>0.176991</v>
+        <v>0.177923</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1698,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.079747</v>
+        <v>-0.08354400000000001</v>
       </c>
       <c r="F35" s="7">
-        <v>0.075762</v>
+        <v>0.073229</v>
       </c>
       <c r="G35" s="7">
-        <v>0.205239</v>
+        <v>0.199867</v>
       </c>
       <c r="H35" s="7">
-        <v>0.210859</v>
+        <v>0.20586300000000002</v>
       </c>
       <c r="I35" s="7">
-        <v>0.42885199999999996</v>
+        <v>0.422956</v>
       </c>
       <c r="J35" s="7">
-        <v>1.8785239999999999</v>
+        <v>1.797527</v>
       </c>
       <c r="K35" s="7">
-        <v>9.170677</v>
+        <v>9.055556000000001</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1733,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.031416</v>
+        <v>0.032639999999999995</v>
       </c>
       <c r="F36" s="7">
-        <v>0.103448</v>
+        <v>0.103794</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20841300000000001</v>
+        <v>0.209269</v>
       </c>
       <c r="H36" s="7">
-        <v>0.177457</v>
+        <v>0.178854</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>10.06.2026 10:56:56</t>
+    <t>11.06.2026 10:17:08</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.059674</v>
+        <v>-0.064629</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.010215</v>
+        <v>-0.063275</v>
       </c>
       <c r="G6" s="7">
-        <v>0.00021999999999999998</v>
+        <v>0.006666999999999999</v>
       </c>
       <c r="H6" s="7">
-        <v>0.003084</v>
+        <v>-0.002203</v>
       </c>
       <c r="I6" s="7">
-        <v>0.280652</v>
+        <v>0.210259</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.095731</v>
+        <v>-0.086385</v>
       </c>
       <c r="F7" s="7">
-        <v>0.105962</v>
+        <v>0.07745</v>
       </c>
       <c r="G7" s="7">
-        <v>0.335323</v>
+        <v>0.327827</v>
       </c>
       <c r="H7" s="7">
-        <v>0.319086</v>
+        <v>0.33271900000000004</v>
       </c>
       <c r="I7" s="7">
-        <v>0.524053</v>
+        <v>0.5229469999999999</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.09706899999999999</v>
+        <v>-0.093945</v>
       </c>
       <c r="F8" s="7">
-        <v>0.071266</v>
+        <v>0.033717000000000004</v>
       </c>
       <c r="G8" s="7">
-        <v>0.235778</v>
+        <v>0.235583</v>
       </c>
       <c r="H8" s="7">
-        <v>0.229712</v>
+        <v>0.233966</v>
       </c>
       <c r="I8" s="7">
-        <v>0.452087</v>
+        <v>0.430577</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.03236</v>
+        <v>0.033064</v>
       </c>
       <c r="F9" s="7">
-        <v>0.10255399999999999</v>
+        <v>0.102064</v>
       </c>
       <c r="G9" s="7">
-        <v>0.205339</v>
+        <v>0.204923</v>
       </c>
       <c r="H9" s="7">
-        <v>0.17541</v>
+        <v>0.17621099999999998</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.076186</v>
+        <v>-0.09665699999999999</v>
       </c>
       <c r="F10" s="7">
-        <v>0.19031700000000001</v>
+        <v>0.121983</v>
       </c>
       <c r="G10" s="7">
-        <v>0.124961</v>
+        <v>0.128886</v>
       </c>
       <c r="H10" s="7">
-        <v>0.233564</v>
+        <v>0.20622800000000002</v>
       </c>
       <c r="I10" s="7">
-        <v>0.450366</v>
+        <v>0.410479</v>
       </c>
       <c r="J10" s="7">
-        <v>0.77983</v>
+        <v>0.740389</v>
       </c>
       <c r="K10" s="7">
-        <v>6.848965</v>
+        <v>6.628009</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.074653</v>
+        <v>-0.10546900000000001</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.14136100000000001</v>
+        <v>-0.188583</v>
       </c>
       <c r="G11" s="7">
-        <v>0.073947</v>
+        <v>0.047256</v>
       </c>
       <c r="H11" s="7">
-        <v>-0.0018729999999999999</v>
+        <v>-0.035112000000000004</v>
       </c>
       <c r="I11" s="7">
-        <v>0.461475</v>
+        <v>0.433639</v>
       </c>
       <c r="J11" s="7">
-        <v>3.0563170000000004</v>
+        <v>2.9212329999999995</v>
       </c>
       <c r="K11" s="7">
-        <v>10.660468000000002</v>
+        <v>10.452545</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.16022099999999997</v>
+        <v>-0.180249</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.18004</v>
+        <v>-0.23910299999999998</v>
       </c>
       <c r="G12" s="7">
-        <v>0.193327</v>
+        <v>0.149637</v>
       </c>
       <c r="H12" s="7">
-        <v>-0.054065</v>
+        <v>-0.076624</v>
       </c>
       <c r="I12" s="7">
-        <v>1.1637009999999999</v>
+        <v>1.085383</v>
       </c>
       <c r="J12" s="7">
-        <v>4.14818</v>
+        <v>4.025402000000001</v>
       </c>
       <c r="K12" s="7">
-        <v>11.325156999999999</v>
+        <v>11.211934000000001</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.014609</v>
+        <v>0.013431</v>
       </c>
       <c r="F13" s="7">
-        <v>0.04211</v>
+        <v>0.043932</v>
       </c>
       <c r="G13" s="7">
-        <v>0.08436199999999999</v>
+        <v>0.08419499999999999</v>
       </c>
       <c r="H13" s="7">
-        <v>0.071677</v>
+        <v>0.07043300000000001</v>
       </c>
       <c r="I13" s="7">
-        <v>0.16757000000000002</v>
+        <v>0.169068</v>
       </c>
       <c r="J13" s="7">
-        <v>0.929211</v>
+        <v>0.9269710000000001</v>
       </c>
       <c r="K13" s="7">
-        <v>4.267278</v>
+        <v>4.329616</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.099723</v>
+        <v>-0.11980600000000001</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.1875</v>
+        <v>-0.21104900000000001</v>
       </c>
       <c r="G14" s="7">
-        <v>0.015625</v>
+        <v>-0.003528</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.076705</v>
+        <v>-0.097301</v>
       </c>
       <c r="I14" s="7">
-        <v>0.487414</v>
+        <v>0.457569</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,9 +1087,11 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.073881</v>
-      </c>
-      <c r="F16" s="7"/>
+        <v>-0.10995200000000001</v>
+      </c>
+      <c r="F16" s="7">
+        <v>-0.174304</v>
+      </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -1110,16 +1112,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.09285700000000001</v>
+        <v>-0.107143</v>
       </c>
       <c r="F17" s="7">
-        <v>0.067675</v>
+        <v>0.0004</v>
       </c>
       <c r="G17" s="7">
-        <v>0.17701599999999998</v>
+        <v>0.16009299999999999</v>
       </c>
       <c r="H17" s="7">
-        <v>0.16567199999999999</v>
+        <v>0.147315</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1139,14 +1141,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.031745999999999996</v>
+        <v>0.032833</v>
       </c>
       <c r="F18" s="7">
-        <v>0.100162</v>
+        <v>0.099537</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.176922</v>
+        <v>0.178162</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1166,19 +1168,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.047031</v>
+        <v>-0.041250999999999996</v>
       </c>
       <c r="F19" s="7">
-        <v>0.20819500000000002</v>
+        <v>0.196786</v>
       </c>
       <c r="G19" s="7">
-        <v>0.48040799999999995</v>
+        <v>0.489084</v>
       </c>
       <c r="H19" s="7">
-        <v>0.46014499999999997</v>
+        <v>0.469002</v>
       </c>
       <c r="I19" s="7">
-        <v>0.797324</v>
+        <v>0.78</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1197,19 +1199,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.09192600000000001</v>
+        <v>-0.08968899999999999</v>
       </c>
       <c r="F20" s="7">
-        <v>0.091398</v>
+        <v>0.04359</v>
       </c>
       <c r="G20" s="7">
-        <v>0.237428</v>
+        <v>0.24199</v>
       </c>
       <c r="H20" s="7">
-        <v>0.231423</v>
+        <v>0.234456</v>
       </c>
       <c r="I20" s="7">
-        <v>0.452594</v>
+        <v>0.426569</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1228,19 +1230,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.077875</v>
+        <v>-0.08187799999999999</v>
       </c>
       <c r="F21" s="7">
-        <v>0.054735</v>
+        <v>0.013864000000000001</v>
       </c>
       <c r="G21" s="7">
-        <v>0.17125</v>
+        <v>0.16913799999999998</v>
       </c>
       <c r="H21" s="7">
-        <v>0.170439</v>
+        <v>0.16535799999999998</v>
       </c>
       <c r="I21" s="7">
-        <v>0.371583</v>
+        <v>0.34345</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1259,19 +1261,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.07595299999999999</v>
+        <v>-0.079877</v>
       </c>
       <c r="F22" s="7">
-        <v>0.091722</v>
+        <v>0.048882</v>
       </c>
       <c r="G22" s="7">
-        <v>0.152394</v>
+        <v>0.148705</v>
       </c>
       <c r="H22" s="7">
-        <v>0.155626</v>
+        <v>0.150719</v>
       </c>
       <c r="I22" s="7">
-        <v>0.471875</v>
+        <v>0.429256</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1290,25 +1292,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.096774</v>
+        <v>-0.095217</v>
       </c>
       <c r="F23" s="7">
-        <v>0.073506</v>
+        <v>0.029881</v>
       </c>
       <c r="G23" s="7">
-        <v>0.235921</v>
+        <v>0.239939</v>
       </c>
       <c r="H23" s="7">
-        <v>0.232544</v>
+        <v>0.234669</v>
       </c>
       <c r="I23" s="7">
-        <v>0.453114</v>
+        <v>0.427518</v>
       </c>
       <c r="J23" s="7">
-        <v>1.553459</v>
+        <v>1.557862</v>
       </c>
       <c r="K23" s="7">
-        <v>10.074741</v>
+        <v>9.845333</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,25 +1327,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.061952999999999994</v>
+        <v>-0.06997099999999999</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.013289</v>
+        <v>-0.067251</v>
       </c>
       <c r="G24" s="7">
-        <v>-0.001552</v>
+        <v>0.001832</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.000776</v>
+        <v>-0.009316999999999999</v>
       </c>
       <c r="I24" s="7">
-        <v>0.286143</v>
+        <v>0.214082</v>
       </c>
       <c r="J24" s="7">
-        <v>2.426518</v>
+        <v>2.3972309999999997</v>
       </c>
       <c r="K24" s="7">
-        <v>14.82377</v>
+        <v>14.497976000000001</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1360,25 +1362,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.089588</v>
+        <v>-0.096021</v>
       </c>
       <c r="F25" s="7">
-        <v>0.092651</v>
+        <v>0.042308000000000005</v>
       </c>
       <c r="G25" s="7">
-        <v>0.284802</v>
+        <v>0.28566600000000003</v>
       </c>
       <c r="H25" s="7">
-        <v>0.291751</v>
+        <v>0.282623</v>
       </c>
       <c r="I25" s="7">
-        <v>0.483883</v>
+        <v>0.449752</v>
       </c>
       <c r="J25" s="7">
-        <v>1.291317</v>
+        <v>1.275126</v>
       </c>
       <c r="K25" s="7">
-        <v>9.071165</v>
+        <v>8.947562</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,22 +1397,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.060156</v>
+        <v>-0.062109</v>
       </c>
       <c r="F26" s="7">
-        <v>0.018197</v>
+        <v>-0.062109</v>
       </c>
       <c r="G26" s="7">
-        <v>0.122201</v>
+        <v>0.10137600000000001</v>
       </c>
       <c r="H26" s="7">
-        <v>0.099132</v>
+        <v>0.09684799999999999</v>
       </c>
       <c r="I26" s="7">
-        <v>0.321978</v>
+        <v>0.292528</v>
       </c>
       <c r="J26" s="7">
-        <v>1.026617</v>
+        <v>1.022406</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1428,25 +1430,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.08540800000000001</v>
+        <v>-0.11479900000000001</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.157106</v>
+        <v>-0.201995</v>
       </c>
       <c r="G27" s="7">
-        <v>0.032397</v>
+        <v>0.003922</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.053329</v>
+        <v>-0.08375099999999999</v>
       </c>
       <c r="I27" s="7">
-        <v>0.492664</v>
+        <v>0.459188</v>
       </c>
       <c r="J27" s="7">
-        <v>3.2306459999999997</v>
+        <v>3.09469</v>
       </c>
       <c r="K27" s="7">
-        <v>11.740848000000002</v>
+        <v>11.578616</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1465,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.056791</v>
+        <v>-0.04045</v>
       </c>
       <c r="F28" s="7">
-        <v>0.252134</v>
+        <v>0.259494</v>
       </c>
       <c r="G28" s="7">
-        <v>0.532202</v>
+        <v>0.545965</v>
       </c>
       <c r="H28" s="7">
-        <v>0.441261</v>
+        <v>0.46623</v>
       </c>
       <c r="I28" s="7">
-        <v>0.795696</v>
+        <v>0.8138549999999999</v>
       </c>
       <c r="J28" s="7">
-        <v>1.793558</v>
+        <v>1.841955</v>
       </c>
       <c r="K28" s="7">
-        <v>7.95473</v>
+        <v>8.091371</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1500,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.063973</v>
+        <v>-0.038533</v>
       </c>
       <c r="F29" s="7">
-        <v>0.169159</v>
+        <v>0.167121</v>
       </c>
       <c r="G29" s="7">
-        <v>0.439172</v>
+        <v>0.461473</v>
       </c>
       <c r="H29" s="7">
-        <v>0.352432</v>
+        <v>0.389189</v>
       </c>
       <c r="I29" s="7">
-        <v>0.713699</v>
+        <v>0.734728</v>
       </c>
       <c r="J29" s="7">
-        <v>1.9393799999999999</v>
+        <v>2.019267</v>
       </c>
       <c r="K29" s="7">
-        <v>11.373887</v>
+        <v>12.105558</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1535,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.104276</v>
+        <v>-0.089085</v>
       </c>
       <c r="F30" s="7">
-        <v>0.09466</v>
+        <v>0.081496</v>
       </c>
       <c r="G30" s="7">
-        <v>0.32556199999999996</v>
+        <v>0.34171300000000004</v>
       </c>
       <c r="H30" s="7">
-        <v>0.312809</v>
+        <v>0.335074</v>
       </c>
       <c r="I30" s="7">
-        <v>0.518601</v>
+        <v>0.530728</v>
       </c>
       <c r="J30" s="7">
-        <v>1.512098</v>
+        <v>1.554702</v>
       </c>
       <c r="K30" s="7">
-        <v>10.480769</v>
+        <v>10.586355000000001</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,22 +1570,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.062308</v>
+        <v>-0.051923000000000004</v>
       </c>
       <c r="F31" s="7">
-        <v>0.274038</v>
+        <v>0.23894300000000002</v>
       </c>
       <c r="G31" s="7">
-        <v>0.465497</v>
+        <v>0.48065800000000003</v>
       </c>
       <c r="H31" s="7">
-        <v>0.492775</v>
+        <v>0.5093070000000001</v>
       </c>
       <c r="I31" s="7">
-        <v>0.559621</v>
+        <v>0.570464</v>
       </c>
       <c r="J31" s="7">
-        <v>2.414566</v>
+        <v>2.452381</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1601,25 +1603,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.091906</v>
+        <v>-0.090862</v>
       </c>
       <c r="F32" s="7">
-        <v>0.115101</v>
+        <v>0.06941</v>
       </c>
       <c r="G32" s="7">
-        <v>0.35172899999999996</v>
+        <v>0.349612</v>
       </c>
       <c r="H32" s="7">
-        <v>0.34963099999999997</v>
+        <v>0.351184</v>
       </c>
       <c r="I32" s="7">
-        <v>0.51679</v>
+        <v>0.491859</v>
       </c>
       <c r="J32" s="7">
-        <v>1.1078789999999998</v>
+        <v>1.110303</v>
       </c>
       <c r="K32" s="7">
-        <v>8.294495</v>
+        <v>8.245884</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,22 +1638,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.08928599999999999</v>
+        <v>-0.089482</v>
       </c>
       <c r="F33" s="7">
-        <v>0.045270000000000005</v>
+        <v>0.010452999999999999</v>
       </c>
       <c r="G33" s="7">
-        <v>0.17762</v>
+        <v>0.178862</v>
       </c>
       <c r="H33" s="7">
-        <v>0.177919</v>
+        <v>0.17766500000000002</v>
       </c>
       <c r="I33" s="7">
-        <v>0.392857</v>
+        <v>0.36190199999999995</v>
       </c>
       <c r="J33" s="7">
-        <v>1.653516</v>
+        <v>1.6529449999999999</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1669,16 +1671,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.032666</v>
+        <v>0.033891</v>
       </c>
       <c r="F34" s="7">
-        <v>0.104367</v>
+        <v>0.10423</v>
       </c>
       <c r="G34" s="7">
-        <v>0.208313</v>
+        <v>0.209169</v>
       </c>
       <c r="H34" s="7">
-        <v>0.177923</v>
+        <v>0.17931999999999998</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1698,25 +1700,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.08354400000000001</v>
+        <v>-0.08557000000000001</v>
       </c>
       <c r="F35" s="7">
-        <v>0.073229</v>
+        <v>0.035847000000000004</v>
       </c>
       <c r="G35" s="7">
-        <v>0.199867</v>
+        <v>0.20319800000000002</v>
       </c>
       <c r="H35" s="7">
-        <v>0.20586300000000002</v>
+        <v>0.20319800000000002</v>
       </c>
       <c r="I35" s="7">
-        <v>0.422956</v>
+        <v>0.394056</v>
       </c>
       <c r="J35" s="7">
-        <v>1.797527</v>
+        <v>1.791345</v>
       </c>
       <c r="K35" s="7">
-        <v>9.055556000000001</v>
+        <v>8.988938000000001</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,16 +1735,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.032639999999999995</v>
+        <v>0.033864</v>
       </c>
       <c r="F36" s="7">
-        <v>0.103794</v>
+        <v>0.10462099999999999</v>
       </c>
       <c r="G36" s="7">
-        <v>0.209269</v>
+        <v>0.208969</v>
       </c>
       <c r="H36" s="7">
-        <v>0.178854</v>
+        <v>0.18025200000000002</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>11.06.2026 10:17:08</t>
+    <t>12.06.2026 12:02:06</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.064629</v>
+        <v>-0.080872</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.063275</v>
+        <v>-0.057841</v>
       </c>
       <c r="G6" s="7">
-        <v>0.006666999999999999</v>
+        <v>0.006469</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.002203</v>
+        <v>-0.006167000000000001</v>
       </c>
       <c r="I6" s="7">
-        <v>0.210259</v>
+        <v>0.209651</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.086385</v>
+        <v>-0.090106</v>
       </c>
       <c r="F7" s="7">
-        <v>0.07745</v>
+        <v>0.07196</v>
       </c>
       <c r="G7" s="7">
-        <v>0.327827</v>
+        <v>0.328787</v>
       </c>
       <c r="H7" s="7">
-        <v>0.33271900000000004</v>
+        <v>0.328298</v>
       </c>
       <c r="I7" s="7">
-        <v>0.5229469999999999</v>
+        <v>0.514706</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.093945</v>
+        <v>-0.09679</v>
       </c>
       <c r="F8" s="7">
-        <v>0.033717000000000004</v>
+        <v>0.03401</v>
       </c>
       <c r="G8" s="7">
-        <v>0.235583</v>
+        <v>0.236066</v>
       </c>
       <c r="H8" s="7">
-        <v>0.233966</v>
+        <v>0.233639</v>
       </c>
       <c r="I8" s="7">
-        <v>0.430577</v>
+        <v>0.424792</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.033064</v>
+        <v>0.035501</v>
       </c>
       <c r="F9" s="7">
-        <v>0.102064</v>
+        <v>0.104198</v>
       </c>
       <c r="G9" s="7">
-        <v>0.204923</v>
+        <v>0.204662</v>
       </c>
       <c r="H9" s="7">
-        <v>0.17621099999999998</v>
+        <v>0.179816</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.09665699999999999</v>
+        <v>-0.141258</v>
       </c>
       <c r="F10" s="7">
-        <v>0.121983</v>
+        <v>0.10921900000000001</v>
       </c>
       <c r="G10" s="7">
-        <v>0.128886</v>
+        <v>0.118924</v>
       </c>
       <c r="H10" s="7">
-        <v>0.20622800000000002</v>
+        <v>0.19481</v>
       </c>
       <c r="I10" s="7">
-        <v>0.410479</v>
+        <v>0.398825</v>
       </c>
       <c r="J10" s="7">
-        <v>0.740389</v>
+        <v>0.7239140000000001</v>
       </c>
       <c r="K10" s="7">
-        <v>6.628009</v>
+        <v>6.5491909999999995</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.10546900000000001</v>
+        <v>-0.12279899999999999</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.188583</v>
+        <v>-0.18540700000000002</v>
       </c>
       <c r="G11" s="7">
-        <v>0.047256</v>
+        <v>0.031818</v>
       </c>
       <c r="H11" s="7">
-        <v>-0.035112000000000004</v>
+        <v>-0.043539</v>
       </c>
       <c r="I11" s="7">
-        <v>0.433639</v>
+        <v>0.42428899999999997</v>
       </c>
       <c r="J11" s="7">
-        <v>2.9212329999999995</v>
+        <v>2.886986</v>
       </c>
       <c r="K11" s="7">
-        <v>10.452545</v>
+        <v>10.516347000000001</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.180249</v>
+        <v>-0.218802</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.23910299999999998</v>
+        <v>-0.218025</v>
       </c>
       <c r="G12" s="7">
-        <v>0.149637</v>
+        <v>0.10694200000000001</v>
       </c>
       <c r="H12" s="7">
-        <v>-0.076624</v>
+        <v>-0.08206899999999999</v>
       </c>
       <c r="I12" s="7">
-        <v>1.085383</v>
+        <v>1.078197</v>
       </c>
       <c r="J12" s="7">
-        <v>4.025402000000001</v>
+        <v>3.9957659999999997</v>
       </c>
       <c r="K12" s="7">
-        <v>11.211934000000001</v>
+        <v>11.159934</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.013431</v>
+        <v>0.018876999999999998</v>
       </c>
       <c r="F13" s="7">
-        <v>0.043932</v>
+        <v>0.047804</v>
       </c>
       <c r="G13" s="7">
-        <v>0.08419499999999999</v>
+        <v>0.086563</v>
       </c>
       <c r="H13" s="7">
-        <v>0.07043300000000001</v>
+        <v>0.07466400000000001</v>
       </c>
       <c r="I13" s="7">
-        <v>0.169068</v>
+        <v>0.174327</v>
       </c>
       <c r="J13" s="7">
-        <v>0.9269710000000001</v>
+        <v>0.934588</v>
       </c>
       <c r="K13" s="7">
-        <v>4.329616</v>
+        <v>4.41035</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.11980600000000001</v>
+        <v>-0.106769</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.21104900000000001</v>
+        <v>-0.201248</v>
       </c>
       <c r="G14" s="7">
-        <v>-0.003528</v>
+        <v>-0.0023380000000000002</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.097301</v>
+        <v>-0.09090899999999999</v>
       </c>
       <c r="I14" s="7">
-        <v>0.457569</v>
+        <v>0.46252299999999996</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,10 +1087,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.10995200000000001</v>
+        <v>-0.12080199999999999</v>
       </c>
       <c r="F16" s="7">
-        <v>-0.174304</v>
+        <v>-0.185208</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -1112,16 +1112,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.107143</v>
+        <v>-0.10094099999999999</v>
       </c>
       <c r="F17" s="7">
-        <v>0.0004</v>
+        <v>-0.006397000000000001</v>
       </c>
       <c r="G17" s="7">
-        <v>0.16009299999999999</v>
+        <v>0.151529</v>
       </c>
       <c r="H17" s="7">
-        <v>0.147315</v>
+        <v>0.140431</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1141,14 +1141,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.032833</v>
+        <v>0.034767</v>
       </c>
       <c r="F18" s="7">
-        <v>0.099537</v>
+        <v>0.101295</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.178162</v>
+        <v>0.18113900000000002</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1168,19 +1168,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.041250999999999996</v>
+        <v>-0.071338</v>
       </c>
       <c r="F19" s="7">
-        <v>0.196786</v>
+        <v>0.197044</v>
       </c>
       <c r="G19" s="7">
-        <v>0.489084</v>
+        <v>0.467391</v>
       </c>
       <c r="H19" s="7">
-        <v>0.469002</v>
+        <v>0.467391</v>
       </c>
       <c r="I19" s="7">
-        <v>0.78</v>
+        <v>0.76087</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1199,19 +1199,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.08968899999999999</v>
+        <v>-0.09443199999999999</v>
       </c>
       <c r="F20" s="7">
-        <v>0.04359</v>
+        <v>0.042564000000000005</v>
       </c>
       <c r="G20" s="7">
-        <v>0.24199</v>
+        <v>0.23774699999999999</v>
       </c>
       <c r="H20" s="7">
-        <v>0.234456</v>
+        <v>0.233242</v>
       </c>
       <c r="I20" s="7">
-        <v>0.426569</v>
+        <v>0.421678</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1230,19 +1230,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.08187799999999999</v>
+        <v>-0.079898</v>
       </c>
       <c r="F21" s="7">
-        <v>0.013864000000000001</v>
+        <v>0.013666000000000001</v>
       </c>
       <c r="G21" s="7">
-        <v>0.16913799999999998</v>
+        <v>0.163016</v>
       </c>
       <c r="H21" s="7">
-        <v>0.16535799999999998</v>
+        <v>0.164896</v>
       </c>
       <c r="I21" s="7">
-        <v>0.34345</v>
+        <v>0.336867</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1261,19 +1261,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.079877</v>
+        <v>-0.079944</v>
       </c>
       <c r="F22" s="7">
-        <v>0.048882</v>
+        <v>0.041601</v>
       </c>
       <c r="G22" s="7">
-        <v>0.148705</v>
+        <v>0.142857</v>
       </c>
       <c r="H22" s="7">
-        <v>0.150719</v>
+        <v>0.149667</v>
       </c>
       <c r="I22" s="7">
-        <v>0.429256</v>
+        <v>0.416235</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1292,25 +1292,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.095217</v>
+        <v>-0.103212</v>
       </c>
       <c r="F23" s="7">
-        <v>0.029881</v>
+        <v>0.031067</v>
       </c>
       <c r="G23" s="7">
-        <v>0.239939</v>
+        <v>0.23107299999999997</v>
       </c>
       <c r="H23" s="7">
-        <v>0.234669</v>
+        <v>0.229205</v>
       </c>
       <c r="I23" s="7">
-        <v>0.427518</v>
+        <v>0.41722099999999995</v>
       </c>
       <c r="J23" s="7">
-        <v>1.557862</v>
+        <v>1.546541</v>
       </c>
       <c r="K23" s="7">
-        <v>9.845333</v>
+        <v>9.961018000000001</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1327,25 +1327,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.06997099999999999</v>
+        <v>-0.07696</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.067251</v>
+        <v>-0.050555</v>
       </c>
       <c r="G24" s="7">
-        <v>0.001832</v>
+        <v>0.013158000000000001</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.009316999999999999</v>
+        <v>-0.003623</v>
       </c>
       <c r="I24" s="7">
-        <v>0.214082</v>
+        <v>0.22183399999999998</v>
       </c>
       <c r="J24" s="7">
-        <v>2.3972309999999997</v>
+        <v>2.416755</v>
       </c>
       <c r="K24" s="7">
-        <v>14.497976000000001</v>
+        <v>14.599675999999999</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1362,25 +1362,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.096021</v>
+        <v>-0.10351300000000001</v>
       </c>
       <c r="F25" s="7">
-        <v>0.042308000000000005</v>
+        <v>0.048538</v>
       </c>
       <c r="G25" s="7">
-        <v>0.28566600000000003</v>
+        <v>0.280566</v>
       </c>
       <c r="H25" s="7">
-        <v>0.282623</v>
+        <v>0.285328</v>
       </c>
       <c r="I25" s="7">
-        <v>0.449752</v>
+        <v>0.446728</v>
       </c>
       <c r="J25" s="7">
-        <v>1.275126</v>
+        <v>1.279923</v>
       </c>
       <c r="K25" s="7">
-        <v>8.947562</v>
+        <v>8.963312</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1397,22 +1397,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.062109</v>
+        <v>-0.08906700000000001</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.062109</v>
+        <v>-0.021757</v>
       </c>
       <c r="G26" s="7">
-        <v>0.10137600000000001</v>
+        <v>0.08862500000000001</v>
       </c>
       <c r="H26" s="7">
-        <v>0.09684799999999999</v>
+        <v>0.08862500000000001</v>
       </c>
       <c r="I26" s="7">
-        <v>0.292528</v>
+        <v>0.272426</v>
       </c>
       <c r="J26" s="7">
-        <v>1.022406</v>
+        <v>1.007244</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1430,25 +1430,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.11479900000000001</v>
+        <v>-0.106449</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.201995</v>
+        <v>-0.19468800000000003</v>
       </c>
       <c r="G27" s="7">
-        <v>0.003922</v>
+        <v>0.00507</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.08375099999999999</v>
+        <v>-0.077666</v>
       </c>
       <c r="I27" s="7">
-        <v>0.459188</v>
+        <v>0.46854300000000004</v>
       </c>
       <c r="J27" s="7">
-        <v>3.09469</v>
+        <v>3.121881</v>
       </c>
       <c r="K27" s="7">
-        <v>11.578616</v>
+        <v>11.843900000000001</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1465,25 +1465,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.04045</v>
+        <v>-0.055275</v>
       </c>
       <c r="F28" s="7">
-        <v>0.259494</v>
+        <v>0.234375</v>
       </c>
       <c r="G28" s="7">
-        <v>0.545965</v>
+        <v>0.5063559999999999</v>
       </c>
       <c r="H28" s="7">
-        <v>0.46623</v>
+        <v>0.455178</v>
       </c>
       <c r="I28" s="7">
-        <v>0.8138549999999999</v>
+        <v>0.775724</v>
       </c>
       <c r="J28" s="7">
-        <v>1.841955</v>
+        <v>1.8205330000000002</v>
       </c>
       <c r="K28" s="7">
-        <v>8.091371</v>
+        <v>7.98635</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1500,25 +1500,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.038533</v>
+        <v>-0.077509</v>
       </c>
       <c r="F29" s="7">
-        <v>0.167121</v>
+        <v>0.13830299999999998</v>
       </c>
       <c r="G29" s="7">
-        <v>0.461473</v>
+        <v>0.386313</v>
       </c>
       <c r="H29" s="7">
-        <v>0.389189</v>
+        <v>0.341351</v>
       </c>
       <c r="I29" s="7">
-        <v>0.734728</v>
+        <v>0.648837</v>
       </c>
       <c r="J29" s="7">
-        <v>2.019267</v>
+        <v>1.9152959999999999</v>
       </c>
       <c r="K29" s="7">
-        <v>12.105558</v>
+        <v>11.164216</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1535,25 +1535,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.089085</v>
+        <v>-0.09188299999999999</v>
       </c>
       <c r="F30" s="7">
-        <v>0.081496</v>
+        <v>0.068302</v>
       </c>
       <c r="G30" s="7">
-        <v>0.34171300000000004</v>
+        <v>0.329208</v>
       </c>
       <c r="H30" s="7">
-        <v>0.335074</v>
+        <v>0.328477</v>
       </c>
       <c r="I30" s="7">
-        <v>0.530728</v>
+        <v>0.5183789999999999</v>
       </c>
       <c r="J30" s="7">
-        <v>1.554702</v>
+        <v>1.542079</v>
       </c>
       <c r="K30" s="7">
-        <v>10.586355000000001</v>
+        <v>10.512625</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1570,22 +1570,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.051923000000000004</v>
+        <v>-0.041699</v>
       </c>
       <c r="F31" s="7">
-        <v>0.23894300000000002</v>
+        <v>0.24367799999999998</v>
       </c>
       <c r="G31" s="7">
-        <v>0.48065800000000003</v>
+        <v>0.478831</v>
       </c>
       <c r="H31" s="7">
-        <v>0.5093070000000001</v>
+        <v>0.505633</v>
       </c>
       <c r="I31" s="7">
-        <v>0.570464</v>
+        <v>0.558302</v>
       </c>
       <c r="J31" s="7">
-        <v>2.452381</v>
+        <v>2.443978</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1603,25 +1603,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.090862</v>
+        <v>-0.093726</v>
       </c>
       <c r="F32" s="7">
-        <v>0.06941</v>
+        <v>0.07372</v>
       </c>
       <c r="G32" s="7">
-        <v>0.349612</v>
+        <v>0.349748</v>
       </c>
       <c r="H32" s="7">
-        <v>0.351184</v>
+        <v>0.350795</v>
       </c>
       <c r="I32" s="7">
-        <v>0.491859</v>
+        <v>0.48253799999999997</v>
       </c>
       <c r="J32" s="7">
-        <v>1.110303</v>
+        <v>1.109697</v>
       </c>
       <c r="K32" s="7">
-        <v>8.245884</v>
+        <v>8.223635</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1638,22 +1638,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.089482</v>
+        <v>-0.093234</v>
       </c>
       <c r="F33" s="7">
-        <v>0.010452999999999999</v>
+        <v>0.001303</v>
       </c>
       <c r="G33" s="7">
-        <v>0.178862</v>
+        <v>0.168568</v>
       </c>
       <c r="H33" s="7">
-        <v>0.17766500000000002</v>
+        <v>0.17005099999999998</v>
       </c>
       <c r="I33" s="7">
-        <v>0.36190199999999995</v>
+        <v>0.345985</v>
       </c>
       <c r="J33" s="7">
-        <v>1.6529449999999999</v>
+        <v>1.635792</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1671,16 +1671,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.033891</v>
+        <v>0.036312000000000004</v>
       </c>
       <c r="F34" s="7">
-        <v>0.10423</v>
+        <v>0.106272</v>
       </c>
       <c r="G34" s="7">
-        <v>0.209169</v>
+        <v>0.208373</v>
       </c>
       <c r="H34" s="7">
-        <v>0.17931999999999998</v>
+        <v>0.18304600000000001</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1700,25 +1700,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.08557000000000001</v>
+        <v>-0.08959400000000001</v>
       </c>
       <c r="F35" s="7">
-        <v>0.035847000000000004</v>
+        <v>0.028678</v>
       </c>
       <c r="G35" s="7">
-        <v>0.20319800000000002</v>
+        <v>0.188535</v>
       </c>
       <c r="H35" s="7">
-        <v>0.20319800000000002</v>
+        <v>0.19487</v>
       </c>
       <c r="I35" s="7">
-        <v>0.394056</v>
+        <v>0.384942</v>
       </c>
       <c r="J35" s="7">
-        <v>1.791345</v>
+        <v>1.772025</v>
       </c>
       <c r="K35" s="7">
-        <v>8.988938000000001</v>
+        <v>8.876101</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1735,16 +1735,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.033864</v>
+        <v>0.035859999999999996</v>
       </c>
       <c r="F36" s="7">
-        <v>0.10462099999999999</v>
+        <v>0.10617900000000001</v>
       </c>
       <c r="G36" s="7">
-        <v>0.208969</v>
+        <v>0.208749</v>
       </c>
       <c r="H36" s="7">
-        <v>0.18025200000000002</v>
+        <v>0.183978</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>12.06.2026 12:02:06</t>
+    <t>15.06.2026 12:03:26</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>-0.080872</v>
+        <v>0.007406</v>
       </c>
       <c r="F6" s="7">
-        <v>-0.057841</v>
+        <v>0.035</v>
       </c>
       <c r="G6" s="7">
-        <v>0.006469</v>
+        <v>0.057999999999999996</v>
       </c>
       <c r="H6" s="7">
-        <v>-0.006167000000000001</v>
+        <v>0.048678</v>
       </c>
       <c r="I6" s="7">
-        <v>0.209651</v>
+        <v>0.328033</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.090106</v>
+        <v>-0.074416</v>
       </c>
       <c r="F7" s="7">
-        <v>0.07196</v>
+        <v>0.060882</v>
       </c>
       <c r="G7" s="7">
-        <v>0.328787</v>
+        <v>0.318348</v>
       </c>
       <c r="H7" s="7">
-        <v>0.328298</v>
+        <v>0.329035</v>
       </c>
       <c r="I7" s="7">
-        <v>0.514706</v>
+        <v>0.5847979999999999</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.09679</v>
+        <v>-0.061505000000000004</v>
       </c>
       <c r="F8" s="7">
-        <v>0.03401</v>
+        <v>0.059181</v>
       </c>
       <c r="G8" s="7">
-        <v>0.236066</v>
+        <v>0.24918500000000002</v>
       </c>
       <c r="H8" s="7">
-        <v>0.233639</v>
+        <v>0.253272</v>
       </c>
       <c r="I8" s="7">
-        <v>0.424792</v>
+        <v>0.512638</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.035501</v>
+        <v>0.031107999999999997</v>
       </c>
       <c r="F9" s="7">
-        <v>0.104198</v>
+        <v>0.100746</v>
       </c>
       <c r="G9" s="7">
-        <v>0.204662</v>
+        <v>0.205065</v>
       </c>
       <c r="H9" s="7">
-        <v>0.179816</v>
+        <v>0.181418</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.141258</v>
+        <v>-0.14464</v>
       </c>
       <c r="F10" s="7">
-        <v>0.10921900000000001</v>
+        <v>0.108468</v>
       </c>
       <c r="G10" s="7">
-        <v>0.118924</v>
+        <v>0.141038</v>
       </c>
       <c r="H10" s="7">
-        <v>0.19481</v>
+        <v>0.209343</v>
       </c>
       <c r="I10" s="7">
-        <v>0.398825</v>
+        <v>0.492952</v>
       </c>
       <c r="J10" s="7">
-        <v>0.7239140000000001</v>
+        <v>0.823637</v>
       </c>
       <c r="K10" s="7">
-        <v>6.5491909999999995</v>
+        <v>6.652726</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.12279899999999999</v>
+        <v>-0.082753</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.18540700000000002</v>
+        <v>-0.145985</v>
       </c>
       <c r="G11" s="7">
-        <v>0.031818</v>
+        <v>0.041028</v>
       </c>
       <c r="H11" s="7">
-        <v>-0.043539</v>
+        <v>-0.014045</v>
       </c>
       <c r="I11" s="7">
-        <v>0.42428899999999997</v>
+        <v>0.400638</v>
       </c>
       <c r="J11" s="7">
-        <v>2.886986</v>
+        <v>3.0798140000000003</v>
       </c>
       <c r="K11" s="7">
-        <v>10.516347000000001</v>
+        <v>10.925255</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.218802</v>
+        <v>-0.182927</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.218025</v>
+        <v>-0.151027</v>
       </c>
       <c r="G12" s="7">
-        <v>0.10694200000000001</v>
+        <v>0.11969300000000001</v>
       </c>
       <c r="H12" s="7">
-        <v>-0.08206899999999999</v>
+        <v>-0.035783999999999996</v>
       </c>
       <c r="I12" s="7">
-        <v>1.078197</v>
+        <v>1.1459489999999999</v>
       </c>
       <c r="J12" s="7">
-        <v>3.9957659999999997</v>
+        <v>4.31746</v>
       </c>
       <c r="K12" s="7">
-        <v>11.159934</v>
+        <v>11.778351</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.018876999999999998</v>
+        <v>0.019779</v>
       </c>
       <c r="F13" s="7">
-        <v>0.047804</v>
+        <v>0.043865999999999995</v>
       </c>
       <c r="G13" s="7">
-        <v>0.086563</v>
+        <v>0.08928599999999999</v>
       </c>
       <c r="H13" s="7">
-        <v>0.07466400000000001</v>
+        <v>0.077899</v>
       </c>
       <c r="I13" s="7">
-        <v>0.174327</v>
+        <v>0.1677</v>
       </c>
       <c r="J13" s="7">
-        <v>0.934588</v>
+        <v>0.925745</v>
       </c>
       <c r="K13" s="7">
-        <v>4.41035</v>
+        <v>4.38213</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.106769</v>
+        <v>-0.067989</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.201248</v>
+        <v>-0.155327</v>
       </c>
       <c r="G14" s="7">
-        <v>-0.0023380000000000002</v>
+        <v>0.028527</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.09090899999999999</v>
+        <v>-0.065341</v>
       </c>
       <c r="I14" s="7">
-        <v>0.46252299999999996</v>
+        <v>0.467767</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,10 +1087,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.12080199999999999</v>
+        <v>-0.073041</v>
       </c>
       <c r="F16" s="7">
-        <v>-0.185208</v>
+        <v>-0.134712</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -1112,16 +1112,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.10094099999999999</v>
+        <v>-0.060773</v>
       </c>
       <c r="F17" s="7">
-        <v>-0.006397000000000001</v>
+        <v>0.017964</v>
       </c>
       <c r="G17" s="7">
-        <v>0.151529</v>
+        <v>0.16491499999999998</v>
       </c>
       <c r="H17" s="7">
-        <v>0.140431</v>
+        <v>0.170262</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1141,14 +1141,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.034767</v>
+        <v>0.030689</v>
       </c>
       <c r="F18" s="7">
-        <v>0.101295</v>
+        <v>0.098089</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.18113900000000002</v>
+        <v>0.182875</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1168,19 +1168,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.071338</v>
+        <v>-0.032351</v>
       </c>
       <c r="F19" s="7">
-        <v>0.197044</v>
+        <v>0.191772</v>
       </c>
       <c r="G19" s="7">
-        <v>0.467391</v>
+        <v>0.48107900000000003</v>
       </c>
       <c r="H19" s="7">
-        <v>0.467391</v>
+        <v>0.48107900000000003</v>
       </c>
       <c r="I19" s="7">
-        <v>0.76087</v>
+        <v>0.820836</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1199,19 +1199,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.09443199999999999</v>
+        <v>-0.058004</v>
       </c>
       <c r="F20" s="7">
-        <v>0.042564000000000005</v>
+        <v>0.062323</v>
       </c>
       <c r="G20" s="7">
-        <v>0.23774699999999999</v>
+        <v>0.248487</v>
       </c>
       <c r="H20" s="7">
-        <v>0.233242</v>
+        <v>0.251137</v>
       </c>
       <c r="I20" s="7">
-        <v>0.421678</v>
+        <v>0.5154299999999999</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1230,19 +1230,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.079898</v>
+        <v>-0.044477</v>
       </c>
       <c r="F21" s="7">
-        <v>0.013666000000000001</v>
+        <v>0.034303</v>
       </c>
       <c r="G21" s="7">
-        <v>0.163016</v>
+        <v>0.17905300000000002</v>
       </c>
       <c r="H21" s="7">
-        <v>0.164896</v>
+        <v>0.190762</v>
       </c>
       <c r="I21" s="7">
-        <v>0.336867</v>
+        <v>0.428255</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1261,19 +1261,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.079944</v>
+        <v>-0.048029999999999996</v>
       </c>
       <c r="F22" s="7">
-        <v>0.041601</v>
+        <v>0.057508</v>
       </c>
       <c r="G22" s="7">
-        <v>0.142857</v>
+        <v>0.156534</v>
       </c>
       <c r="H22" s="7">
-        <v>0.149667</v>
+        <v>0.160182</v>
       </c>
       <c r="I22" s="7">
-        <v>0.416235</v>
+        <v>0.47767899999999996</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1292,25 +1292,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.103212</v>
+        <v>-0.061765</v>
       </c>
       <c r="F23" s="7">
-        <v>0.031067</v>
+        <v>0.064425</v>
       </c>
       <c r="G23" s="7">
-        <v>0.23107299999999997</v>
+        <v>0.25287</v>
       </c>
       <c r="H23" s="7">
-        <v>0.229205</v>
+        <v>0.258956</v>
       </c>
       <c r="I23" s="7">
-        <v>0.41722099999999995</v>
+        <v>0.5124</v>
       </c>
       <c r="J23" s="7">
-        <v>1.546541</v>
+        <v>1.742725</v>
       </c>
       <c r="K23" s="7">
-        <v>9.961018000000001</v>
+        <v>10.232394000000001</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1327,25 +1327,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.07696</v>
+        <v>0.010697000000000002</v>
       </c>
       <c r="F24" s="7">
-        <v>-0.050555</v>
+        <v>0.056422</v>
       </c>
       <c r="G24" s="7">
-        <v>0.013158000000000001</v>
+        <v>0.06417</v>
       </c>
       <c r="H24" s="7">
-        <v>-0.003623</v>
+        <v>0.051501</v>
       </c>
       <c r="I24" s="7">
-        <v>0.22183399999999998</v>
+        <v>0.34269700000000003</v>
       </c>
       <c r="J24" s="7">
-        <v>2.416755</v>
+        <v>2.6815879999999996</v>
       </c>
       <c r="K24" s="7">
-        <v>14.599675999999999</v>
+        <v>15.570146999999999</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1362,25 +1362,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.10351300000000001</v>
+        <v>-0.050453</v>
       </c>
       <c r="F25" s="7">
-        <v>0.048538</v>
+        <v>0.082356</v>
       </c>
       <c r="G25" s="7">
-        <v>0.280566</v>
+        <v>0.297958</v>
       </c>
       <c r="H25" s="7">
-        <v>0.285328</v>
+        <v>0.310683</v>
       </c>
       <c r="I25" s="7">
-        <v>0.446728</v>
+        <v>0.545237</v>
       </c>
       <c r="J25" s="7">
-        <v>1.279923</v>
+        <v>1.462525</v>
       </c>
       <c r="K25" s="7">
-        <v>8.963312</v>
+        <v>9.202632</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1397,22 +1397,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.08906700000000001</v>
+        <v>-0.054880000000000005</v>
       </c>
       <c r="F26" s="7">
-        <v>-0.021757</v>
+        <v>0.009209</v>
       </c>
       <c r="G26" s="7">
-        <v>0.08862500000000001</v>
+        <v>0.08996399999999999</v>
       </c>
       <c r="H26" s="7">
-        <v>0.08862500000000001</v>
+        <v>0.101416</v>
       </c>
       <c r="I26" s="7">
-        <v>0.272426</v>
+        <v>0.383406</v>
       </c>
       <c r="J26" s="7">
-        <v>1.007244</v>
+        <v>1.1193739999999999</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1430,25 +1430,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.106449</v>
+        <v>-0.075843</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.19468800000000003</v>
+        <v>-0.147668</v>
       </c>
       <c r="G27" s="7">
-        <v>0.00507</v>
+        <v>0.008816000000000001</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.077666</v>
+        <v>-0.057981</v>
       </c>
       <c r="I27" s="7">
-        <v>0.46854300000000004</v>
+        <v>0.454144</v>
       </c>
       <c r="J27" s="7">
-        <v>3.121881</v>
+        <v>3.199107</v>
       </c>
       <c r="K27" s="7">
-        <v>11.843900000000001</v>
+        <v>12.194305</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1465,25 +1465,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.055275</v>
+        <v>-0.025183</v>
       </c>
       <c r="F28" s="7">
-        <v>0.234375</v>
+        <v>0.254355</v>
       </c>
       <c r="G28" s="7">
-        <v>0.5063559999999999</v>
+        <v>0.536492</v>
       </c>
       <c r="H28" s="7">
-        <v>0.455178</v>
+        <v>0.473598</v>
       </c>
       <c r="I28" s="7">
-        <v>0.775724</v>
+        <v>0.875</v>
       </c>
       <c r="J28" s="7">
-        <v>1.8205330000000002</v>
+        <v>1.994012</v>
       </c>
       <c r="K28" s="7">
-        <v>7.98635</v>
+        <v>8.193054</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1500,25 +1500,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.077509</v>
+        <v>-0.040060000000000005</v>
       </c>
       <c r="F29" s="7">
-        <v>0.13830299999999998</v>
+        <v>0.159817</v>
       </c>
       <c r="G29" s="7">
-        <v>0.386313</v>
+        <v>0.42018500000000003</v>
       </c>
       <c r="H29" s="7">
-        <v>0.341351</v>
+        <v>0.372973</v>
       </c>
       <c r="I29" s="7">
-        <v>0.648837</v>
+        <v>0.751724</v>
       </c>
       <c r="J29" s="7">
-        <v>1.9152959999999999</v>
+        <v>2.132708</v>
       </c>
       <c r="K29" s="7">
-        <v>11.164216</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1535,25 +1535,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.09188299999999999</v>
+        <v>-0.071838</v>
       </c>
       <c r="F30" s="7">
-        <v>0.068302</v>
+        <v>0.069337</v>
       </c>
       <c r="G30" s="7">
-        <v>0.329208</v>
+        <v>0.326597</v>
       </c>
       <c r="H30" s="7">
-        <v>0.328477</v>
+        <v>0.335349</v>
       </c>
       <c r="I30" s="7">
-        <v>0.5183789999999999</v>
+        <v>0.592787</v>
       </c>
       <c r="J30" s="7">
-        <v>1.542079</v>
+        <v>1.657549</v>
       </c>
       <c r="K30" s="7">
-        <v>10.512625</v>
+        <v>10.62201</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1570,22 +1570,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.041699</v>
+        <v>-0.00317</v>
       </c>
       <c r="F31" s="7">
-        <v>0.24367799999999998</v>
+        <v>0.276639</v>
       </c>
       <c r="G31" s="7">
-        <v>0.478831</v>
+        <v>0.506587</v>
       </c>
       <c r="H31" s="7">
-        <v>0.505633</v>
+        <v>0.5405340000000001</v>
       </c>
       <c r="I31" s="7">
-        <v>0.558302</v>
+        <v>0.655263</v>
       </c>
       <c r="J31" s="7">
-        <v>2.443978</v>
+        <v>2.7</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1603,25 +1603,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.093726</v>
+        <v>-0.035985</v>
       </c>
       <c r="F32" s="7">
-        <v>0.07372</v>
+        <v>0.101051</v>
       </c>
       <c r="G32" s="7">
-        <v>0.349748</v>
+        <v>0.36670499999999995</v>
       </c>
       <c r="H32" s="7">
-        <v>0.350795</v>
+        <v>0.382615</v>
       </c>
       <c r="I32" s="7">
-        <v>0.48253799999999997</v>
+        <v>0.580745</v>
       </c>
       <c r="J32" s="7">
-        <v>1.109697</v>
+        <v>1.30287</v>
       </c>
       <c r="K32" s="7">
-        <v>8.223635</v>
+        <v>8.455945</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1638,22 +1638,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.093234</v>
+        <v>-0.056695</v>
       </c>
       <c r="F33" s="7">
-        <v>0.001303</v>
+        <v>0.024902</v>
       </c>
       <c r="G33" s="7">
-        <v>0.168568</v>
+        <v>0.177415</v>
       </c>
       <c r="H33" s="7">
-        <v>0.17005099999999998</v>
+        <v>0.190863</v>
       </c>
       <c r="I33" s="7">
-        <v>0.345985</v>
+        <v>0.451284</v>
       </c>
       <c r="J33" s="7">
-        <v>1.635792</v>
+        <v>1.7648789999999999</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1671,16 +1671,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.036312000000000004</v>
+        <v>0.031643</v>
       </c>
       <c r="F34" s="7">
-        <v>0.106272</v>
+        <v>0.102775</v>
       </c>
       <c r="G34" s="7">
-        <v>0.208373</v>
+        <v>0.20864999999999997</v>
       </c>
       <c r="H34" s="7">
-        <v>0.18304600000000001</v>
+        <v>0.184443</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1700,25 +1700,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.08959400000000001</v>
+        <v>-0.050363</v>
       </c>
       <c r="F35" s="7">
-        <v>0.028678</v>
+        <v>0.050244</v>
       </c>
       <c r="G35" s="7">
-        <v>0.188535</v>
+        <v>0.19699000000000003</v>
       </c>
       <c r="H35" s="7">
-        <v>0.19487</v>
+        <v>0.218521</v>
       </c>
       <c r="I35" s="7">
-        <v>0.384942</v>
+        <v>0.493061</v>
       </c>
       <c r="J35" s="7">
-        <v>1.772025</v>
+        <v>1.959547</v>
       </c>
       <c r="K35" s="7">
-        <v>8.876101</v>
+        <v>9.08269</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1735,16 +1735,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.035859999999999996</v>
+        <v>0.031617</v>
       </c>
       <c r="F36" s="7">
-        <v>0.10617900000000001</v>
+        <v>0.102686</v>
       </c>
       <c r="G36" s="7">
-        <v>0.208749</v>
+        <v>0.209026</v>
       </c>
       <c r="H36" s="7">
-        <v>0.183978</v>
+        <v>0.185375</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>15.06.2026 12:03:26</t>
+    <t>16.06.2026 10:57:15</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.007406</v>
+        <v>0.09544499999999999</v>
       </c>
       <c r="F6" s="7">
-        <v>0.035</v>
+        <v>0.09782600000000001</v>
       </c>
       <c r="G6" s="7">
-        <v>0.057999999999999996</v>
+        <v>0.10940200000000001</v>
       </c>
       <c r="H6" s="7">
-        <v>0.048678</v>
+        <v>0.11233499999999999</v>
       </c>
       <c r="I6" s="7">
-        <v>0.328033</v>
+        <v>0.408647</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.074416</v>
+        <v>-0.026521</v>
       </c>
       <c r="F7" s="7">
-        <v>0.060882</v>
+        <v>0.10117599999999999</v>
       </c>
       <c r="G7" s="7">
-        <v>0.318348</v>
+        <v>0.34482799999999997</v>
       </c>
       <c r="H7" s="7">
-        <v>0.329035</v>
+        <v>0.379514</v>
       </c>
       <c r="I7" s="7">
-        <v>0.5847979999999999</v>
+        <v>0.644991</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.061505000000000004</v>
+        <v>-0.011125000000000001</v>
       </c>
       <c r="F8" s="7">
-        <v>0.059181</v>
+        <v>0.106195</v>
       </c>
       <c r="G8" s="7">
-        <v>0.24918500000000002</v>
+        <v>0.28164</v>
       </c>
       <c r="H8" s="7">
-        <v>0.253272</v>
+        <v>0.308901</v>
       </c>
       <c r="I8" s="7">
-        <v>0.512638</v>
+        <v>0.5797789999999999</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.031107999999999997</v>
+        <v>0.029997</v>
       </c>
       <c r="F9" s="7">
-        <v>0.100746</v>
+        <v>0.101866</v>
       </c>
       <c r="G9" s="7">
-        <v>0.205065</v>
+        <v>0.20555199999999998</v>
       </c>
       <c r="H9" s="7">
-        <v>0.181418</v>
+        <v>0.182619</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.14464</v>
+        <v>-0.092864</v>
       </c>
       <c r="F10" s="7">
-        <v>0.108468</v>
+        <v>0.137012</v>
       </c>
       <c r="G10" s="7">
-        <v>0.141038</v>
+        <v>0.16965699999999997</v>
       </c>
       <c r="H10" s="7">
-        <v>0.209343</v>
+        <v>0.240484</v>
       </c>
       <c r="I10" s="7">
-        <v>0.492952</v>
+        <v>0.531397</v>
       </c>
       <c r="J10" s="7">
-        <v>0.823637</v>
+        <v>0.831418</v>
       </c>
       <c r="K10" s="7">
-        <v>6.652726</v>
+        <v>6.896476</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.082753</v>
+        <v>-0.026833999999999997</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.145985</v>
+        <v>-0.117599</v>
       </c>
       <c r="G11" s="7">
-        <v>0.041028</v>
+        <v>0.08745599999999999</v>
       </c>
       <c r="H11" s="7">
-        <v>-0.014045</v>
+        <v>0.018727</v>
       </c>
       <c r="I11" s="7">
-        <v>0.400638</v>
+        <v>0.44719299999999995</v>
       </c>
       <c r="J11" s="7">
-        <v>3.0798140000000003</v>
+        <v>3.202395</v>
       </c>
       <c r="K11" s="7">
-        <v>10.925255</v>
+        <v>11.150994</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.182927</v>
+        <v>-0.067972</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.151027</v>
+        <v>-0.103082</v>
       </c>
       <c r="G12" s="7">
-        <v>0.11969300000000001</v>
+        <v>0.190455</v>
       </c>
       <c r="H12" s="7">
-        <v>-0.035783999999999996</v>
+        <v>0.01867</v>
       </c>
       <c r="I12" s="7">
-        <v>1.1459489999999999</v>
+        <v>1.26714</v>
       </c>
       <c r="J12" s="7">
-        <v>4.31746</v>
+        <v>4.668831</v>
       </c>
       <c r="K12" s="7">
-        <v>11.778351</v>
+        <v>12.441797999999999</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.019779</v>
+        <v>0.016228</v>
       </c>
       <c r="F13" s="7">
-        <v>0.043865999999999995</v>
+        <v>0.041456</v>
       </c>
       <c r="G13" s="7">
-        <v>0.08928599999999999</v>
+        <v>0.085406</v>
       </c>
       <c r="H13" s="7">
-        <v>0.077899</v>
+        <v>0.075411</v>
       </c>
       <c r="I13" s="7">
-        <v>0.1677</v>
+        <v>0.16500399999999998</v>
       </c>
       <c r="J13" s="7">
-        <v>0.925745</v>
+        <v>0.9212980000000001</v>
       </c>
       <c r="K13" s="7">
-        <v>4.38213</v>
+        <v>4.303793</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.067989</v>
+        <v>0.005488</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.155327</v>
+        <v>-0.11810000000000001</v>
       </c>
       <c r="G14" s="7">
-        <v>0.028527</v>
+        <v>0.08831699999999999</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.065341</v>
+        <v>-0.024148</v>
       </c>
       <c r="I14" s="7">
-        <v>0.467767</v>
+        <v>0.532456</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,10 +1087,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.073041</v>
+        <v>-0.023852</v>
       </c>
       <c r="F16" s="7">
-        <v>-0.134712</v>
+        <v>-0.10371999999999999</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -1112,16 +1112,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.060773</v>
+        <v>0.0030299999999999997</v>
       </c>
       <c r="F17" s="7">
-        <v>0.017964</v>
+        <v>0.057086</v>
       </c>
       <c r="G17" s="7">
-        <v>0.16491499999999998</v>
+        <v>0.19118300000000002</v>
       </c>
       <c r="H17" s="7">
-        <v>0.170262</v>
+        <v>0.21523599999999998</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1141,14 +1141,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030689</v>
+        <v>0.029329</v>
       </c>
       <c r="F18" s="7">
-        <v>0.098089</v>
+        <v>0.09901</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.182875</v>
+        <v>0.183867</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1168,19 +1168,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.032351</v>
+        <v>0.002394</v>
       </c>
       <c r="F19" s="7">
-        <v>0.191772</v>
+        <v>0.22060300000000002</v>
       </c>
       <c r="G19" s="7">
-        <v>0.48107900000000003</v>
+        <v>0.497615</v>
       </c>
       <c r="H19" s="7">
-        <v>0.48107900000000003</v>
+        <v>0.516908</v>
       </c>
       <c r="I19" s="7">
-        <v>0.820836</v>
+        <v>0.864885</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1199,19 +1199,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.058004</v>
+        <v>0.001161</v>
       </c>
       <c r="F20" s="7">
-        <v>0.062323</v>
+        <v>0.110482</v>
       </c>
       <c r="G20" s="7">
-        <v>0.248487</v>
+        <v>0.28180700000000003</v>
       </c>
       <c r="H20" s="7">
-        <v>0.251137</v>
+        <v>0.30785599999999996</v>
       </c>
       <c r="I20" s="7">
-        <v>0.5154299999999999</v>
+        <v>0.584129</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1230,19 +1230,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.044477</v>
+        <v>-0.003352</v>
       </c>
       <c r="F21" s="7">
-        <v>0.034303</v>
+        <v>0.07362099999999999</v>
       </c>
       <c r="G21" s="7">
-        <v>0.17905300000000002</v>
+        <v>0.20269700000000002</v>
       </c>
       <c r="H21" s="7">
-        <v>0.190762</v>
+        <v>0.236028</v>
       </c>
       <c r="I21" s="7">
-        <v>0.428255</v>
+        <v>0.48254800000000003</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1261,19 +1261,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.048029999999999996</v>
+        <v>-0.011932</v>
       </c>
       <c r="F22" s="7">
-        <v>0.057508</v>
+        <v>0.084665</v>
       </c>
       <c r="G22" s="7">
-        <v>0.156534</v>
+        <v>0.177593</v>
       </c>
       <c r="H22" s="7">
-        <v>0.160182</v>
+        <v>0.18997499999999998</v>
       </c>
       <c r="I22" s="7">
-        <v>0.47767899999999996</v>
+        <v>0.515625</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1292,25 +1292,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.061765</v>
+        <v>-0.004161000000000001</v>
       </c>
       <c r="F23" s="7">
-        <v>0.064425</v>
+        <v>0.105749</v>
       </c>
       <c r="G23" s="7">
-        <v>0.25287</v>
+        <v>0.28138</v>
       </c>
       <c r="H23" s="7">
-        <v>0.258956</v>
+        <v>0.307832</v>
       </c>
       <c r="I23" s="7">
-        <v>0.5124</v>
+        <v>0.5711160000000001</v>
       </c>
       <c r="J23" s="7">
-        <v>1.742725</v>
+        <v>1.781508</v>
       </c>
       <c r="K23" s="7">
-        <v>10.232394000000001</v>
+        <v>10.732026000000001</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1327,25 +1327,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.010697000000000002</v>
+        <v>0.09386900000000001</v>
       </c>
       <c r="F24" s="7">
-        <v>0.056422</v>
+        <v>0.11804500000000001</v>
       </c>
       <c r="G24" s="7">
-        <v>0.06417</v>
+        <v>0.111686</v>
       </c>
       <c r="H24" s="7">
-        <v>0.051501</v>
+        <v>0.11283599999999999</v>
       </c>
       <c r="I24" s="7">
-        <v>0.34269700000000003</v>
+        <v>0.42101799999999995</v>
       </c>
       <c r="J24" s="7">
-        <v>2.6815879999999996</v>
+        <v>2.7339350000000002</v>
       </c>
       <c r="K24" s="7">
-        <v>15.570146999999999</v>
+        <v>16.408907</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1362,25 +1362,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.050453</v>
+        <v>0.016032</v>
       </c>
       <c r="F25" s="7">
-        <v>0.082356</v>
+        <v>0.132328</v>
       </c>
       <c r="G25" s="7">
-        <v>0.297958</v>
+        <v>0.340826</v>
       </c>
       <c r="H25" s="7">
-        <v>0.310683</v>
+        <v>0.371197</v>
       </c>
       <c r="I25" s="7">
-        <v>0.545237</v>
+        <v>0.61658</v>
       </c>
       <c r="J25" s="7">
-        <v>1.462525</v>
+        <v>1.518003</v>
       </c>
       <c r="K25" s="7">
-        <v>9.202632</v>
+        <v>9.718816</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1397,22 +1397,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.054880000000000005</v>
+        <v>-0.007649</v>
       </c>
       <c r="F26" s="7">
-        <v>0.009209</v>
+        <v>0.031812</v>
       </c>
       <c r="G26" s="7">
-        <v>0.08996399999999999</v>
+        <v>0.104886</v>
       </c>
       <c r="H26" s="7">
-        <v>0.101416</v>
+        <v>0.126085</v>
       </c>
       <c r="I26" s="7">
-        <v>0.383406</v>
+        <v>0.414391</v>
       </c>
       <c r="J26" s="7">
-        <v>1.1193739999999999</v>
+        <v>1.13753</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1430,25 +1430,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.075843</v>
+        <v>-0.010043</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.147668</v>
+        <v>-0.106218</v>
       </c>
       <c r="G27" s="7">
-        <v>0.008816000000000001</v>
+        <v>0.069767</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.057981</v>
+        <v>-0.012169000000000001</v>
       </c>
       <c r="I27" s="7">
-        <v>0.454144</v>
+        <v>0.5248619999999999</v>
       </c>
       <c r="J27" s="7">
-        <v>3.199107</v>
+        <v>3.431599</v>
       </c>
       <c r="K27" s="7">
-        <v>12.194305</v>
+        <v>12.641756</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1465,25 +1465,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.025183</v>
+        <v>0.009911999999999999</v>
       </c>
       <c r="F28" s="7">
-        <v>0.254355</v>
+        <v>0.278049</v>
       </c>
       <c r="G28" s="7">
-        <v>0.536492</v>
+        <v>0.5548960000000001</v>
       </c>
       <c r="H28" s="7">
-        <v>0.473598</v>
+        <v>0.501433</v>
       </c>
       <c r="I28" s="7">
-        <v>0.875</v>
+        <v>0.910417</v>
       </c>
       <c r="J28" s="7">
-        <v>1.994012</v>
+        <v>1.994775</v>
       </c>
       <c r="K28" s="7">
-        <v>8.193054</v>
+        <v>8.468250000000001</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1500,25 +1500,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.040060000000000005</v>
+        <v>-0.002302</v>
       </c>
       <c r="F29" s="7">
-        <v>0.159817</v>
+        <v>0.187215</v>
       </c>
       <c r="G29" s="7">
-        <v>0.42018500000000003</v>
+        <v>0.439646</v>
       </c>
       <c r="H29" s="7">
-        <v>0.372973</v>
+        <v>0.405405</v>
       </c>
       <c r="I29" s="7">
-        <v>0.751724</v>
+        <v>0.793103</v>
       </c>
       <c r="J29" s="7">
-        <v>2.132708</v>
+        <v>2.153044</v>
       </c>
       <c r="K29" s="7">
-        <v>11.5</v>
+        <v>11.961117</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1535,25 +1535,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.071838</v>
+        <v>-0.032357</v>
       </c>
       <c r="F30" s="7">
-        <v>0.069337</v>
+        <v>0.105877</v>
       </c>
       <c r="G30" s="7">
-        <v>0.326597</v>
+        <v>0.349812</v>
       </c>
       <c r="H30" s="7">
-        <v>0.335349</v>
+        <v>0.380979</v>
       </c>
       <c r="I30" s="7">
-        <v>0.592787</v>
+        <v>0.647213</v>
       </c>
       <c r="J30" s="7">
-        <v>1.657549</v>
+        <v>1.719792</v>
       </c>
       <c r="K30" s="7">
-        <v>10.62201</v>
+        <v>11.111861</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1570,22 +1570,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.00317</v>
+        <v>0.037728000000000005</v>
       </c>
       <c r="F31" s="7">
-        <v>0.276639</v>
+        <v>0.29795</v>
       </c>
       <c r="G31" s="7">
-        <v>0.506587</v>
+        <v>0.515762</v>
       </c>
       <c r="H31" s="7">
-        <v>0.5405340000000001</v>
+        <v>0.56625</v>
       </c>
       <c r="I31" s="7">
-        <v>0.655263</v>
+        <v>0.682895</v>
       </c>
       <c r="J31" s="7">
-        <v>2.7</v>
+        <v>2.7061720000000005</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1603,25 +1603,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.035985</v>
+        <v>0.010215</v>
       </c>
       <c r="F32" s="7">
-        <v>0.101051</v>
+        <v>0.130717</v>
       </c>
       <c r="G32" s="7">
-        <v>0.36670499999999995</v>
+        <v>0.37763599999999997</v>
       </c>
       <c r="H32" s="7">
-        <v>0.382615</v>
+        <v>0.419868</v>
       </c>
       <c r="I32" s="7">
-        <v>0.580745</v>
+        <v>0.623336</v>
       </c>
       <c r="J32" s="7">
-        <v>1.30287</v>
+        <v>1.257527</v>
       </c>
       <c r="K32" s="7">
-        <v>8.455945</v>
+        <v>8.788656999999999</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1638,22 +1638,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.056695</v>
+        <v>0.011885</v>
       </c>
       <c r="F33" s="7">
-        <v>0.024902</v>
+        <v>0.078637</v>
       </c>
       <c r="G33" s="7">
-        <v>0.177415</v>
+        <v>0.221068</v>
       </c>
       <c r="H33" s="7">
-        <v>0.190863</v>
+        <v>0.253299</v>
       </c>
       <c r="I33" s="7">
-        <v>0.451284</v>
+        <v>0.527374</v>
       </c>
       <c r="J33" s="7">
-        <v>1.7648789999999999</v>
+        <v>1.8233279999999998</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1671,16 +1671,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.031643</v>
+        <v>0.030364</v>
       </c>
       <c r="F34" s="7">
-        <v>0.102775</v>
+        <v>0.103643</v>
       </c>
       <c r="G34" s="7">
-        <v>0.20864999999999997</v>
+        <v>0.20845199999999997</v>
       </c>
       <c r="H34" s="7">
-        <v>0.184443</v>
+        <v>0.185375</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1700,25 +1700,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.050363</v>
+        <v>0.013764</v>
       </c>
       <c r="F35" s="7">
-        <v>0.050244</v>
+        <v>0.099627</v>
       </c>
       <c r="G35" s="7">
-        <v>0.19699000000000003</v>
+        <v>0.23508500000000002</v>
       </c>
       <c r="H35" s="7">
-        <v>0.218521</v>
+        <v>0.275816</v>
       </c>
       <c r="I35" s="7">
-        <v>0.493061</v>
+        <v>0.563265</v>
       </c>
       <c r="J35" s="7">
-        <v>1.959547</v>
+        <v>2.039683</v>
       </c>
       <c r="K35" s="7">
-        <v>9.08269</v>
+        <v>9.621186999999999</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1735,16 +1735,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.031617</v>
+        <v>0.030328</v>
       </c>
       <c r="F36" s="7">
-        <v>0.102686</v>
+        <v>0.103986</v>
       </c>
       <c r="G36" s="7">
-        <v>0.209026</v>
+        <v>0.209877</v>
       </c>
       <c r="H36" s="7">
-        <v>0.185375</v>
+        <v>0.186772</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>16.06.2026 10:57:15</t>
+    <t>17.06.2026 10:02:47</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.09544499999999999</v>
+        <v>0.090239</v>
       </c>
       <c r="F6" s="7">
-        <v>0.09782600000000001</v>
+        <v>0.11194699999999999</v>
       </c>
       <c r="G6" s="7">
-        <v>0.10940200000000001</v>
+        <v>0.113178</v>
       </c>
       <c r="H6" s="7">
-        <v>0.11233499999999999</v>
+        <v>0.107048</v>
       </c>
       <c r="I6" s="7">
-        <v>0.408647</v>
+        <v>0.374726</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.026521</v>
+        <v>-0.022881</v>
       </c>
       <c r="F7" s="7">
-        <v>0.10117599999999999</v>
+        <v>0.133635</v>
       </c>
       <c r="G7" s="7">
-        <v>0.34482799999999997</v>
+        <v>0.377061</v>
       </c>
       <c r="H7" s="7">
-        <v>0.379514</v>
+        <v>0.38467199999999996</v>
       </c>
       <c r="I7" s="7">
-        <v>0.644991</v>
+        <v>0.6439199999999999</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.011125000000000001</v>
+        <v>-0.010878</v>
       </c>
       <c r="F8" s="7">
-        <v>0.106195</v>
+        <v>0.11448499999999999</v>
       </c>
       <c r="G8" s="7">
-        <v>0.28164</v>
+        <v>0.297341</v>
       </c>
       <c r="H8" s="7">
-        <v>0.308901</v>
+        <v>0.309228</v>
       </c>
       <c r="I8" s="7">
-        <v>0.5797789999999999</v>
+        <v>0.557415</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.029997</v>
+        <v>0.031042999999999998</v>
       </c>
       <c r="F9" s="7">
-        <v>0.101866</v>
+        <v>0.102163</v>
       </c>
       <c r="G9" s="7">
-        <v>0.20555199999999998</v>
+        <v>0.205546</v>
       </c>
       <c r="H9" s="7">
-        <v>0.182619</v>
+        <v>0.183821</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.092864</v>
+        <v>-0.09008100000000001</v>
       </c>
       <c r="F10" s="7">
-        <v>0.137012</v>
+        <v>0.15404400000000001</v>
       </c>
       <c r="G10" s="7">
-        <v>0.16965699999999997</v>
+        <v>0.158132</v>
       </c>
       <c r="H10" s="7">
-        <v>0.240484</v>
+        <v>0.24429099999999998</v>
       </c>
       <c r="I10" s="7">
-        <v>0.531397</v>
+        <v>0.521151</v>
       </c>
       <c r="J10" s="7">
-        <v>0.831418</v>
+        <v>0.837976</v>
       </c>
       <c r="K10" s="7">
-        <v>6.896476</v>
+        <v>6.962799</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.026833999999999997</v>
+        <v>-0.033095</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.117599</v>
+        <v>-0.118989</v>
       </c>
       <c r="G11" s="7">
-        <v>0.08745599999999999</v>
+        <v>0.07135799999999999</v>
       </c>
       <c r="H11" s="7">
-        <v>0.018727</v>
+        <v>0.012172</v>
       </c>
       <c r="I11" s="7">
-        <v>0.44719299999999995</v>
+        <v>0.46081099999999997</v>
       </c>
       <c r="J11" s="7">
-        <v>3.202395</v>
+        <v>3.202955</v>
       </c>
       <c r="K11" s="7">
-        <v>11.150994</v>
+        <v>11.091723</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.067972</v>
+        <v>-0.082918</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.103082</v>
+        <v>-0.101151</v>
       </c>
       <c r="G12" s="7">
-        <v>0.190455</v>
+        <v>0.17886600000000002</v>
       </c>
       <c r="H12" s="7">
-        <v>0.01867</v>
+        <v>0.002334</v>
       </c>
       <c r="I12" s="7">
-        <v>1.26714</v>
+        <v>1.218492</v>
       </c>
       <c r="J12" s="7">
-        <v>4.668831</v>
+        <v>4.56828</v>
       </c>
       <c r="K12" s="7">
-        <v>12.441797999999999</v>
+        <v>12.147959</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.016228</v>
+        <v>0.015757</v>
       </c>
       <c r="F13" s="7">
-        <v>0.041456</v>
+        <v>0.042481</v>
       </c>
       <c r="G13" s="7">
-        <v>0.085406</v>
+        <v>0.083814</v>
       </c>
       <c r="H13" s="7">
-        <v>0.075411</v>
+        <v>0.074913</v>
       </c>
       <c r="I13" s="7">
-        <v>0.16500399999999998</v>
+        <v>0.167929</v>
       </c>
       <c r="J13" s="7">
-        <v>0.9212980000000001</v>
+        <v>0.946197</v>
       </c>
       <c r="K13" s="7">
-        <v>4.303793</v>
+        <v>4.296787</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>0.005488</v>
+        <v>-0.004391</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.11810000000000001</v>
+        <v>-0.127325</v>
       </c>
       <c r="G14" s="7">
-        <v>0.08831699999999999</v>
+        <v>0.084496</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.024148</v>
+        <v>-0.033736</v>
       </c>
       <c r="I14" s="7">
-        <v>0.532456</v>
+        <v>0.549897</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,10 +1087,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.023852</v>
+        <v>-0.029703</v>
       </c>
       <c r="F16" s="7">
-        <v>-0.10371999999999999</v>
+        <v>-0.09870699999999999</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -1112,16 +1112,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.0030299999999999997</v>
+        <v>-0.002273</v>
       </c>
       <c r="F17" s="7">
-        <v>0.057086</v>
+        <v>0.060385999999999995</v>
       </c>
       <c r="G17" s="7">
-        <v>0.19118300000000002</v>
+        <v>0.193475</v>
       </c>
       <c r="H17" s="7">
-        <v>0.21523599999999998</v>
+        <v>0.208811</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1141,14 +1141,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.029329</v>
+        <v>0.030623</v>
       </c>
       <c r="F18" s="7">
-        <v>0.09901</v>
+        <v>0.09937900000000001</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.183867</v>
+        <v>0.185355</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1168,19 +1168,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.002394</v>
+        <v>0</v>
       </c>
       <c r="F19" s="7">
-        <v>0.22060300000000002</v>
+        <v>0.214147</v>
       </c>
       <c r="G19" s="7">
-        <v>0.497615</v>
+        <v>0.50601</v>
       </c>
       <c r="H19" s="7">
-        <v>0.516908</v>
+        <v>0.513285</v>
       </c>
       <c r="I19" s="7">
-        <v>0.864885</v>
+        <v>0.865972</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1199,19 +1199,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.001161</v>
+        <v>0.003715</v>
       </c>
       <c r="F20" s="7">
-        <v>0.110482</v>
+        <v>0.11878899999999999</v>
       </c>
       <c r="G20" s="7">
-        <v>0.28180700000000003</v>
+        <v>0.298978</v>
       </c>
       <c r="H20" s="7">
-        <v>0.30785599999999996</v>
+        <v>0.31119199999999997</v>
       </c>
       <c r="I20" s="7">
-        <v>0.584129</v>
+        <v>0.5522440000000001</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1230,19 +1230,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.003352</v>
+        <v>-0.011546</v>
       </c>
       <c r="F21" s="7">
-        <v>0.07362099999999999</v>
+        <v>0.070593</v>
       </c>
       <c r="G21" s="7">
-        <v>0.20269700000000002</v>
+        <v>0.20966300000000002</v>
       </c>
       <c r="H21" s="7">
-        <v>0.236028</v>
+        <v>0.225866</v>
       </c>
       <c r="I21" s="7">
-        <v>0.48254800000000003</v>
+        <v>0.455443</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1261,19 +1261,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.011932</v>
+        <v>-0.005239000000000001</v>
       </c>
       <c r="F22" s="7">
-        <v>0.084665</v>
+        <v>0.095513</v>
       </c>
       <c r="G22" s="7">
-        <v>0.177593</v>
+        <v>0.203521</v>
       </c>
       <c r="H22" s="7">
-        <v>0.18997499999999998</v>
+        <v>0.198037</v>
       </c>
       <c r="I22" s="7">
-        <v>0.515625</v>
+        <v>0.49453400000000003</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1292,25 +1292,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.004161000000000001</v>
+        <v>0.000925</v>
       </c>
       <c r="F23" s="7">
-        <v>0.105749</v>
+        <v>0.118285</v>
       </c>
       <c r="G23" s="7">
-        <v>0.28138</v>
+        <v>0.305396</v>
       </c>
       <c r="H23" s="7">
-        <v>0.307832</v>
+        <v>0.314511</v>
       </c>
       <c r="I23" s="7">
-        <v>0.5711160000000001</v>
+        <v>0.566004</v>
       </c>
       <c r="J23" s="7">
-        <v>1.781508</v>
+        <v>1.7921070000000001</v>
       </c>
       <c r="K23" s="7">
-        <v>10.732026000000001</v>
+        <v>10.869518000000001</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1327,25 +1327,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.09386900000000001</v>
+        <v>0.08750999999999999</v>
       </c>
       <c r="F24" s="7">
-        <v>0.11804500000000001</v>
+        <v>0.11328099999999999</v>
       </c>
       <c r="G24" s="7">
-        <v>0.111686</v>
+        <v>0.113861</v>
       </c>
       <c r="H24" s="7">
-        <v>0.11283599999999999</v>
+        <v>0.106366</v>
       </c>
       <c r="I24" s="7">
-        <v>0.42101799999999995</v>
+        <v>0.38528799999999996</v>
       </c>
       <c r="J24" s="7">
-        <v>2.7339350000000002</v>
+        <v>2.746057</v>
       </c>
       <c r="K24" s="7">
-        <v>16.408907</v>
+        <v>16.563681</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1362,25 +1362,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.016032</v>
+        <v>0.023046</v>
       </c>
       <c r="F25" s="7">
-        <v>0.132328</v>
+        <v>0.142058</v>
       </c>
       <c r="G25" s="7">
-        <v>0.340826</v>
+        <v>0.36269599999999996</v>
       </c>
       <c r="H25" s="7">
-        <v>0.371197</v>
+        <v>0.380663</v>
       </c>
       <c r="I25" s="7">
-        <v>0.61658</v>
+        <v>0.6053459999999999</v>
       </c>
       <c r="J25" s="7">
-        <v>1.518003</v>
+        <v>1.4902440000000001</v>
       </c>
       <c r="K25" s="7">
-        <v>9.718816</v>
+        <v>9.902296</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1397,22 +1397,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.007649</v>
+        <v>-0.013688</v>
       </c>
       <c r="F26" s="7">
-        <v>0.031812</v>
+        <v>0.034628</v>
       </c>
       <c r="G26" s="7">
-        <v>0.104886</v>
+        <v>0.103107</v>
       </c>
       <c r="H26" s="7">
-        <v>0.126085</v>
+        <v>0.11923299999999999</v>
       </c>
       <c r="I26" s="7">
-        <v>0.414391</v>
+        <v>0.372395</v>
       </c>
       <c r="J26" s="7">
-        <v>1.13753</v>
+        <v>1.107708</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1430,25 +1430,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.010043</v>
+        <v>-0.014347</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.106218</v>
+        <v>-0.107792</v>
       </c>
       <c r="G27" s="7">
-        <v>0.069767</v>
+        <v>0.068429</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.012169000000000001</v>
+        <v>-0.016464</v>
       </c>
       <c r="I27" s="7">
-        <v>0.5248619999999999</v>
+        <v>0.549741</v>
       </c>
       <c r="J27" s="7">
-        <v>3.431599</v>
+        <v>3.405258</v>
       </c>
       <c r="K27" s="7">
-        <v>12.641756</v>
+        <v>12.603959999999999</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1465,25 +1465,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.009911999999999999</v>
+        <v>0.013216</v>
       </c>
       <c r="F28" s="7">
-        <v>0.278049</v>
+        <v>0.234899</v>
       </c>
       <c r="G28" s="7">
-        <v>0.5548960000000001</v>
+        <v>0.5619689999999999</v>
       </c>
       <c r="H28" s="7">
-        <v>0.501433</v>
+        <v>0.506345</v>
       </c>
       <c r="I28" s="7">
-        <v>0.910417</v>
+        <v>0.916667</v>
       </c>
       <c r="J28" s="7">
-        <v>1.994775</v>
+        <v>2.000652</v>
       </c>
       <c r="K28" s="7">
-        <v>8.468250000000001</v>
+        <v>8.618400000000001</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1500,25 +1500,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.002302</v>
+        <v>-0.004221</v>
       </c>
       <c r="F29" s="7">
-        <v>0.187215</v>
+        <v>0.153333</v>
       </c>
       <c r="G29" s="7">
-        <v>0.439646</v>
+        <v>0.449721</v>
       </c>
       <c r="H29" s="7">
-        <v>0.405405</v>
+        <v>0.402703</v>
       </c>
       <c r="I29" s="7">
-        <v>0.793103</v>
+        <v>0.765306</v>
       </c>
       <c r="J29" s="7">
-        <v>2.153044</v>
+        <v>2.095181</v>
       </c>
       <c r="K29" s="7">
-        <v>11.961117</v>
+        <v>12.046757</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1535,25 +1535,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.032357</v>
+        <v>-0.029276</v>
       </c>
       <c r="F30" s="7">
-        <v>0.105877</v>
+        <v>0.120747</v>
       </c>
       <c r="G30" s="7">
-        <v>0.349812</v>
+        <v>0.37742600000000004</v>
       </c>
       <c r="H30" s="7">
-        <v>0.380979</v>
+        <v>0.385377</v>
       </c>
       <c r="I30" s="7">
-        <v>0.647213</v>
+        <v>0.6433</v>
       </c>
       <c r="J30" s="7">
-        <v>1.719792</v>
+        <v>1.71962</v>
       </c>
       <c r="K30" s="7">
-        <v>11.111861</v>
+        <v>11.209302000000001</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1570,22 +1570,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.037728000000000005</v>
+        <v>0.048276000000000006</v>
       </c>
       <c r="F31" s="7">
-        <v>0.29795</v>
+        <v>0.324585</v>
       </c>
       <c r="G31" s="7">
-        <v>0.515762</v>
+        <v>0.555128</v>
       </c>
       <c r="H31" s="7">
-        <v>0.56625</v>
+        <v>0.58217</v>
       </c>
       <c r="I31" s="7">
-        <v>0.682895</v>
+        <v>0.676181</v>
       </c>
       <c r="J31" s="7">
-        <v>2.7061720000000005</v>
+        <v>2.676722</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1603,25 +1603,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.010215</v>
+        <v>0.019326</v>
       </c>
       <c r="F32" s="7">
-        <v>0.130717</v>
+        <v>0.143742</v>
       </c>
       <c r="G32" s="7">
-        <v>0.37763599999999997</v>
+        <v>0.40808500000000003</v>
       </c>
       <c r="H32" s="7">
-        <v>0.419868</v>
+        <v>0.432674</v>
       </c>
       <c r="I32" s="7">
-        <v>0.623336</v>
+        <v>0.61717</v>
       </c>
       <c r="J32" s="7">
-        <v>1.257527</v>
+        <v>1.3069229999999998</v>
       </c>
       <c r="K32" s="7">
-        <v>8.788656999999999</v>
+        <v>8.908749</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1638,22 +1638,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.011885</v>
+        <v>0.01332</v>
       </c>
       <c r="F33" s="7">
-        <v>0.078637</v>
+        <v>0.085859</v>
       </c>
       <c r="G33" s="7">
-        <v>0.221068</v>
+        <v>0.239038</v>
       </c>
       <c r="H33" s="7">
-        <v>0.253299</v>
+        <v>0.255076</v>
       </c>
       <c r="I33" s="7">
-        <v>0.527374</v>
+        <v>0.497577</v>
       </c>
       <c r="J33" s="7">
-        <v>1.8233279999999998</v>
+        <v>1.837063</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1671,16 +1671,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.030364</v>
+        <v>0.031984</v>
       </c>
       <c r="F34" s="7">
-        <v>0.103643</v>
+        <v>0.103941</v>
       </c>
       <c r="G34" s="7">
-        <v>0.20845199999999997</v>
+        <v>0.209203</v>
       </c>
       <c r="H34" s="7">
-        <v>0.185375</v>
+        <v>0.18723800000000002</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1700,25 +1700,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.013764</v>
+        <v>0.005823</v>
       </c>
       <c r="F35" s="7">
-        <v>0.099627</v>
+        <v>0.094155</v>
       </c>
       <c r="G35" s="7">
-        <v>0.23508500000000002</v>
+        <v>0.2394</v>
       </c>
       <c r="H35" s="7">
-        <v>0.275816</v>
+        <v>0.265823</v>
       </c>
       <c r="I35" s="7">
-        <v>0.563265</v>
+        <v>0.515152</v>
       </c>
       <c r="J35" s="7">
-        <v>2.039683</v>
+        <v>1.95858</v>
       </c>
       <c r="K35" s="7">
-        <v>9.621186999999999</v>
+        <v>9.555556000000001</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1735,16 +1735,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.030328</v>
+        <v>0.030732</v>
       </c>
       <c r="F36" s="7">
-        <v>0.103986</v>
+        <v>0.103463</v>
       </c>
       <c r="G36" s="7">
-        <v>0.209877</v>
+        <v>0.20862999999999998</v>
       </c>
       <c r="H36" s="7">
-        <v>0.186772</v>
+        <v>0.18723800000000002</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>17.06.2026 10:02:47</t>
+    <t>18.06.2026 10:29:51</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.090239</v>
+        <v>0.096746</v>
       </c>
       <c r="F6" s="7">
-        <v>0.11194699999999999</v>
+        <v>0.08195999999999999</v>
       </c>
       <c r="G6" s="7">
-        <v>0.113178</v>
+        <v>0.116854</v>
       </c>
       <c r="H6" s="7">
-        <v>0.107048</v>
+        <v>0.11365600000000001</v>
       </c>
       <c r="I6" s="7">
-        <v>0.374726</v>
+        <v>0.408357</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.022881</v>
+        <v>-0.028601</v>
       </c>
       <c r="F7" s="7">
-        <v>0.133635</v>
+        <v>0.09048500000000001</v>
       </c>
       <c r="G7" s="7">
-        <v>0.377061</v>
+        <v>0.375552</v>
       </c>
       <c r="H7" s="7">
-        <v>0.38467199999999996</v>
+        <v>0.37656599999999996</v>
       </c>
       <c r="I7" s="7">
-        <v>0.6439199999999999</v>
+        <v>0.61243</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.010878</v>
+        <v>-0.014833</v>
       </c>
       <c r="F8" s="7">
-        <v>0.11448499999999999</v>
+        <v>0.084354</v>
       </c>
       <c r="G8" s="7">
-        <v>0.297341</v>
+        <v>0.29804600000000003</v>
       </c>
       <c r="H8" s="7">
-        <v>0.309228</v>
+        <v>0.303992</v>
       </c>
       <c r="I8" s="7">
-        <v>0.557415</v>
+        <v>0.548776</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,16 +868,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.031042999999999998</v>
+        <v>0.032089</v>
       </c>
       <c r="F9" s="7">
-        <v>0.102163</v>
+        <v>0.097145</v>
       </c>
       <c r="G9" s="7">
-        <v>0.205546</v>
+        <v>0.20554099999999997</v>
       </c>
       <c r="H9" s="7">
-        <v>0.183821</v>
+        <v>0.185022</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -897,25 +897,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.09008100000000001</v>
+        <v>-0.106528</v>
       </c>
       <c r="F10" s="7">
-        <v>0.15404400000000001</v>
+        <v>0.126675</v>
       </c>
       <c r="G10" s="7">
-        <v>0.158132</v>
+        <v>0.159225</v>
       </c>
       <c r="H10" s="7">
-        <v>0.24429099999999998</v>
+        <v>0.221799</v>
       </c>
       <c r="I10" s="7">
-        <v>0.521151</v>
+        <v>0.491447</v>
       </c>
       <c r="J10" s="7">
-        <v>0.837976</v>
+        <v>0.804753</v>
       </c>
       <c r="K10" s="7">
-        <v>6.962799</v>
+        <v>6.901096</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +932,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.033095</v>
+        <v>-0.022809</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.118989</v>
+        <v>-0.111789</v>
       </c>
       <c r="G11" s="7">
-        <v>0.07135799999999999</v>
+        <v>0.076355</v>
       </c>
       <c r="H11" s="7">
-        <v>0.012172</v>
+        <v>0.022940000000000002</v>
       </c>
       <c r="I11" s="7">
-        <v>0.46081099999999997</v>
+        <v>0.483166</v>
       </c>
       <c r="J11" s="7">
-        <v>3.202955</v>
+        <v>3.2476670000000003</v>
       </c>
       <c r="K11" s="7">
-        <v>11.091723</v>
+        <v>11.505723</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +967,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.082918</v>
+        <v>-0.08363</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.101151</v>
+        <v>-0.102162</v>
       </c>
       <c r="G12" s="7">
-        <v>0.17886600000000002</v>
+        <v>0.140895</v>
       </c>
       <c r="H12" s="7">
-        <v>0.002334</v>
+        <v>0.0015559999999999999</v>
       </c>
       <c r="I12" s="7">
-        <v>1.218492</v>
+        <v>1.171896</v>
       </c>
       <c r="J12" s="7">
-        <v>4.56828</v>
+        <v>4.563959</v>
       </c>
       <c r="K12" s="7">
-        <v>12.147959</v>
+        <v>12.561197</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1002,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.015757</v>
+        <v>0.01317</v>
       </c>
       <c r="F13" s="7">
-        <v>0.042481</v>
+        <v>0.039826</v>
       </c>
       <c r="G13" s="7">
-        <v>0.083814</v>
+        <v>0.081054</v>
       </c>
       <c r="H13" s="7">
-        <v>0.074913</v>
+        <v>0.072175</v>
       </c>
       <c r="I13" s="7">
-        <v>0.167929</v>
+        <v>0.162753</v>
       </c>
       <c r="J13" s="7">
-        <v>0.946197</v>
+        <v>0.94124</v>
       </c>
       <c r="K13" s="7">
-        <v>4.296787</v>
+        <v>4.2022699999999995</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.004391</v>
+        <v>-0.004757</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.127325</v>
+        <v>-0.12258100000000001</v>
       </c>
       <c r="G14" s="7">
-        <v>0.084496</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.033736</v>
+        <v>-0.034091</v>
       </c>
       <c r="I14" s="7">
-        <v>0.549897</v>
+        <v>0.551449</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,10 +1087,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.029703</v>
+        <v>-0.032403</v>
       </c>
       <c r="F16" s="7">
-        <v>-0.09870699999999999</v>
+        <v>-0.101623</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -1112,16 +1112,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.002273</v>
+        <v>-0.004545</v>
       </c>
       <c r="F17" s="7">
-        <v>0.060385999999999995</v>
+        <v>0.040792</v>
       </c>
       <c r="G17" s="7">
-        <v>0.193475</v>
+        <v>0.194545</v>
       </c>
       <c r="H17" s="7">
-        <v>0.208811</v>
+        <v>0.206058</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1141,14 +1141,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.030623</v>
+        <v>0.031702</v>
       </c>
       <c r="F18" s="7">
-        <v>0.09937900000000001</v>
+        <v>0.09448600000000001</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.185355</v>
+        <v>0.186595</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1168,19 +1168,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0</v>
+        <v>-0.001862</v>
       </c>
       <c r="F19" s="7">
-        <v>0.214147</v>
+        <v>0.191111</v>
       </c>
       <c r="G19" s="7">
-        <v>0.50601</v>
+        <v>0.515041</v>
       </c>
       <c r="H19" s="7">
-        <v>0.513285</v>
+        <v>0.510467</v>
       </c>
       <c r="I19" s="7">
-        <v>0.865972</v>
+        <v>0.845548</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1199,19 +1199,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.003715</v>
+        <v>-0.003947</v>
       </c>
       <c r="F20" s="7">
-        <v>0.11878899999999999</v>
+        <v>0.091881</v>
       </c>
       <c r="G20" s="7">
-        <v>0.298978</v>
+        <v>0.296073</v>
       </c>
       <c r="H20" s="7">
-        <v>0.31119199999999997</v>
+        <v>0.30118300000000003</v>
       </c>
       <c r="I20" s="7">
-        <v>0.5522440000000001</v>
+        <v>0.549855</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1230,19 +1230,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.011546</v>
+        <v>-0.018994</v>
       </c>
       <c r="F21" s="7">
-        <v>0.070593</v>
+        <v>0.047316000000000004</v>
       </c>
       <c r="G21" s="7">
-        <v>0.20966300000000002</v>
+        <v>0.202465</v>
       </c>
       <c r="H21" s="7">
-        <v>0.225866</v>
+        <v>0.21662800000000001</v>
       </c>
       <c r="I21" s="7">
-        <v>0.455443</v>
+        <v>0.448048</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1261,19 +1261,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.005239000000000001</v>
+        <v>-0.011059000000000001</v>
       </c>
       <c r="F22" s="7">
-        <v>0.095513</v>
+        <v>0.057579000000000005</v>
       </c>
       <c r="G22" s="7">
-        <v>0.203521</v>
+        <v>0.191863</v>
       </c>
       <c r="H22" s="7">
-        <v>0.198037</v>
+        <v>0.19102699999999997</v>
       </c>
       <c r="I22" s="7">
-        <v>0.49453400000000003</v>
+        <v>0.481901</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1292,25 +1292,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.000925</v>
+        <v>-0.006704</v>
       </c>
       <c r="F23" s="7">
-        <v>0.118285</v>
+        <v>0.085101</v>
       </c>
       <c r="G23" s="7">
-        <v>0.305396</v>
+        <v>0.30133299999999996</v>
       </c>
       <c r="H23" s="7">
-        <v>0.314511</v>
+        <v>0.304493</v>
       </c>
       <c r="I23" s="7">
-        <v>0.566004</v>
+        <v>0.5535070000000001</v>
       </c>
       <c r="J23" s="7">
-        <v>1.7921070000000001</v>
+        <v>1.7708279999999998</v>
       </c>
       <c r="K23" s="7">
-        <v>10.869518000000001</v>
+        <v>10.903046999999999</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1327,25 +1327,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.08750999999999999</v>
+        <v>0.09361499999999999</v>
       </c>
       <c r="F24" s="7">
-        <v>0.11328099999999999</v>
+        <v>0.08560600000000002</v>
       </c>
       <c r="G24" s="7">
-        <v>0.113861</v>
+        <v>0.121576</v>
       </c>
       <c r="H24" s="7">
-        <v>0.106366</v>
+        <v>0.112578</v>
       </c>
       <c r="I24" s="7">
-        <v>0.38528799999999996</v>
+        <v>0.41647399999999996</v>
       </c>
       <c r="J24" s="7">
-        <v>2.746057</v>
+        <v>2.767087</v>
       </c>
       <c r="K24" s="7">
-        <v>16.563681</v>
+        <v>17.093434</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1362,25 +1362,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.023046</v>
+        <v>0.011273</v>
       </c>
       <c r="F25" s="7">
-        <v>0.142058</v>
+        <v>0.104817</v>
       </c>
       <c r="G25" s="7">
-        <v>0.36269599999999996</v>
+        <v>0.346564</v>
       </c>
       <c r="H25" s="7">
-        <v>0.380663</v>
+        <v>0.364773</v>
       </c>
       <c r="I25" s="7">
-        <v>0.6053459999999999</v>
+        <v>0.598812</v>
       </c>
       <c r="J25" s="7">
-        <v>1.4902440000000001</v>
+        <v>1.4615850000000001</v>
       </c>
       <c r="K25" s="7">
-        <v>9.902296</v>
+        <v>9.904916</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1397,22 +1397,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.013688</v>
+        <v>-0.022543999999999998</v>
       </c>
       <c r="F26" s="7">
-        <v>0.034628</v>
+        <v>0.002477</v>
       </c>
       <c r="G26" s="7">
-        <v>0.103107</v>
+        <v>0.09468</v>
       </c>
       <c r="H26" s="7">
-        <v>0.11923299999999999</v>
+        <v>0.109182</v>
       </c>
       <c r="I26" s="7">
-        <v>0.372395</v>
+        <v>0.36989400000000006</v>
       </c>
       <c r="J26" s="7">
-        <v>1.107708</v>
+        <v>1.0887820000000001</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1430,25 +1430,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.014347</v>
+        <v>-0.017575</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.107792</v>
+        <v>-0.111868</v>
       </c>
       <c r="G27" s="7">
-        <v>0.068429</v>
+        <v>0.06825300000000001</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.016464</v>
+        <v>-0.019684999999999998</v>
       </c>
       <c r="I27" s="7">
-        <v>0.549741</v>
+        <v>0.548157</v>
       </c>
       <c r="J27" s="7">
-        <v>3.405258</v>
+        <v>3.3908300000000002</v>
       </c>
       <c r="K27" s="7">
-        <v>12.603959999999999</v>
+        <v>12.864142999999999</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1468,22 +1468,22 @@
         <v>0.013216</v>
       </c>
       <c r="F28" s="7">
-        <v>0.234899</v>
+        <v>0.21452100000000002</v>
       </c>
       <c r="G28" s="7">
-        <v>0.5619689999999999</v>
+        <v>0.5606450000000001</v>
       </c>
       <c r="H28" s="7">
         <v>0.506345</v>
       </c>
       <c r="I28" s="7">
-        <v>0.916667</v>
+        <v>0.9051560000000001</v>
       </c>
       <c r="J28" s="7">
         <v>2.000652</v>
       </c>
       <c r="K28" s="7">
-        <v>8.618400000000001</v>
+        <v>8.740603</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1500,25 +1500,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.004221</v>
+        <v>-0.009977</v>
       </c>
       <c r="F29" s="7">
-        <v>0.153333</v>
+        <v>0.151786</v>
       </c>
       <c r="G29" s="7">
-        <v>0.449721</v>
+        <v>0.441341</v>
       </c>
       <c r="H29" s="7">
-        <v>0.402703</v>
+        <v>0.394595</v>
       </c>
       <c r="I29" s="7">
-        <v>0.765306</v>
+        <v>0.743243</v>
       </c>
       <c r="J29" s="7">
-        <v>2.095181</v>
+        <v>2.07729</v>
       </c>
       <c r="K29" s="7">
-        <v>12.046757</v>
+        <v>12.129771</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1535,25 +1535,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.029276</v>
+        <v>-0.032743</v>
       </c>
       <c r="F30" s="7">
-        <v>0.120747</v>
+        <v>0.093879</v>
       </c>
       <c r="G30" s="7">
-        <v>0.37742600000000004</v>
+        <v>0.384997</v>
       </c>
       <c r="H30" s="7">
-        <v>0.385377</v>
+        <v>0.380429</v>
       </c>
       <c r="I30" s="7">
-        <v>0.6433</v>
+        <v>0.623142</v>
       </c>
       <c r="J30" s="7">
-        <v>1.71962</v>
+        <v>1.709907</v>
       </c>
       <c r="K30" s="7">
-        <v>11.209302000000001</v>
+        <v>11.242808</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1570,22 +1570,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.048276000000000006</v>
+        <v>0.051521</v>
       </c>
       <c r="F31" s="7">
-        <v>0.324585</v>
+        <v>0.299378</v>
       </c>
       <c r="G31" s="7">
-        <v>0.555128</v>
+        <v>0.578178</v>
       </c>
       <c r="H31" s="7">
-        <v>0.58217</v>
+        <v>0.587068</v>
       </c>
       <c r="I31" s="7">
-        <v>0.676181</v>
+        <v>0.6640989999999999</v>
       </c>
       <c r="J31" s="7">
-        <v>2.676722</v>
+        <v>2.6881049999999997</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1603,25 +1603,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.019326</v>
+        <v>0.008007</v>
       </c>
       <c r="F32" s="7">
-        <v>0.143742</v>
+        <v>0.106364</v>
       </c>
       <c r="G32" s="7">
-        <v>0.40808500000000003</v>
+        <v>0.398851</v>
       </c>
       <c r="H32" s="7">
-        <v>0.432674</v>
+        <v>0.416764</v>
       </c>
       <c r="I32" s="7">
-        <v>0.61717</v>
+        <v>0.6083700000000001</v>
       </c>
       <c r="J32" s="7">
-        <v>1.3069229999999998</v>
+        <v>1.2813050000000001</v>
       </c>
       <c r="K32" s="7">
-        <v>8.908749</v>
+        <v>8.872904</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1638,22 +1638,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.01332</v>
+        <v>0.005328</v>
       </c>
       <c r="F33" s="7">
-        <v>0.085859</v>
+        <v>0.055054</v>
       </c>
       <c r="G33" s="7">
-        <v>0.239038</v>
+        <v>0.234524</v>
       </c>
       <c r="H33" s="7">
-        <v>0.255076</v>
+        <v>0.245178</v>
       </c>
       <c r="I33" s="7">
-        <v>0.497577</v>
+        <v>0.498015</v>
       </c>
       <c r="J33" s="7">
-        <v>1.837063</v>
+        <v>1.8146870000000002</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1671,16 +1671,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.031984</v>
+        <v>0.032794</v>
       </c>
       <c r="F34" s="7">
-        <v>0.103941</v>
+        <v>0.09909499999999999</v>
       </c>
       <c r="G34" s="7">
-        <v>0.209203</v>
+        <v>0.209005</v>
       </c>
       <c r="H34" s="7">
-        <v>0.18723800000000002</v>
+        <v>0.18817</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1700,25 +1700,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.005823</v>
+        <v>-0.003441</v>
       </c>
       <c r="F35" s="7">
-        <v>0.094155</v>
+        <v>0.069602</v>
       </c>
       <c r="G35" s="7">
-        <v>0.2394</v>
+        <v>0.232809</v>
       </c>
       <c r="H35" s="7">
-        <v>0.265823</v>
+        <v>0.254164</v>
       </c>
       <c r="I35" s="7">
-        <v>0.515152</v>
+        <v>0.5029939999999999</v>
       </c>
       <c r="J35" s="7">
-        <v>1.95858</v>
+        <v>1.93133</v>
       </c>
       <c r="K35" s="7">
-        <v>9.555556000000001</v>
+        <v>9.587739000000001</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1735,16 +1735,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.030732</v>
+        <v>0.032349</v>
       </c>
       <c r="F36" s="7">
-        <v>0.103463</v>
+        <v>0.09901</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20862999999999998</v>
+        <v>0.20937899999999998</v>
       </c>
       <c r="H36" s="7">
-        <v>0.18723800000000002</v>
+        <v>0.189101</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>18.06.2026 10:29:51</t>
+    <t>19.06.2026 10:07:19</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.096746</v>
+        <v>0.146533</v>
       </c>
       <c r="F6" s="7">
-        <v>0.08195999999999999</v>
+        <v>0.14180199999999998</v>
       </c>
       <c r="G6" s="7">
-        <v>0.116854</v>
+        <v>0.146533</v>
       </c>
       <c r="H6" s="7">
-        <v>0.11365600000000001</v>
+        <v>0.15814999999999999</v>
       </c>
       <c r="I6" s="7">
-        <v>0.408357</v>
+        <v>0.468715</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.028601</v>
+        <v>0.009524</v>
       </c>
       <c r="F7" s="7">
-        <v>0.09048500000000001</v>
+        <v>0.119062</v>
       </c>
       <c r="G7" s="7">
-        <v>0.375552</v>
+        <v>0.40448999999999996</v>
       </c>
       <c r="H7" s="7">
-        <v>0.37656599999999996</v>
+        <v>0.40604300000000004</v>
       </c>
       <c r="I7" s="7">
-        <v>0.61243</v>
+        <v>0.681057</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.014833</v>
+        <v>0.033937</v>
       </c>
       <c r="F8" s="7">
-        <v>0.084354</v>
+        <v>0.116253</v>
       </c>
       <c r="G8" s="7">
-        <v>0.29804600000000003</v>
+        <v>0.318581</v>
       </c>
       <c r="H8" s="7">
-        <v>0.303992</v>
+        <v>0.325916</v>
       </c>
       <c r="I8" s="7">
-        <v>0.548776</v>
+        <v>0.607299</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,18 +868,20 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.032089</v>
+        <v>0.034495</v>
       </c>
       <c r="F9" s="7">
-        <v>0.097145</v>
+        <v>0.09963</v>
       </c>
       <c r="G9" s="7">
-        <v>0.20554099999999997</v>
+        <v>0.20593</v>
       </c>
       <c r="H9" s="7">
-        <v>0.185022</v>
-      </c>
-      <c r="I9" s="7"/>
+        <v>0.189027</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0.482511</v>
+      </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
     </row>
@@ -897,25 +899,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.106528</v>
+        <v>-0.056375</v>
       </c>
       <c r="F10" s="7">
-        <v>0.126675</v>
+        <v>0.133186</v>
       </c>
       <c r="G10" s="7">
-        <v>0.159225</v>
+        <v>0.182569</v>
       </c>
       <c r="H10" s="7">
-        <v>0.221799</v>
+        <v>0.23944600000000002</v>
       </c>
       <c r="I10" s="7">
-        <v>0.491447</v>
+        <v>0.540314</v>
       </c>
       <c r="J10" s="7">
-        <v>0.804753</v>
+        <v>0.8308199999999999</v>
       </c>
       <c r="K10" s="7">
-        <v>6.901096</v>
+        <v>7.161312000000001</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -932,25 +934,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.022809</v>
+        <v>-0.041237</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.111789</v>
+        <v>-0.11391899999999999</v>
       </c>
       <c r="G11" s="7">
-        <v>0.076355</v>
+        <v>0.048529</v>
       </c>
       <c r="H11" s="7">
-        <v>0.022940000000000002</v>
+        <v>0.0014039999999999999</v>
       </c>
       <c r="I11" s="7">
-        <v>0.483166</v>
+        <v>0.45115299999999997</v>
       </c>
       <c r="J11" s="7">
-        <v>3.2476670000000003</v>
+        <v>3.158243</v>
       </c>
       <c r="K11" s="7">
-        <v>11.505723</v>
+        <v>11.220064</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,25 +969,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.08363</v>
+        <v>-0.13229</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.102162</v>
+        <v>-0.126387</v>
       </c>
       <c r="G12" s="7">
-        <v>0.140895</v>
+        <v>0.077263</v>
       </c>
       <c r="H12" s="7">
-        <v>0.0015559999999999999</v>
+        <v>-0.050953</v>
       </c>
       <c r="I12" s="7">
-        <v>1.171896</v>
+        <v>1.072011</v>
       </c>
       <c r="J12" s="7">
-        <v>4.563959</v>
+        <v>4.272256</v>
       </c>
       <c r="K12" s="7">
-        <v>12.561197</v>
+        <v>11.842104999999998</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1002,25 +1004,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.01317</v>
+        <v>0.014554000000000001</v>
       </c>
       <c r="F13" s="7">
-        <v>0.039826</v>
+        <v>0.042199</v>
       </c>
       <c r="G13" s="7">
-        <v>0.081054</v>
+        <v>0.082665</v>
       </c>
       <c r="H13" s="7">
-        <v>0.072175</v>
+        <v>0.07566</v>
       </c>
       <c r="I13" s="7">
-        <v>0.162753</v>
+        <v>0.169689</v>
       </c>
       <c r="J13" s="7">
-        <v>0.94124</v>
+        <v>0.9475490000000001</v>
       </c>
       <c r="K13" s="7">
-        <v>4.2022699999999995</v>
+        <v>4.189098</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1037,19 +1039,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.004757</v>
+        <v>-0.01909</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.12258100000000001</v>
+        <v>-0.140283</v>
       </c>
       <c r="G14" s="7">
-        <v>0.08800000000000001</v>
+        <v>0.058636999999999995</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.034091</v>
+        <v>-0.051136</v>
       </c>
       <c r="I14" s="7">
-        <v>0.551449</v>
+        <v>0.524418</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1087,10 +1089,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.032403</v>
+        <v>-0.050564</v>
       </c>
       <c r="F16" s="7">
-        <v>-0.101623</v>
+        <v>-0.12208500000000001</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -1112,16 +1114,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.004545</v>
+        <v>0.033682</v>
       </c>
       <c r="F17" s="7">
-        <v>0.040792</v>
+        <v>0.074879</v>
       </c>
       <c r="G17" s="7">
-        <v>0.194545</v>
+        <v>0.208145</v>
       </c>
       <c r="H17" s="7">
-        <v>0.206058</v>
+        <v>0.225333</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1141,14 +1143,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.031702</v>
+        <v>0.033822</v>
       </c>
       <c r="F18" s="7">
-        <v>0.09448600000000001</v>
+        <v>0.096914</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.186595</v>
+        <v>0.190316</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1168,19 +1170,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.001862</v>
+        <v>0.038095</v>
       </c>
       <c r="F19" s="7">
-        <v>0.191111</v>
+        <v>0.219239</v>
       </c>
       <c r="G19" s="7">
-        <v>0.515041</v>
+        <v>0.538617</v>
       </c>
       <c r="H19" s="7">
-        <v>0.510467</v>
+        <v>0.535829</v>
       </c>
       <c r="I19" s="7">
-        <v>0.845548</v>
+        <v>0.883951</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1199,19 +1201,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.003947</v>
+        <v>0.036136</v>
       </c>
       <c r="F20" s="7">
-        <v>0.091881</v>
+        <v>0.12718400000000002</v>
       </c>
       <c r="G20" s="7">
-        <v>0.296073</v>
+        <v>0.32537799999999995</v>
       </c>
       <c r="H20" s="7">
-        <v>0.30118300000000003</v>
+        <v>0.330604</v>
       </c>
       <c r="I20" s="7">
-        <v>0.549855</v>
+        <v>0.607549</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1230,19 +1232,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.018994</v>
+        <v>0.032357</v>
       </c>
       <c r="F21" s="7">
-        <v>0.047316000000000004</v>
+        <v>0.076521</v>
       </c>
       <c r="G21" s="7">
-        <v>0.202465</v>
+        <v>0.224863</v>
       </c>
       <c r="H21" s="7">
-        <v>0.21662800000000001</v>
+        <v>0.237875</v>
       </c>
       <c r="I21" s="7">
-        <v>0.448048</v>
+        <v>0.465682</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1261,19 +1263,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.011059000000000001</v>
+        <v>0.026842</v>
       </c>
       <c r="F22" s="7">
-        <v>0.057579000000000005</v>
+        <v>0.06925500000000001</v>
       </c>
       <c r="G22" s="7">
-        <v>0.191863</v>
+        <v>0.20849399999999998</v>
       </c>
       <c r="H22" s="7">
-        <v>0.19102699999999997</v>
+        <v>0.20679999999999998</v>
       </c>
       <c r="I22" s="7">
-        <v>0.481901</v>
+        <v>0.516072</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1292,25 +1294,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.006704</v>
+        <v>0.041225</v>
       </c>
       <c r="F23" s="7">
-        <v>0.085101</v>
+        <v>0.132752</v>
       </c>
       <c r="G23" s="7">
-        <v>0.30133299999999996</v>
+        <v>0.334541</v>
       </c>
       <c r="H23" s="7">
-        <v>0.304493</v>
+        <v>0.34183399999999997</v>
       </c>
       <c r="I23" s="7">
-        <v>0.5535070000000001</v>
+        <v>0.622018</v>
       </c>
       <c r="J23" s="7">
-        <v>1.7708279999999998</v>
+        <v>1.850142</v>
       </c>
       <c r="K23" s="7">
-        <v>10.903046999999999</v>
+        <v>11.450704</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1327,25 +1329,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.09361499999999999</v>
+        <v>0.143878</v>
       </c>
       <c r="F24" s="7">
-        <v>0.08560600000000002</v>
+        <v>0.149449</v>
       </c>
       <c r="G24" s="7">
-        <v>0.121576</v>
+        <v>0.155075</v>
       </c>
       <c r="H24" s="7">
-        <v>0.112578</v>
+        <v>0.16045500000000001</v>
       </c>
       <c r="I24" s="7">
-        <v>0.41647399999999996</v>
+        <v>0.48182400000000003</v>
       </c>
       <c r="J24" s="7">
-        <v>2.767087</v>
+        <v>2.929197</v>
       </c>
       <c r="K24" s="7">
-        <v>17.093434</v>
+        <v>17.983912</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1362,25 +1364,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.011273</v>
+        <v>0.061125</v>
       </c>
       <c r="F25" s="7">
-        <v>0.104817</v>
+        <v>0.14455199999999999</v>
       </c>
       <c r="G25" s="7">
-        <v>0.346564</v>
+        <v>0.383461</v>
       </c>
       <c r="H25" s="7">
-        <v>0.364773</v>
+        <v>0.402637</v>
       </c>
       <c r="I25" s="7">
-        <v>0.598812</v>
+        <v>0.6696179999999999</v>
       </c>
       <c r="J25" s="7">
-        <v>1.4615850000000001</v>
+        <v>1.5298779999999998</v>
       </c>
       <c r="K25" s="7">
-        <v>9.904916</v>
+        <v>10.360897999999999</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1397,22 +1399,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.022543999999999998</v>
+        <v>0.024702</v>
       </c>
       <c r="F26" s="7">
-        <v>0.002477</v>
+        <v>0.035789</v>
       </c>
       <c r="G26" s="7">
-        <v>0.09468</v>
+        <v>0.121171</v>
       </c>
       <c r="H26" s="7">
-        <v>0.109182</v>
+        <v>0.137049</v>
       </c>
       <c r="I26" s="7">
-        <v>0.36989400000000006</v>
+        <v>0.42652500000000004</v>
       </c>
       <c r="J26" s="7">
-        <v>1.0887820000000001</v>
+        <v>1.141259</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1430,25 +1432,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.017575</v>
+        <v>-0.024602</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.111868</v>
+        <v>-0.129199</v>
       </c>
       <c r="G27" s="7">
-        <v>0.06825300000000001</v>
+        <v>0.044152</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.019684999999999998</v>
+        <v>-0.035074999999999995</v>
       </c>
       <c r="I27" s="7">
-        <v>0.548157</v>
+        <v>0.528691</v>
       </c>
       <c r="J27" s="7">
-        <v>3.3908300000000002</v>
+        <v>3.321898</v>
       </c>
       <c r="K27" s="7">
-        <v>12.864142999999999</v>
+        <v>12.564096999999999</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1465,25 +1467,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.013216</v>
+        <v>0.011251</v>
       </c>
       <c r="F28" s="7">
-        <v>0.21452100000000002</v>
+        <v>0.258968</v>
       </c>
       <c r="G28" s="7">
-        <v>0.5606450000000001</v>
+        <v>0.577483</v>
       </c>
       <c r="H28" s="7">
-        <v>0.506345</v>
+        <v>0.508391</v>
       </c>
       <c r="I28" s="7">
-        <v>0.9051560000000001</v>
+        <v>0.9152809999999999</v>
       </c>
       <c r="J28" s="7">
-        <v>2.000652</v>
+        <v>2.004729</v>
       </c>
       <c r="K28" s="7">
-        <v>8.740603</v>
+        <v>8.911242999999999</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1500,25 +1502,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.009977</v>
+        <v>0.022612</v>
       </c>
       <c r="F29" s="7">
-        <v>0.151786</v>
+        <v>0.17676100000000003</v>
       </c>
       <c r="G29" s="7">
-        <v>0.441341</v>
+        <v>0.473596</v>
       </c>
       <c r="H29" s="7">
-        <v>0.394595</v>
+        <v>0.417838</v>
       </c>
       <c r="I29" s="7">
-        <v>0.743243</v>
+        <v>0.789833</v>
       </c>
       <c r="J29" s="7">
-        <v>2.07729</v>
+        <v>2.128578</v>
       </c>
       <c r="K29" s="7">
-        <v>12.129771</v>
+        <v>12.583635</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1535,25 +1537,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.032743</v>
+        <v>0.018182</v>
       </c>
       <c r="F30" s="7">
-        <v>0.093879</v>
+        <v>0.125382</v>
       </c>
       <c r="G30" s="7">
-        <v>0.384997</v>
+        <v>0.421241</v>
       </c>
       <c r="H30" s="7">
-        <v>0.380429</v>
+        <v>0.416163</v>
       </c>
       <c r="I30" s="7">
-        <v>0.623142</v>
+        <v>0.6919540000000001</v>
       </c>
       <c r="J30" s="7">
-        <v>1.709907</v>
+        <v>1.7800559999999999</v>
       </c>
       <c r="K30" s="7">
-        <v>11.242808</v>
+        <v>11.8223</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1570,22 +1572,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.051521</v>
+        <v>0.072607</v>
       </c>
       <c r="F31" s="7">
-        <v>0.299378</v>
+        <v>0.301562</v>
       </c>
       <c r="G31" s="7">
-        <v>0.578178</v>
+        <v>0.565134</v>
       </c>
       <c r="H31" s="7">
-        <v>0.587068</v>
+        <v>0.591967</v>
       </c>
       <c r="I31" s="7">
-        <v>0.6640989999999999</v>
+        <v>0.663255</v>
       </c>
       <c r="J31" s="7">
-        <v>2.6881049999999997</v>
+        <v>2.699488</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1603,25 +1605,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.008007</v>
+        <v>0.061299</v>
       </c>
       <c r="F32" s="7">
-        <v>0.106364</v>
+        <v>0.150689</v>
       </c>
       <c r="G32" s="7">
-        <v>0.398851</v>
+        <v>0.44333500000000003</v>
       </c>
       <c r="H32" s="7">
-        <v>0.416764</v>
+        <v>0.45789700000000005</v>
       </c>
       <c r="I32" s="7">
-        <v>0.6083700000000001</v>
+        <v>0.678731</v>
       </c>
       <c r="J32" s="7">
-        <v>1.2813050000000001</v>
+        <v>1.3475380000000001</v>
       </c>
       <c r="K32" s="7">
-        <v>8.872904</v>
+        <v>9.332783</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1638,22 +1640,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.005328</v>
+        <v>0.041666999999999996</v>
       </c>
       <c r="F33" s="7">
-        <v>0.055054</v>
+        <v>0.081081</v>
       </c>
       <c r="G33" s="7">
-        <v>0.234524</v>
+        <v>0.257229</v>
       </c>
       <c r="H33" s="7">
-        <v>0.245178</v>
+        <v>0.269036</v>
       </c>
       <c r="I33" s="7">
-        <v>0.498015</v>
+        <v>0.539409</v>
       </c>
       <c r="J33" s="7">
-        <v>1.8146870000000002</v>
+        <v>1.8686170000000002</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1671,16 +1673,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.032794</v>
+        <v>0.035179999999999996</v>
       </c>
       <c r="F34" s="7">
-        <v>0.09909499999999999</v>
+        <v>0.101549</v>
       </c>
       <c r="G34" s="7">
-        <v>0.209005</v>
+        <v>0.209258</v>
       </c>
       <c r="H34" s="7">
-        <v>0.18817</v>
+        <v>0.192361</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1700,25 +1702,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.003441</v>
+        <v>0.034742999999999996</v>
       </c>
       <c r="F35" s="7">
-        <v>0.069602</v>
+        <v>0.103072</v>
       </c>
       <c r="G35" s="7">
-        <v>0.232809</v>
+        <v>0.25637699999999997</v>
       </c>
       <c r="H35" s="7">
-        <v>0.254164</v>
+        <v>0.27981300000000003</v>
       </c>
       <c r="I35" s="7">
-        <v>0.5029939999999999</v>
+        <v>0.5485690000000001</v>
       </c>
       <c r="J35" s="7">
-        <v>1.93133</v>
+        <v>1.99128</v>
       </c>
       <c r="K35" s="7">
-        <v>9.587739000000001</v>
+        <v>9.983419</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1735,16 +1737,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.032349</v>
+        <v>0.034747</v>
       </c>
       <c r="F36" s="7">
-        <v>0.09901</v>
+        <v>0.101032</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20937899999999998</v>
+        <v>0.20916</v>
       </c>
       <c r="H36" s="7">
-        <v>0.189101</v>
+        <v>0.19282699999999997</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>

--- a/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/borsa-yatirim-fonlari-getiri/data/borsa-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>19.06.2026 10:07:19</t>
+    <t>22.06.2026 10:00:22</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -775,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="E6" s="7">
-        <v>0.146533</v>
+        <v>0.213841</v>
       </c>
       <c r="F6" s="7">
-        <v>0.14180199999999998</v>
+        <v>0.164159</v>
       </c>
       <c r="G6" s="7">
-        <v>0.146533</v>
+        <v>0.15016400000000002</v>
       </c>
       <c r="H6" s="7">
-        <v>0.15814999999999999</v>
+        <v>0.159031</v>
       </c>
       <c r="I6" s="7">
-        <v>0.468715</v>
+        <v>0.486441</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -806,19 +806,19 @@
         <v>7</v>
       </c>
       <c r="E7" s="7">
-        <v>0.009524</v>
+        <v>0.083429</v>
       </c>
       <c r="F7" s="7">
-        <v>0.119062</v>
+        <v>0.113984</v>
       </c>
       <c r="G7" s="7">
-        <v>0.40448999999999996</v>
+        <v>0.39360500000000004</v>
       </c>
       <c r="H7" s="7">
-        <v>0.40604300000000004</v>
+        <v>0.3972</v>
       </c>
       <c r="I7" s="7">
-        <v>0.681057</v>
+        <v>0.6602450000000001</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -837,19 +837,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="7">
-        <v>0.033937</v>
+        <v>0.097594</v>
       </c>
       <c r="F8" s="7">
-        <v>0.116253</v>
+        <v>0.126214</v>
       </c>
       <c r="G8" s="7">
-        <v>0.318581</v>
+        <v>0.317326</v>
       </c>
       <c r="H8" s="7">
-        <v>0.325916</v>
+        <v>0.328534</v>
       </c>
       <c r="I8" s="7">
-        <v>0.607299</v>
+        <v>0.615599</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -868,19 +868,19 @@
         <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>0.034495</v>
+        <v>0.031239</v>
       </c>
       <c r="F9" s="7">
-        <v>0.09963</v>
+        <v>0.10037000000000001</v>
       </c>
       <c r="G9" s="7">
-        <v>0.20593</v>
+        <v>0.205518</v>
       </c>
       <c r="H9" s="7">
-        <v>0.189027</v>
+        <v>0.189828</v>
       </c>
       <c r="I9" s="7">
-        <v>0.482511</v>
+        <v>0.47610399999999997</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -899,25 +899,25 @@
         <v>7</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.056375</v>
+        <v>0.028571</v>
       </c>
       <c r="F10" s="7">
-        <v>0.133186</v>
+        <v>0.1378</v>
       </c>
       <c r="G10" s="7">
-        <v>0.182569</v>
+        <v>0.198402</v>
       </c>
       <c r="H10" s="7">
-        <v>0.23944600000000002</v>
+        <v>0.24567499999999998</v>
       </c>
       <c r="I10" s="7">
-        <v>0.540314</v>
+        <v>0.550388</v>
       </c>
       <c r="J10" s="7">
-        <v>0.8308199999999999</v>
+        <v>0.938089</v>
       </c>
       <c r="K10" s="7">
-        <v>7.161312000000001</v>
+        <v>7.14664</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -934,25 +934,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.041237</v>
+        <v>-0.057180999999999996</v>
       </c>
       <c r="F11" s="7">
-        <v>-0.11391899999999999</v>
+        <v>-0.109315</v>
       </c>
       <c r="G11" s="7">
-        <v>0.048529</v>
+        <v>0.032544</v>
       </c>
       <c r="H11" s="7">
-        <v>0.0014039999999999999</v>
+        <v>-0.019663</v>
       </c>
       <c r="I11" s="7">
-        <v>0.45115299999999997</v>
+        <v>0.42101</v>
       </c>
       <c r="J11" s="7">
-        <v>3.158243</v>
+        <v>3.2098910000000003</v>
       </c>
       <c r="K11" s="7">
-        <v>11.220064</v>
+        <v>10.849253000000001</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -969,25 +969,25 @@
         <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.13229</v>
+        <v>-0.137026</v>
       </c>
       <c r="F12" s="7">
-        <v>-0.126387</v>
+        <v>-0.11740600000000001</v>
       </c>
       <c r="G12" s="7">
-        <v>0.077263</v>
+        <v>0.028671000000000002</v>
       </c>
       <c r="H12" s="7">
-        <v>-0.050953</v>
+        <v>-0.078958</v>
       </c>
       <c r="I12" s="7">
-        <v>1.072011</v>
+        <v>1.046319</v>
       </c>
       <c r="J12" s="7">
-        <v>4.272256</v>
+        <v>4.431193</v>
       </c>
       <c r="K12" s="7">
-        <v>11.842104999999998</v>
+        <v>11.457911999999999</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1004,25 +1004,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.014554000000000001</v>
+        <v>0.007705</v>
       </c>
       <c r="F13" s="7">
-        <v>0.042199</v>
+        <v>0.0375</v>
       </c>
       <c r="G13" s="7">
-        <v>0.082665</v>
+        <v>0.08035</v>
       </c>
       <c r="H13" s="7">
-        <v>0.07566</v>
+        <v>0.074166</v>
       </c>
       <c r="I13" s="7">
-        <v>0.169689</v>
+        <v>0.158347</v>
       </c>
       <c r="J13" s="7">
-        <v>0.9475490000000001</v>
+        <v>0.953737</v>
       </c>
       <c r="K13" s="7">
-        <v>4.189098</v>
+        <v>4.152202</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1039,19 +1039,19 @@
         <v>6</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.01909</v>
+        <v>-0.043668</v>
       </c>
       <c r="F14" s="7">
-        <v>-0.140283</v>
+        <v>-0.146753</v>
       </c>
       <c r="G14" s="7">
-        <v>0.058636999999999995</v>
+        <v>0.04038</v>
       </c>
       <c r="H14" s="7">
-        <v>-0.051136</v>
+        <v>-0.066761</v>
       </c>
       <c r="I14" s="7">
-        <v>0.524418</v>
+        <v>0.501028</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1089,10 +1089,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.050564</v>
+        <v>-0.059573</v>
       </c>
       <c r="F16" s="7">
-        <v>-0.12208500000000001</v>
+        <v>-0.136219</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -1114,16 +1114,16 @@
         <v>7</v>
       </c>
       <c r="E17" s="7">
-        <v>0.033682</v>
+        <v>0.066773</v>
       </c>
       <c r="F17" s="7">
-        <v>0.074879</v>
+        <v>0.074507</v>
       </c>
       <c r="G17" s="7">
-        <v>0.208145</v>
+        <v>0.21549</v>
       </c>
       <c r="H17" s="7">
-        <v>0.225333</v>
+        <v>0.224415</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -1143,14 +1143,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7">
-        <v>0.033822</v>
+        <v>0.030901</v>
       </c>
       <c r="F18" s="7">
-        <v>0.096914</v>
+        <v>0.098057</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>0.190316</v>
+        <v>0.191556</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -1170,19 +1170,19 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.038095</v>
+        <v>0.088629</v>
       </c>
       <c r="F19" s="7">
-        <v>0.219239</v>
+        <v>0.220837</v>
       </c>
       <c r="G19" s="7">
-        <v>0.538617</v>
+        <v>0.545307</v>
       </c>
       <c r="H19" s="7">
-        <v>0.535829</v>
+        <v>0.5378419999999999</v>
       </c>
       <c r="I19" s="7">
-        <v>0.883951</v>
+        <v>0.890153</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1201,19 +1201,19 @@
         <v>6</v>
       </c>
       <c r="E20" s="7">
-        <v>0.036136</v>
+        <v>0.08419800000000001</v>
       </c>
       <c r="F20" s="7">
-        <v>0.12718400000000002</v>
+        <v>0.155864</v>
       </c>
       <c r="G20" s="7">
-        <v>0.32537799999999995</v>
+        <v>0.315959</v>
       </c>
       <c r="H20" s="7">
-        <v>0.330604</v>
+        <v>0.363057</v>
       </c>
       <c r="I20" s="7">
-        <v>0.607549</v>
+        <v>0.650386</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1232,19 +1232,19 @@
         <v>6</v>
       </c>
       <c r="E21" s="7">
-        <v>0.032357</v>
+        <v>0.07767</v>
       </c>
       <c r="F21" s="7">
-        <v>0.076521</v>
+        <v>0.073977</v>
       </c>
       <c r="G21" s="7">
-        <v>0.224863</v>
+        <v>0.22145800000000002</v>
       </c>
       <c r="H21" s="7">
-        <v>0.237875</v>
+        <v>0.230485</v>
       </c>
       <c r="I21" s="7">
-        <v>0.465682</v>
+        <v>0.45852699999999996</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1263,19 +1263,19 @@
         <v>7</v>
       </c>
       <c r="E22" s="7">
-        <v>0.026842</v>
+        <v>0.061349999999999995</v>
       </c>
       <c r="F22" s="7">
-        <v>0.06925500000000001</v>
+        <v>0.072868</v>
       </c>
       <c r="G22" s="7">
-        <v>0.20849399999999998</v>
+        <v>0.212334</v>
       </c>
       <c r="H22" s="7">
-        <v>0.20679999999999998</v>
+        <v>0.212758</v>
       </c>
       <c r="I22" s="7">
-        <v>0.516072</v>
+        <v>0.526246</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1294,25 +1294,25 @@
         <v>7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.041225</v>
+        <v>0.095</v>
       </c>
       <c r="F23" s="7">
-        <v>0.132752</v>
+        <v>0.124807</v>
       </c>
       <c r="G23" s="7">
-        <v>0.334541</v>
+        <v>0.32047</v>
       </c>
       <c r="H23" s="7">
-        <v>0.34183399999999997</v>
+        <v>0.32969000000000004</v>
       </c>
       <c r="I23" s="7">
-        <v>0.622018</v>
+        <v>0.61743</v>
       </c>
       <c r="J23" s="7">
-        <v>1.850142</v>
+        <v>1.988537</v>
       </c>
       <c r="K23" s="7">
-        <v>11.450704</v>
+        <v>11.227806000000001</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1329,25 +1329,25 @@
         <v>7</v>
       </c>
       <c r="E24" s="7">
-        <v>0.143878</v>
+        <v>0.289451</v>
       </c>
       <c r="F24" s="7">
-        <v>0.149449</v>
+        <v>0.165498</v>
       </c>
       <c r="G24" s="7">
-        <v>0.155075</v>
+        <v>0.155888</v>
       </c>
       <c r="H24" s="7">
-        <v>0.16045500000000001</v>
+        <v>0.160973</v>
       </c>
       <c r="I24" s="7">
-        <v>0.48182400000000003</v>
+        <v>0.49783</v>
       </c>
       <c r="J24" s="7">
-        <v>2.929197</v>
+        <v>3.021155</v>
       </c>
       <c r="K24" s="7">
-        <v>17.983912</v>
+        <v>17.848739000000002</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1364,25 +1364,25 @@
         <v>7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.061125</v>
+        <v>0.127822</v>
       </c>
       <c r="F25" s="7">
-        <v>0.14455199999999999</v>
+        <v>0.153547</v>
       </c>
       <c r="G25" s="7">
-        <v>0.383461</v>
+        <v>0.382794</v>
       </c>
       <c r="H25" s="7">
-        <v>0.402637</v>
+        <v>0.401961</v>
       </c>
       <c r="I25" s="7">
-        <v>0.6696179999999999</v>
+        <v>0.672852</v>
       </c>
       <c r="J25" s="7">
-        <v>1.5298779999999998</v>
+        <v>1.729008</v>
       </c>
       <c r="K25" s="7">
-        <v>10.360897999999999</v>
+        <v>10.293572999999999</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1399,22 +1399,22 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.024702</v>
+        <v>0.026482000000000002</v>
       </c>
       <c r="F26" s="7">
-        <v>0.035789</v>
+        <v>0.010343</v>
       </c>
       <c r="G26" s="7">
-        <v>0.121171</v>
+        <v>0.103978</v>
       </c>
       <c r="H26" s="7">
-        <v>0.137049</v>
+        <v>0.115578</v>
       </c>
       <c r="I26" s="7">
-        <v>0.42652500000000004</v>
+        <v>0.384982</v>
       </c>
       <c r="J26" s="7">
-        <v>1.141259</v>
+        <v>1.256932</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -1432,25 +1432,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.024602</v>
+        <v>-0.047122000000000004</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.129199</v>
+        <v>-0.125454</v>
       </c>
       <c r="G27" s="7">
-        <v>0.044152</v>
+        <v>0.017672</v>
       </c>
       <c r="H27" s="7">
-        <v>-0.035074999999999995</v>
+        <v>-0.051897</v>
       </c>
       <c r="I27" s="7">
-        <v>0.528691</v>
+        <v>0.49728700000000003</v>
       </c>
       <c r="J27" s="7">
-        <v>3.321898</v>
+        <v>3.423848</v>
       </c>
       <c r="K27" s="7">
-        <v>12.564096999999999</v>
+        <v>12.245</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1467,25 +1467,25 @@
         <v>6</v>
       </c>
       <c r="E28" s="7">
-        <v>0.011251</v>
+        <v>0.058046</v>
       </c>
       <c r="F28" s="7">
-        <v>0.258968</v>
+        <v>0.219205</v>
       </c>
       <c r="G28" s="7">
-        <v>0.577483</v>
+        <v>0.560169</v>
       </c>
       <c r="H28" s="7">
-        <v>0.508391</v>
+        <v>0.5071629999999999</v>
       </c>
       <c r="I28" s="7">
-        <v>0.9152809999999999</v>
+        <v>0.937895</v>
       </c>
       <c r="J28" s="7">
-        <v>2.004729</v>
+        <v>2.203968</v>
       </c>
       <c r="K28" s="7">
-        <v>8.911242999999999</v>
+        <v>8.866024</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1502,25 +1502,25 @@
         <v>6</v>
       </c>
       <c r="E29" s="7">
-        <v>0.022612</v>
+        <v>0.11767200000000001</v>
       </c>
       <c r="F29" s="7">
-        <v>0.17676100000000003</v>
+        <v>0.180927</v>
       </c>
       <c r="G29" s="7">
-        <v>0.473596</v>
+        <v>0.452055</v>
       </c>
       <c r="H29" s="7">
-        <v>0.417838</v>
+        <v>0.43243200000000004</v>
       </c>
       <c r="I29" s="7">
-        <v>0.789833</v>
+        <v>0.816313</v>
       </c>
       <c r="J29" s="7">
-        <v>2.128578</v>
+        <v>2.429977</v>
       </c>
       <c r="K29" s="7">
-        <v>12.583635</v>
+        <v>12.603696</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1537,25 +1537,25 @@
         <v>7</v>
       </c>
       <c r="E30" s="7">
-        <v>0.018182</v>
+        <v>0.069249</v>
       </c>
       <c r="F30" s="7">
-        <v>0.125382</v>
+        <v>0.118943</v>
       </c>
       <c r="G30" s="7">
-        <v>0.421241</v>
+        <v>0.3914</v>
       </c>
       <c r="H30" s="7">
-        <v>0.416163</v>
+        <v>0.396372</v>
       </c>
       <c r="I30" s="7">
-        <v>0.6919540000000001</v>
+        <v>0.6661199999999999</v>
       </c>
       <c r="J30" s="7">
-        <v>1.7800559999999999</v>
+        <v>1.912176</v>
       </c>
       <c r="K30" s="7">
-        <v>11.8223</v>
+        <v>11.630532</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1572,22 +1572,22 @@
         <v>7</v>
       </c>
       <c r="E31" s="7">
-        <v>0.072607</v>
+        <v>0.118954</v>
       </c>
       <c r="F31" s="7">
-        <v>0.301562</v>
+        <v>0.279522</v>
       </c>
       <c r="G31" s="7">
-        <v>0.565134</v>
+        <v>0.533684</v>
       </c>
       <c r="H31" s="7">
-        <v>0.591967</v>
+        <v>0.572373</v>
       </c>
       <c r="I31" s="7">
-        <v>0.663255</v>
+        <v>0.671875</v>
       </c>
       <c r="J31" s="7">
-        <v>2.699488</v>
+        <v>2.930211</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -1605,25 +1605,25 @@
         <v>6</v>
       </c>
       <c r="E32" s="7">
-        <v>0.061299</v>
+        <v>0.077414</v>
       </c>
       <c r="F32" s="7">
-        <v>0.150689</v>
+        <v>0.137783</v>
       </c>
       <c r="G32" s="7">
-        <v>0.44333500000000003</v>
+        <v>0.428681</v>
       </c>
       <c r="H32" s="7">
-        <v>0.45789700000000005</v>
+        <v>0.441987</v>
       </c>
       <c r="I32" s="7">
-        <v>0.678731</v>
+        <v>0.669362</v>
       </c>
       <c r="J32" s="7">
-        <v>1.3475380000000001</v>
+        <v>1.4866169999999999</v>
       </c>
       <c r="K32" s="7">
-        <v>9.332783</v>
+        <v>9.136388</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1640,22 +1640,22 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.041666999999999996</v>
+        <v>0.07445700000000001</v>
       </c>
       <c r="F33" s="7">
-        <v>0.081081</v>
+        <v>0.084963</v>
       </c>
       <c r="G33" s="7">
-        <v>0.257229</v>
+        <v>0.255469</v>
       </c>
       <c r="H33" s="7">
-        <v>0.269036</v>
+        <v>0.26725899999999997</v>
       </c>
       <c r="I33" s="7">
-        <v>0.539409</v>
+        <v>0.538675</v>
       </c>
       <c r="J33" s="7">
-        <v>1.8686170000000002</v>
+        <v>2.033414</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -1673,16 +1673,16 @@
         <v>2</v>
       </c>
       <c r="E34" s="7">
-        <v>0.035179999999999996</v>
+        <v>0.031401</v>
       </c>
       <c r="F34" s="7">
-        <v>0.101549</v>
+        <v>0.10241</v>
       </c>
       <c r="G34" s="7">
-        <v>0.209258</v>
+        <v>0.209061</v>
       </c>
       <c r="H34" s="7">
-        <v>0.192361</v>
+        <v>0.193293</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
@@ -1702,25 +1702,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.034742999999999996</v>
+        <v>0.091951</v>
       </c>
       <c r="F35" s="7">
-        <v>0.103072</v>
+        <v>0.091013</v>
       </c>
       <c r="G35" s="7">
-        <v>0.25637699999999997</v>
+        <v>0.252711</v>
       </c>
       <c r="H35" s="7">
-        <v>0.27981300000000003</v>
+        <v>0.26982</v>
       </c>
       <c r="I35" s="7">
-        <v>0.5485690000000001</v>
+        <v>0.5414479999999999</v>
       </c>
       <c r="J35" s="7">
-        <v>1.99128</v>
+        <v>2.154585</v>
       </c>
       <c r="K35" s="7">
-        <v>9.983419</v>
+        <v>9.768362</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1737,16 +1737,16 @@
         <v>2</v>
       </c>
       <c r="E36" s="7">
-        <v>0.034747</v>
+        <v>0.031376</v>
       </c>
       <c r="F36" s="7">
-        <v>0.101032</v>
+        <v>0.102796</v>
       </c>
       <c r="G36" s="7">
-        <v>0.20916</v>
+        <v>0.210005</v>
       </c>
       <c r="H36" s="7">
-        <v>0.19282699999999997</v>
+        <v>0.194224</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
